--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v3\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF0BC2E-6E13-49D5-94F5-8BE664BDE235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEE6529-41E1-469F-A390-18DA05A36668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="4" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="321">
   <si>
     <t>Company Info:</t>
   </si>
@@ -551,619 +551,644 @@
     <t>Normalized Payout Ratio</t>
   </si>
   <si>
+    <t>CN Riskfree</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY</t>
+  </si>
+  <si>
+    <t>https://yield.chinabond.com.cn/cbweb-mn/yield_main?locale=en_US</t>
+  </si>
+  <si>
+    <t>US BBB Bond yield</t>
+  </si>
+  <si>
+    <t>https://iftp.chinamoney.com.cn/chinese/scsjzqxx/</t>
+  </si>
+  <si>
+    <t>https://tradingeconomics.com/china/government-bond-yield</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/DGS10</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>CN Onshore BBB- Bond yield</t>
+  </si>
+  <si>
+    <t>CN Offshore BBB- Bond yield</t>
+  </si>
+  <si>
+    <t>PB Ratio</t>
+  </si>
+  <si>
+    <t>HK</t>
+  </si>
+  <si>
+    <t>Watchlist &amp; Comp_Group:</t>
+  </si>
+  <si>
+    <t>Normalized D/P</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Name:</t>
+  </si>
+  <si>
+    <t>Valued @</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avg of E and D method</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Avg Valuation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAGR Calculator</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inputs =</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAGR =</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Initial Value (PV)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Final Value (FV)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t># of Years</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Case</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pessimistic Case</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dividend per share</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E/P Initial Rate of Retrun</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>E/P Future Value is</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D/P Future Value is</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target Return</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lower</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inputs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Watchlist</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comp_Group:</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reporting Currency:</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Most Recent Quarter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D/P Dividend Yield</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earnings Power Checklist</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Present</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Consumer monopoly?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. Conservatively financed?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Future</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5. Can earnings be sustained?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consumer Monopoly Test</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>If you had access to billions of dollars and your pick of the top fifty managers in the country, could you start a business and successfully compete with the business in question?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6. No big MCX-D&amp;A required?</t>
+  </si>
+  <si>
+    <t>EBIT =</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBIT</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(OPEX+R&amp;D)/Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAPX/Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(CAPX-D&amp;A)/Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mid</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. Upward earnings trend?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4. Stable margin and ROE?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Pre-tax Non-controling Interests</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBIT/Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBIT Growth</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>unclear</t>
+  </si>
+  <si>
+    <t>- (CAPX - D&amp;A)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- (OPEX + R&amp;D) =</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Valuation method</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dividend Yield</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discount Rate (US)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discount Rate (CN)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice of Discount Rate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Interest Expense</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Case Valuation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized PE Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LT AR or Prepayments</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prepayments or Contract Assets</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ΔWC/Δsales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profibility Analysis</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asset Turnover</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leverage Analysis</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common_Equity / Total Assets</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBIT ROE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-tax ROE</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sales/Total_Assets</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST_AR / Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ST_Inventory / Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EBIT Margin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interest Expense</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized ΔWC</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized CAPX-D&amp;A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROE &amp; Cost Structure</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Liabilities</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asset Turnover Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t># In general, the higher the accounts receivable, the higher the inventory, and the lower the fixed assets, the lower the asset turnover ratio.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlaceHolder_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlaceHolder_4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contingent Liabilities</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contin. Liabilities / Total Assets</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leverage Ratio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/countrytaxrates.html</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nonop Assets Valuation</t>
+  </si>
+  <si>
+    <t>Nonop Assets per share</t>
+  </si>
+  <si>
+    <t>Net Nonop Assets FV</t>
+  </si>
+  <si>
+    <t>Net Nonop Assets PV</t>
+  </si>
+  <si>
+    <t>HKD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Yields</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price Indicators</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balance Sheet items Adjustments</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Asset Model Output</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model last updated:</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>External Drivers</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Internal Drivers</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dividend method</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selecting the Valuation method</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Liabilities</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C0003</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Reinvest Nonop @</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0590.HK</t>
+  </si>
+  <si>
+    <t>Reported Net Income</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlaceHolder_2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inputs from Statements</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Non-Operating Income</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Pre-tax FCF</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. After-tax FCF</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superior Cycl. </t>
+  </si>
+  <si>
+    <t>Strongly agree</t>
+  </si>
+  <si>
+    <t>agree</t>
+  </si>
+  <si>
+    <t>Consumer Monopoly</t>
+  </si>
+  <si>
+    <t>Valuation Summary</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized Year Forecast</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>% Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>% of Revenue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>COGS</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gross Proift</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPEX + R&amp;D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Non-controling Interests</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fixed Costs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variable Costs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>D&amp;A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contribution Margin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Income Tax Expense</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Divisional Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Categories</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Items</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Results</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capex - D&amp;A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Administrative and General Expenses</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre-tax Profit (EBT)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Income</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FCFF </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Adjustments</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selling and Distribution Costs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other Variable Operating Expenses</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Variable Costs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Sales - Total Variable Costs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contribution Margin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other Fixed Operating Expenses</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Component</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amount ($)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Percentage of Sales</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Revenue	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribution Margin	</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>US Riskfree</t>
-  </si>
-  <si>
-    <t>CN Riskfree</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/BAMLC0A4CBBBEY</t>
-  </si>
-  <si>
-    <t>https://yield.chinabond.com.cn/cbweb-mn/yield_main?locale=en_US</t>
-  </si>
-  <si>
-    <t>US BBB Bond yield</t>
-  </si>
-  <si>
-    <t>https://iftp.chinamoney.com.cn/chinese/scsjzqxx/</t>
-  </si>
-  <si>
-    <t>https://tradingeconomics.com/china/government-bond-yield</t>
-  </si>
-  <si>
-    <t>https://fred.stlouisfed.org/series/DGS10</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>CN Onshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>CN Offshore BBB- Bond yield</t>
-  </si>
-  <si>
-    <t>PB Ratio</t>
-  </si>
-  <si>
-    <t>HK</t>
-  </si>
-  <si>
-    <t>Watchlist &amp; Comp_Group:</t>
-  </si>
-  <si>
-    <t>Normalized D/P</t>
-  </si>
-  <si>
-    <t>Symbol:</t>
-  </si>
-  <si>
-    <t>Name:</t>
-  </si>
-  <si>
-    <t>Valued @</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Avg of E and D method</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Avg Valuation</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAGR Calculator</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inputs =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAGR =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Initial Value (PV)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Final Value (FV)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t># of Years</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Case</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pessimistic Case</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend per share</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>E/P Initial Rate of Retrun</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>E/P Future Value is</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>D/P Future Value is</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Return</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lower</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inputs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Watchlist</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Comp_Group:</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Number of Shares:</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reporting Currency:</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Most Recent Quarter</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>D/P Dividend Yield</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Earnings Power Checklist</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Present</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Consumer monopoly?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2. Conservatively financed?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Future</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>5. Can earnings be sustained?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Consumer Monopoly Test</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>If you had access to billions of dollars and your pick of the top fifty managers in the country, could you start a business and successfully compete with the business in question?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>6. No big MCX-D&amp;A required?</t>
-  </si>
-  <si>
-    <t>EBIT =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EBIT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(OPEX+R&amp;D)/Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAPX/Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(CAPX-D&amp;A)/Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mid</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>3. Upward earnings trend?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>4. Stable margin and ROE?</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Pre-tax Non-controling Interests</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EBIT/Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EBIT Growth</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>unclear</t>
-  </si>
-  <si>
-    <t>- (CAPX - D&amp;A)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>- (OPEX + R&amp;D) =</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Valuation method</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Discount Rate (US)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Discount Rate (CN)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Choice of Discount Rate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>- Interest Expense</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Case Valuation</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normalized PE Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>LT AR or Prepayments</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prepayments or Contract Assets</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ΔWC/Δsales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Profibility Analysis</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asset Turnover</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leverage Analysis</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Common_Equity / Total Assets</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EBIT ROE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pre-tax ROE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sales/Total_Assets</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ST_AR / Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ST_Inventory / Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EBIT Margin</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Interest Expense</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normalized ΔWC</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normalized CAPX-D&amp;A</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ROE &amp; Cost Structure</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total Liabilities</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asset Turnover Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t># In general, the higher the accounts receivable, the higher the inventory, and the lower the fixed assets, the lower the asset turnover ratio.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlaceHolder_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlaceHolder_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Contingent Liabilities</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Contin. Liabilities / Total Assets</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leverage Ratio</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/countrytaxrates.html</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nonop Assets Valuation</t>
-  </si>
-  <si>
-    <t>Nonop Assets per share</t>
-  </si>
-  <si>
-    <t>Net Nonop Assets FV</t>
-  </si>
-  <si>
-    <t>Net Nonop Assets PV</t>
-  </si>
-  <si>
-    <t>HKD</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Yields</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Price Indicators</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Balance Sheet items Adjustments</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Asset Model Output</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model last updated:</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>External Drivers</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Internal Drivers</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend method</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Selecting the Valuation method</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Liabilities</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>C0003</t>
-  </si>
-  <si>
-    <t>Profit</t>
-  </si>
-  <si>
-    <t>Reinvest Nonop @</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0590.HK</t>
-  </si>
-  <si>
-    <t>Reported Net Income</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlaceHolder_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inputs from Statements</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Net Non-Operating Income</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Est. Pre-tax FCF</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Est. After-tax FCF</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>六福珠宝</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Superior Cycl. </t>
-  </si>
-  <si>
-    <t>Strongly agree</t>
-  </si>
-  <si>
-    <t>agree</t>
-  </si>
-  <si>
-    <t>Consumer Monopoly</t>
-  </si>
-  <si>
-    <t>Valuation Summary</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normalized Year Forecast</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>% Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>% of Revenue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>COGS</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gross Proift</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>OPEX + R&amp;D</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Non-controling Interests</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fixed Costs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Variable Costs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>D&amp;A</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Contribution Margin</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Income Tax Expense</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Divisional Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total Sales</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Categories</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Items</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Results</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Capex - D&amp;A</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Administrative and General Expenses</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pre-tax Profit (EBT)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Net Income</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">FCFF </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Adjustments</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Selling and Distribution Costs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Variable Operating Expenses</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total Variable Costs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total Sales - Total Variable Costs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Contribution Margin</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Fixed Operating Expenses</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1171,7 +1196,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
@@ -1187,9 +1212,10 @@
     <numFmt numFmtId="187" formatCode="&quot;g = &quot;0.00%"/>
     <numFmt numFmtId="188" formatCode="&quot;Riskfree = &quot;0.00%"/>
     <numFmt numFmtId="189" formatCode="0_)"/>
-    <numFmt numFmtId="191" formatCode="&quot;for &quot;0&quot; Yrs&quot;"/>
+    <numFmt numFmtId="190" formatCode="&quot;for &quot;0&quot; Yrs&quot;"/>
+    <numFmt numFmtId="191" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1432,8 +1458,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1509,6 +1542,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2F75B5"/>
         <bgColor rgb="FF1C4587"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0047AB"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1892,7 +1931,7 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="326">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2589,7 +2628,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="21" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2635,25 +2674,13 @@
     <xf numFmtId="181" fontId="29" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2662,6 +2689,18 @@
     <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2671,6 +2710,16 @@
     <xf numFmtId="181" fontId="29" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
@@ -3104,31 +3153,31 @@
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B4" s="45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B5" s="45" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C5" s="60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" s="45" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C6" s="61">
         <v>45643</v>
@@ -3144,23 +3193,23 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B8" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B9" s="38" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="112" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" s="38" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="63">
         <v>587107850</v>
@@ -3168,7 +3217,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B11" s="38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C11" s="62" t="s">
         <v>2</v>
@@ -3192,7 +3241,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" s="64" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" s="65">
         <v>45382</v>
@@ -3200,10 +3249,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B15" s="64" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C15" s="110" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -3215,66 +3264,66 @@
       </c>
       <c r="D16" s="68"/>
       <c r="E16" s="24" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B17" s="55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C17" s="114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D17" s="68"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="55" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D18" s="68"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C19" s="114" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D19" s="68"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C20" s="114" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D20" s="68"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C21" s="114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D21" s="68"/>
     </row>
     <row r="22" spans="2:13" ht="69.75" x14ac:dyDescent="0.35">
       <c r="B22" s="58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C22" s="115" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D22" s="68"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C24" s="276">
         <f>C12</f>
@@ -3423,7 +3472,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="257" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C29" s="71">
         <v>59596</v>
@@ -3451,7 +3500,7 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="292" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C30" s="291">
         <v>1767305</v>
@@ -3617,7 +3666,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="256" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C37" s="71">
         <v>3990166</v>
@@ -3641,7 +3690,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="256" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C38" s="71">
         <f>20356+1075000</f>
@@ -3784,7 +3833,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="290" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C44" s="74">
         <f>0.72+0.64</f>
@@ -3818,7 +3867,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="290" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C45" s="75">
         <f>IF(C44="","",C44*Exchange_Rate/Dashboard!$G$3)</f>
@@ -3874,7 +3923,7 @@
         <v>28</v>
       </c>
       <c r="D47" s="77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E47" s="78" t="s">
         <v>30</v>
@@ -3948,7 +3997,7 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C54" s="79">
         <v>366595</v>
@@ -4066,7 +4115,7 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C64" s="79">
         <v>103050</v>
@@ -4240,7 +4289,7 @@
     </row>
     <row r="82" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B82" s="289" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C82" s="72">
         <v>473357</v>
@@ -4248,7 +4297,7 @@
     </row>
     <row r="83" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B83" s="289" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C83" s="72">
         <v>12890860</v>
@@ -4268,7 +4317,7 @@
     </row>
     <row r="86" spans="2:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B86" s="289" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C86" s="72">
         <v>5</v>
@@ -4277,10 +4326,10 @@
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B87" s="88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C87" s="100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D87" s="101">
         <v>0.02</v>
@@ -4296,10 +4345,10 @@
       </c>
       <c r="D89" s="306"/>
       <c r="E89" s="48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F89" s="48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H89" s="88"/>
     </row>
@@ -4360,7 +4409,7 @@
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B93" s="93" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C93" s="90">
         <f>C27+C28</f>
@@ -4381,7 +4430,7 @@
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B94" s="93" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C94" s="90">
         <f>C29</f>
@@ -4399,7 +4448,7 @@
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B95" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C95" s="90">
         <f>ABS(MAX(C34,0)-C33)</f>
@@ -4456,7 +4505,7 @@
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B98" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C98" s="97">
         <f>C44</f>
@@ -4588,21 +4637,21 @@
       <c r="D2" s="2"/>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="308" t="str">
+      <c r="G2" s="310" t="str">
         <f>IF(Inputs!D4="","",Inputs!D4)</f>
         <v>HOLD</v>
       </c>
-      <c r="H2" s="308"/>
+      <c r="H2" s="310"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="C3" s="313" t="str">
+        <v>167</v>
+      </c>
+      <c r="C3" s="308" t="str">
         <f>Inputs!C4</f>
         <v>0590.HK</v>
       </c>
-      <c r="D3" s="314"/>
+      <c r="D3" s="309"/>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
         <v>1</v>
@@ -4611,47 +4660,47 @@
         <v>13.82</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" s="308" t="str">
+        <v>168</v>
+      </c>
+      <c r="C4" s="310" t="str">
         <f>Inputs!C5</f>
         <v>六福珠宝</v>
       </c>
-      <c r="D4" s="315"/>
+      <c r="D4" s="311"/>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="318">
+      <c r="G4" s="314">
         <f>Inputs!C10</f>
         <v>587107850</v>
       </c>
-      <c r="H4" s="318"/>
+      <c r="H4" s="314"/>
       <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="316">
+      <c r="C5" s="312">
         <f>Inputs!C6</f>
         <v>45643</v>
       </c>
-      <c r="D5" s="317"/>
+      <c r="D5" s="313"/>
       <c r="E5" s="15"/>
       <c r="F5" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="311">
+      <c r="G5" s="317">
         <f>G3*G4/1000000</f>
         <v>8113.8304870000002</v>
       </c>
-      <c r="H5" s="311"/>
+      <c r="H5" s="317"/>
       <c r="I5" s="16"/>
       <c r="J5" s="17"/>
     </row>
@@ -4674,16 +4723,16 @@
       <c r="F6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="312" t="str">
+      <c r="G6" s="318" t="str">
         <f>Inputs!C11</f>
         <v>HKD</v>
       </c>
-      <c r="H6" s="312"/>
+      <c r="H6" s="318"/>
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C7" s="116" t="str">
         <f>Inputs!C8</f>
@@ -4708,42 +4757,42 @@
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="76" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C9" s="275"/>
       <c r="D9" s="275"/>
       <c r="F9" s="22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>320</v>
       </c>
       <c r="C10" s="23">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="26">
         <v>5.2299999999999999E-2</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B12" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C12" s="108">
         <v>7.0000000000000007E-2</v>
@@ -4756,29 +4805,29 @@
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="23">
         <v>1.8100000000000002E-2</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C15" s="23">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C16" s="26">
         <v>0.16</v>
@@ -4788,12 +4837,12 @@
         <v>HK</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C17" s="107">
         <v>0.08</v>
@@ -4803,27 +4852,27 @@
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B19" s="76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C19" s="275"/>
       <c r="D19" s="275"/>
       <c r="E19" s="2"/>
       <c r="F19" s="76" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G19" s="275"/>
       <c r="H19" s="275"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C20" s="30">
         <f>C21*C22*C23</f>
         <v>0.14558943313324324</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G20" s="109">
         <v>0.15</v>
@@ -4834,7 +4883,7 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B21" s="31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C21" s="32">
         <f>Data!C13</f>
@@ -4845,28 +4894,28 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C22" s="35">
         <f>Data!C50</f>
         <v>0.90933332162498015</v>
       </c>
       <c r="F22" s="76" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G22" s="275"/>
       <c r="H22" s="275"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B23" s="36" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C23" s="37">
         <f>1/Data!C55</f>
         <v>1.3074429479491672</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" s="39">
         <f>G3/(Data!C36*Data!C4/Common_Shares*Exchange_Rate)</f>
@@ -4875,14 +4924,14 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C24" s="41">
         <f>Fin_Analysis!I81</f>
         <v>3.8885650375487034E-3</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G24" s="42">
         <f>G3/(Fin_Analysis!H86*G7)</f>
@@ -4891,7 +4940,7 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="27" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C25" s="43">
         <f>Fin_Analysis!I80</f>
@@ -4907,14 +4956,14 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="44" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C26" s="43">
         <f>Fin_Analysis!I80+Fin_Analysis!I82</f>
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="F26" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G26" s="46">
         <f>Fin_Analysis!H88*Exchange_Rate/G3</f>
@@ -4935,12 +4984,12 @@
       </c>
       <c r="E28" s="50"/>
       <c r="F28" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="G28" s="309" t="s">
-        <v>224</v>
-      </c>
-      <c r="H28" s="309"/>
+        <v>208</v>
+      </c>
+      <c r="G28" s="315" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="315"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
@@ -4959,29 +5008,29 @@
         <f>IF(Fin_Analysis!C117="Profit",Fin_Analysis!F109,IF(Fin_Analysis!C117="Dividend",Fin_Analysis!F112,Fin_Analysis!F115))</f>
         <v>16.072921931882622</v>
       </c>
-      <c r="G29" s="310">
+      <c r="G29" s="316">
         <f>IF(Fin_Analysis!C117="Profit",Fin_Analysis!I109,IF(Fin_Analysis!C117="Dividend",Fin_Analysis!I112,Fin_Analysis!I115))</f>
         <v>22.697676647472843</v>
       </c>
-      <c r="H29" s="310"/>
+      <c r="H29" s="316"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="76" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C32" s="275"/>
       <c r="D32" s="275"/>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C33" s="105" t="str">
         <f>Inputs!C17</f>
@@ -4990,7 +5039,7 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="56" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C34" s="57" t="str">
         <f>IF(AND(OR(Fin_Analysis!I26&lt;0.8,Fin_Analysis!I46&lt;0.6),Data!C56&lt;0.8),"Strongly disagree",
@@ -5000,14 +5049,14 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="76" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C35" s="275"/>
       <c r="D35" s="275"/>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="55" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C36" s="105" t="str">
         <f>Inputs!C18</f>
@@ -5016,7 +5065,7 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C37" s="105" t="str">
         <f>Inputs!C19</f>
@@ -5025,14 +5074,14 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="76" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C38" s="275"/>
       <c r="D38" s="275"/>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="56" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C39" s="105" t="str">
         <f>Inputs!C20</f>
@@ -5041,7 +5090,7 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C40" s="105" t="str">
         <f>Inputs!C21</f>
@@ -5052,12 +5101,12 @@
     <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="58.15" x14ac:dyDescent="0.35">
       <c r="B43" s="58" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C43" s="106" t="str">
         <f>Inputs!C22</f>
@@ -5946,15 +5995,15 @@
     <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C11:C12 C16:C17">
@@ -6035,16 +6084,16 @@
       <c r="C2" s="123"/>
       <c r="D2" s="124"/>
       <c r="E2" s="125" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F2" s="126" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="G2" s="125" t="s">
+      <c r="H2" s="127" t="s">
         <v>177</v>
-      </c>
-      <c r="H2" s="127" t="s">
-        <v>178</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="2"/>
@@ -6062,7 +6111,7 @@
         <v>45382</v>
       </c>
       <c r="E3" s="131" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F3" s="132">
         <f>H14</f>
@@ -6095,7 +6144,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F4" s="134">
         <f>(G3/F3)^(1/H3)-1</f>
@@ -6462,7 +6511,7 @@
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="128"/>
       <c r="B12" s="259" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C12" s="137">
         <f>IF(Inputs!C31="","",MAX(Inputs!C31,0)/(1-Fin_Analysis!$I$84))</f>
@@ -6513,7 +6562,7 @@
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="128"/>
       <c r="B13" s="280" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C13" s="281">
         <f t="shared" ref="C13:M13" si="3">IF(C14="","",C14/C6)</f>
@@ -6564,7 +6613,7 @@
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="128"/>
       <c r="B14" s="282" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C14" s="283">
         <f>IF(C6="","",C9-C10-MAX(C11,0)-MAX(C12,0))</f>
@@ -6615,7 +6664,7 @@
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="128"/>
       <c r="B15" s="284" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C15" s="285">
         <f>IF(D14="","",IF(ABS(C14+D14)=ABS(C14)+ABS(D14),IF(C14&lt;0,-1,1)*(C14-D14)/D14,"Turn"))</f>
@@ -6666,7 +6715,7 @@
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="128"/>
       <c r="B16" s="257" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C16" s="140">
         <f>IF(C17="","",C17-C14)</f>
@@ -6717,7 +6766,7 @@
     <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="128"/>
       <c r="B17" s="295" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C17" s="296">
         <f>IF(Inputs!C30="","",Inputs!C30)</f>
@@ -6819,7 +6868,7 @@
     <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="128"/>
       <c r="B19" s="257" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C19" s="137">
         <f>IF(Inputs!C29="","",Inputs!C29)</f>
@@ -6964,7 +7013,7 @@
     <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="128"/>
       <c r="B22" s="272" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C22" s="220">
         <f t="shared" ref="C22:M22" si="8">IF(C6="","",MAX(C23,0)/C6)</f>
@@ -7066,7 +7115,7 @@
     <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="128"/>
       <c r="B24" s="297" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C24" s="298">
         <f t="shared" ref="C24:M24" si="9">IF(C6="","",C14-MAX(C18,0)-MAX(C19,0)-ABS(MAX(C23,0)-MAX(C21,0)))</f>
@@ -7168,7 +7217,7 @@
     <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="128"/>
       <c r="B26" s="267" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C26" s="268">
         <f>IF(C6="","",C24*(1-Fin_Analysis!$I$84))</f>
@@ -7474,7 +7523,7 @@
     <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="128"/>
       <c r="B32" s="256" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C32" s="140">
         <f>Inputs!C37</f>
@@ -7933,7 +7982,7 @@
     <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="122"/>
       <c r="B41" s="261" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C41" s="142"/>
       <c r="D41" s="142"/>
@@ -8002,7 +8051,7 @@
     <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="128"/>
       <c r="B43" s="256" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C43" s="139">
         <f t="shared" ref="C43:M43" si="36">IF(C6="","",(C10+MAX(C11,0))/C6)</f>
@@ -8206,7 +8255,7 @@
     <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="128"/>
       <c r="B47" s="256" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C47" s="139">
         <f t="shared" ref="C47:M47" si="40">IF(C6="","",ABS(MAX(C23,0)-MAX(C21,0))/C6)</f>
@@ -8308,10 +8357,10 @@
     <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="122"/>
       <c r="B49" s="263" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C49" s="144" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D49" s="145"/>
       <c r="E49" s="145"/>
@@ -8328,7 +8377,7 @@
     <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="128"/>
       <c r="B50" s="264" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C50" s="146">
         <f t="shared" ref="C50:M50" si="42">IF(C6="","",C6/C29)</f>
@@ -8379,7 +8428,7 @@
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="128"/>
       <c r="B51" s="256" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C51" s="139">
         <f t="shared" ref="C51:M51" si="43">IF(C30="","",C30/C6)</f>
@@ -8430,7 +8479,7 @@
     <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="128"/>
       <c r="B52" s="256" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C52" s="139">
         <f t="shared" ref="C52:M52" si="44">IF(C31="","",C31/C6)</f>
@@ -8481,7 +8530,7 @@
     <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="128"/>
       <c r="B53" s="256" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C53" s="139">
         <f t="shared" ref="C53:M53" si="45">IF(D6="","",C18/(C6-D6))</f>
@@ -8532,7 +8581,7 @@
     <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="122"/>
       <c r="B54" s="263" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C54" s="145"/>
       <c r="D54" s="145"/>
@@ -8549,7 +8598,7 @@
     <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="128"/>
       <c r="B55" s="262" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C55" s="143">
         <f t="shared" ref="C55:M55" si="46">IF(C36="","",(C36-C37)/C29)</f>
@@ -8699,7 +8748,7 @@
     <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="128"/>
       <c r="B58" s="256" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C58" s="139">
         <f>IF(C36="","",IF(Inputs!C38=0,0,Inputs!C38/C29))</f>
@@ -8749,7 +8798,7 @@
     <row r="59" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="122"/>
       <c r="B59" s="263" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C59" s="148" t="str">
         <f t="shared" ref="C59:M59" si="49">IFERROR(IF(C13*C50*(1/C55)=C60,"","Error"),"")</f>
@@ -8799,7 +8848,7 @@
     <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="128"/>
       <c r="B60" s="264" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C60" s="149">
         <f t="shared" ref="C60:M60" si="50">IF(C14="","",C14/(C36-C37))</f>
@@ -8849,7 +8898,7 @@
     <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="128"/>
       <c r="B61" s="264" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C61" s="149">
         <f t="shared" ref="C61:M61" si="51">IF(C24="","",C24/(C36-C37))</f>
@@ -10201,7 +10250,7 @@
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="150"/>
       <c r="B2" s="151" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C2" s="151"/>
       <c r="D2" s="152"/>
@@ -10347,13 +10396,13 @@
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="76" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C10" s="73" t="s">
         <v>28</v>
       </c>
       <c r="D10" s="73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E10" s="73" t="s">
         <v>29</v>
@@ -10363,7 +10412,7 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="76" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I10" s="73" t="s">
         <v>28</v>
@@ -11337,7 +11386,7 @@
     </row>
     <row r="51" spans="2:11" ht="11.65" x14ac:dyDescent="0.35">
       <c r="B51" s="76" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C51" s="275"/>
       <c r="D51" s="275"/>
@@ -11409,7 +11458,7 @@
         <f>I15+I34</f>
         <v>2034922</v>
       </c>
-      <c r="E56" s="317"/>
+      <c r="E56" s="313"/>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="I56" s="163"/>
@@ -11420,11 +11469,11 @@
         <v>83</v>
       </c>
       <c r="C57" s="2"/>
-      <c r="D57" s="318">
+      <c r="D57" s="314">
         <f>Inputs!C84</f>
         <v>0</v>
       </c>
-      <c r="E57" s="317"/>
+      <c r="E57" s="313"/>
       <c r="G57" s="2"/>
       <c r="I57" s="2"/>
       <c r="K57" s="165" t="s">
@@ -11436,11 +11485,11 @@
         <v>85</v>
       </c>
       <c r="C58" s="2"/>
-      <c r="D58" s="318">
+      <c r="D58" s="314">
         <f>Inputs!C85</f>
         <v>0</v>
       </c>
-      <c r="E58" s="317"/>
+      <c r="E58" s="313"/>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
       <c r="I58" s="2"/>
@@ -11467,7 +11516,7 @@
       <c r="F60" s="194"/>
       <c r="G60" s="194"/>
       <c r="H60" s="76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I60" s="76"/>
       <c r="K60" s="165"/>
@@ -11491,7 +11540,7 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I61" s="196">
         <f>C108*Data!$C$4/Common_Shares</f>
@@ -11518,7 +11567,7 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I62" s="287">
         <f>IF(OR(C101="CN",C101="HK"),Dashboard!C14,Dashboard!C10)</f>
@@ -11545,7 +11594,7 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="I63" s="200">
         <f>IF(I61&gt;0,FV(I62,D102,0,-I61),I61)</f>
@@ -11566,7 +11615,7 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I64" s="200">
         <f>IF(I61&gt;0,PV(C103,D102,0,-I63),I61)</f>
@@ -11687,11 +11736,11 @@
       </c>
       <c r="D72" s="306"/>
       <c r="E72" s="320" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F72" s="320"/>
       <c r="H72" s="320" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I72" s="320"/>
       <c r="K72" s="153" t="s">
@@ -11791,7 +11840,7 @@
     </row>
     <row r="77" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="93" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C77" s="90">
         <f>Data!C10+MAX(Data!C11,0)</f>
@@ -11847,7 +11896,7 @@
     </row>
     <row r="79" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="208" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C79" s="209">
         <f>C76-C77-C78</f>
@@ -11910,7 +11959,7 @@
     </row>
     <row r="81" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="93" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C81" s="90">
         <f>MAX(Data!C19,0)</f>
@@ -11940,7 +11989,7 @@
     </row>
     <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C82" s="90">
         <f>ABS(MAX(Data!C23,0)-MAX(Data!C21,0))</f>
@@ -12073,7 +12122,7 @@
     </row>
     <row r="87" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C87" s="225">
         <f>C86*Exchange_Rate/Dashboard!G3</f>
@@ -12094,7 +12143,7 @@
     </row>
     <row r="88" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C88" s="227">
         <f>Inputs!C44</f>
@@ -12124,7 +12173,7 @@
     </row>
     <row r="89" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C89" s="225">
         <f>C88*Exchange_Rate/Dashboard!G3</f>
@@ -12149,13 +12198,13 @@
     </row>
     <row r="91" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B91" s="303" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C91" s="304"/>
     </row>
     <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B92" s="17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="139">
         <f>C75/C74</f>
@@ -12164,7 +12213,7 @@
     </row>
     <row r="93" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B93" s="305" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C93" s="274">
         <f>C76/C74</f>
@@ -12173,7 +12222,7 @@
     </row>
     <row r="94" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B94" s="17" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C94" s="149">
         <f>C77/$C$74</f>
@@ -12182,7 +12231,7 @@
     </row>
     <row r="95" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B95" s="17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C95" s="169"/>
     </row>
@@ -12215,22 +12264,22 @@
     </row>
     <row r="101" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B101" s="76" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C101" s="251" t="str">
         <f>Inputs!C15</f>
         <v>HK</v>
       </c>
       <c r="D101" s="76" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E101" s="320" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F101" s="320"/>
       <c r="G101" s="2"/>
       <c r="H101" s="320" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I101" s="320"/>
       <c r="K101" s="68"/>
@@ -12249,14 +12298,14 @@
         <v>4</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F102" s="230">
         <f>FV(E87,D102,0,-(E86/(C102-D103)))*Exchange_Rate</f>
         <v>26.100486241176593</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I102" s="230">
         <f>FV(H87,D102,0,-(H86/(C102-D103)))*Exchange_Rate</f>
@@ -12266,7 +12315,7 @@
     </row>
     <row r="103" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C103" s="231">
         <f>Dashboard!G20</f>
@@ -12277,14 +12326,14 @@
         <v>0.02</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F103" s="230">
         <f>FV(E89,D102,0,-(E88/(C102-D103)))*Exchange_Rate</f>
         <v>24.043514669218538</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I103" s="230">
         <f>FV(H89,D102,0,-(H88/(C102-D103)))*Exchange_Rate</f>
@@ -12307,14 +12356,14 @@
         <v>HKD</v>
       </c>
       <c r="D105" s="233" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E105" s="234" t="str">
         <f>E72</f>
         <v>Pessimistic Case</v>
       </c>
       <c r="F105" s="235" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H105" s="234" t="str">
         <f>H72</f>
@@ -12421,18 +12470,18 @@
     </row>
     <row r="111" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B111" s="76" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C111" s="232"/>
       <c r="D111" s="233" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E111" s="234" t="str">
         <f>E105</f>
         <v>Pessimistic Case</v>
       </c>
       <c r="F111" s="235" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H111" s="234" t="str">
         <f>H105</f>
@@ -12476,18 +12525,18 @@
     </row>
     <row r="114" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="76" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C114" s="232"/>
       <c r="D114" s="233" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E114" s="245" t="str">
         <f>E105</f>
         <v>Pessimistic Case</v>
       </c>
       <c r="F114" s="235" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H114" s="245" t="str">
         <f>H105</f>
@@ -12500,7 +12549,7 @@
     </row>
     <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C115" s="236"/>
       <c r="D115" s="244">
@@ -12530,7 +12579,7 @@
     </row>
     <row r="117" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B117" s="76" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C117" s="252" t="str">
         <f>Inputs!C87</f>
@@ -12624,7 +12673,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
-  <dimension ref="B2:G43"/>
+  <dimension ref="B2:G51"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -12635,216 +12684,287 @@
   <sheetData>
     <row r="2" spans="2:4" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B2" s="299" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B5" s="299" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B6" s="299" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" s="299" t="s">
         <v>300</v>
       </c>
-      <c r="C5" s="299" t="s">
+      <c r="D6" s="299" t="s">
         <v>301</v>
-      </c>
-      <c r="D5" s="299" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B6" s="300" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="300" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="300" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" s="300" t="s">
-        <v>294</v>
+        <v>115</v>
       </c>
       <c r="C7" s="300" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="D7" s="300" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B8" s="300"/>
+      <c r="B8" s="300" t="s">
+        <v>293</v>
+      </c>
       <c r="C8" s="300" t="s">
-        <v>309</v>
+        <v>288</v>
+      </c>
+      <c r="D8" s="300" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" s="300"/>
       <c r="C9" s="300" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="300" t="s">
-        <v>313</v>
-      </c>
+      <c r="B10" s="300"/>
       <c r="C10" s="300" t="s">
-        <v>312</v>
-      </c>
-      <c r="D10" s="300" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" s="300" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C11" s="300" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="300" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="300" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="300" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="300" t="s">
         <v>304</v>
       </c>
-      <c r="D11" s="300" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="300"/>
-      <c r="C12" s="300" t="s">
-        <v>314</v>
-      </c>
-      <c r="D12" s="300"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="300"/>
       <c r="C13" s="300" t="s">
-        <v>240</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="D13" s="300"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="300" t="s">
-        <v>297</v>
-      </c>
       <c r="C14" s="300" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="300" t="s">
-        <v>306</v>
+        <v>239</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B15" s="300" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C15" s="300" t="s">
-        <v>295</v>
+        <v>89</v>
       </c>
       <c r="D15" s="300" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B16" s="300" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C16" s="300" t="s">
-        <v>303</v>
+        <v>294</v>
+      </c>
+      <c r="D16" s="300" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C17" s="300" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C18" s="300" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B21" s="301" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="302"/>
+    <row r="20" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B20" s="322" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="299" t="s">
+        <v>315</v>
+      </c>
+      <c r="D20" s="299" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="300" t="s">
+        <v>317</v>
+      </c>
+      <c r="C21" s="323">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="324">
+        <f>C21/$C$21</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B22" s="89" t="str">
+      <c r="B22" s="300" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="323">
+        <v>600</v>
+      </c>
+      <c r="D22" s="324">
+        <f t="shared" ref="D22:D25" si="0">C22/$C$21</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B23" s="299" t="s">
+        <v>318</v>
+      </c>
+      <c r="C23" s="323">
+        <v>400</v>
+      </c>
+      <c r="D23" s="324">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="300" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" s="323">
+        <v>300</v>
+      </c>
+      <c r="D24" s="324">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B25" s="299" t="s">
+        <v>319</v>
+      </c>
+      <c r="C25" s="323">
+        <v>100</v>
+      </c>
+      <c r="D25" s="324">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B29" s="301" t="s">
+        <v>285</v>
+      </c>
+      <c r="C29" s="302"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="89" t="str">
         <f>"(Numbers in "&amp;Data!C4&amp;Dashboard!G6&amp;")"</f>
         <v>(Numbers in 1000HKD)</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B23" s="8" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="8" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B24" s="93" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B32" s="93" t="s">
         <v>98</v>
       </c>
-      <c r="G24" s="300"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B25" s="11" t="s">
+      <c r="G32" s="300"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" s="11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B26" s="93" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B27" s="86" t="s">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" s="93" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" s="86" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B28" s="208" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B29" s="17" t="s">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" s="208" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" s="17" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B30" s="93" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B31" s="17" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="214" t="s">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B38" s="93" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" s="17" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B40" s="214" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="13.15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="17" t="s">
+    <row r="41" spans="2:2" ht="13.15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B34" s="221" t="s">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" s="221" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B37" s="300" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B41" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B42" s="7" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
-        <v>194</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" s="300" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B51" s="2" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -12856,9 +12976,37 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F585343-0A90-4A64-BB12-9F2BC0754C37}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:I22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4.59765625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B2" s="325" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="325"/>
+      <c r="D2" s="325"/>
+      <c r="E2" s="325"/>
+      <c r="F2" s="325"/>
+      <c r="G2" s="325"/>
+      <c r="H2" s="325"/>
+      <c r="I2" s="325"/>
+    </row>
+    <row r="22" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B22" s="325" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="325"/>
+      <c r="D22" s="325"/>
+      <c r="E22" s="325"/>
+      <c r="F22" s="325"/>
+      <c r="G22" s="325"/>
+      <c r="H22" s="325"/>
+      <c r="I22" s="325"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc_v4/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2D24C4-1EF7-9F40-A0C6-DA3962250B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0483F29-D7EF-462B-A695-56EFD47A331C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -35,17 +35,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
@@ -54,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="335">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1365,26 +1354,35 @@
   <si>
     <t>C0003</t>
   </si>
+  <si>
+    <t>Debt per share (HKD)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Common Equity/Total Asset</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="14">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="&quot;in&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
+  <numFmts count="15">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.00\x"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="181" formatCode="&quot;in&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="182" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="183" formatCode="#,##0_ "/>
+    <numFmt numFmtId="184" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="185" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="186" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="187" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="188" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="189" formatCode="0.000_ "/>
+    <numFmt numFmtId="190" formatCode="#,##0_);\(#,##0\)"/>
   </numFmts>
   <fonts count="40" x14ac:knownFonts="1">
     <font>
@@ -1790,7 +1788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1822,7 +1820,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1865,23 +1863,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1893,16 +1891,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2014,14 +2012,11 @@
     <xf numFmtId="37" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2038,7 +2033,7 @@
     <xf numFmtId="37" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2107,7 +2102,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2117,7 +2112,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2129,20 +2124,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2151,14 +2146,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="185" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="185" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2174,7 +2169,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2188,34 +2183,34 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
@@ -2223,7 +2218,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2250,17 +2245,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2293,11 +2288,11 @@
     <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="26" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2305,7 +2300,7 @@
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2314,6 +2309,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="190" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2322,7 +2326,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
@@ -2599,27 +2603,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" style="1" customWidth="1"/>
     <col min="4" max="5" width="25.6640625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B1" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="226" t="s">
         <v>330</v>
       </c>
       <c r="D1" s="56" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>62</v>
       </c>
@@ -2627,11 +2631,11 @@
         <v>45643</v>
       </c>
       <c r="D2" s="59"/>
-      <c r="E2" s="122" t="s">
+      <c r="E2" s="121" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A3" s="39" t="s">
         <v>120</v>
       </c>
@@ -2644,13 +2648,13 @@
       <c r="H3" s="25"/>
       <c r="I3" s="25"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" s="50" t="s">
         <v>118</v>
       </c>
       <c r="C4" s="51"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>119</v>
       </c>
@@ -2659,7 +2663,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B6" s="2" t="s">
         <v>72</v>
       </c>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>73</v>
       </c>
@@ -2677,7 +2681,7 @@
         <v>45626</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B9" s="50" t="str">
         <f>D1&amp;" Stock Information"</f>
         <v>0590.HK Stock Information</v>
@@ -2685,7 +2689,7 @@
       <c r="C9" s="51"/>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>185</v>
       </c>
@@ -2696,7 +2700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2709,7 @@
       </c>
       <c r="D11" s="37"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
         <v>1</v>
       </c>
@@ -2714,7 +2718,7 @@
       </c>
       <c r="D12" s="35"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B13" s="5" t="s">
         <v>2</v>
       </c>
@@ -2726,7 +2730,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
@@ -2736,10 +2740,10 @@
       </c>
       <c r="D14" s="55"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D15" s="6"/>
     </row>
-    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A16" s="39" t="s">
         <v>121</v>
       </c>
@@ -2748,7 +2752,7 @@
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="str">
         <f>"1."</f>
         <v>1.</v>
@@ -2757,30 +2761,30 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B19" s="52" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B22" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="147">
+      <c r="C22" s="146">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C23" s="100">
+      <c r="C23" s="99">
         <f>Normalized_FCF!C16</f>
         <v>1156950.0267037901</v>
       </c>
@@ -2789,72 +2793,72 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="100">
+      <c r="C24" s="99">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B25" s="144" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="143" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="100">
+      <c r="C25" s="99">
         <f>C23+C24</f>
         <v>1156950.0267037901</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C27" s="100">
+      <c r="C27" s="99">
         <f>Normalized_FCF!C19</f>
         <v>1156950.0267037901</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C28" s="143">
+      <c r="C28" s="142">
         <f>C27/(Common_Shares/Data!C3)</f>
         <v>1.9705919903877798</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C29" s="123">
+      <c r="C29" s="122">
         <f>C28/Market_Price</f>
         <v>0.12567550959105739</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="53" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B32" s="53" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B33" s="53" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B34" s="53" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="str">
         <f>"2."</f>
         <v>2.</v>
@@ -2863,53 +2867,53 @@
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C37" s="165">
+      <c r="C37" s="164">
         <v>0.1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="C38" s="123"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C38" s="122"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B39" s="18" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B40" s="144" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="143" t="s">
         <v>203</v>
       </c>
-      <c r="C40" s="150">
+      <c r="C40" s="149">
         <v>0</v>
       </c>
       <c r="D40" s="54" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B41" s="144" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="143" t="s">
         <v>204</v>
       </c>
-      <c r="C41" s="150">
-        <v>0</v>
-      </c>
-      <c r="D41" s="149" t="s">
+      <c r="C41" s="149">
+        <v>0</v>
+      </c>
+      <c r="D41" s="148" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="B42" s="144" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="143" t="s">
         <v>205</v>
       </c>
-      <c r="C42" s="150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="C42" s="149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B43" s="91" t="s">
         <v>202</v>
       </c>
@@ -2918,7 +2922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="19" t="str">
         <f>"3."</f>
         <v>3.</v>
@@ -2927,32 +2931,32 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" s="52" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B50" s="52" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="19" t="str">
         <f>"4."</f>
         <v>4.</v>
@@ -2961,93 +2965,93 @@
         <v>122</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B54" s="52" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B57" s="52" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B60" s="52" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B65" s="52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="B66" s="138" t="s">
+    <row r="66" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B66" s="137" t="s">
         <v>243</v>
       </c>
       <c r="C66"/>
     </row>
-    <row r="67" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="B67" s="138" t="s">
+    <row r="67" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B67" s="137" t="s">
         <v>241</v>
       </c>
-      <c r="C67" s="196">
+      <c r="C67" s="195">
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="13" x14ac:dyDescent="0.15">
-      <c r="B68" s="138" t="s">
+    <row r="68" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B68" s="137" t="s">
         <v>281</v>
       </c>
-      <c r="C68" s="216">
+      <c r="C68" s="215">
         <v>0.2</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C69" s="201">
+      <c r="C69" s="200">
         <f>Scenarios!F83</f>
         <v>-0.25653469314758881</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B71" s="52" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B72" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="19" t="str">
         <f>"5."</f>
         <v>5.</v>
@@ -3056,32 +3060,32 @@
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B75" s="52" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B76" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B78" s="52" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A82" s="39" t="s">
         <v>116</v>
       </c>
@@ -3090,57 +3094,57 @@
       <c r="D82" s="39"/>
       <c r="E82" s="39"/>
     </row>
-    <row r="84" spans="1:5" ht="14" x14ac:dyDescent="0.2">
-      <c r="B84" s="172" t="s">
+    <row r="84" spans="1:5" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B84" s="171" t="s">
         <v>227</v>
       </c>
-      <c r="C84" s="172" t="s">
+      <c r="C84" s="171" t="s">
         <v>252</v>
       </c>
-      <c r="D84" s="173" t="s">
+      <c r="D84" s="172" t="s">
         <v>222</v>
       </c>
-      <c r="E84" s="173" t="s">
+      <c r="E84" s="172" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B85" s="171" t="s">
+    <row r="85" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B85" s="170" t="s">
         <v>224</v>
       </c>
-      <c r="C85" s="187"/>
-      <c r="D85" s="180"/>
-      <c r="E85" s="187"/>
-    </row>
-    <row r="86" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B86" s="171" t="s">
+      <c r="C85" s="186"/>
+      <c r="D85" s="179"/>
+      <c r="E85" s="186"/>
+    </row>
+    <row r="86" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B86" s="170" t="s">
         <v>225</v>
       </c>
-      <c r="C86" s="187"/>
-      <c r="D86" s="180"/>
-      <c r="E86" s="187"/>
-    </row>
-    <row r="87" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B87" s="171" t="s">
+      <c r="C86" s="186"/>
+      <c r="D86" s="179"/>
+      <c r="E86" s="186"/>
+    </row>
+    <row r="87" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B87" s="170" t="s">
         <v>223</v>
       </c>
-      <c r="C87" s="187"/>
-      <c r="D87" s="180"/>
-      <c r="E87" s="187"/>
-    </row>
-    <row r="88" spans="1:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B88" s="171" t="s">
+      <c r="C87" s="186"/>
+      <c r="D87" s="179"/>
+      <c r="E87" s="186"/>
+    </row>
+    <row r="88" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="B88" s="170" t="s">
         <v>226</v>
       </c>
-      <c r="C88" s="187"/>
-      <c r="D88" s="180"/>
-      <c r="E88" s="187"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="C88" s="186"/>
+      <c r="D88" s="179"/>
+      <c r="E88" s="186"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B90" s="52" t="s">
         <v>117</v>
       </c>
-      <c r="C90" s="192">
+      <c r="C90" s="191">
         <f>Scenarios!C83</f>
         <v>12.927104280778764</v>
       </c>
@@ -3149,7 +3153,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A92" s="39" t="s">
         <v>108</v>
       </c>
@@ -3158,32 +3162,32 @@
       <c r="D92" s="39"/>
       <c r="E92" s="39"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B93" s="52" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B96" s="52" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B97" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B99" s="52" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B100" s="1" t="s">
         <v>114</v>
       </c>
@@ -3220,20 +3224,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B1" s="120" t="str">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B1" s="119" t="str">
         <f>Thesis!C12</f>
         <v>HKD</v>
       </c>
-      <c r="C1" s="142">
+      <c r="C1" s="141">
         <v>45382</v>
       </c>
       <c r="D1" s="41">
@@ -3277,7 +3281,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
         <v>190</v>
       </c>
@@ -3293,15 +3297,15 @@
       <c r="L2" s="40"/>
       <c r="M2" s="40"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="145">
+      <c r="C3" s="144">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="35" t="s">
         <v>3</v>
       </c>
@@ -3329,7 +3333,7 @@
       <c r="L4" s="76"/>
       <c r="M4" s="76"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="44" t="s">
         <v>66</v>
       </c>
@@ -3357,7 +3361,7 @@
       <c r="L5" s="76"/>
       <c r="M5" s="76"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="44" t="s">
         <v>80</v>
       </c>
@@ -3385,7 +3389,7 @@
       <c r="L6" s="76"/>
       <c r="M6" s="76"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="89" t="s">
         <v>129</v>
       </c>
@@ -3409,7 +3413,7 @@
       <c r="L7" s="90"/>
       <c r="M7" s="90"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="44" t="s">
         <v>74</v>
       </c>
@@ -3425,7 +3429,7 @@
       <c r="L8" s="76"/>
       <c r="M8" s="76"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="44" t="s">
         <v>303</v>
       </c>
@@ -3445,7 +3449,7 @@
       <c r="L9" s="76"/>
       <c r="M9" s="76"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="44" t="s">
         <v>314</v>
       </c>
@@ -3461,7 +3465,7 @@
       <c r="L10" s="76"/>
       <c r="M10" s="76"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="44" t="s">
         <v>300</v>
       </c>
@@ -3477,7 +3481,7 @@
       <c r="L11" s="76"/>
       <c r="M11" s="76"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="44" t="s">
         <v>58</v>
       </c>
@@ -3505,7 +3509,7 @@
       <c r="L12" s="76"/>
       <c r="M12" s="76"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="44" t="s">
         <v>139</v>
       </c>
@@ -3529,7 +3533,7 @@
       <c r="L13" s="76"/>
       <c r="M13" s="76"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="44" t="s">
         <v>75</v>
       </c>
@@ -3553,7 +3557,7 @@
       <c r="L14" s="76"/>
       <c r="M14" s="76"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="47" t="s">
         <v>64</v>
       </c>
@@ -3579,7 +3583,7 @@
       <c r="L15" s="88"/>
       <c r="M15" s="88"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="31" t="s">
         <v>67</v>
       </c>
@@ -3607,13 +3611,13 @@
       <c r="L16" s="76"/>
       <c r="M16" s="76"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="18" t="s">
         <v>76</v>
       </c>
       <c r="C18" s="11"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="30" t="s">
         <v>70</v>
       </c>
@@ -3637,7 +3641,7 @@
       <c r="L19" s="76"/>
       <c r="M19" s="76"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="30" t="s">
         <v>78</v>
       </c>
@@ -3661,7 +3665,7 @@
       <c r="L20" s="76"/>
       <c r="M20" s="76"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="30" t="s">
         <v>77</v>
       </c>
@@ -3685,7 +3689,7 @@
       <c r="L21" s="76"/>
       <c r="M21" s="76"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -3714,13 +3718,13 @@
       <c r="L22" s="42"/>
       <c r="M22" s="42"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="11"/>
     </row>
-    <row r="25" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="29" t="s">
         <v>32</v>
       </c>
@@ -3742,7 +3746,7 @@
       <c r="L25" s="76"/>
       <c r="M25" s="76"/>
     </row>
-    <row r="26" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="29" t="s">
         <v>41</v>
       </c>
@@ -3764,7 +3768,7 @@
       <c r="L26" s="76"/>
       <c r="M26" s="76"/>
     </row>
-    <row r="27" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="32" t="s">
         <v>59</v>
       </c>
@@ -3788,7 +3792,7 @@
       <c r="L27" s="88"/>
       <c r="M27" s="88"/>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="32" t="s">
         <v>39</v>
       </c>
@@ -3812,13 +3816,13 @@
       <c r="L28" s="88"/>
       <c r="M28" s="88"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B30" s="18" t="s">
         <v>79</v>
       </c>
       <c r="C30" s="11"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="29" t="s">
         <v>60</v>
       </c>
@@ -3842,7 +3846,7 @@
       <c r="L31" s="76"/>
       <c r="M31" s="76"/>
     </row>
-    <row r="33" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B33" s="39" t="s">
         <v>167</v>
       </c>
@@ -3858,12 +3862,12 @@
       <c r="L33" s="40"/>
       <c r="M33" s="40"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B34" s="18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="35" t="s">
         <v>3</v>
       </c>
@@ -3912,7 +3916,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="44" t="s">
         <v>66</v>
       </c>
@@ -3961,7 +3965,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="34" t="s">
         <v>126</v>
       </c>
@@ -4010,7 +4014,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="44" t="s">
         <v>80</v>
       </c>
@@ -4059,7 +4063,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="89" t="s">
         <v>129</v>
       </c>
@@ -4108,7 +4112,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="89" t="s">
         <v>133</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="44" t="s">
         <v>74</v>
       </c>
@@ -4206,7 +4210,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
         <v>294</v>
       </c>
@@ -4255,105 +4259,105 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="47" t="s">
         <v>315</v>
       </c>
-      <c r="C43" s="233">
+      <c r="C43" s="232">
         <f t="shared" ref="C43:M43" si="18">IF(C$4="","",C46-C45-C44-C42)</f>
         <v>248317</v>
       </c>
-      <c r="D43" s="233">
+      <c r="D43" s="232">
         <f t="shared" si="18"/>
         <v>190177</v>
       </c>
-      <c r="E43" s="233">
+      <c r="E43" s="232">
         <f t="shared" si="18"/>
         <v>200697</v>
       </c>
-      <c r="F43" s="233">
+      <c r="F43" s="232">
         <f t="shared" si="18"/>
         <v>281254</v>
       </c>
-      <c r="G43" s="233">
+      <c r="G43" s="232">
         <f t="shared" si="18"/>
         <v>-275378</v>
       </c>
-      <c r="H43" s="233">
+      <c r="H43" s="232">
         <f t="shared" si="18"/>
         <v>-1582814</v>
       </c>
-      <c r="I43" s="233" t="str">
+      <c r="I43" s="232" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J43" s="233" t="str">
+      <c r="J43" s="232" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="K43" s="233" t="str">
+      <c r="K43" s="232" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L43" s="233" t="str">
+      <c r="L43" s="232" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M43" s="233" t="str">
+      <c r="M43" s="232" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="C44" s="100">
+      <c r="C44" s="99">
         <f t="shared" ref="C44:M44" si="19">IF(C$4="","",C50+C51)</f>
         <v>-30619</v>
       </c>
-      <c r="D44" s="100">
+      <c r="D44" s="99">
         <f t="shared" si="19"/>
         <v>12362</v>
       </c>
-      <c r="E44" s="100">
+      <c r="E44" s="99">
         <f t="shared" si="19"/>
         <v>64247</v>
       </c>
-      <c r="F44" s="100">
+      <c r="F44" s="99">
         <f t="shared" si="19"/>
         <v>34549</v>
       </c>
-      <c r="G44" s="100">
+      <c r="G44" s="99">
         <f t="shared" si="19"/>
         <v>-63075</v>
       </c>
-      <c r="H44" s="100">
+      <c r="H44" s="99">
         <f t="shared" si="19"/>
         <v>-34253</v>
       </c>
-      <c r="I44" s="100" t="str">
+      <c r="I44" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J44" s="100" t="str">
+      <c r="J44" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K44" s="100" t="str">
+      <c r="K44" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L44" s="100" t="str">
+      <c r="L44" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M44" s="100" t="str">
+      <c r="M44" s="99" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="44" t="s">
         <v>75</v>
       </c>
@@ -4402,7 +4406,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
         <v>64</v>
       </c>
@@ -4451,7 +4455,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="31" t="s">
         <v>67</v>
       </c>
@@ -4500,12 +4504,12 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B49" s="18" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="44" t="s">
         <v>58</v>
       </c>
@@ -4554,7 +4558,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="44" t="s">
         <v>139</v>
       </c>
@@ -4603,214 +4607,214 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B53" s="234" t="s">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B53" s="233" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="C54" s="100">
+      <c r="C54" s="99">
         <f t="shared" ref="C54:M54" si="25">IF(C$4="","",C9)</f>
         <v>639</v>
       </c>
-      <c r="D54" s="100">
+      <c r="D54" s="99">
         <f t="shared" si="25"/>
         <v>927</v>
       </c>
-      <c r="E54" s="100">
+      <c r="E54" s="99">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="F54" s="100">
+      <c r="F54" s="99">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="G54" s="100">
+      <c r="G54" s="99">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H54" s="100">
+      <c r="H54" s="99">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="I54" s="100" t="str">
+      <c r="I54" s="99" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="J54" s="100" t="str">
+      <c r="J54" s="99" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="K54" s="100" t="str">
+      <c r="K54" s="99" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="L54" s="100" t="str">
+      <c r="L54" s="99" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M54" s="100" t="str">
+      <c r="M54" s="99" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="C55" s="100">
+      <c r="C55" s="99">
         <f t="shared" ref="C55:M55" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D55" s="100">
+      <c r="D55" s="99">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E55" s="100">
+      <c r="E55" s="99">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F55" s="100">
+      <c r="F55" s="99">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="G55" s="100">
+      <c r="G55" s="99">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H55" s="100">
+      <c r="H55" s="99">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="I55" s="100" t="str">
+      <c r="I55" s="99" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="J55" s="100" t="str">
+      <c r="J55" s="99" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="K55" s="100" t="str">
+      <c r="K55" s="99" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="L55" s="100" t="str">
+      <c r="L55" s="99" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M55" s="100" t="str">
+      <c r="M55" s="99" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="44" t="s">
         <v>300</v>
       </c>
-      <c r="C56" s="100">
+      <c r="C56" s="99">
         <f>IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="100">
+      <c r="D56" s="99">
         <f t="shared" ref="D56:M56" si="27">IF(D$4="","",D11)</f>
         <v>0</v>
       </c>
-      <c r="E56" s="100">
+      <c r="E56" s="99">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F56" s="100">
+      <c r="F56" s="99">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G56" s="100">
+      <c r="G56" s="99">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H56" s="100">
+      <c r="H56" s="99">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="I56" s="100" t="str">
+      <c r="I56" s="99" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="J56" s="100" t="str">
+      <c r="J56" s="99" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="K56" s="100" t="str">
+      <c r="K56" s="99" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="L56" s="100" t="str">
+      <c r="L56" s="99" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="M56" s="100" t="str">
+      <c r="M56" s="99" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="C57" s="100">
+      <c r="C57" s="99">
         <f>IF(C$4="","",C43-C54-C55-C56)</f>
         <v>247678</v>
       </c>
-      <c r="D57" s="100">
+      <c r="D57" s="99">
         <f t="shared" ref="D57:M57" si="28">IF(D$4="","",D43-D54-D55-D56)</f>
         <v>189250</v>
       </c>
-      <c r="E57" s="100">
+      <c r="E57" s="99">
         <f t="shared" si="28"/>
         <v>200697</v>
       </c>
-      <c r="F57" s="100">
+      <c r="F57" s="99">
         <f t="shared" si="28"/>
         <v>281254</v>
       </c>
-      <c r="G57" s="100">
+      <c r="G57" s="99">
         <f t="shared" si="28"/>
         <v>-275378</v>
       </c>
-      <c r="H57" s="100">
+      <c r="H57" s="99">
         <f t="shared" si="28"/>
         <v>-1582814</v>
       </c>
-      <c r="I57" s="100" t="str">
+      <c r="I57" s="99" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="J57" s="100" t="str">
+      <c r="J57" s="99" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="K57" s="100" t="str">
+      <c r="K57" s="99" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="L57" s="100" t="str">
+      <c r="L57" s="99" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="M57" s="100" t="str">
+      <c r="M57" s="99" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B59" s="18" t="s">
         <v>76</v>
       </c>
       <c r="C59" s="11"/>
     </row>
-    <row r="60" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="30" t="s">
         <v>70</v>
       </c>
@@ -4859,7 +4863,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="30" t="s">
         <v>78</v>
       </c>
@@ -4908,7 +4912,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="30" t="s">
         <v>77</v>
       </c>
@@ -4957,7 +4961,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
         <v>54</v>
       </c>
@@ -5006,262 +5010,262 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B65" s="121" t="s">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="120" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="str">
         <f>B35</f>
         <v>Sales</v>
       </c>
-      <c r="C66" s="123">
+      <c r="C66" s="122">
         <f t="shared" ref="C66:M66" si="33">IF(D$35="","",C35/D35-1)</f>
         <v>0.27952593137796744</v>
       </c>
-      <c r="D66" s="123">
+      <c r="D66" s="122">
         <f t="shared" si="33"/>
         <v>2.0450249505806095E-2</v>
       </c>
-      <c r="E66" s="123">
+      <c r="E66" s="122">
         <f t="shared" si="33"/>
         <v>0.32460887665346139</v>
       </c>
-      <c r="F66" s="123">
+      <c r="F66" s="122">
         <f t="shared" si="33"/>
         <v>-0.21118785490642455</v>
       </c>
-      <c r="G66" s="123">
+      <c r="G66" s="122">
         <f t="shared" si="33"/>
         <v>-0.29169116752280422</v>
       </c>
-      <c r="H66" s="123" t="str">
+      <c r="H66" s="122" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="I66" s="123" t="str">
+      <c r="I66" s="122" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="J66" s="123" t="str">
+      <c r="J66" s="122" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="K66" s="123" t="str">
+      <c r="K66" s="122" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="L66" s="123" t="str">
+      <c r="L66" s="122" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="M66" s="123" t="str">
+      <c r="M66" s="122" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B67" s="107" t="str">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="106" t="str">
         <f>B42</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C67" s="139">
+      <c r="C67" s="138">
         <f t="shared" ref="C67:M67" si="34">IF(D$35="","",C36/D36-1)</f>
         <v>0.27484316281081789</v>
       </c>
-      <c r="D67" s="139">
+      <c r="D67" s="138">
         <f t="shared" si="34"/>
         <v>2.8630254836090829E-2</v>
       </c>
-      <c r="E67" s="139">
+      <c r="E67" s="138">
         <f t="shared" si="34"/>
         <v>0.36521892689379709</v>
       </c>
-      <c r="F67" s="139">
+      <c r="F67" s="138">
         <f t="shared" si="34"/>
         <v>-0.21258803367720713</v>
       </c>
-      <c r="G67" s="139">
+      <c r="G67" s="138">
         <f t="shared" si="34"/>
         <v>-0.33107999439209057</v>
       </c>
-      <c r="H67" s="139" t="str">
+      <c r="H67" s="138" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="I67" s="139" t="str">
+      <c r="I67" s="138" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="J67" s="139" t="str">
+      <c r="J67" s="138" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="K67" s="139" t="str">
+      <c r="K67" s="138" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="L67" s="139" t="str">
+      <c r="L67" s="138" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="M67" s="139" t="str">
+      <c r="M67" s="138" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="str">
         <f>B57</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C68" s="123">
+      <c r="C68" s="122">
         <f t="shared" ref="C68:M68" si="35">IF(D$35="","",C37/D37-1)</f>
         <v>0.29220619013700166</v>
       </c>
-      <c r="D68" s="123">
+      <c r="D68" s="122">
         <f t="shared" si="35"/>
         <v>-1.0606627998344109E-3</v>
       </c>
-      <c r="E68" s="123">
+      <c r="E68" s="122">
         <f t="shared" si="35"/>
         <v>0.22851064557243328</v>
       </c>
-      <c r="F68" s="123">
+      <c r="F68" s="122">
         <f t="shared" si="35"/>
         <v>-0.20785460213901807</v>
       </c>
-      <c r="G68" s="123">
+      <c r="G68" s="122">
         <f t="shared" si="35"/>
         <v>-0.1762134107583947</v>
       </c>
-      <c r="H68" s="123" t="str">
+      <c r="H68" s="122" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="I68" s="123" t="str">
+      <c r="I68" s="122" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="J68" s="123" t="str">
+      <c r="J68" s="122" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="K68" s="123" t="str">
+      <c r="K68" s="122" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="L68" s="123" t="str">
+      <c r="L68" s="122" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="M68" s="123" t="str">
+      <c r="M68" s="122" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B69" s="107" t="str">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="106" t="str">
         <f>B46</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C69" s="139">
+      <c r="C69" s="138">
         <f t="shared" ref="C69:M69" si="36">IF(D$35="","",C38/D38-1)</f>
         <v>0.23027981033619538</v>
       </c>
-      <c r="D69" s="139">
+      <c r="D69" s="138">
         <f t="shared" si="36"/>
         <v>2.88709616106122E-2</v>
       </c>
-      <c r="E69" s="139">
+      <c r="E69" s="138">
         <f t="shared" si="36"/>
         <v>7.1190571738822594E-2</v>
       </c>
-      <c r="F69" s="139">
+      <c r="F69" s="138">
         <f t="shared" si="36"/>
         <v>-0.20005740582329201</v>
       </c>
-      <c r="G69" s="139">
+      <c r="G69" s="138">
         <f t="shared" si="36"/>
         <v>-0.12351904546938497</v>
       </c>
-      <c r="H69" s="139" t="str">
+      <c r="H69" s="138" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="I69" s="139" t="str">
+      <c r="I69" s="138" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="J69" s="139" t="str">
+      <c r="J69" s="138" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="K69" s="139" t="str">
+      <c r="K69" s="138" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="L69" s="139" t="str">
+      <c r="L69" s="138" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="M69" s="139" t="str">
+      <c r="M69" s="138" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="str">
         <f>B47</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C70" s="123">
+      <c r="C70" s="122">
         <f>IF(D$35="","",C63/D63-1)</f>
         <v>0.23636363636363611</v>
       </c>
-      <c r="D70" s="123">
+      <c r="D70" s="122">
         <f t="shared" ref="D70:M70" si="37">IF(E$35="","",D63/E63-1)</f>
         <v>0</v>
       </c>
-      <c r="E70" s="123">
+      <c r="E70" s="122">
         <f t="shared" si="37"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="F70" s="123">
+      <c r="F70" s="122">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="G70" s="123">
+      <c r="G70" s="122">
         <f t="shared" si="37"/>
         <v>-0.13043478260869557</v>
       </c>
-      <c r="H70" s="123" t="str">
+      <c r="H70" s="122" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="I70" s="123" t="str">
+      <c r="I70" s="122" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J70" s="123" t="str">
+      <c r="J70" s="122" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="K70" s="123" t="str">
+      <c r="K70" s="122" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="L70" s="123" t="str">
+      <c r="L70" s="122" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="M70" s="123" t="str">
+      <c r="M70" s="122" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B72" s="39" t="s">
         <v>168</v>
       </c>
@@ -5277,63 +5281,63 @@
       <c r="L72" s="40"/>
       <c r="M72" s="40"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B73" s="18" t="s">
         <v>37</v>
       </c>
       <c r="C73" s="11"/>
     </row>
-    <row r="74" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C74" s="100">
+      <c r="C74" s="99">
         <f>IF(C$4="","",C77+C78)</f>
         <v>16854064</v>
       </c>
-      <c r="D74" s="100">
+      <c r="D74" s="99">
         <f t="shared" ref="D74:M74" si="38">IF(D$4="","",D77+D78)</f>
         <v>14687373</v>
       </c>
-      <c r="E74" s="100">
+      <c r="E74" s="99">
         <f t="shared" si="38"/>
         <v>15987114</v>
       </c>
-      <c r="F74" s="100">
+      <c r="F74" s="99">
         <f t="shared" si="38"/>
         <v>14270996</v>
       </c>
-      <c r="G74" s="100">
+      <c r="G74" s="99">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="H74" s="100">
+      <c r="H74" s="99">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="I74" s="100" t="str">
+      <c r="I74" s="99" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="J74" s="100" t="str">
+      <c r="J74" s="99" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="K74" s="100" t="str">
+      <c r="K74" s="99" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="L74" s="100" t="str">
+      <c r="L74" s="99" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="M74" s="100" t="str">
+      <c r="M74" s="99" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
-    <row r="75" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B75" s="126" t="s">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="125" t="s">
         <v>171</v>
       </c>
       <c r="C75" s="94">
@@ -5360,14 +5364,14 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I75" s="127"/>
-      <c r="J75" s="127"/>
-      <c r="K75" s="127"/>
-      <c r="L75" s="127"/>
-      <c r="M75" s="127"/>
-    </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="B76" s="126" t="s">
+      <c r="I75" s="126"/>
+      <c r="J75" s="126"/>
+      <c r="K75" s="126"/>
+      <c r="L75" s="126"/>
+      <c r="M75" s="126"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="125" t="s">
         <v>172</v>
       </c>
       <c r="C76" s="94">
@@ -5394,13 +5398,13 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="I76" s="127"/>
-      <c r="J76" s="127"/>
-      <c r="K76" s="127"/>
-      <c r="L76" s="127"/>
-      <c r="M76" s="127"/>
-    </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+      <c r="I76" s="126"/>
+      <c r="J76" s="126"/>
+      <c r="K76" s="126"/>
+      <c r="L76" s="126"/>
+      <c r="M76" s="126"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="29" t="s">
         <v>59</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="29" t="s">
         <v>39</v>
       </c>
@@ -5525,21 +5529,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q819"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
-      <c r="B1" s="120" t="str">
+      <c r="B1" s="119" t="str">
         <f>Thesis!C12</f>
         <v>HKD</v>
       </c>
@@ -5594,7 +5598,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="61" t="s">
         <v>199</v>
@@ -5617,12 +5621,12 @@
       <c r="P2" s="40"/>
       <c r="Q2" s="40"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12"/>
       <c r="B3" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C3" s="146">
+      <c r="C3" s="145">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
@@ -5630,7 +5634,7 @@
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="12"/>
       <c r="B4" s="29" t="s">
         <v>3</v>
@@ -5687,7 +5691,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="12"/>
       <c r="B5" s="2" t="s">
         <v>69</v>
@@ -5742,7 +5746,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="34" t="s">
         <v>71</v>
@@ -5797,7 +5801,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12"/>
       <c r="B7" s="10" t="s">
         <v>68</v>
@@ -5852,7 +5856,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12"/>
       <c r="B8" s="2" t="s">
         <v>136</v>
@@ -5907,7 +5911,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12"/>
       <c r="B9" s="2" t="s">
         <v>166</v>
@@ -5962,7 +5966,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="32" t="s">
         <v>294</v>
@@ -5972,7 +5976,7 @@
         <v>1533151.5022127144</v>
       </c>
       <c r="D10" s="67"/>
-      <c r="E10" s="103"/>
+      <c r="E10" s="102"/>
       <c r="F10" s="67"/>
       <c r="G10" s="80">
         <f>IF(G$4="","",SUM(G6:G9))</f>
@@ -6019,20 +6023,20 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12"/>
       <c r="B11" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="C11" s="237">
+      <c r="C11" s="236">
         <f>C67</f>
         <v>0</v>
       </c>
-      <c r="D11" s="224"/>
+      <c r="D11" s="223"/>
       <c r="E11" s="85" t="s">
         <v>318</v>
       </c>
-      <c r="F11" s="224"/>
+      <c r="F11" s="223"/>
       <c r="G11" s="68">
         <f>G67</f>
         <v>248317</v>
@@ -6078,7 +6082,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12"/>
       <c r="B12" s="2" t="s">
         <v>140</v>
@@ -6133,7 +6137,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12"/>
       <c r="B13" s="91" t="s">
         <v>309</v>
@@ -6188,7 +6192,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="2" t="s">
         <v>132</v>
@@ -6243,7 +6247,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12"/>
       <c r="B15" s="44" t="s">
         <v>67</v>
@@ -6300,7 +6304,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12"/>
       <c r="B16" s="45" t="s">
         <v>296</v>
@@ -6310,7 +6314,7 @@
         <v>1156950.0267037901</v>
       </c>
       <c r="D16" s="70"/>
-      <c r="E16" s="104"/>
+      <c r="E16" s="103"/>
       <c r="F16" s="70"/>
       <c r="G16" s="80">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -6357,7 +6361,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12"/>
       <c r="B17" s="30" t="s">
         <v>77</v>
@@ -6371,19 +6375,19 @@
         <v>288</v>
       </c>
       <c r="F17" s="66"/>
-      <c r="G17" s="221"/>
-      <c r="H17" s="221"/>
-      <c r="I17" s="221"/>
-      <c r="J17" s="221"/>
-      <c r="K17" s="221"/>
-      <c r="L17" s="221"/>
-      <c r="M17" s="221"/>
-      <c r="N17" s="221"/>
-      <c r="O17" s="221"/>
-      <c r="P17" s="221"/>
-      <c r="Q17" s="221"/>
-    </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G17" s="220"/>
+      <c r="H17" s="220"/>
+      <c r="I17" s="220"/>
+      <c r="J17" s="220"/>
+      <c r="K17" s="220"/>
+      <c r="L17" s="220"/>
+      <c r="M17" s="220"/>
+      <c r="N17" s="220"/>
+      <c r="O17" s="220"/>
+      <c r="P17" s="220"/>
+      <c r="Q17" s="220"/>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12"/>
       <c r="B18" s="30" t="s">
         <v>197</v>
@@ -6396,19 +6400,19 @@
         <v>196</v>
       </c>
       <c r="F18" s="66"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="148"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="148"/>
-      <c r="O18" s="148"/>
-      <c r="P18" s="148"/>
-      <c r="Q18" s="148"/>
-    </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G18" s="147"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="147"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="147"/>
+      <c r="L18" s="147"/>
+      <c r="M18" s="147"/>
+      <c r="N18" s="147"/>
+      <c r="O18" s="147"/>
+      <c r="P18" s="147"/>
+      <c r="Q18" s="147"/>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12"/>
       <c r="B19" s="34" t="s">
         <v>265</v>
@@ -6465,7 +6469,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12"/>
       <c r="B20" s="30"/>
       <c r="C20" s="74"/>
@@ -6484,7 +6488,7 @@
       <c r="P20" s="14"/>
       <c r="Q20" s="14"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="93" t="s">
         <v>65</v>
@@ -6505,12 +6509,12 @@
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12"/>
       <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="101">
+      <c r="C22" s="100">
         <f>ABS(C5/C$4)</f>
         <v>0.85899904876773536</v>
       </c>
@@ -6562,12 +6566,12 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12"/>
       <c r="B23" s="34" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="102">
+      <c r="C23" s="101">
         <f>ABS(C6/C$4)</f>
         <v>0.14100095123226461</v>
       </c>
@@ -6619,12 +6623,12 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12"/>
       <c r="B24" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C24" s="101">
+      <c r="C24" s="100">
         <f>ABS(C7/C$4)</f>
         <v>2.3191910456354398E-2</v>
       </c>
@@ -6676,12 +6680,12 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12"/>
       <c r="B25" s="32" t="s">
         <v>294</v>
       </c>
-      <c r="C25" s="102">
+      <c r="C25" s="101">
         <f>ABS(C10/C$4)</f>
         <v>0.11780904077591021</v>
       </c>
@@ -6733,12 +6737,12 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12"/>
       <c r="B26" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="101">
+      <c r="C26" s="100">
         <f>ABS(C12/C$4)</f>
         <v>2.3527974986891549E-3</v>
       </c>
@@ -6790,12 +6794,12 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="101">
+      <c r="C27" s="100">
         <f>ABS(C14/C$4)</f>
         <v>2.6554935953760846E-2</v>
       </c>
@@ -6847,10 +6851,10 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12"/>
       <c r="B28" s="45"/>
-      <c r="C28" s="102">
+      <c r="C28" s="101">
         <f>ABS(C16/C$4)</f>
         <v>8.8901307323460216E-2</v>
       </c>
@@ -6902,12 +6906,12 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12"/>
       <c r="B29" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="101">
+      <c r="C29" s="100">
         <f>ABS(C11/C$4)</f>
         <v>0</v>
       </c>
@@ -6959,12 +6963,12 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="101">
+      <c r="C30" s="100">
         <f>ABS(C8/C$4)</f>
         <v>3.5610007774013616E-2</v>
       </c>
@@ -7016,12 +7020,12 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12"/>
       <c r="B31" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C31" s="117">
+      <c r="C31" s="116">
         <f>MAX(AVERAGE(G31:J31),C30)</f>
         <v>3.5610007774013616E-2</v>
       </c>
@@ -7075,12 +7079,12 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="117">
+      <c r="C32" s="116">
         <f>MIN(AVERAGE(G32:J32)/2,0)</f>
         <v>0</v>
       </c>
@@ -7134,12 +7138,12 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12"/>
       <c r="B33" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="117">
+      <c r="C33" s="116">
         <f>IF(BS!G33&lt;=0,0,BS!G33/BS!G34)</f>
         <v>0</v>
       </c>
@@ -7191,18 +7195,18 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12"/>
       <c r="B34" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="C34" s="102">
+      <c r="C34" s="101">
         <f>ABS(C19/C$4)</f>
         <v>8.8901307323460216E-2</v>
       </c>
-      <c r="D34" s="99"/>
+      <c r="D34" s="98"/>
       <c r="E34" s="86"/>
-      <c r="F34" s="99"/>
+      <c r="F34" s="98"/>
       <c r="G34" s="79">
         <f t="shared" ref="G34:Q34" si="22">IF(G$4="","",ABS(G19/G$4))</f>
         <v>0.10141888646207005</v>
@@ -7248,7 +7252,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12"/>
       <c r="B35" s="93" t="s">
         <v>154</v>
@@ -7269,7 +7273,7 @@
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12"/>
       <c r="B36" s="30" t="s">
         <v>320</v>
@@ -7327,7 +7331,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12"/>
       <c r="B37" s="30"/>
       <c r="C37" s="74"/>
@@ -7346,9 +7350,9 @@
       <c r="P37" s="14"/>
       <c r="Q37" s="14"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12"/>
-      <c r="B38" s="206" t="s">
+      <c r="B38" s="205" t="s">
         <v>269</v>
       </c>
       <c r="C38" s="74"/>
@@ -7367,12 +7371,12 @@
       <c r="P38" s="14"/>
       <c r="Q38" s="14"/>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="C39" s="101">
+      <c r="C39" s="100">
         <f>C4/G4-1</f>
         <v>-0.15086115529539579</v>
       </c>
@@ -7424,7 +7428,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12"/>
       <c r="B40" s="30"/>
       <c r="C40" s="74"/>
@@ -7443,12 +7447,12 @@
       <c r="P40" s="14"/>
       <c r="Q40" s="14"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12"/>
-      <c r="B41" s="239" t="s">
+      <c r="B41" s="238" t="s">
         <v>319</v>
       </c>
-      <c r="C41" s="240"/>
+      <c r="C41" s="239"/>
       <c r="D41" s="30"/>
       <c r="E41" s="86"/>
       <c r="F41" s="30"/>
@@ -7464,122 +7468,122 @@
       <c r="P41" s="14"/>
       <c r="Q41" s="14"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12"/>
       <c r="B42" s="30" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C42" s="238">
+      <c r="C42" s="237">
         <f>C19*$C$3/Common_Shares*Exchange_Rate</f>
         <v>1.9705919903877795</v>
       </c>
       <c r="D42" s="30"/>
       <c r="E42" s="86"/>
       <c r="F42" s="30"/>
-      <c r="G42" s="238">
+      <c r="G42" s="237">
         <f t="shared" ref="G42:Q42" si="25">IF(G$4="","",G19*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>2.6474556591263427</v>
       </c>
-      <c r="H42" s="238">
+      <c r="H42" s="237">
         <f t="shared" si="25"/>
         <v>2.638699175969117</v>
       </c>
-      <c r="I42" s="238">
+      <c r="I42" s="237">
         <f t="shared" si="25"/>
         <v>2.337820896109633</v>
       </c>
-      <c r="J42" s="238">
+      <c r="J42" s="237">
         <f t="shared" si="25"/>
         <v>2.3802900949118633</v>
       </c>
-      <c r="K42" s="238">
+      <c r="K42" s="237">
         <f t="shared" si="25"/>
         <v>1.4732863817099362</v>
       </c>
-      <c r="L42" s="238">
+      <c r="L42" s="237">
         <f t="shared" si="25"/>
         <v>-1.8579209935619154E-2</v>
       </c>
-      <c r="M42" s="238" t="str">
+      <c r="M42" s="237" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="N42" s="238" t="str">
+      <c r="N42" s="237" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O42" s="238" t="str">
+      <c r="O42" s="237" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="P42" s="238" t="str">
+      <c r="P42" s="237" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="Q42" s="238" t="str">
+      <c r="Q42" s="237" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12"/>
       <c r="B43" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="C43" s="101">
+      <c r="C43" s="100">
         <f>C42/Market_Price</f>
         <v>0.12567550959105736</v>
       </c>
       <c r="D43" s="30"/>
       <c r="E43" s="86"/>
       <c r="F43" s="30"/>
-      <c r="G43" s="101">
+      <c r="G43" s="100">
         <f t="shared" ref="G43:Q43" si="26">IF(G$4="","",G42/Market_Price)</f>
         <v>0.16884283540346573</v>
       </c>
-      <c r="H43" s="101">
+      <c r="H43" s="100">
         <f t="shared" si="26"/>
         <v>0.1682843862225202</v>
       </c>
-      <c r="I43" s="101">
+      <c r="I43" s="100">
         <f t="shared" si="26"/>
         <v>0.14909572041515518</v>
       </c>
-      <c r="J43" s="101">
+      <c r="J43" s="100">
         <f t="shared" si="26"/>
         <v>0.15180421523672596</v>
       </c>
-      <c r="K43" s="101">
+      <c r="K43" s="100">
         <f t="shared" si="26"/>
         <v>9.3959590670276538E-2</v>
       </c>
-      <c r="L43" s="101">
+      <c r="L43" s="100">
         <f t="shared" si="26"/>
         <v>-1.1848985928328542E-3</v>
       </c>
-      <c r="M43" s="101" t="str">
+      <c r="M43" s="100" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="N43" s="101" t="str">
+      <c r="N43" s="100" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="O43" s="101" t="str">
+      <c r="O43" s="100" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="P43" s="101" t="str">
+      <c r="P43" s="100" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="Q43" s="101" t="str">
+      <c r="Q43" s="100" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="12"/>
       <c r="B44" s="30"/>
       <c r="C44" s="74"/>
@@ -7598,7 +7602,7 @@
       <c r="P44" s="14"/>
       <c r="Q44" s="14"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="12"/>
       <c r="B45" s="61" t="s">
         <v>138</v>
@@ -7621,7 +7625,7 @@
       <c r="P45" s="40"/>
       <c r="Q45" s="40"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12"/>
       <c r="B46" s="78" t="s">
         <v>131</v>
@@ -7642,240 +7646,240 @@
       <c r="P46" s="14"/>
       <c r="Q46" s="14"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12"/>
       <c r="B47" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="98">
+      <c r="C47" s="240">
         <f>-C4*C55</f>
         <v>-9486667.5980516188</v>
       </c>
       <c r="D47" s="66"/>
       <c r="E47" s="85"/>
       <c r="F47" s="66"/>
-      <c r="G47" s="65">
+      <c r="G47" s="244">
         <f>Data!C36</f>
         <v>-11151623</v>
       </c>
-      <c r="H47" s="65">
+      <c r="H47" s="244">
         <f>Data!D36</f>
         <v>-8747447</v>
       </c>
-      <c r="I47" s="65">
+      <c r="I47" s="244">
         <f>Data!E36</f>
         <v>-8503976</v>
       </c>
-      <c r="J47" s="65">
+      <c r="J47" s="244">
         <f>Data!F36</f>
         <v>-6229020</v>
       </c>
-      <c r="K47" s="65">
+      <c r="K47" s="244">
         <f>Data!G36</f>
         <v>-7910751</v>
       </c>
-      <c r="L47" s="65">
+      <c r="L47" s="244">
         <f>Data!H36</f>
         <v>-11826154</v>
       </c>
-      <c r="M47" s="65" t="str">
+      <c r="M47" s="244" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N47" s="65" t="str">
+      <c r="N47" s="244" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O47" s="65" t="str">
+      <c r="O47" s="244" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P47" s="65" t="str">
+      <c r="P47" s="244" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q47" s="65" t="str">
+      <c r="Q47" s="244" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="12"/>
       <c r="B48" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="C48" s="77">
+      <c r="C48" s="241">
         <f>-C4*C56</f>
         <v>-1692234.0664023331</v>
       </c>
       <c r="D48" s="30"/>
       <c r="E48" s="86"/>
       <c r="F48" s="30"/>
-      <c r="G48" s="65">
+      <c r="G48" s="244">
         <f>Data!C39</f>
         <v>-2043459</v>
       </c>
-      <c r="H48" s="65">
+      <c r="H48" s="244">
         <f>Data!D39</f>
         <v>-1517989</v>
       </c>
-      <c r="I48" s="65">
+      <c r="I48" s="244">
         <f>Data!E39</f>
         <v>-1491293</v>
       </c>
-      <c r="J48" s="65">
+      <c r="J48" s="244">
         <f>Data!F39</f>
         <v>-1412494</v>
       </c>
-      <c r="K48" s="65">
+      <c r="K48" s="244">
         <f>Data!G39</f>
         <v>0</v>
       </c>
-      <c r="L48" s="65">
+      <c r="L48" s="244">
         <f>Data!H39</f>
         <v>0</v>
       </c>
-      <c r="M48" s="65" t="str">
+      <c r="M48" s="244" t="str">
         <f>Data!I39</f>
         <v/>
       </c>
-      <c r="N48" s="65" t="str">
+      <c r="N48" s="244" t="str">
         <f>Data!J39</f>
         <v/>
       </c>
-      <c r="O48" s="65" t="str">
+      <c r="O48" s="244" t="str">
         <f>Data!K39</f>
         <v/>
       </c>
-      <c r="P48" s="65" t="str">
+      <c r="P48" s="244" t="str">
         <f>Data!L39</f>
         <v/>
       </c>
-      <c r="Q48" s="65" t="str">
+      <c r="Q48" s="244" t="str">
         <f>Data!M39</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12"/>
       <c r="B49" s="91" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="80">
+      <c r="C49" s="242">
         <f>C47+C48</f>
         <v>-11178901.664453952</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="82"/>
       <c r="F49" s="11"/>
-      <c r="G49" s="80">
+      <c r="G49" s="242">
         <f>IF(G$4="","",G47+G48)</f>
         <v>-13195082</v>
       </c>
-      <c r="H49" s="80">
+      <c r="H49" s="242">
         <f t="shared" ref="H49:Q49" si="27">IF(H$4="","",H47+H48)</f>
         <v>-10265436</v>
       </c>
-      <c r="I49" s="80">
+      <c r="I49" s="242">
         <f t="shared" si="27"/>
         <v>-9995269</v>
       </c>
-      <c r="J49" s="80">
+      <c r="J49" s="242">
         <f t="shared" si="27"/>
         <v>-7641514</v>
       </c>
-      <c r="K49" s="80">
+      <c r="K49" s="242">
         <f t="shared" si="27"/>
         <v>-7910751</v>
       </c>
-      <c r="L49" s="80">
+      <c r="L49" s="242">
         <f t="shared" si="27"/>
         <v>-11826154</v>
       </c>
-      <c r="M49" s="80" t="str">
+      <c r="M49" s="242" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="N49" s="80" t="str">
+      <c r="N49" s="242" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="O49" s="80" t="str">
+      <c r="O49" s="242" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="P49" s="80" t="str">
+      <c r="P49" s="242" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="Q49" s="80" t="str">
+      <c r="Q49" s="242" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="97">
+      <c r="C50" s="243">
         <f>AVERAGE(G50:H50)</f>
         <v>-301816.5</v>
       </c>
       <c r="E50" s="83" t="s">
         <v>165</v>
       </c>
-      <c r="G50" s="77">
+      <c r="G50" s="241">
         <f>Data!C40</f>
         <v>-254107</v>
       </c>
-      <c r="H50" s="77">
+      <c r="H50" s="241">
         <f>Data!D40</f>
         <v>-349526</v>
       </c>
-      <c r="I50" s="77">
+      <c r="I50" s="241">
         <f>Data!E40</f>
         <v>-323818</v>
       </c>
-      <c r="J50" s="77">
+      <c r="J50" s="241">
         <f>Data!F40</f>
         <v>-281986</v>
       </c>
-      <c r="K50" s="77">
+      <c r="K50" s="241">
         <f>Data!G40</f>
         <v>-2118252</v>
       </c>
-      <c r="L50" s="77">
+      <c r="L50" s="241">
         <f>Data!H40</f>
         <v>-2416769</v>
       </c>
-      <c r="M50" s="77" t="str">
+      <c r="M50" s="241" t="str">
         <f>Data!I40</f>
         <v/>
       </c>
-      <c r="N50" s="77" t="str">
+      <c r="N50" s="241" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O50" s="77" t="str">
+      <c r="O50" s="241" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P50" s="77" t="str">
+      <c r="P50" s="241" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q50" s="77" t="str">
+      <c r="Q50" s="241" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12"/>
       <c r="B51" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="97">
+      <c r="C51" s="243">
         <f>AVERAGE(G51:J51)</f>
         <v>0</v>
       </c>
@@ -7884,118 +7888,118 @@
         <v>165</v>
       </c>
       <c r="F51" s="66"/>
-      <c r="G51" s="65">
+      <c r="G51" s="244">
         <f>Data!C41</f>
         <v>0</v>
       </c>
-      <c r="H51" s="65">
+      <c r="H51" s="244">
         <f>Data!D41</f>
         <v>0</v>
       </c>
-      <c r="I51" s="65">
+      <c r="I51" s="244">
         <f>Data!E41</f>
         <v>0</v>
       </c>
-      <c r="J51" s="65">
+      <c r="J51" s="244">
         <f>Data!F41</f>
         <v>0</v>
       </c>
-      <c r="K51" s="65">
+      <c r="K51" s="244">
         <f>Data!G41</f>
         <v>0</v>
       </c>
-      <c r="L51" s="65">
+      <c r="L51" s="244">
         <f>Data!H41</f>
         <v>0</v>
       </c>
-      <c r="M51" s="65" t="str">
+      <c r="M51" s="244" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N51" s="65" t="str">
+      <c r="N51" s="244" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O51" s="65" t="str">
+      <c r="O51" s="244" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P51" s="65" t="str">
+      <c r="P51" s="244" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q51" s="65" t="str">
+      <c r="Q51" s="244" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12"/>
       <c r="B52" s="91" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="80">
+      <c r="C52" s="242">
         <f>C50+C51</f>
         <v>-301816.5</v>
       </c>
       <c r="D52" s="66"/>
       <c r="E52" s="85"/>
       <c r="F52" s="66"/>
-      <c r="G52" s="80">
+      <c r="G52" s="242">
         <f t="shared" ref="G52:Q52" si="28">IF(G4="","",G50+G51)</f>
         <v>-254107</v>
       </c>
-      <c r="H52" s="80">
+      <c r="H52" s="242">
         <f t="shared" si="28"/>
         <v>-349526</v>
       </c>
-      <c r="I52" s="80">
+      <c r="I52" s="242">
         <f t="shared" si="28"/>
         <v>-323818</v>
       </c>
-      <c r="J52" s="80">
+      <c r="J52" s="242">
         <f t="shared" si="28"/>
         <v>-281986</v>
       </c>
-      <c r="K52" s="80">
+      <c r="K52" s="242">
         <f t="shared" si="28"/>
         <v>-2118252</v>
       </c>
-      <c r="L52" s="80">
+      <c r="L52" s="242">
         <f t="shared" si="28"/>
         <v>-2416769</v>
       </c>
-      <c r="M52" s="80" t="str">
+      <c r="M52" s="242" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="N52" s="80" t="str">
+      <c r="N52" s="242" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="O52" s="80" t="str">
+      <c r="O52" s="242" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="P52" s="80" t="str">
+      <c r="P52" s="242" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="Q52" s="80" t="str">
+      <c r="Q52" s="242" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="12"/>
       <c r="B54" s="93" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="12"/>
       <c r="B55" s="29" t="s">
         <v>66</v>
@@ -8054,7 +8058,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="12"/>
       <c r="B56" s="87" t="str">
         <f>B48</f>
@@ -8114,7 +8118,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="91" t="s">
         <v>69</v>
@@ -8168,7 +8172,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12"/>
       <c r="B58" s="2" t="str">
         <f>B50</f>
@@ -8226,7 +8230,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12"/>
       <c r="B59" s="30" t="str">
         <f>B51</f>
@@ -8284,7 +8288,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="12"/>
       <c r="B60" s="91" t="s">
         <v>68</v>
@@ -8338,16 +8342,16 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="12"/>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="12"/>
       <c r="B62" s="78" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
       <c r="B63" s="44" t="s">
         <v>314</v>
@@ -8401,7 +8405,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="12"/>
       <c r="B64" s="44" t="s">
         <v>303</v>
@@ -8455,7 +8459,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12"/>
       <c r="B65" s="44" t="s">
         <v>300</v>
@@ -8509,7 +8513,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12"/>
       <c r="B66" s="44" t="s">
         <v>304</v>
@@ -8565,7 +8569,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12"/>
       <c r="B67" s="34" t="s">
         <v>295</v>
@@ -8619,21 +8623,21 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="12"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
-      <c r="B69" s="133" t="s">
+      <c r="B69" s="132" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="12"/>
       <c r="B70" s="44" t="s">
         <v>314</v>
       </c>
-      <c r="C70" s="236">
+      <c r="C70" s="235">
         <f>G70</f>
         <v>0</v>
       </c>
@@ -8641,23 +8645,23 @@
         <f>IFERROR(G63/BS!$G$25,0)</f>
         <v>0</v>
       </c>
-      <c r="H70" s="235"/>
-      <c r="I70" s="235"/>
-      <c r="J70" s="235"/>
-      <c r="K70" s="235"/>
-      <c r="L70" s="235"/>
-      <c r="M70" s="235"/>
-      <c r="N70" s="235"/>
-      <c r="O70" s="235"/>
-      <c r="P70" s="235"/>
-      <c r="Q70" s="235"/>
-    </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H70" s="234"/>
+      <c r="I70" s="234"/>
+      <c r="J70" s="234"/>
+      <c r="K70" s="234"/>
+      <c r="L70" s="234"/>
+      <c r="M70" s="234"/>
+      <c r="N70" s="234"/>
+      <c r="O70" s="234"/>
+      <c r="P70" s="234"/>
+      <c r="Q70" s="234"/>
+    </row>
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="12"/>
-      <c r="B71" s="144" t="s">
+      <c r="B71" s="143" t="s">
         <v>299</v>
       </c>
-      <c r="C71" s="236">
+      <c r="C71" s="235">
         <f>G71</f>
         <v>0</v>
       </c>
@@ -8665,23 +8669,23 @@
         <f>IFERROR(G64/BS!$G$26,0)</f>
         <v>0</v>
       </c>
-      <c r="H71" s="235"/>
-      <c r="I71" s="235"/>
-      <c r="J71" s="235"/>
-      <c r="K71" s="235"/>
-      <c r="L71" s="235"/>
-      <c r="M71" s="235"/>
-      <c r="N71" s="235"/>
-      <c r="O71" s="235"/>
-      <c r="P71" s="235"/>
-      <c r="Q71" s="235"/>
-    </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H71" s="234"/>
+      <c r="I71" s="234"/>
+      <c r="J71" s="234"/>
+      <c r="K71" s="234"/>
+      <c r="L71" s="234"/>
+      <c r="M71" s="234"/>
+      <c r="N71" s="234"/>
+      <c r="O71" s="234"/>
+      <c r="P71" s="234"/>
+      <c r="Q71" s="234"/>
+    </row>
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="12"/>
-      <c r="B72" s="144" t="s">
+      <c r="B72" s="143" t="s">
         <v>300</v>
       </c>
-      <c r="C72" s="236">
+      <c r="C72" s="235">
         <f>G72</f>
         <v>0</v>
       </c>
@@ -8689,18 +8693,18 @@
         <f>IFERROR(G65/BS!$G$27,0)</f>
         <v>0</v>
       </c>
-      <c r="H72" s="235"/>
-      <c r="I72" s="235"/>
-      <c r="J72" s="235"/>
-      <c r="K72" s="235"/>
-      <c r="L72" s="235"/>
-      <c r="M72" s="235"/>
-      <c r="N72" s="235"/>
-      <c r="O72" s="235"/>
-      <c r="P72" s="235"/>
-      <c r="Q72" s="235"/>
-    </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H72" s="234"/>
+      <c r="I72" s="234"/>
+      <c r="J72" s="234"/>
+      <c r="K72" s="234"/>
+      <c r="L72" s="234"/>
+      <c r="M72" s="234"/>
+      <c r="N72" s="234"/>
+      <c r="O72" s="234"/>
+      <c r="P72" s="234"/>
+      <c r="Q72" s="234"/>
+    </row>
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12"/>
       <c r="B73" s="34" t="s">
         <v>295</v>
@@ -8716,27 +8720,27 @@
         <f>G67/SUM(BS!G25:G27)</f>
         <v>0.26824027844092097</v>
       </c>
-      <c r="H73" s="235"/>
-      <c r="I73" s="235"/>
-      <c r="J73" s="235"/>
-      <c r="K73" s="235"/>
-      <c r="L73" s="235"/>
-      <c r="M73" s="235"/>
-      <c r="N73" s="235"/>
-      <c r="O73" s="235"/>
-      <c r="P73" s="235"/>
-      <c r="Q73" s="235"/>
-    </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H73" s="234"/>
+      <c r="I73" s="234"/>
+      <c r="J73" s="234"/>
+      <c r="K73" s="234"/>
+      <c r="L73" s="234"/>
+      <c r="M73" s="234"/>
+      <c r="N73" s="234"/>
+      <c r="O73" s="234"/>
+      <c r="P73" s="234"/>
+      <c r="Q73" s="234"/>
+    </row>
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12"/>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="78" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12"/>
       <c r="B76" s="2" t="s">
         <v>58</v>
@@ -8790,7 +8794,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12"/>
       <c r="B77" s="2" t="s">
         <v>139</v>
@@ -8844,7 +8848,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12"/>
       <c r="B78" s="91" t="s">
         <v>140</v>
@@ -8898,21 +8902,21 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12"/>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12"/>
       <c r="B80" s="93" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12"/>
       <c r="B81" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C81" s="109">
+      <c r="C81" s="108">
         <f>Normalized_FCF!G81</f>
         <v>2.9286626219579916E-2</v>
       </c>
@@ -8923,23 +8927,23 @@
         <f>IFERROR(ABS(Normalized_FCF!G76/BS!$G$31),0)</f>
         <v>2.9286626219579916E-2</v>
       </c>
-      <c r="H81" s="225"/>
-      <c r="I81" s="225"/>
-      <c r="J81" s="225"/>
-      <c r="K81" s="225"/>
-      <c r="L81" s="225"/>
-      <c r="M81" s="225"/>
-      <c r="N81" s="225"/>
-      <c r="O81" s="225"/>
-      <c r="P81" s="225"/>
-      <c r="Q81" s="225"/>
-    </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H81" s="224"/>
+      <c r="I81" s="224"/>
+      <c r="J81" s="224"/>
+      <c r="K81" s="224"/>
+      <c r="L81" s="224"/>
+      <c r="M81" s="224"/>
+      <c r="N81" s="224"/>
+      <c r="O81" s="224"/>
+      <c r="P81" s="224"/>
+      <c r="Q81" s="224"/>
+    </row>
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="12"/>
       <c r="B82" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C82" s="116">
+      <c r="C82" s="115">
         <f>G82</f>
         <v>1.4501413508729523E-2</v>
       </c>
@@ -8950,21 +8954,21 @@
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G77/BS!$G$24)</f>
         <v>1.4501413508729523E-2</v>
       </c>
-      <c r="H82" s="225"/>
-      <c r="I82" s="225"/>
-      <c r="J82" s="225"/>
-      <c r="K82" s="225"/>
-      <c r="L82" s="225"/>
-      <c r="M82" s="225"/>
-      <c r="N82" s="225"/>
-      <c r="O82" s="225"/>
-      <c r="P82" s="225"/>
-      <c r="Q82" s="225"/>
-    </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H82" s="224"/>
+      <c r="I82" s="224"/>
+      <c r="J82" s="224"/>
+      <c r="K82" s="224"/>
+      <c r="L82" s="224"/>
+      <c r="M82" s="224"/>
+      <c r="N82" s="224"/>
+      <c r="O82" s="224"/>
+      <c r="P82" s="224"/>
+      <c r="Q82" s="224"/>
+    </row>
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A84" s="3"/>
       <c r="B84" s="61" t="s">
         <v>187</v>
@@ -8987,18 +8991,18 @@
       <c r="P84" s="40"/>
       <c r="Q84" s="40"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12"/>
       <c r="B85" s="78" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="12"/>
       <c r="B86" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="C86" s="128">
+      <c r="C86" s="127">
         <f>BS!G23</f>
         <v>16854064</v>
       </c>
@@ -9050,126 +9054,126 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12"/>
-      <c r="B87" s="126" t="s">
+      <c r="B87" s="125" t="s">
         <v>171</v>
       </c>
-      <c r="C87" s="129">
+      <c r="C87" s="128">
         <f>BS!C4</f>
         <v>265773</v>
       </c>
-      <c r="D87" s="118"/>
-      <c r="E87" s="118"/>
-      <c r="F87" s="118"/>
-      <c r="G87" s="130">
+      <c r="D87" s="117"/>
+      <c r="E87" s="117"/>
+      <c r="F87" s="117"/>
+      <c r="G87" s="129">
         <f>IF(G$4="","",Data!D75)</f>
         <v>213823</v>
       </c>
-      <c r="H87" s="130">
+      <c r="H87" s="129">
         <f>IF(H$4="","",Data!E75)</f>
         <v>187711</v>
       </c>
-      <c r="I87" s="130">
+      <c r="I87" s="129">
         <f>IF(I$4="","",Data!F75)</f>
         <v>277338</v>
       </c>
-      <c r="J87" s="130">
+      <c r="J87" s="129">
         <f>IF(J$4="","",Data!G75)</f>
         <v>0</v>
       </c>
-      <c r="K87" s="130">
+      <c r="K87" s="129">
         <f>IF(K$4="","",Data!H75)</f>
         <v>0</v>
       </c>
-      <c r="L87" s="130">
+      <c r="L87" s="129">
         <f>IF(L$4="","",Data!I75)</f>
         <v>0</v>
       </c>
-      <c r="M87" s="130" t="str">
+      <c r="M87" s="129" t="str">
         <f>IF(M$4="","",Data!J75)</f>
         <v/>
       </c>
-      <c r="N87" s="130" t="str">
+      <c r="N87" s="129" t="str">
         <f>IF(N$4="","",Data!K75)</f>
         <v/>
       </c>
-      <c r="O87" s="130" t="str">
+      <c r="O87" s="129" t="str">
         <f>IF(O$4="","",Data!L75)</f>
         <v/>
       </c>
-      <c r="P87" s="130" t="str">
+      <c r="P87" s="129" t="str">
         <f>IF(P$4="","",Data!M75)</f>
         <v/>
       </c>
-      <c r="Q87" s="130" t="str">
+      <c r="Q87" s="129" t="str">
         <f>IF(Q$4="","",Data!N75)</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12"/>
-      <c r="B88" s="126" t="s">
+      <c r="B88" s="125" t="s">
         <v>172</v>
       </c>
-      <c r="C88" s="129">
+      <c r="C88" s="128">
         <f>BS!C7+BS!C8</f>
         <v>9672256</v>
       </c>
-      <c r="D88" s="118"/>
-      <c r="E88" s="118"/>
-      <c r="F88" s="118"/>
-      <c r="G88" s="130">
+      <c r="D88" s="117"/>
+      <c r="E88" s="117"/>
+      <c r="F88" s="117"/>
+      <c r="G88" s="129">
         <f>IF(G$4="","",Data!D76)</f>
         <v>8852611</v>
       </c>
-      <c r="H88" s="130">
+      <c r="H88" s="129">
         <f>IF(H$4="","",Data!E76)</f>
         <v>8769304</v>
       </c>
-      <c r="I88" s="130">
+      <c r="I88" s="129">
         <f>IF(I$4="","",Data!F76)</f>
         <v>7321614</v>
       </c>
-      <c r="J88" s="130">
+      <c r="J88" s="129">
         <f>IF(J$4="","",Data!G76)</f>
         <v>0</v>
       </c>
-      <c r="K88" s="130">
+      <c r="K88" s="129">
         <f>IF(K$4="","",Data!H76)</f>
         <v>0</v>
       </c>
-      <c r="L88" s="130">
+      <c r="L88" s="129">
         <f>IF(L$4="","",Data!I76)</f>
         <v>0</v>
       </c>
-      <c r="M88" s="130" t="str">
+      <c r="M88" s="129" t="str">
         <f>IF(M$4="","",Data!J76)</f>
         <v/>
       </c>
-      <c r="N88" s="130" t="str">
+      <c r="N88" s="129" t="str">
         <f>IF(N$4="","",Data!K76)</f>
         <v/>
       </c>
-      <c r="O88" s="130" t="str">
+      <c r="O88" s="129" t="str">
         <f>IF(O$4="","",Data!L76)</f>
         <v/>
       </c>
-      <c r="P88" s="130" t="str">
+      <c r="P88" s="129" t="str">
         <f>IF(P$4="","",Data!M76)</f>
         <v/>
       </c>
-      <c r="Q88" s="130" t="str">
+      <c r="Q88" s="129" t="str">
         <f>IF(Q$4="","",Data!N76)</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
       <c r="B89" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C89" s="128">
+      <c r="C89" s="127">
         <f>BS!G30</f>
         <v>3990166</v>
       </c>
@@ -9221,12 +9225,12 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12"/>
       <c r="B90" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C90" s="128">
+      <c r="C90" s="127">
         <f>BS!G32</f>
         <v>12863898</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12"/>
       <c r="B91" s="29"/>
       <c r="C91" s="29"/>
@@ -9297,9 +9301,9 @@
       <c r="P91" s="14"/>
       <c r="Q91" s="14"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="12"/>
-      <c r="B92" s="121" t="s">
+      <c r="B92" s="120" t="s">
         <v>65</v>
       </c>
       <c r="C92" s="29"/>
@@ -9318,121 +9322,121 @@
       <c r="P92" s="14"/>
       <c r="Q92" s="14"/>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="12"/>
       <c r="B93" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="C93" s="131">
+      <c r="C93" s="130">
         <f>C87/C$4</f>
         <v>2.0422288435909493E-2</v>
       </c>
       <c r="D93" s="29"/>
       <c r="E93" s="29"/>
       <c r="F93" s="29"/>
-      <c r="G93" s="131">
+      <c r="G93" s="130">
         <f>IF(G$4="","",G87/G$4)</f>
         <v>1.3951685381968192E-2</v>
       </c>
-      <c r="H93" s="131">
+      <c r="H93" s="130">
         <f t="shared" ref="H93:Q93" si="40">IF(H$4="","",H87/H$4)</f>
         <v>1.5671518179732512E-2</v>
       </c>
-      <c r="I93" s="131">
+      <c r="I93" s="130">
         <f t="shared" si="40"/>
         <v>2.3627760663558588E-2</v>
       </c>
-      <c r="J93" s="131">
+      <c r="J93" s="130">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K93" s="131">
+      <c r="K93" s="130">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="L93" s="131">
+      <c r="L93" s="130">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="M93" s="131" t="str">
+      <c r="M93" s="130" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="N93" s="131" t="str">
+      <c r="N93" s="130" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="O93" s="131" t="str">
+      <c r="O93" s="130" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="P93" s="131" t="str">
+      <c r="P93" s="130" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="Q93" s="131" t="str">
+      <c r="Q93" s="130" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="12"/>
       <c r="B94" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="C94" s="131">
+      <c r="C94" s="130">
         <f>C88/C$4</f>
         <v>0.74322674559852286</v>
       </c>
       <c r="D94" s="29"/>
       <c r="E94" s="29"/>
       <c r="F94" s="29"/>
-      <c r="G94" s="131">
+      <c r="G94" s="130">
         <f>IF(G$4="","",G88/G$4)</f>
         <v>0.57762188109301071</v>
       </c>
-      <c r="H94" s="131">
+      <c r="H94" s="130">
         <f t="shared" ref="H94:Q94" si="41">IF(H$4="","",H88/H$4)</f>
         <v>0.73212708397270831</v>
       </c>
-      <c r="I94" s="131">
+      <c r="I94" s="130">
         <f t="shared" si="41"/>
         <v>0.62376357824373097</v>
       </c>
-      <c r="J94" s="131">
+      <c r="J94" s="130">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="K94" s="131">
+      <c r="K94" s="130">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="L94" s="131">
+      <c r="L94" s="130">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="M94" s="131" t="str">
+      <c r="M94" s="130" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="N94" s="131" t="str">
+      <c r="N94" s="130" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="O94" s="131" t="str">
+      <c r="O94" s="130" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="P94" s="131" t="str">
+      <c r="P94" s="130" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q94" s="131" t="str">
+      <c r="Q94" s="130" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="12"/>
       <c r="B95" s="29"/>
       <c r="C95" s="29"/>
@@ -9451,13 +9455,13 @@
       <c r="P95" s="14"/>
       <c r="Q95" s="14"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="12"/>
-      <c r="B96" s="121" t="s">
+      <c r="B96" s="120" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12"/>
       <c r="B97" s="29" t="s">
         <v>179</v>
@@ -9511,7 +9515,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="12"/>
       <c r="B98" s="29" t="s">
         <v>178</v>
@@ -9565,12 +9569,12 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="12"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="12"/>
-      <c r="B100" s="121" t="s">
+      <c r="B100" s="120" t="s">
         <v>56</v>
       </c>
       <c r="C100" s="62"/>
@@ -9622,7 +9626,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="12"/>
       <c r="B101" s="9" t="s">
         <v>181</v>
@@ -9676,7 +9680,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B102" s="9" t="s">
         <v>169</v>
       </c>
@@ -9729,7 +9733,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="9" t="s">
         <v>182</v>
       </c>
@@ -9785,67 +9789,67 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="12"/>
       <c r="B104" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="C104" s="140">
+      <c r="C104" s="139">
         <f>C10/C90</f>
         <v>0.11918249835413142</v>
       </c>
-      <c r="D104" s="141"/>
-      <c r="E104" s="141"/>
-      <c r="F104" s="141"/>
-      <c r="G104" s="140">
+      <c r="D104" s="140"/>
+      <c r="E104" s="140"/>
+      <c r="F104" s="140"/>
+      <c r="G104" s="139">
         <f t="shared" ref="G104:Q104" si="47">IF(G$4="","",G10/G90)</f>
         <v>0.1293394894766734</v>
       </c>
-      <c r="H104" s="140">
+      <c r="H104" s="139">
         <f t="shared" si="47"/>
         <v>0.13315880232473079</v>
       </c>
-      <c r="I104" s="140">
+      <c r="I104" s="139">
         <f t="shared" si="47"/>
         <v>0.11581750690150323</v>
       </c>
-      <c r="J104" s="140">
+      <c r="J104" s="139">
         <f t="shared" si="47"/>
         <v>0.1165453809461911</v>
       </c>
-      <c r="K104" s="140" t="e">
+      <c r="K104" s="139" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L104" s="140" t="e">
+      <c r="L104" s="139" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M104" s="140" t="str">
+      <c r="M104" s="139" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="N104" s="140" t="str">
+      <c r="N104" s="139" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O104" s="140" t="str">
+      <c r="O104" s="139" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P104" s="140" t="str">
+      <c r="P104" s="139" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q104" s="140" t="str">
+      <c r="Q104" s="139" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="12"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A106" s="12"/>
       <c r="B106" s="61" t="s">
         <v>200</v>
@@ -9868,67 +9872,67 @@
       <c r="P106" s="40"/>
       <c r="Q106" s="40"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="12"/>
       <c r="B107" s="78" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="12"/>
       <c r="B108" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C108" s="157">
+      <c r="C108" s="156">
         <f>G108</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="G108" s="156">
+      <c r="G108" s="155">
         <f>Data!C63</f>
         <v>1.3599999999999999</v>
       </c>
-      <c r="H108" s="156">
+      <c r="H108" s="155">
         <f>Data!D63</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="I108" s="156">
+      <c r="I108" s="155">
         <f>Data!E63</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="J108" s="156">
+      <c r="J108" s="155">
         <f>Data!F63</f>
         <v>1</v>
       </c>
-      <c r="K108" s="156">
+      <c r="K108" s="155">
         <f>Data!G63</f>
         <v>1</v>
       </c>
-      <c r="L108" s="156">
+      <c r="L108" s="155">
         <f>Data!H63</f>
         <v>1.1499999999999999</v>
       </c>
-      <c r="M108" s="156" t="str">
+      <c r="M108" s="155" t="str">
         <f>Data!I63</f>
         <v/>
       </c>
-      <c r="N108" s="156" t="str">
+      <c r="N108" s="155" t="str">
         <f>Data!J63</f>
         <v/>
       </c>
-      <c r="O108" s="156" t="str">
+      <c r="O108" s="155" t="str">
         <f>Data!K63</f>
         <v/>
       </c>
-      <c r="P108" s="156" t="str">
+      <c r="P108" s="155" t="str">
         <f>Data!L63</f>
         <v/>
       </c>
-      <c r="Q108" s="156" t="str">
+      <c r="Q108" s="155" t="str">
         <f>Data!M63</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="12"/>
       <c r="B109" s="2" t="s">
         <v>198</v>
@@ -9982,7 +9986,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="12"/>
       <c r="B110" s="2" t="s">
         <v>201</v>
@@ -9991,812 +9995,812 @@
         <f>C108/(C19*$C$3/Common_Shares)</f>
         <v>0.6901479386061925</v>
       </c>
-      <c r="G110" s="226">
+      <c r="G110" s="225">
         <f t="shared" ref="G110:Q110" si="49">IF(G$4="","",G108/(G19*$C$3/Common_Shares))</f>
         <v>0.51370076598329062</v>
       </c>
-      <c r="H110" s="226">
+      <c r="H110" s="225">
         <f t="shared" si="49"/>
         <v>0.41687207470173337</v>
       </c>
-      <c r="I110" s="226">
+      <c r="I110" s="225">
         <f t="shared" si="49"/>
         <v>0.47052364098144123</v>
       </c>
-      <c r="J110" s="226">
+      <c r="J110" s="225">
         <f t="shared" si="49"/>
         <v>0.42011685976327506</v>
       </c>
-      <c r="K110" s="226">
+      <c r="K110" s="225">
         <f t="shared" si="49"/>
         <v>0.67875466196828127</v>
       </c>
-      <c r="L110" s="226">
+      <c r="L110" s="225">
         <f t="shared" si="49"/>
         <v>-61.897142235056833</v>
       </c>
-      <c r="M110" s="226" t="str">
+      <c r="M110" s="225" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N110" s="226" t="str">
+      <c r="N110" s="225" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O110" s="226" t="str">
+      <c r="O110" s="225" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P110" s="226" t="str">
+      <c r="P110" s="225" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q110" s="226" t="str">
+      <c r="Q110" s="225" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="12"/>
     </row>
-    <row r="113" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="12"/>
     </row>
-    <row r="114" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="12"/>
     </row>
-    <row r="115" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="12"/>
     </row>
-    <row r="116" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12"/>
     </row>
-    <row r="117" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="12"/>
     </row>
-    <row r="118" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="12"/>
     </row>
-    <row r="119" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="12"/>
     </row>
-    <row r="120" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12"/>
     </row>
-    <row r="121" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="12"/>
     </row>
-    <row r="122" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="12"/>
     </row>
-    <row r="123" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="12"/>
     </row>
-    <row r="124" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="12"/>
     </row>
-    <row r="125" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12"/>
     </row>
-    <row r="126" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="12"/>
     </row>
-    <row r="127" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="12"/>
     </row>
-    <row r="128" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="12"/>
     </row>
-    <row r="129" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="12"/>
     </row>
-    <row r="130" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="12"/>
     </row>
-    <row r="131" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="12"/>
     </row>
-    <row r="132" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="12"/>
     </row>
-    <row r="133" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12"/>
     </row>
-    <row r="134" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12"/>
     </row>
-    <row r="135" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="12"/>
     </row>
-    <row r="136" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="12"/>
     </row>
-    <row r="137" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="138" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="140" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="141" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="142" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="143" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="144" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G47:Q48 G51:Q51">
@@ -10818,8 +10822,8 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="B1:H51"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -10830,21 +10834,21 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="136">
+      <c r="C1" s="135">
         <v>45382</v>
       </c>
-      <c r="F1" s="115" t="str">
+      <c r="F1" s="114" t="str">
         <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
         <v>FY Report</v>
       </c>
       <c r="H1" s="4"/>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="105" t="s">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="104" t="s">
         <v>298</v>
       </c>
       <c r="C2" s="40"/>
@@ -10854,33 +10858,33 @@
       <c r="G2" s="40"/>
       <c r="H2" s="40"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="146">
+      <c r="C3" s="145">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
-      <c r="D3" s="114" t="s">
+      <c r="D3" s="113" t="s">
         <v>45</v>
       </c>
       <c r="F3" s="18" t="s">
         <v>142</v>
       </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="114" t="s">
+      <c r="H3" s="113" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="22">
         <v>265773</v>
       </c>
-      <c r="D4" s="109">
+      <c r="D4" s="108">
         <v>0.6</v>
       </c>
       <c r="E4" s="28"/>
@@ -10890,18 +10894,18 @@
       <c r="G4" s="22">
         <v>1998219</v>
       </c>
-      <c r="H4" s="109">
+      <c r="H4" s="108">
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="22">
         <v>0</v>
       </c>
-      <c r="D5" s="109">
+      <c r="D5" s="108">
         <v>0.6</v>
       </c>
       <c r="E5" s="28"/>
@@ -10911,18 +10915,18 @@
       <c r="G5" s="22">
         <v>0</v>
       </c>
-      <c r="H5" s="109">
+      <c r="H5" s="108">
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="22">
         <v>366595</v>
       </c>
-      <c r="D6" s="109">
+      <c r="D6" s="108">
         <v>0.1</v>
       </c>
       <c r="E6" s="28"/>
@@ -10932,18 +10936,18 @@
       <c r="G6" s="22">
         <v>0</v>
       </c>
-      <c r="H6" s="109">
+      <c r="H6" s="108">
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="22">
         <v>9672256</v>
       </c>
-      <c r="D7" s="109">
+      <c r="D7" s="108">
         <v>0.5</v>
       </c>
       <c r="E7" s="28"/>
@@ -10953,18 +10957,18 @@
       <c r="G7" s="22">
         <v>0</v>
       </c>
-      <c r="H7" s="109">
+      <c r="H7" s="108">
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C8" s="22">
         <v>0</v>
       </c>
-      <c r="D8" s="109">
+      <c r="D8" s="108">
         <v>0.6</v>
       </c>
       <c r="E8" s="28"/>
@@ -10974,18 +10978,18 @@
       <c r="G8" s="22">
         <v>0</v>
       </c>
-      <c r="H8" s="109">
+      <c r="H8" s="108">
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="22">
         <v>29465</v>
       </c>
-      <c r="D9" s="109">
+      <c r="D9" s="108">
         <v>0.9</v>
       </c>
       <c r="E9" s="28"/>
@@ -10995,24 +10999,24 @@
       <c r="G9" s="22">
         <v>0</v>
       </c>
-      <c r="H9" s="109">
+      <c r="H9" s="108">
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="22">
         <v>0</v>
       </c>
-      <c r="D10" s="109">
+      <c r="D10" s="108">
         <v>0.05</v>
       </c>
-      <c r="F10" s="107" t="s">
+      <c r="F10" s="106" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="107">
         <f>SUM(G4:G9)</f>
         <v>1998219</v>
       </c>
@@ -11021,11 +11025,11 @@
         <v>1798397.1</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="107" t="s">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="106" t="s">
         <v>145</v>
       </c>
-      <c r="C11" s="108">
+      <c r="C11" s="107">
         <f>SUM(C4:C10)</f>
         <v>10334089</v>
       </c>
@@ -11039,18 +11043,18 @@
       <c r="G11" s="22">
         <v>0</v>
       </c>
-      <c r="H11" s="109">
+      <c r="H11" s="108">
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
         <v>146</v>
       </c>
       <c r="C12" s="22">
         <v>103050</v>
       </c>
-      <c r="D12" s="109">
+      <c r="D12" s="108">
         <v>0.4</v>
       </c>
       <c r="F12" s="5" t="s">
@@ -11059,18 +11063,18 @@
       <c r="G12" s="22">
         <v>0</v>
       </c>
-      <c r="H12" s="109">
+      <c r="H12" s="108">
         <v>0.6</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="22">
         <v>0</v>
       </c>
-      <c r="D13" s="109">
+      <c r="D13" s="108">
         <v>0.5</v>
       </c>
       <c r="F13" s="5" t="s">
@@ -11079,18 +11083,18 @@
       <c r="G13" s="22">
         <v>0</v>
       </c>
-      <c r="H13" s="109">
+      <c r="H13" s="108">
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>301</v>
       </c>
       <c r="C14" s="22">
         <v>0</v>
       </c>
-      <c r="D14" s="109">
+      <c r="D14" s="108">
         <v>0.6</v>
       </c>
       <c r="F14" s="5" t="s">
@@ -11099,18 +11103,18 @@
       <c r="G14" s="22">
         <v>0</v>
       </c>
-      <c r="H14" s="109">
+      <c r="H14" s="108">
         <v>0.1</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="22">
         <v>2522337</v>
       </c>
-      <c r="D15" s="109">
+      <c r="D15" s="108">
         <v>0.1</v>
       </c>
       <c r="F15" s="5" t="s">
@@ -11119,18 +11123,18 @@
       <c r="G15" s="22">
         <v>925726</v>
       </c>
-      <c r="H15" s="109">
+      <c r="H15" s="108">
         <v>0.2</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C16" s="22">
         <v>0</v>
       </c>
-      <c r="D16" s="109">
+      <c r="D16" s="108">
         <v>0.05</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -11139,24 +11143,24 @@
       <c r="G16" s="22">
         <v>0</v>
       </c>
-      <c r="H16" s="109">
+      <c r="H16" s="108">
         <v>0.1</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="22">
         <v>538321</v>
       </c>
-      <c r="D17" s="109">
+      <c r="D17" s="108">
         <v>0.05</v>
       </c>
-      <c r="F17" s="107" t="s">
+      <c r="F17" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="G17" s="108">
+      <c r="G17" s="107">
         <f>SUM(G11:G16)</f>
         <v>925726</v>
       </c>
@@ -11165,31 +11169,31 @@
         <v>185145.2</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="22">
         <v>154648</v>
       </c>
-      <c r="D18" s="109">
+      <c r="D18" s="108">
         <v>0.9</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C19" s="22">
         <v>277674</v>
       </c>
-      <c r="D19" s="109">
+      <c r="D19" s="108">
         <v>0</v>
       </c>
       <c r="F19" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="108">
+      <c r="G19" s="107">
         <f>C11+C20</f>
         <v>13930119</v>
       </c>
@@ -11198,11 +11202,11 @@
         <v>5518322.75</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="107" t="s">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="106" t="s">
         <v>148</v>
       </c>
-      <c r="C20" s="108">
+      <c r="C20" s="107">
         <f>SUM(C12:C19)</f>
         <v>3596030</v>
       </c>
@@ -11213,7 +11217,7 @@
       <c r="F20" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="G20" s="108">
+      <c r="G20" s="107">
         <f>G10+G17</f>
         <v>2923945</v>
       </c>
@@ -11222,18 +11226,18 @@
         <v>1983542.3</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="205" t="s">
+      <c r="G22" s="204" t="s">
         <v>261</v>
       </c>
-      <c r="H22" s="205" t="s">
+      <c r="H22" s="204" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="5" t="s">
         <v>6</v>
       </c>
@@ -11243,7 +11247,7 @@
       <c r="F23" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="108">
+      <c r="G23" s="107">
         <f>G19+G20</f>
         <v>16854064</v>
       </c>
@@ -11252,14 +11256,14 @@
         <v>7501865.0499999998</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="22">
         <v>287697</v>
       </c>
-      <c r="F24" s="106" t="s">
+      <c r="F24" s="105" t="s">
         <v>155</v>
       </c>
       <c r="G24" s="23">
@@ -11268,14 +11272,14 @@
       </c>
       <c r="H24" s="23"/>
     </row>
-    <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="22">
         <v>0</v>
       </c>
-      <c r="F25" s="106" t="s">
+      <c r="F25" s="105" t="s">
         <v>327</v>
       </c>
       <c r="G25" s="23">
@@ -11283,14 +11287,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="22">
         <v>0</v>
       </c>
-      <c r="F26" s="106" t="s">
+      <c r="F26" s="105" t="s">
         <v>292</v>
       </c>
       <c r="G26" s="23">
@@ -11298,15 +11302,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="107" t="s">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="108">
+      <c r="C27" s="107">
         <f>SUM(C23:C26)</f>
         <v>1715502</v>
       </c>
-      <c r="F27" s="106" t="s">
+      <c r="F27" s="105" t="s">
         <v>293</v>
       </c>
       <c r="G27" s="23">
@@ -11314,7 +11318,7 @@
         <v>925726</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
@@ -11322,7 +11326,7 @@
         <f>C29-C27</f>
         <v>1801307</v>
       </c>
-      <c r="F28" s="106" t="s">
+      <c r="F28" s="105" t="s">
         <v>328</v>
       </c>
       <c r="G28" s="23">
@@ -11334,14 +11338,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="110" t="s">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="109" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="112">
+      <c r="C29" s="111">
         <v>3516809</v>
       </c>
-      <c r="F29" s="106" t="s">
+      <c r="F29" s="105" t="s">
         <v>161</v>
       </c>
       <c r="G29" s="23">
@@ -11349,7 +11353,7 @@
         <v>3986384</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="5" t="s">
         <v>16</v>
       </c>
@@ -11359,19 +11363,19 @@
       <c r="F30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="113">
+      <c r="G30" s="112">
         <f>C29+C36</f>
         <v>3990166</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="22">
         <v>319420</v>
       </c>
-      <c r="F31" s="106" t="s">
+      <c r="F31" s="105" t="s">
         <v>152</v>
       </c>
       <c r="G31" s="23">
@@ -11379,7 +11383,7 @@
         <v>2034922</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="5" t="s">
         <v>18</v>
       </c>
@@ -11389,7 +11393,7 @@
       <c r="F32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G32" s="113">
+      <c r="G32" s="112">
         <f>G23-G30</f>
         <v>12863898</v>
       </c>
@@ -11398,29 +11402,29 @@
         <v>3511699.05</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C33" s="22">
         <v>0</v>
       </c>
-      <c r="F33" s="111" t="s">
+      <c r="F33" s="110" t="s">
         <v>150</v>
       </c>
       <c r="G33" s="14">
         <v>-26962</v>
       </c>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="107" t="s">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="108">
+      <c r="C34" s="107">
         <f>SUM(C30:C33)</f>
         <v>319420</v>
       </c>
-      <c r="F34" s="106" t="s">
+      <c r="F34" s="105" t="s">
         <v>151</v>
       </c>
       <c r="G34" s="16">
@@ -11432,7 +11436,7 @@
         <v>3538661.05</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="5" t="s">
         <v>20</v>
       </c>
@@ -11441,16 +11445,16 @@
         <v>153937</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="110" t="s">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="112">
+      <c r="C36" s="111">
         <v>473357</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="105" t="s">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="104" t="s">
         <v>187</v>
       </c>
       <c r="C38" s="40"/>
@@ -11460,51 +11464,51 @@
       <c r="G38" s="40"/>
       <c r="H38" s="40"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="C39" s="205" t="s">
+      <c r="C39" s="204" t="s">
         <v>261</v>
       </c>
-      <c r="D39" s="205" t="s">
+      <c r="D39" s="204" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
-      <c r="C40" s="192">
+      <c r="C40" s="191">
         <f>G34*C3/Common_Shares*Exchange_Rate</f>
         <v>21.956545121990789</v>
       </c>
-      <c r="D40" s="192">
+      <c r="D40" s="191">
         <f>H34*C3/Common_Shares*Exchange_Rate</f>
         <v>6.0272759936696465</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="133" t="s">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="132" t="s">
         <v>268</v>
       </c>
-      <c r="C42" s="134" t="s">
+      <c r="C42" s="133" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="134" t="s">
+      <c r="D42" s="133" t="s">
         <v>186</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="137" t="s">
+      <c r="F42" s="136" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C43" s="116">
+      <c r="C43" s="115">
         <f>D43</f>
         <v>0.11625172085779995</v>
       </c>
@@ -11516,59 +11520,79 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="135"/>
-      <c r="D44" s="123">
+      <c r="C44" s="134"/>
+      <c r="D44" s="122">
         <f>G29/G23</f>
         <v>0.23652360641326625</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C45" s="135"/>
-      <c r="D45" s="132">
+      <c r="C45" s="134"/>
+      <c r="D45" s="131">
         <f>BS!G31/Normalized_FCF!C10</f>
         <v>1.3272804397106923</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B47" s="133" t="s">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C46" s="134"/>
+      <c r="D46" s="191">
+        <f>G31*C3/Common_Shares</f>
+        <v>3.4660105464438944</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C47" s="134"/>
+      <c r="D47" s="122">
+        <f>G34/G23</f>
+        <v>0.76485172952944758</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="132" t="s">
         <v>267</v>
       </c>
-      <c r="C47" s="134" t="s">
+      <c r="C49" s="133" t="s">
         <v>125</v>
       </c>
-      <c r="D47" s="134" t="s">
+      <c r="D49" s="133" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="1" t="s">
+    <row r="50" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C50" s="122">
         <f>Normalized_FCF!C10/G19</f>
         <v>0.11006018701008329</v>
       </c>
-      <c r="D48" s="123">
+      <c r="D50" s="122">
         <f>Normalized_FCF!G10/G19</f>
         <v>0.11943975496548163</v>
       </c>
     </row>
-    <row r="49" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="1" t="s">
+    <row r="51" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C51" s="122">
         <f>Normalized_FCF!C11/G20</f>
         <v>0</v>
       </c>
-      <c r="D49" s="123">
+      <c r="D51" s="122">
         <f>Normalized_FCF!G11/G20</f>
         <v>8.4925332042839377E-2</v>
       </c>
@@ -11586,16 +11610,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H93"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
         <v>210</v>
       </c>
@@ -11603,28 +11627,28 @@
       <c r="D2" s="40"/>
       <c r="E2" s="40"/>
       <c r="F2" s="40"/>
-      <c r="H2" s="174" t="s">
+      <c r="H2" s="173" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B3" s="151" t="s">
+    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B3" s="150" t="s">
         <v>308</v>
       </c>
-      <c r="C3" s="146">
+      <c r="C3" s="145">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
-      <c r="E3" s="151" t="s">
+      <c r="E3" s="150" t="s">
         <v>239</v>
       </c>
-      <c r="H3" s="164"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B4" s="138" t="s">
+      <c r="H3" s="163"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B4" s="137" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="152">
+      <c r="C4" s="151">
         <f>Normalized_FCF!C19</f>
         <v>1156950.0267037901</v>
       </c>
@@ -11632,65 +11656,65 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E4" s="138" t="s">
+      <c r="E4" s="137" t="s">
         <v>244</v>
       </c>
-      <c r="F4" s="178">
-        <v>0</v>
-      </c>
-      <c r="H4" s="164"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B5" s="193" t="s">
+      <c r="F4" s="177">
+        <v>0</v>
+      </c>
+      <c r="H4" s="163"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="192" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="178">
+      <c r="C5" s="177">
         <f>Thesis!C37</f>
         <v>0.1</v>
       </c>
-      <c r="E5" s="193" t="s">
+      <c r="E5" s="192" t="s">
         <v>240</v>
       </c>
-      <c r="H5" s="164"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B6" s="195" t="s">
+      <c r="H5" s="163"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="194" t="s">
         <v>235</v>
       </c>
-      <c r="C6" s="179">
+      <c r="C6" s="178">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>11569500.2670379</v>
       </c>
-      <c r="E6" s="193" t="s">
+      <c r="E6" s="192" t="s">
         <v>245</v>
       </c>
-      <c r="H6" s="164"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B7" s="193" t="s">
+      <c r="H6" s="163"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B7" s="192" t="s">
         <v>237</v>
       </c>
-      <c r="C7" s="155">
+      <c r="C7" s="154">
         <f>BS!G31</f>
         <v>2034922</v>
       </c>
-      <c r="H7" s="164"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B8" s="193" t="s">
+      <c r="H7" s="163"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B8" s="192" t="s">
         <v>329</v>
       </c>
-      <c r="C8" s="155">
+      <c r="C8" s="154">
         <f>BS!H28</f>
         <v>0</v>
       </c>
-      <c r="H8" s="164"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B9" s="195" t="s">
+      <c r="H8" s="163"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B9" s="194" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="179">
+      <c r="C9" s="178">
         <f>C6-C7+C8</f>
         <v>9534578.2670379002</v>
       </c>
@@ -11698,23 +11722,23 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="H9" s="164"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B10" s="195" t="s">
+      <c r="H9" s="163"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B10" s="194" t="s">
         <v>313</v>
       </c>
-      <c r="C10" s="231">
+      <c r="C10" s="230">
         <f>Exchange_Rate</f>
         <v>1</v>
       </c>
-      <c r="H10" s="164"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B11" s="194" t="s">
+      <c r="H10" s="163"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B11" s="193" t="s">
         <v>209</v>
       </c>
-      <c r="C11" s="154">
+      <c r="C11" s="153">
         <f>(C9*C3)/Common_Shares*C10</f>
         <v>16.239909357433906</v>
       </c>
@@ -11722,12 +11746,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="H11" s="164"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="H12" s="164"/>
-    </row>
-    <row r="13" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+      <c r="H11" s="163"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H12" s="163"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B13" s="39" t="s">
         <v>189</v>
       </c>
@@ -11735,39 +11759,39 @@
       <c r="D13" s="40"/>
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
-      <c r="H13" s="164"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B14" s="163" t="s">
+      <c r="H13" s="163"/>
+    </row>
+    <row r="14" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B14" s="162" t="s">
         <v>255</v>
       </c>
-      <c r="H14" s="164"/>
-    </row>
-    <row r="15" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="198" t="s">
+      <c r="H14" s="163"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C15" s="210">
+      <c r="C15" s="209">
         <f>Scenarios!C25</f>
         <v>0.12</v>
       </c>
-      <c r="H15" s="164"/>
-    </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="162" t="s">
+      <c r="H15" s="163"/>
+    </row>
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="211">
+      <c r="C16" s="210">
         <f>Scenarios!C24</f>
         <v>15</v>
       </c>
-      <c r="H16" s="164"/>
-    </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="199" t="s">
+      <c r="H16" s="163"/>
+    </row>
+    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="198" t="s">
         <v>215</v>
       </c>
-      <c r="C17" s="185">
+      <c r="C17" s="184">
         <f>(F51-C7)/Common_Shares*C3</f>
         <v>36.063209392072409</v>
       </c>
@@ -11775,1267 +11799,1267 @@
         <f>IF(ROUND(C17,1)=ROUND(Scenarios!C29,1),"equals Market Price","a Current Projection")</f>
         <v>a Current Projection</v>
       </c>
-      <c r="H17" s="164"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="H18" s="164"/>
-    </row>
-    <row r="19" spans="2:8" ht="14" x14ac:dyDescent="0.2">
-      <c r="B19" s="172" t="s">
+      <c r="H17" s="163"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H18" s="163"/>
+    </row>
+    <row r="19" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B19" s="171" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="172" t="s">
+      <c r="C19" s="171" t="s">
         <v>217</v>
       </c>
-      <c r="D19" s="172" t="s">
+      <c r="D19" s="171" t="s">
         <v>229</v>
       </c>
-      <c r="E19" s="172" t="s">
+      <c r="E19" s="171" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="173" t="s">
+      <c r="F19" s="172" t="s">
         <v>219</v>
       </c>
-      <c r="H19" s="164"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B20" s="166">
+      <c r="H19" s="163"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="165">
         <v>1</v>
       </c>
-      <c r="C20" s="167">
+      <c r="C20" s="166">
         <f>C4*(1+D20)</f>
         <v>1295784.029908245</v>
       </c>
-      <c r="D20" s="183">
+      <c r="D20" s="182">
         <f>IF($C$16&lt;B20,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E20" s="168">
+      <c r="E20" s="167">
         <f t="shared" ref="E20:E49" si="0">IF($C$16&lt;B20,0,1/(1+Equity_Cost)^B20)</f>
         <v>0.90909090909090906</v>
       </c>
-      <c r="F20" s="169">
+      <c r="F20" s="168">
         <f t="shared" ref="F20:F50" si="1">C20*E20</f>
         <v>1177985.481734768</v>
       </c>
-      <c r="H20" s="164"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B21" s="166">
+      <c r="H20" s="163"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="165">
         <v>2</v>
       </c>
-      <c r="C21" s="167">
+      <c r="C21" s="166">
         <f t="shared" ref="C21:C49" si="2">IF(ROW()-ROW($C$20)&lt;$C$16, $C$20*(1+D21)^(ROW()-ROW($C$20)), 0)</f>
         <v>1451278.1134972344</v>
       </c>
-      <c r="D21" s="183">
+      <c r="D21" s="182">
         <f>IF($C$16&lt;B21,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E21" s="168">
+      <c r="E21" s="167">
         <f t="shared" si="0"/>
         <v>0.82644628099173545</v>
       </c>
-      <c r="F21" s="169">
+      <c r="F21" s="168">
         <f t="shared" si="1"/>
         <v>1199403.399584491</v>
       </c>
-      <c r="H21" s="164"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B22" s="166">
+      <c r="H21" s="163"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="165">
         <v>3</v>
       </c>
-      <c r="C22" s="167">
+      <c r="C22" s="166">
         <f t="shared" si="2"/>
         <v>1625431.4871169028</v>
       </c>
-      <c r="D22" s="183">
+      <c r="D22" s="182">
         <f>IF($C$16&lt;B22,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E22" s="168">
+      <c r="E22" s="167">
         <f t="shared" si="0"/>
         <v>0.75131480090157754</v>
       </c>
-      <c r="F22" s="169">
+      <c r="F22" s="168">
         <f t="shared" si="1"/>
         <v>1221210.7341223909</v>
       </c>
-      <c r="H22" s="164"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B23" s="166">
+      <c r="H22" s="163"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="165">
         <v>4</v>
       </c>
-      <c r="C23" s="167">
+      <c r="C23" s="166">
         <f t="shared" si="2"/>
         <v>1820483.2655709314</v>
       </c>
-      <c r="D23" s="183">
+      <c r="D23" s="182">
         <f>IF($C$16&lt;B23,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E23" s="168">
+      <c r="E23" s="167">
         <f t="shared" si="0"/>
         <v>0.68301345536507052</v>
       </c>
-      <c r="F23" s="169">
+      <c r="F23" s="168">
         <f t="shared" si="1"/>
         <v>1243414.5656518892</v>
       </c>
-      <c r="H23" s="164"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B24" s="166">
+      <c r="H23" s="163"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="165">
         <v>5</v>
       </c>
-      <c r="C24" s="167">
+      <c r="C24" s="166">
         <f t="shared" si="2"/>
         <v>2038941.2574394429</v>
       </c>
-      <c r="D24" s="183">
+      <c r="D24" s="182">
         <f>IF($C$16&lt;B24,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E24" s="168">
+      <c r="E24" s="167">
         <f t="shared" si="0"/>
         <v>0.62092132305915493</v>
       </c>
-      <c r="F24" s="169">
+      <c r="F24" s="168">
         <f t="shared" si="1"/>
         <v>1266022.1032091959</v>
       </c>
-      <c r="H24" s="164"/>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B25" s="166">
+      <c r="H24" s="163"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="165">
         <v>6</v>
       </c>
-      <c r="C25" s="167">
+      <c r="C25" s="166">
         <f t="shared" si="2"/>
         <v>2283614.2083321763</v>
       </c>
-      <c r="D25" s="183">
+      <c r="D25" s="182">
         <f>IF($C$16&lt;B25,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E25" s="168">
+      <c r="E25" s="167">
         <f t="shared" si="0"/>
         <v>0.56447393005377722</v>
       </c>
-      <c r="F25" s="169">
+      <c r="F25" s="168">
         <f t="shared" si="1"/>
         <v>1289040.6869039086</v>
       </c>
-      <c r="H25" s="164"/>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B26" s="166">
+      <c r="H25" s="163"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="165">
         <v>7</v>
       </c>
-      <c r="C26" s="167">
+      <c r="C26" s="166">
         <f t="shared" si="2"/>
         <v>2557647.9133320376</v>
       </c>
-      <c r="D26" s="183">
+      <c r="D26" s="182">
         <f>IF($C$16&lt;B26,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E26" s="168">
+      <c r="E26" s="167">
         <f t="shared" si="0"/>
         <v>0.51315811823070645</v>
       </c>
-      <c r="F26" s="169">
+      <c r="F26" s="168">
         <f t="shared" si="1"/>
         <v>1312477.7903021614</v>
       </c>
-      <c r="H26" s="164"/>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B27" s="166">
+      <c r="H26" s="163"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="165">
         <v>8</v>
       </c>
-      <c r="C27" s="167">
+      <c r="C27" s="166">
         <f t="shared" si="2"/>
         <v>2864565.6629318823</v>
       </c>
-      <c r="D27" s="183">
+      <c r="D27" s="182">
         <f>IF($C$16&lt;B27,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E27" s="168">
+      <c r="E27" s="167">
         <f t="shared" si="0"/>
         <v>0.46650738020973315</v>
       </c>
-      <c r="F27" s="169">
+      <c r="F27" s="168">
         <f t="shared" si="1"/>
         <v>1336341.02285311</v>
       </c>
-      <c r="H27" s="164"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B28" s="166">
+      <c r="H27" s="163"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="165">
         <v>9</v>
       </c>
-      <c r="C28" s="167">
+      <c r="C28" s="166">
         <f t="shared" si="2"/>
         <v>3208313.5424837084</v>
       </c>
-      <c r="D28" s="183">
+      <c r="D28" s="182">
         <f>IF($C$16&lt;B28,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E28" s="168">
+      <c r="E28" s="167">
         <f t="shared" si="0"/>
         <v>0.42409761837248466</v>
       </c>
-      <c r="F28" s="169">
+      <c r="F28" s="168">
         <f t="shared" si="1"/>
         <v>1360638.1323595301</v>
       </c>
-      <c r="H28" s="164"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B29" s="166">
+      <c r="H28" s="163"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="165">
         <v>10</v>
       </c>
-      <c r="C29" s="167">
+      <c r="C29" s="166">
         <f t="shared" si="2"/>
         <v>3593311.1675817533</v>
       </c>
-      <c r="D29" s="183">
+      <c r="D29" s="182">
         <f>IF($C$16&lt;B29,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E29" s="168">
+      <c r="E29" s="167">
         <f t="shared" si="0"/>
         <v>0.38554328942953148</v>
       </c>
-      <c r="F29" s="169">
+      <c r="F29" s="168">
         <f t="shared" si="1"/>
         <v>1385377.0074933397</v>
       </c>
-      <c r="H29" s="164"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B30" s="166">
+      <c r="H29" s="163"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="165">
         <v>11</v>
       </c>
-      <c r="C30" s="167">
+      <c r="C30" s="166">
         <f t="shared" si="2"/>
         <v>4024508.5076915645</v>
       </c>
-      <c r="D30" s="183">
+      <c r="D30" s="182">
         <f>IF($C$16&lt;B30,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E30" s="168">
+      <c r="E30" s="167">
         <f t="shared" si="0"/>
         <v>0.3504938994813922</v>
       </c>
-      <c r="F30" s="169">
+      <c r="F30" s="168">
         <f t="shared" si="1"/>
         <v>1410565.680356855</v>
       </c>
-      <c r="H30" s="164"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B31" s="166">
+      <c r="H30" s="163"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="165">
         <v>12</v>
       </c>
-      <c r="C31" s="167">
+      <c r="C31" s="166">
         <f t="shared" si="2"/>
         <v>4507449.5286145527</v>
       </c>
-      <c r="D31" s="183">
+      <c r="D31" s="182">
         <f>IF($C$16&lt;B31,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E31" s="168">
+      <c r="E31" s="167">
         <f t="shared" si="0"/>
         <v>0.31863081771035656</v>
       </c>
-      <c r="F31" s="169">
+      <c r="F31" s="168">
         <f t="shared" si="1"/>
         <v>1436212.3290906162</v>
       </c>
-      <c r="H31" s="164"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B32" s="166">
+      <c r="H31" s="163"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="165">
         <v>13</v>
       </c>
-      <c r="C32" s="167">
+      <c r="C32" s="166">
         <f t="shared" si="2"/>
         <v>5048343.4720482985</v>
       </c>
-      <c r="D32" s="183">
+      <c r="D32" s="182">
         <f>IF($C$16&lt;B32,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E32" s="168">
+      <c r="E32" s="167">
         <f t="shared" si="0"/>
         <v>0.28966437973668779</v>
       </c>
-      <c r="F32" s="169">
+      <c r="F32" s="168">
         <f t="shared" si="1"/>
         <v>1462325.2805286273</v>
       </c>
-      <c r="H32" s="164"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B33" s="166">
+      <c r="H32" s="163"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="165">
         <v>14</v>
       </c>
-      <c r="C33" s="167">
+      <c r="C33" s="166">
         <f t="shared" si="2"/>
         <v>5654144.6886940952</v>
       </c>
-      <c r="D33" s="183">
+      <c r="D33" s="182">
         <f>IF($C$16&lt;B33,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E33" s="168">
+      <c r="E33" s="167">
         <f t="shared" si="0"/>
         <v>0.26333125430607973</v>
       </c>
-      <c r="F33" s="169">
+      <c r="F33" s="168">
         <f t="shared" si="1"/>
         <v>1488913.0129018747</v>
       </c>
-      <c r="H33" s="164"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B34" s="166">
+      <c r="H33" s="163"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="165">
         <v>15</v>
       </c>
-      <c r="C34" s="167">
+      <c r="C34" s="166">
         <f t="shared" si="2"/>
         <v>6332642.0513373874</v>
       </c>
-      <c r="D34" s="183">
+      <c r="D34" s="182">
         <f>IF($C$16&lt;B34,0,Valuation_Model!$C$15)</f>
         <v>0.12</v>
       </c>
-      <c r="E34" s="168">
+      <c r="E34" s="167">
         <f t="shared" si="0"/>
         <v>0.23939204936916339</v>
       </c>
-      <c r="F34" s="169">
+      <c r="F34" s="168">
         <f t="shared" si="1"/>
         <v>1515984.1585909999</v>
       </c>
-      <c r="H34" s="164"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B35" s="166">
+      <c r="H34" s="163"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="165">
         <v>16</v>
       </c>
-      <c r="C35" s="167">
+      <c r="C35" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D35" s="183">
+      <c r="D35" s="182">
         <f>IF($C$16&lt;B35,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="168">
+      <c r="E35" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F35" s="169">
+      <c r="F35" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="164"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B36" s="166">
+      <c r="H35" s="163"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="165">
         <v>17</v>
       </c>
-      <c r="C36" s="167">
+      <c r="C36" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D36" s="183">
+      <c r="D36" s="182">
         <f>IF($C$16&lt;B36,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="168">
+      <c r="E36" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F36" s="169">
+      <c r="F36" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H36" s="164"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B37" s="166">
+      <c r="H36" s="163"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="165">
         <v>18</v>
       </c>
-      <c r="C37" s="167">
+      <c r="C37" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D37" s="183">
+      <c r="D37" s="182">
         <f>IF($C$16&lt;B37,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E37" s="168">
+      <c r="E37" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F37" s="169">
+      <c r="F37" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H37" s="164"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B38" s="166">
+      <c r="H37" s="163"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="165">
         <v>19</v>
       </c>
-      <c r="C38" s="167">
+      <c r="C38" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D38" s="183">
+      <c r="D38" s="182">
         <f>IF($C$16&lt;B38,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="168">
+      <c r="E38" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F38" s="169">
+      <c r="F38" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H38" s="164"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B39" s="166">
+      <c r="H38" s="163"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="165">
         <v>20</v>
       </c>
-      <c r="C39" s="167">
+      <c r="C39" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D39" s="183">
+      <c r="D39" s="182">
         <f>IF($C$16&lt;B39,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="168">
+      <c r="E39" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F39" s="169">
+      <c r="F39" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H39" s="164"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B40" s="166">
+      <c r="H39" s="163"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="165">
         <v>21</v>
       </c>
-      <c r="C40" s="167">
+      <c r="C40" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D40" s="183">
+      <c r="D40" s="182">
         <f>IF($C$16&lt;B40,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="168">
+      <c r="E40" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F40" s="169">
+      <c r="F40" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H40" s="164"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B41" s="166">
+      <c r="H40" s="163"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="165">
         <v>22</v>
       </c>
-      <c r="C41" s="167">
+      <c r="C41" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D41" s="183">
+      <c r="D41" s="182">
         <f>IF($C$16&lt;B41,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="168">
+      <c r="E41" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F41" s="169">
+      <c r="F41" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H41" s="164"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B42" s="166">
+      <c r="H41" s="163"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="165">
         <v>23</v>
       </c>
-      <c r="C42" s="167">
+      <c r="C42" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D42" s="183">
+      <c r="D42" s="182">
         <f>IF($C$16&lt;B42,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="168">
+      <c r="E42" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F42" s="169">
+      <c r="F42" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H42" s="164"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B43" s="166">
+      <c r="H42" s="163"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="165">
         <v>24</v>
       </c>
-      <c r="C43" s="167">
+      <c r="C43" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D43" s="183">
+      <c r="D43" s="182">
         <f>IF($C$16&lt;B43,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E43" s="168">
+      <c r="E43" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F43" s="169">
+      <c r="F43" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H43" s="164"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B44" s="166">
+      <c r="H43" s="163"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="165">
         <v>25</v>
       </c>
-      <c r="C44" s="167">
+      <c r="C44" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D44" s="183">
+      <c r="D44" s="182">
         <f>IF($C$16&lt;B44,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="168">
+      <c r="E44" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F44" s="169">
+      <c r="F44" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H44" s="164"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B45" s="166">
+      <c r="H44" s="163"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="165">
         <v>26</v>
       </c>
-      <c r="C45" s="167">
+      <c r="C45" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D45" s="183">
+      <c r="D45" s="182">
         <f>IF($C$16&lt;B45,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="168">
+      <c r="E45" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F45" s="169">
+      <c r="F45" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H45" s="164"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B46" s="166">
+      <c r="H45" s="163"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="165">
         <v>27</v>
       </c>
-      <c r="C46" s="167">
+      <c r="C46" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D46" s="183">
+      <c r="D46" s="182">
         <f>IF($C$16&lt;B46,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E46" s="168">
+      <c r="E46" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F46" s="169">
+      <c r="F46" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H46" s="164"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B47" s="166">
+      <c r="H46" s="163"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="165">
         <v>28</v>
       </c>
-      <c r="C47" s="167">
+      <c r="C47" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D47" s="183">
+      <c r="D47" s="182">
         <f>IF($C$16&lt;B47,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E47" s="168">
+      <c r="E47" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F47" s="169">
+      <c r="F47" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="164"/>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B48" s="166">
+      <c r="H47" s="163"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="165">
         <v>29</v>
       </c>
-      <c r="C48" s="167">
+      <c r="C48" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D48" s="183">
+      <c r="D48" s="182">
         <f>IF($C$16&lt;B48,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="168">
+      <c r="E48" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F48" s="169">
+      <c r="F48" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="164"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B49" s="166">
+      <c r="H48" s="163"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="165">
         <v>30</v>
       </c>
-      <c r="C49" s="167">
+      <c r="C49" s="166">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="D49" s="183">
+      <c r="D49" s="182">
         <f>IF($C$16&lt;B49,0,Valuation_Model!$C$15)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="168">
+      <c r="E49" s="167">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F49" s="169">
+      <c r="F49" s="168">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="164"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B50" s="170" t="s">
+      <c r="H49" s="163"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="169" t="s">
         <v>251</v>
       </c>
-      <c r="C50" s="167">
+      <c r="C50" s="166">
         <f>C$20*(1+Terminal_Growth)^$C$16/Equity_Cost</f>
         <v>12957840.299082449</v>
       </c>
-      <c r="D50" s="184">
+      <c r="D50" s="183">
         <f>Terminal_Growth</f>
         <v>0</v>
       </c>
-      <c r="E50" s="168">
+      <c r="E50" s="167">
         <f>1/(1+Equity_Cost)^C16</f>
         <v>0.23939204936916339</v>
       </c>
-      <c r="F50" s="169">
+      <c r="F50" s="168">
         <f t="shared" si="1"/>
         <v>3102003.9445956806</v>
       </c>
-      <c r="H50" s="164"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C51" s="158"/>
-      <c r="E51" s="171" t="s">
+      <c r="H50" s="163"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C51" s="157"/>
+      <c r="E51" s="170" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="182">
+      <c r="F51" s="181">
         <f>SUM(F20:F50)</f>
         <v>23207915.33027944</v>
       </c>
-      <c r="H51" s="164"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C52" s="158"/>
-      <c r="H52" s="164"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B53" s="163" t="s">
+      <c r="H51" s="163"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C52" s="157"/>
+      <c r="H52" s="163"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B53" s="162" t="s">
         <v>249</v>
       </c>
-      <c r="C53" s="181"/>
-      <c r="D53" s="181"/>
-      <c r="E53" s="161"/>
-      <c r="F53" s="161"/>
-      <c r="H53" s="164"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A54" s="177">
+      <c r="C53" s="180"/>
+      <c r="D53" s="180"/>
+      <c r="E53" s="160"/>
+      <c r="F53" s="160"/>
+      <c r="H53" s="163"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A54" s="176">
         <f>F51</f>
         <v>23207915.33027944</v>
       </c>
-      <c r="B54" s="175">
+      <c r="B54" s="174">
         <f>C77</f>
         <v>-0.05</v>
       </c>
-      <c r="C54" s="175">
+      <c r="C54" s="174">
         <f>C76</f>
         <v>0</v>
       </c>
-      <c r="D54" s="175">
+      <c r="D54" s="174">
         <f>C75</f>
         <v>0.02</v>
       </c>
-      <c r="E54" s="175">
+      <c r="E54" s="174">
         <f>C74</f>
         <v>0.05</v>
       </c>
-      <c r="F54" s="175">
+      <c r="F54" s="174">
         <f>C73</f>
         <v>0.1</v>
       </c>
-      <c r="H54" s="164"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A55" s="188">
+      <c r="H54" s="163"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A55" s="187">
         <v>5</v>
       </c>
-      <c r="B55" s="167">
+      <c r="B55" s="166">
         <f t="dataTable" ref="B55:F60" dt2D="1" dtr="1" r1="C15" r2="C16"/>
         <v>10631434.819595248</v>
       </c>
-      <c r="C55" s="167">
+      <c r="C55" s="166">
         <v>11569500.267037896</v>
       </c>
-      <c r="D55" s="167">
+      <c r="D55" s="166">
         <v>11965951.468842616</v>
       </c>
-      <c r="E55" s="167">
+      <c r="E55" s="166">
         <v>12585064.901116043</v>
       </c>
-      <c r="F55" s="167">
+      <c r="F55" s="166">
         <v>13686874.487755612</v>
       </c>
-      <c r="H55" s="164"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A56" s="188">
+      <c r="H55" s="163"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A56" s="187">
         <v>10</v>
       </c>
-      <c r="B56" s="167">
+      <c r="B56" s="166">
         <v>9873427.9475794099</v>
       </c>
-      <c r="C56" s="167">
+      <c r="C56" s="166">
         <v>11569500.267037895</v>
       </c>
-      <c r="D56" s="167">
+      <c r="D56" s="166">
         <v>12368210.88935476</v>
       </c>
-      <c r="E56" s="167">
+      <c r="E56" s="166">
         <v>13721435.757387349</v>
       </c>
-      <c r="F56" s="167">
+      <c r="F56" s="166">
         <v>16476097.7760485</v>
       </c>
-      <c r="H56" s="164"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A57" s="188">
+      <c r="H56" s="163"/>
+    </row>
+    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A57" s="187">
         <v>15</v>
       </c>
-      <c r="B57" s="167">
+      <c r="B57" s="166">
         <v>9145850.7398200184</v>
       </c>
-      <c r="C57" s="167">
+      <c r="C57" s="166">
         <v>11569500.267037895</v>
       </c>
-      <c r="D57" s="167">
+      <c r="D57" s="166">
         <v>12823488.450422456</v>
       </c>
-      <c r="E57" s="167">
+      <c r="E57" s="166">
         <v>15112497.859340815</v>
       </c>
-      <c r="F57" s="167">
+      <c r="F57" s="166">
         <v>20400861.417570464</v>
       </c>
-      <c r="H57" s="164"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A58" s="189">
+      <c r="H57" s="163"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A58" s="188">
         <v>20</v>
       </c>
-      <c r="B58" s="167">
+      <c r="B58" s="166">
         <v>8570646.1085517909</v>
       </c>
-      <c r="C58" s="167">
+      <c r="C58" s="166">
         <v>11569500.267037893</v>
       </c>
-      <c r="D58" s="167">
+      <c r="D58" s="166">
         <v>13247064.157170108</v>
       </c>
-      <c r="E58" s="167">
+      <c r="E58" s="166">
         <v>16519448.891378088</v>
       </c>
-      <c r="F58" s="167">
+      <c r="F58" s="166">
         <v>25030706.277606491</v>
       </c>
-      <c r="H58" s="164"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A59" s="189">
+      <c r="H58" s="163"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A59" s="188">
         <v>25</v>
       </c>
-      <c r="B59" s="167">
+      <c r="B59" s="166">
         <v>8154183.3813003954</v>
       </c>
-      <c r="C59" s="167">
+      <c r="C59" s="166">
         <v>11569500.267037893</v>
       </c>
-      <c r="D59" s="167">
+      <c r="D59" s="166">
         <v>13606654.103566449</v>
       </c>
-      <c r="E59" s="167">
+      <c r="E59" s="166">
         <v>17823533.375544701</v>
       </c>
-      <c r="F59" s="167">
+      <c r="F59" s="166">
         <v>30098351.100706428</v>
       </c>
-      <c r="H59" s="164"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A60" s="189">
+      <c r="H59" s="163"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A60" s="188">
         <v>30</v>
       </c>
-      <c r="B60" s="167">
+      <c r="B60" s="166">
         <v>7867098.8507852424</v>
       </c>
-      <c r="C60" s="167">
+      <c r="C60" s="166">
         <v>11569500.267037893</v>
       </c>
-      <c r="D60" s="167">
+      <c r="D60" s="166">
         <v>13896143.219179772</v>
       </c>
-      <c r="E60" s="167">
+      <c r="E60" s="166">
         <v>18974408.793221079</v>
       </c>
-      <c r="F60" s="167">
+      <c r="F60" s="166">
         <v>35437835.256107256</v>
       </c>
-      <c r="H60" s="164"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="C61" s="158"/>
-      <c r="D61" s="158"/>
-      <c r="E61" s="158"/>
-      <c r="F61" s="158"/>
-      <c r="H61" s="164"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B62" s="163" t="s">
+      <c r="H60" s="163"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="C61" s="157"/>
+      <c r="D61" s="157"/>
+      <c r="E61" s="157"/>
+      <c r="F61" s="157"/>
+      <c r="H61" s="163"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+      <c r="B62" s="162" t="s">
         <v>250</v>
       </c>
-      <c r="C62" s="158"/>
-      <c r="D62" s="158"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="158"/>
-      <c r="H62" s="164"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B63" s="176">
+      <c r="C62" s="157"/>
+      <c r="D62" s="157"/>
+      <c r="E62" s="157"/>
+      <c r="F62" s="157"/>
+      <c r="H62" s="163"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B63" s="175">
         <f>B54</f>
         <v>-0.05</v>
       </c>
-      <c r="C63" s="176">
+      <c r="C63" s="175">
         <f>C54</f>
         <v>0</v>
       </c>
-      <c r="D63" s="176">
+      <c r="D63" s="175">
         <f>D54</f>
         <v>0.02</v>
       </c>
-      <c r="E63" s="176">
+      <c r="E63" s="175">
         <f>E54</f>
         <v>0.05</v>
       </c>
-      <c r="F63" s="176">
+      <c r="F63" s="175">
         <f>F54</f>
         <v>0.1</v>
       </c>
-      <c r="H63" s="164"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A64" s="188">
-        <v>0</v>
-      </c>
-      <c r="B64" s="168">
+      <c r="H63" s="163"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A64" s="187">
+        <v>0</v>
+      </c>
+      <c r="B64" s="167">
         <f>C11</f>
         <v>16.239909357433906</v>
       </c>
-      <c r="C64" s="168">
+      <c r="C64" s="167">
         <f>C11</f>
         <v>16.239909357433906</v>
       </c>
-      <c r="D64" s="168">
+      <c r="D64" s="167">
         <f>C11</f>
         <v>16.239909357433906</v>
       </c>
-      <c r="E64" s="186">
+      <c r="E64" s="185">
         <f>C11</f>
         <v>16.239909357433906</v>
       </c>
-      <c r="F64" s="168">
+      <c r="F64" s="167">
         <f>C11</f>
         <v>16.239909357433906</v>
       </c>
-      <c r="H64" s="164"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A65" s="188">
+      <c r="H64" s="163"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A65" s="187">
         <f t="shared" ref="A65:A70" si="3">A55</f>
         <v>5</v>
       </c>
-      <c r="B65" s="168">
+      <c r="B65" s="167">
         <f t="shared" ref="B65:F70" si="4">(B55-$C$7+$C$8)/Common_Shares*$C$3*Exchange_Rate</f>
         <v>14.642135715942562</v>
       </c>
-      <c r="C65" s="168">
+      <c r="C65" s="167">
         <f t="shared" si="4"/>
         <v>16.239909357433895</v>
       </c>
-      <c r="D65" s="168">
+      <c r="D65" s="167">
         <f t="shared" si="4"/>
         <v>16.915170643422016</v>
       </c>
-      <c r="E65" s="168">
+      <c r="E65" s="167">
         <f t="shared" si="4"/>
         <v>17.969684617768344</v>
       </c>
-      <c r="F65" s="168">
+      <c r="F65" s="167">
         <f t="shared" si="4"/>
         <v>19.846357850189897</v>
       </c>
-      <c r="H65" s="164"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A66" s="188">
+      <c r="H65" s="163"/>
+    </row>
+    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A66" s="187">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="B66" s="168">
+      <c r="B66" s="167">
         <f t="shared" si="4"/>
         <v>13.351049466600404</v>
       </c>
-      <c r="C66" s="168">
+      <c r="C66" s="167">
         <f t="shared" si="4"/>
         <v>16.239909357433891</v>
       </c>
-      <c r="D66" s="168">
+      <c r="D66" s="167">
         <f t="shared" si="4"/>
         <v>17.600324862552526</v>
       </c>
-      <c r="E66" s="168">
+      <c r="E66" s="167">
         <f t="shared" si="4"/>
         <v>19.905224836267049</v>
       </c>
-      <c r="F66" s="168">
+      <c r="F66" s="167">
         <f t="shared" si="4"/>
         <v>24.59714305650742</v>
       </c>
-      <c r="H66" s="164"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A67" s="188">
+      <c r="H66" s="163"/>
+    </row>
+    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A67" s="187">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="B67" s="168">
+      <c r="B67" s="167">
         <f t="shared" si="4"/>
         <v>12.111792986280149</v>
       </c>
-      <c r="C67" s="168">
+      <c r="C67" s="167">
         <f t="shared" si="4"/>
         <v>16.239909357433891</v>
       </c>
-      <c r="D67" s="168">
+      <c r="D67" s="167">
         <f t="shared" si="4"/>
         <v>18.375783002088045</v>
       </c>
-      <c r="E67" s="168">
+      <c r="E67" s="167">
         <f t="shared" si="4"/>
         <v>22.274571629966818</v>
       </c>
-      <c r="F67" s="168">
+      <c r="F67" s="167">
         <f t="shared" si="4"/>
         <v>31.282053914916084</v>
       </c>
-      <c r="H67" s="164"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A68" s="189">
+      <c r="H67" s="163"/>
+    </row>
+    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A68" s="188">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="B68" s="168">
+      <c r="B68" s="167">
         <f t="shared" si="4"/>
         <v>11.13206731702155</v>
       </c>
-      <c r="C68" s="168">
+      <c r="C68" s="167">
         <f t="shared" si="4"/>
         <v>16.239909357433891</v>
       </c>
-      <c r="D68" s="168">
+      <c r="D68" s="167">
         <f t="shared" si="4"/>
         <v>19.097244496339314</v>
       </c>
-      <c r="E68" s="168">
+      <c r="E68" s="167">
         <f t="shared" si="4"/>
         <v>24.670981475342373</v>
       </c>
-      <c r="F68" s="168">
+      <c r="F68" s="167">
         <f t="shared" si="4"/>
         <v>39.167904632183834</v>
       </c>
-      <c r="H68" s="164"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A69" s="189">
+      <c r="H68" s="163"/>
+    </row>
+    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A69" s="188">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="B69" s="168">
+      <c r="B69" s="167">
         <f t="shared" si="4"/>
         <v>10.42272110873734</v>
       </c>
-      <c r="C69" s="168">
+      <c r="C69" s="167">
         <f t="shared" si="4"/>
         <v>16.239909357433891</v>
       </c>
-      <c r="D69" s="168">
+      <c r="D69" s="167">
         <f t="shared" si="4"/>
         <v>19.709721311964145</v>
       </c>
-      <c r="E69" s="168">
+      <c r="E69" s="167">
         <f t="shared" si="4"/>
         <v>26.89218237423448</v>
       </c>
-      <c r="F69" s="168">
+      <c r="F69" s="167">
         <f t="shared" si="4"/>
         <v>47.79944451552884</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A70" s="189">
+    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A70" s="188">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="B70" s="168">
+      <c r="B70" s="167">
         <f t="shared" si="4"/>
         <v>9.9337401991563272</v>
       </c>
-      <c r="C70" s="168">
+      <c r="C70" s="167">
         <f t="shared" si="4"/>
         <v>16.239909357433891</v>
       </c>
-      <c r="D70" s="168">
+      <c r="D70" s="167">
         <f t="shared" si="4"/>
         <v>20.202797866149758</v>
       </c>
-      <c r="E70" s="168">
+      <c r="E70" s="167">
         <f t="shared" si="4"/>
         <v>28.85242769828589</v>
       </c>
-      <c r="F70" s="168">
+      <c r="F70" s="167">
         <f t="shared" si="4"/>
         <v>56.893998702465403</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="14" x14ac:dyDescent="0.2">
-      <c r="B72" s="228" t="s">
+    <row r="72" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B72" s="227" t="s">
         <v>227</v>
       </c>
-      <c r="C72" s="228" t="s">
+      <c r="C72" s="227" t="s">
         <v>252</v>
       </c>
-      <c r="D72" s="228" t="s">
+      <c r="D72" s="227" t="s">
         <v>221</v>
       </c>
-      <c r="E72" s="229" t="s">
+      <c r="E72" s="228" t="s">
         <v>222</v>
       </c>
-      <c r="F72" s="229" t="s">
+      <c r="F72" s="228" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B73" s="171" t="str">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B73" s="170" t="str">
         <f>Scenarios!B67</f>
         <v>Revaluation</v>
       </c>
-      <c r="C73" s="187">
+      <c r="C73" s="186">
         <f>Scenarios!C69</f>
         <v>0.1</v>
       </c>
-      <c r="D73" s="190">
+      <c r="D73" s="189">
         <f>Scenarios!C68</f>
         <v>10</v>
       </c>
-      <c r="E73" s="180">
+      <c r="E73" s="179">
         <f>INDEX(B$64:F$70, MATCH(D73, A$64:A$70, 0), MATCH(C73, B$63:F$63, 0))</f>
         <v>24.59714305650742</v>
       </c>
-      <c r="F73" s="230">
+      <c r="F73" s="229">
         <f>E73*Common_Shares/1000000</f>
         <v>14441.1757760485</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B74" s="171" t="str">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B74" s="170" t="str">
         <f>Scenarios!B49</f>
         <v>Optimistic</v>
       </c>
-      <c r="C74" s="187">
+      <c r="C74" s="186">
         <f>Scenarios!C51</f>
         <v>0.05</v>
       </c>
-      <c r="D74" s="190">
+      <c r="D74" s="189">
         <f>Scenarios!C50</f>
         <v>5</v>
       </c>
-      <c r="E74" s="180">
+      <c r="E74" s="179">
         <f>INDEX(B$64:F$70, MATCH(D74, A$64:A$70, 0), MATCH(C74, B$63:F$63, 0))</f>
         <v>17.969684617768344</v>
       </c>
-      <c r="F74" s="230">
+      <c r="F74" s="229">
         <f>E74*Common_Shares/1000000</f>
         <v>10550.142901116045</v>
       </c>
-      <c r="H74" s="164" t="s">
+      <c r="H74" s="163" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B75" s="171" t="str">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B75" s="170" t="str">
         <f>Scenarios!B37</f>
         <v>Base</v>
       </c>
-      <c r="C75" s="187">
+      <c r="C75" s="186">
         <f>Scenarios!C39</f>
         <v>0.02</v>
       </c>
-      <c r="D75" s="190">
+      <c r="D75" s="189">
         <f>Scenarios!C38</f>
         <v>5</v>
       </c>
-      <c r="E75" s="180">
+      <c r="E75" s="179">
         <f>INDEX(B$64:F$70, MATCH(D75, A$64:A$70, 0), MATCH(C75, B$63:F$63, 0))</f>
         <v>16.915170643422016</v>
       </c>
-      <c r="F75" s="230">
+      <c r="F75" s="229">
         <f>E75*Common_Shares/1000000</f>
         <v>9931.0294688426166</v>
       </c>
-      <c r="H75" s="164" t="s">
+      <c r="H75" s="163" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B76" s="171" t="str">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B76" s="170" t="str">
         <f>Scenarios!B43</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C76" s="187">
+      <c r="C76" s="186">
         <f>Scenarios!C45</f>
         <v>0</v>
       </c>
-      <c r="D76" s="190">
+      <c r="D76" s="189">
         <f>Scenarios!C44</f>
         <v>5</v>
       </c>
-      <c r="E76" s="180">
+      <c r="E76" s="179">
         <f>INDEX(B$64:F$70, MATCH(D76, A$64:A$70, 0), MATCH(C76, B$63:F$63, 0))</f>
         <v>16.239909357433895</v>
       </c>
-      <c r="F76" s="230">
+      <c r="F76" s="229">
         <f>E76*Common_Shares/1000000</f>
         <v>9534.5782670378958</v>
       </c>
-      <c r="H76" s="164" t="s">
+      <c r="H76" s="163" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B77" s="171" t="str">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B77" s="170" t="str">
         <f>Scenarios!B61</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C77" s="187">
+      <c r="C77" s="186">
         <f>Scenarios!C63</f>
         <v>-0.05</v>
       </c>
-      <c r="D77" s="190">
+      <c r="D77" s="189">
         <f>Scenarios!C62</f>
         <v>10</v>
       </c>
-      <c r="E77" s="180">
+      <c r="E77" s="179">
         <f>INDEX(B$64:F$70, MATCH(D77, A$64:A$70, 0), MATCH(C77, B$63:F$63, 0))</f>
         <v>13.351049466600404</v>
       </c>
-      <c r="F77" s="230">
+      <c r="F77" s="229">
         <f>E77*Common_Shares/1000000</f>
         <v>7838.5059475794105</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B78" s="203"/>
-      <c r="C78" s="203"/>
-      <c r="D78" s="203"/>
-      <c r="E78" s="203"/>
-      <c r="F78" s="204"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C91" s="159"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C92" s="159"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
-      <c r="C93" s="159"/>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B78" s="202"/>
+      <c r="C78" s="202"/>
+      <c r="D78" s="202"/>
+      <c r="E78" s="202"/>
+      <c r="F78" s="203"/>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C91" s="158"/>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C92" s="158"/>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C93" s="158"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -13062,7 +13086,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -13070,7 +13094,7 @@
     <col min="5" max="5" width="83" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="39" t="s">
         <v>271</v>
       </c>
@@ -13080,105 +13104,105 @@
       <c r="F2" s="40"/>
       <c r="G2" s="40"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B3" s="208" t="s">
+    <row r="3" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B3" s="207" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B4" s="198" t="s">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B4" s="197" t="s">
         <v>274</v>
       </c>
-      <c r="C4" s="164">
+      <c r="C4" s="163">
         <v>4</v>
       </c>
-      <c r="D4" s="164"/>
-      <c r="E4" s="138" t="s">
+      <c r="D4" s="163"/>
+      <c r="E4" s="137" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B6" s="208" t="s">
+    <row r="6" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B6" s="207" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="146">
+      <c r="C6" s="145">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
-      <c r="E6" s="138" t="s">
+      <c r="E6" s="137" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B7" s="138" t="s">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="137" t="s">
         <v>287</v>
       </c>
-      <c r="C7" s="158">
+      <c r="C7" s="157">
         <f>Normalized_FCF!G19</f>
         <v>1554342</v>
       </c>
-      <c r="E7" s="241" t="s">
+      <c r="E7" s="245" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B8" s="138" t="s">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="137" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="158">
+      <c r="C8" s="157">
         <f>Normalized_FCF!C19</f>
         <v>1156950.0267037901</v>
       </c>
-      <c r="E8" s="242"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="E9" s="242"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B10" s="208" t="s">
+      <c r="E8" s="246"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E9" s="246"/>
+    </row>
+    <row r="10" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B10" s="207" t="s">
         <v>275</v>
       </c>
-      <c r="E10" s="242"/>
-    </row>
-    <row r="11" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B11" s="162" t="s">
+      <c r="E10" s="246"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="161" t="s">
         <v>273</v>
       </c>
-      <c r="C11" s="207">
+      <c r="C11" s="206">
         <f>AVERAGE(Normalized_FCF!G39:INDEX(Normalized_FCF!G39:Q39, $C$4))</f>
         <v>0.10334930065770259</v>
       </c>
-      <c r="D11" s="207"/>
-      <c r="E11" s="242"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B12" s="193" t="s">
+      <c r="D11" s="206"/>
+      <c r="E11" s="246"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="192" t="s">
         <v>272</v>
       </c>
-      <c r="E12" s="242"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B13" s="138" t="s">
+      <c r="E12" s="246"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="137" t="s">
         <v>160</v>
       </c>
-      <c r="E13" s="242"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B15" s="208" t="s">
+      <c r="E13" s="246"/>
+    </row>
+    <row r="15" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B15" s="207" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B16" s="138" t="s">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="137" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B17" s="193" t="s">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="192" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B19" s="39" t="s">
         <v>279</v>
       </c>
@@ -13188,19 +13212,19 @@
       <c r="F19" s="40"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B20" s="151" t="s">
+    <row r="20" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B20" s="150" t="s">
         <v>278</v>
       </c>
-      <c r="E20" s="208" t="s">
+      <c r="E20" s="207" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B21" s="138" t="s">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B21" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="209">
+      <c r="C21" s="208">
         <f>Valuation_Model!E76</f>
         <v>16.239909357433895</v>
       </c>
@@ -13208,55 +13232,55 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="220" t="s">
+      <c r="E21" s="219" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B23" s="151" t="s">
+    <row r="23" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B23" s="150" t="s">
         <v>277</v>
       </c>
-      <c r="E23" s="222"/>
-    </row>
-    <row r="24" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="198" t="s">
+      <c r="E23" s="221"/>
+    </row>
+    <row r="24" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C24" s="196">
+      <c r="C24" s="195">
         <v>15</v>
       </c>
-      <c r="D24" s="196"/>
-      <c r="E24" s="223"/>
-    </row>
-    <row r="25" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B25" s="162" t="s">
+      <c r="D24" s="195"/>
+      <c r="E24" s="222"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C25" s="197">
+      <c r="C25" s="196">
         <v>0.12</v>
       </c>
-      <c r="D25" s="197"/>
-      <c r="E25" s="223"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B26" s="138" t="s">
+      <c r="D25" s="196"/>
+      <c r="E25" s="222"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C26" s="209">
+      <c r="C26" s="208">
         <f>Valuation_Model!C17</f>
         <v>36.063209392072409</v>
       </c>
-      <c r="D26" s="209"/>
-      <c r="E26" s="223"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B28" s="151" t="s">
+      <c r="D26" s="208"/>
+      <c r="E26" s="222"/>
+    </row>
+    <row r="28" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B28" s="150" t="s">
         <v>257</v>
       </c>
-      <c r="C28" s="200"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B29" s="138" t="s">
+      <c r="C28" s="199"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="137" t="s">
         <v>228</v>
       </c>
       <c r="C29">
@@ -13264,20 +13288,20 @@
         <v>15.68</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B30" s="138" t="s">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="137" t="s">
         <v>259</v>
       </c>
       <c r="C30">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B31" s="138" t="s">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B31" s="137" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B33" s="39" t="s">
         <v>307</v>
       </c>
@@ -13287,107 +13311,107 @@
       <c r="F33" s="40"/>
       <c r="G33" s="40"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B34" s="151" t="s">
+    <row r="34" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B34" s="150" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B35" s="198" t="s">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="196">
+      <c r="C35" s="195">
         <v>5</v>
       </c>
-      <c r="E35" s="138"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B37" s="208" t="s">
+      <c r="E35" s="137"/>
+    </row>
+    <row r="37" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B37" s="207" t="s">
         <v>225</v>
       </c>
-      <c r="E37" s="208" t="s">
+      <c r="E37" s="207" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B38" s="198" t="s">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C38" s="215">
+      <c r="C38" s="214">
         <f>C35</f>
         <v>5</v>
       </c>
-      <c r="D38" s="212"/>
-      <c r="E38" s="242"/>
-    </row>
-    <row r="39" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B39" s="162" t="s">
+      <c r="D38" s="211"/>
+      <c r="E38" s="246"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C39" s="213">
+      <c r="C39" s="212">
         <v>0.02</v>
       </c>
-      <c r="D39" s="213"/>
-      <c r="E39" s="242"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B40" s="138" t="s">
+      <c r="D39" s="212"/>
+      <c r="E39" s="246"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C40" s="209">
+      <c r="C40" s="208">
         <f>Valuation_Model!E75</f>
         <v>16.915170643422016</v>
       </c>
-      <c r="D40" s="209" t="str">
+      <c r="D40" s="208" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="242"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B41" s="138" t="s">
+      <c r="E40" s="246"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="C41" s="214">
+      <c r="C41" s="213">
         <v>0.6</v>
       </c>
-      <c r="D41" s="214"/>
-      <c r="E41" s="242"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B43" s="208" t="s">
+      <c r="D41" s="213"/>
+      <c r="E41" s="246"/>
+    </row>
+    <row r="43" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B43" s="207" t="s">
         <v>226</v>
       </c>
-      <c r="E43" s="208" t="s">
+      <c r="E43" s="207" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B44" s="198" t="s">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B44" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C44" s="215">
+      <c r="C44" s="214">
         <f>C35</f>
         <v>5</v>
       </c>
-      <c r="D44" s="212"/>
-      <c r="E44" s="242"/>
-    </row>
-    <row r="45" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B45" s="162" t="s">
+      <c r="D44" s="211"/>
+      <c r="E44" s="246"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B45" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C45" s="213">
-        <v>0</v>
-      </c>
-      <c r="D45" s="213"/>
-      <c r="E45" s="242"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B46" s="138" t="s">
+      <c r="C45" s="212">
+        <v>0</v>
+      </c>
+      <c r="D45" s="212"/>
+      <c r="E45" s="246"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B46" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C46" s="209">
+      <c r="C46" s="208">
         <f>Valuation_Model!E76</f>
         <v>16.239909357433895</v>
       </c>
@@ -13395,52 +13419,52 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E46" s="242"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B47" s="138" t="s">
+      <c r="E46" s="246"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B47" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="C47" s="214">
+      <c r="C47" s="213">
         <v>0.2</v>
       </c>
-      <c r="D47" s="214"/>
-      <c r="E47" s="242"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B49" s="208" t="s">
+      <c r="D47" s="213"/>
+      <c r="E47" s="246"/>
+    </row>
+    <row r="49" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B49" s="207" t="s">
         <v>224</v>
       </c>
-      <c r="E49" s="208" t="s">
+      <c r="E49" s="207" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B50" s="198" t="s">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B50" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C50" s="215">
+      <c r="C50" s="214">
         <f>C35</f>
         <v>5</v>
       </c>
-      <c r="D50" s="212"/>
-      <c r="E50" s="242"/>
-    </row>
-    <row r="51" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B51" s="162" t="s">
+      <c r="D50" s="211"/>
+      <c r="E50" s="246"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C51" s="213">
+      <c r="C51" s="212">
         <v>0.05</v>
       </c>
-      <c r="D51" s="213"/>
-      <c r="E51" s="242"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B52" s="138" t="s">
+      <c r="D51" s="212"/>
+      <c r="E51" s="246"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B52" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C52" s="209">
+      <c r="C52" s="208">
         <f>Valuation_Model!E74</f>
         <v>17.969684617768344</v>
       </c>
@@ -13448,24 +13472,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="242"/>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B53" s="138" t="s">
+      <c r="E52" s="246"/>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B53" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="C53" s="217">
+      <c r="C53" s="216">
         <f>1-C41-C47</f>
         <v>0.2</v>
       </c>
-      <c r="D53" s="214"/>
-      <c r="E53" s="242"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B55" s="138" t="s">
+      <c r="D53" s="213"/>
+      <c r="E53" s="246"/>
+    </row>
+    <row r="55" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B55" s="137" t="s">
         <v>231</v>
       </c>
-      <c r="C55" s="202">
+      <c r="C55" s="201">
         <f>C40*C41+C46*C47+C52*C53</f>
         <v>16.991021181093657</v>
       </c>
@@ -13474,7 +13498,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B57" s="39" t="s">
         <v>306</v>
       </c>
@@ -13484,60 +13508,60 @@
       <c r="F57" s="40"/>
       <c r="G57" s="40"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B58" s="151" t="s">
+    <row r="58" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B58" s="150" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B59" s="198" t="s">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B59" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C59" s="196">
+      <c r="C59" s="195">
         <v>10</v>
       </c>
-      <c r="E59" s="138"/>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B60" s="208"/>
-      <c r="E60" s="208"/>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B61" s="208" t="s">
+      <c r="E59" s="137"/>
+    </row>
+    <row r="60" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B60" s="207"/>
+      <c r="E60" s="207"/>
+    </row>
+    <row r="61" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B61" s="207" t="s">
         <v>310</v>
       </c>
-      <c r="E61" s="208" t="s">
+      <c r="E61" s="207" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B62" s="198" t="s">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B62" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C62" s="215">
+      <c r="C62" s="214">
         <f>C59</f>
         <v>10</v>
       </c>
-      <c r="D62" s="212"/>
-      <c r="E62" s="241" t="s">
+      <c r="D62" s="211"/>
+      <c r="E62" s="245" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B63" s="162" t="s">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B63" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C63" s="213">
+      <c r="C63" s="212">
         <v>-0.05</v>
       </c>
-      <c r="D63" s="213"/>
-      <c r="E63" s="242"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B64" s="138" t="s">
+      <c r="D63" s="212"/>
+      <c r="E63" s="246"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B64" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C64" s="209">
+      <c r="C64" s="208">
         <f>Valuation_Model!E77</f>
         <v>13.351049466600404</v>
       </c>
@@ -13545,52 +13569,52 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E64" s="242"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B65" s="138" t="s">
+      <c r="E64" s="246"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B65" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="C65" s="214">
+      <c r="C65" s="213">
         <v>0.1</v>
       </c>
-      <c r="D65" s="214"/>
-      <c r="E65" s="242"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B67" s="208" t="s">
+      <c r="D65" s="213"/>
+      <c r="E65" s="246"/>
+    </row>
+    <row r="67" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B67" s="207" t="s">
         <v>311</v>
       </c>
-      <c r="E67" s="208" t="s">
+      <c r="E67" s="207" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B68" s="198" t="s">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B68" s="197" t="s">
         <v>253</v>
       </c>
-      <c r="C68" s="215">
+      <c r="C68" s="214">
         <f>C59</f>
         <v>10</v>
       </c>
-      <c r="D68" s="212"/>
-      <c r="E68" s="241"/>
-    </row>
-    <row r="69" spans="2:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="B69" s="162" t="s">
+      <c r="D68" s="211"/>
+      <c r="E68" s="245"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B69" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="C69" s="213">
+      <c r="C69" s="212">
         <v>0.1</v>
       </c>
-      <c r="D69" s="213"/>
-      <c r="E69" s="242"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B70" s="138" t="s">
+      <c r="D69" s="212"/>
+      <c r="E69" s="246"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B70" s="137" t="s">
         <v>222</v>
       </c>
-      <c r="C70" s="209">
+      <c r="C70" s="208">
         <f>Valuation_Model!E73</f>
         <v>24.59714305650742</v>
       </c>
@@ -13598,23 +13622,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E70" s="242"/>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B71" s="138" t="s">
+      <c r="E70" s="246"/>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B71" s="137" t="s">
         <v>280</v>
       </c>
-      <c r="C71" s="214">
+      <c r="C71" s="213">
         <v>0.1</v>
       </c>
-      <c r="D71" s="214"/>
-      <c r="E71" s="242"/>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B73" s="138" t="s">
+      <c r="D71" s="213"/>
+      <c r="E71" s="246"/>
+    </row>
+    <row r="73" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B73" s="137" t="s">
         <v>231</v>
       </c>
-      <c r="C73" s="202">
+      <c r="C73" s="201">
         <f>C64*C65+C70*C71+C55*(1-C65-C71)</f>
         <v>17.387636197185707</v>
       </c>
@@ -13623,7 +13647,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="75" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B75" s="39" t="s">
         <v>247</v>
       </c>
@@ -13633,36 +13657,36 @@
       <c r="F75" s="40"/>
       <c r="G75" s="40"/>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B76" s="151" t="s">
+    <row r="76" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B76" s="150" t="s">
         <v>242</v>
       </c>
-      <c r="E76" s="151" t="s">
+      <c r="E76" s="150" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B77" s="138" t="s">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B77" s="137" t="s">
         <v>260</v>
       </c>
-      <c r="C77" s="217">
+      <c r="C77" s="216">
         <f>Thesis!C68</f>
         <v>0.2</v>
       </c>
-      <c r="D77" s="178"/>
-      <c r="E77" s="138" t="s">
+      <c r="D77" s="177"/>
+      <c r="E77" s="137" t="s">
         <v>243</v>
       </c>
-      <c r="F77" s="215">
+      <c r="F77" s="214">
         <f>Thesis!C67</f>
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B78" s="138" t="s">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B78" s="137" t="s">
         <v>220</v>
       </c>
-      <c r="C78" s="232">
+      <c r="C78" s="231">
         <f>Normalized_FCF!C108</f>
         <v>1.3599999999999999</v>
       </c>
@@ -13670,41 +13694,41 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E78" s="138" t="s">
+      <c r="E78" s="137" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.15">
-      <c r="B80" s="151" t="s">
+    <row r="80" spans="2:7" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B80" s="150" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B81" s="138" t="s">
+    <row r="81" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B81" s="137" t="s">
         <v>232</v>
       </c>
-      <c r="C81" s="160">
+      <c r="C81" s="159">
         <f>PV(C77, F77, -C78, 0)</f>
         <v>2.8648148148148143</v>
       </c>
-      <c r="D81" s="160"/>
-      <c r="E81" s="138"/>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B82" s="138" t="s">
+      <c r="D81" s="159"/>
+      <c r="E81" s="137"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B82" s="137" t="s">
         <v>234</v>
       </c>
-      <c r="C82" s="160">
+      <c r="C82" s="159">
         <f>C73/(1+C77)^F77</f>
         <v>10.06228946596395</v>
       </c>
-      <c r="D82" s="160"/>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B83" s="153" t="s">
+      <c r="D82" s="159"/>
+    </row>
+    <row r="83" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B83" s="152" t="s">
         <v>208</v>
       </c>
-      <c r="C83" s="154">
+      <c r="C83" s="153">
         <f>C81+C82</f>
         <v>12.927104280778764</v>
       </c>
@@ -13712,35 +13736,35 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E83" s="218" t="s">
+      <c r="E83" s="217" t="s">
         <v>246</v>
       </c>
-      <c r="F83" s="219">
+      <c r="F83" s="218">
         <f>(C83/C73-1)</f>
         <v>-0.25653469314758881</v>
       </c>
-      <c r="I83" s="164" t="s">
+      <c r="I83" s="163" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="D86" s="191"/>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="B87" s="124" t="s">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="D86" s="190"/>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B87" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="C87" s="125" t="s">
+      <c r="C87" s="124" t="s">
         <v>49</v>
       </c>
-      <c r="D87" s="125" t="s">
+      <c r="D87" s="124" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="119" t="s">
+      <c r="E87" s="118" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B88" s="9" t="s">
         <v>47</v>
       </c>
@@ -13756,7 +13780,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B89" s="9" t="s">
         <v>48</v>
       </c>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8C471E-87E8-4BCC-8CA4-94CD81CC95A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A306730-E657-4C0C-9E0F-3C25E8142872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -24,10 +24,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$7</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$9</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$8</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="379">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1932,12 +1932,20 @@
     <t>1x for stable businesses, 2x for for volatile ones</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>Operating Expenses Multiple (months)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Operating Cash Multiple (months)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
@@ -1954,8 +1962,9 @@
     <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
     <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
     <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="192" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="47" x14ac:knownFonts="1">
+  <fonts count="48" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2308,6 +2317,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2514,7 +2531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="317">
+  <cellXfs count="323">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3078,7 +3095,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3155,20 +3171,24 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3179,7 +3199,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="192" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3231,8 +3258,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0000FF"/>
       <color rgb="FFFF0000"/>
-      <color rgb="FF0000FF"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -3474,10 +3501,10 @@
         <v>45730</v>
       </c>
       <c r="D1" s="53"/>
-      <c r="E1" s="304" t="s">
+      <c r="E1" s="303" t="s">
         <v>365</v>
       </c>
-      <c r="F1" s="305" t="s">
+      <c r="F1" s="304" t="s">
         <v>367</v>
       </c>
     </row>
@@ -3539,90 +3566,90 @@
       <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
+      <c r="B8" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C8" s="297">
+        <v>6</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="51">
-        <v>1</v>
-      </c>
-      <c r="D9" s="49" t="str">
-        <f>IF(C8=D6,D6,C8&amp;"/"&amp;D6)</f>
+      <c r="B9" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" s="34">
+        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
+        <v>45716</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="36">
+        <f>Thesis!C6*Thesis!C7/1000000</f>
+        <v>9029.7187329999997</v>
+      </c>
+      <c r="D10" s="33" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="49"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="C10" s="298">
-        <v>6</v>
-      </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="49"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="34">
-        <f>EOMONTH(EDATE(BS!C1,C10+2),0)</f>
-        <v>45716</v>
-      </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="36">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>9029.7187329999997</v>
-      </c>
-      <c r="D12" s="33" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="308" t="s">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="310" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="308"/>
-      <c r="D14" s="308"/>
-      <c r="E14" s="308"/>
-      <c r="F14" s="308"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="46" t="s">
+      <c r="C12" s="310"/>
+      <c r="D12" s="310"/>
+      <c r="E12" s="310"/>
+      <c r="F12" s="310"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="46" t="s">
         <v>352</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="2" t="s">
+      <c r="C14" s="47"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C17" s="33" t="str">
+      <c r="C15" s="33" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Low Growth Asset Play</v>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="33"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="51">
+        <v>1</v>
+      </c>
+      <c r="D17" s="33" t="str">
+        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
+        <v>HKD</v>
       </c>
       <c r="E17" s="5"/>
     </row>
@@ -3650,12 +3677,12 @@
       </c>
       <c r="C20" s="267">
         <f>C121</f>
-        <v>13.853214052679736</v>
+        <v>13.538366385360966</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="E20" s="300">
+      <c r="E20" s="299">
         <f>Scenarios!C76</f>
         <v>3</v>
       </c>
@@ -3664,9 +3691,9 @@
       <c r="B21" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C21" s="299">
+      <c r="C21" s="298">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15562262672344218</v>
+        <v>0.14601322135335382</v>
       </c>
       <c r="D21" s="5" t="str">
         <f>Market_currency</f>
@@ -3689,22 +3716,22 @@
       <c r="F23" s="37"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="308" t="s">
+      <c r="B25" s="310" t="s">
         <v>244</v>
       </c>
-      <c r="C25" s="308"/>
-      <c r="D25" s="308"/>
-      <c r="E25" s="308"/>
-      <c r="F25" s="308"/>
+      <c r="C25" s="310"/>
+      <c r="D25" s="310"/>
+      <c r="E25" s="310"/>
+      <c r="F25" s="310"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="312" t="s">
+      <c r="B26" s="311" t="s">
         <v>265</v>
       </c>
-      <c r="C26" s="312"/>
-      <c r="D26" s="312"/>
-      <c r="E26" s="312"/>
-      <c r="F26" s="312"/>
+      <c r="C26" s="311"/>
+      <c r="D26" s="311"/>
+      <c r="E26" s="311"/>
+      <c r="F26" s="311"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="248" t="s">
@@ -3716,13 +3743,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="310" t="s">
+      <c r="B29" s="309" t="s">
         <v>246</v>
       </c>
-      <c r="C29" s="310"/>
-      <c r="D29" s="310"/>
-      <c r="E29" s="310"/>
-      <c r="F29" s="310"/>
+      <c r="C29" s="309"/>
+      <c r="D29" s="309"/>
+      <c r="E29" s="309"/>
+      <c r="F29" s="309"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="48" t="s">
@@ -3742,13 +3769,13 @@
       <c r="C31" s="83"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="310" t="s">
+      <c r="B32" s="309" t="s">
         <v>248</v>
       </c>
-      <c r="C32" s="310"/>
-      <c r="D32" s="310"/>
-      <c r="E32" s="310"/>
-      <c r="F32" s="310"/>
+      <c r="C32" s="309"/>
+      <c r="D32" s="309"/>
+      <c r="E32" s="309"/>
+      <c r="F32" s="309"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="48" t="s">
@@ -3777,13 +3804,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="310" t="s">
+      <c r="B36" s="309" t="s">
         <v>251</v>
       </c>
-      <c r="C36" s="310"/>
-      <c r="D36" s="310"/>
-      <c r="E36" s="310"/>
-      <c r="F36" s="310"/>
+      <c r="C36" s="309"/>
+      <c r="D36" s="309"/>
+      <c r="E36" s="309"/>
+      <c r="F36" s="309"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="48" t="s">
@@ -3799,13 +3826,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="310" t="s">
+      <c r="B39" s="309" t="s">
         <v>255</v>
       </c>
-      <c r="C39" s="310"/>
-      <c r="D39" s="310"/>
-      <c r="E39" s="310"/>
-      <c r="F39" s="310"/>
+      <c r="C39" s="309"/>
+      <c r="D39" s="309"/>
+      <c r="E39" s="309"/>
+      <c r="F39" s="309"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="48" t="s">
@@ -3813,7 +3840,7 @@
       </c>
       <c r="C40" s="199">
         <f>Normalized_FCF!C12</f>
-        <v>-30619.000000000007</v>
+        <v>-30619</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -3839,13 +3866,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="310" t="s">
+      <c r="B45" s="309" t="s">
         <v>256</v>
       </c>
-      <c r="C45" s="310"/>
-      <c r="D45" s="310"/>
-      <c r="E45" s="310"/>
-      <c r="F45" s="310"/>
+      <c r="C45" s="309"/>
+      <c r="D45" s="309"/>
+      <c r="E45" s="309"/>
+      <c r="F45" s="309"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="48" t="s">
@@ -3861,13 +3888,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="310" t="s">
+      <c r="B48" s="309" t="s">
         <v>259</v>
       </c>
-      <c r="C48" s="311"/>
-      <c r="D48" s="311"/>
-      <c r="E48" s="311"/>
-      <c r="F48" s="311"/>
+      <c r="C48" s="313"/>
+      <c r="D48" s="313"/>
+      <c r="E48" s="313"/>
+      <c r="F48" s="313"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="48" t="s">
@@ -3896,13 +3923,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="308" t="s">
+      <c r="B52" s="310" t="s">
         <v>281</v>
       </c>
-      <c r="C52" s="308"/>
-      <c r="D52" s="308"/>
-      <c r="E52" s="308"/>
-      <c r="F52" s="308"/>
+      <c r="C52" s="310"/>
+      <c r="D52" s="310"/>
+      <c r="E52" s="310"/>
+      <c r="F52" s="310"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="48" t="s">
@@ -3963,22 +3990,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="310" t="s">
+      <c r="B60" s="309" t="s">
         <v>318</v>
       </c>
-      <c r="C60" s="310"/>
-      <c r="D60" s="310"/>
-      <c r="E60" s="310"/>
-      <c r="F60" s="310"/>
+      <c r="C60" s="309"/>
+      <c r="D60" s="309"/>
+      <c r="E60" s="309"/>
+      <c r="F60" s="309"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="312" t="s">
+      <c r="B61" s="311" t="s">
         <v>272</v>
       </c>
-      <c r="C61" s="312"/>
-      <c r="D61" s="312"/>
-      <c r="E61" s="312"/>
-      <c r="F61" s="312"/>
+      <c r="C61" s="311"/>
+      <c r="D61" s="311"/>
+      <c r="E61" s="311"/>
+      <c r="F61" s="311"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="248" t="s">
@@ -3989,7 +4016,7 @@
       <c r="B64" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C64" s="281">
+      <c r="C64" s="132">
         <v>0.08</v>
       </c>
     </row>
@@ -3997,11 +4024,11 @@
       <c r="B65" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C65" s="281">
+      <c r="C65" s="280">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D65" s="307" t="s">
+      <c r="D65" s="306" t="s">
         <v>322</v>
       </c>
     </row>
@@ -4009,11 +4036,11 @@
       <c r="B66" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C66" s="281">
+      <c r="C66" s="280">
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D66" s="307" t="s">
+      <c r="D66" s="306" t="s">
         <v>375</v>
       </c>
     </row>
@@ -4021,7 +4048,7 @@
       <c r="B67" s="89" t="s">
         <v>266</v>
       </c>
-      <c r="C67" s="271">
+      <c r="C67" s="280">
         <f>SUM(C64:C66)</f>
         <v>0.09</v>
       </c>
@@ -4030,28 +4057,28 @@
       <c r="C68" s="132"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="308" t="s">
+      <c r="B69" s="310" t="s">
         <v>326</v>
       </c>
-      <c r="C69" s="308"/>
-      <c r="D69" s="308"/>
-      <c r="E69" s="308"/>
-      <c r="F69" s="308"/>
+      <c r="C69" s="310"/>
+      <c r="D69" s="310"/>
+      <c r="E69" s="310"/>
+      <c r="F69" s="310"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="308" t="s">
+      <c r="B70" s="310" t="s">
         <v>271</v>
       </c>
-      <c r="C70" s="308"/>
-      <c r="D70" s="308"/>
-      <c r="E70" s="308"/>
-      <c r="F70" s="308"/>
+      <c r="C70" s="310"/>
+      <c r="D70" s="310"/>
+      <c r="E70" s="310"/>
+      <c r="F70" s="310"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="C71" s="281">
+      <c r="C71" s="280">
         <v>0</v>
       </c>
     </row>
@@ -4082,13 +4109,13 @@
       <c r="A76" s="247"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="308" t="s">
+      <c r="B77" s="310" t="s">
         <v>274</v>
       </c>
-      <c r="C77" s="308"/>
-      <c r="D77" s="308"/>
-      <c r="E77" s="308"/>
-      <c r="F77" s="308"/>
+      <c r="C77" s="310"/>
+      <c r="D77" s="310"/>
+      <c r="E77" s="310"/>
+      <c r="F77" s="310"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4106,7 +4133,7 @@
       </c>
       <c r="C81" s="199">
         <f>Valuation_Model!C7</f>
-        <v>1715502</v>
+        <v>2034922</v>
       </c>
       <c r="D81" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4119,7 +4146,7 @@
       </c>
       <c r="C82" s="263">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
-        <v>2.9219537773170638</v>
+        <v>3.4660105464438944</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4202,13 +4229,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="308" t="s">
+      <c r="B93" s="310" t="s">
         <v>280</v>
       </c>
-      <c r="C93" s="308"/>
-      <c r="D93" s="308"/>
-      <c r="E93" s="308"/>
-      <c r="F93" s="308"/>
+      <c r="C93" s="310"/>
+      <c r="D93" s="310"/>
+      <c r="E93" s="310"/>
+      <c r="F93" s="310"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="48" t="s">
@@ -4216,7 +4243,7 @@
       </c>
       <c r="C95" s="263">
         <f>Valuation_Model!C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4234,49 +4261,49 @@
       <c r="F97" s="37"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="308" t="s">
+      <c r="B99" s="310" t="s">
         <v>306</v>
       </c>
-      <c r="C99" s="308"/>
-      <c r="D99" s="308"/>
-      <c r="E99" s="308"/>
-      <c r="F99" s="308"/>
+      <c r="C99" s="310"/>
+      <c r="D99" s="310"/>
+      <c r="E99" s="310"/>
+      <c r="F99" s="310"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B101" s="277" t="s">
+      <c r="B101" s="276" t="s">
         <v>129</v>
       </c>
-      <c r="C101" s="277" t="s">
+      <c r="C101" s="276" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="277" t="s">
+      <c r="D101" s="276" t="s">
         <v>124</v>
       </c>
-      <c r="E101" s="277" t="s">
+      <c r="E101" s="276" t="s">
         <v>283</v>
       </c>
-      <c r="F101" s="277" t="s">
+      <c r="F101" s="276" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B102" s="272" t="str">
+      <c r="B102" s="271" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C102" s="273">
+      <c r="C102" s="272">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D102" s="274">
+      <c r="D102" s="273">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E102" s="275" t="str">
+      <c r="E102" s="274" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>24.61 HKD</v>
-      </c>
-      <c r="F102" s="276">
+        <v>24.07 HKD</v>
+      </c>
+      <c r="F102" s="275">
         <f>Valuation_Model!F74</f>
         <v>0.02</v>
       </c>
@@ -4296,7 +4323,7 @@
       </c>
       <c r="E103" s="260" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>20.21 HKD</v>
+        <v>19.66 HKD</v>
       </c>
       <c r="F103" s="261">
         <f>Valuation_Model!F75</f>
@@ -4318,7 +4345,7 @@
       </c>
       <c r="E104" s="260" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>19.2 HKD</v>
+        <v>18.66 HKD</v>
       </c>
       <c r="F104" s="261">
         <f>Valuation_Model!F76</f>
@@ -4340,7 +4367,7 @@
       </c>
       <c r="E105" s="260" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>17.02 HKD</v>
+        <v>16.48 HKD</v>
       </c>
       <c r="F105" s="261">
         <f>Valuation_Model!F77</f>
@@ -4362,7 +4389,7 @@
       </c>
       <c r="E106" s="260" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>14.4 HKD</v>
+        <v>13.86 HKD</v>
       </c>
       <c r="F106" s="261">
         <f>Valuation_Model!F78</f>
@@ -4375,7 +4402,7 @@
       </c>
       <c r="C108" s="256">
         <f>Scenarios!C60</f>
-        <v>18.987953883030585</v>
+        <v>18.443897113903752</v>
       </c>
       <c r="D108" s="251" t="str">
         <f>Market_currency</f>
@@ -4393,13 +4420,13 @@
       <c r="F110" s="37"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="309" t="s">
+      <c r="B112" s="312" t="s">
         <v>288</v>
       </c>
-      <c r="C112" s="309"/>
-      <c r="D112" s="309"/>
-      <c r="E112" s="309"/>
-      <c r="F112" s="309"/>
+      <c r="C112" s="312"/>
+      <c r="D112" s="312"/>
+      <c r="E112" s="312"/>
+      <c r="F112" s="312"/>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B113" s="248" t="s">
@@ -4459,7 +4486,7 @@
       </c>
       <c r="C120" s="255">
         <f>Scenarios!C82</f>
-        <v>10.988399237864922</v>
+        <v>10.673551570546152</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.35">
@@ -4468,7 +4495,7 @@
       </c>
       <c r="C121" s="254">
         <f>Scenarios!C83</f>
-        <v>13.853214052679736</v>
+        <v>13.538366385360966</v>
       </c>
       <c r="D121" s="48" t="str">
         <f>Reporting_currency</f>
@@ -4481,17 +4508,11 @@
       </c>
       <c r="C122" s="165">
         <f>Scenarios!F83</f>
-        <v>-0.27042091327911499</v>
+        <v>-0.26597040193012134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4504,10 +4525,16 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C8" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
@@ -4538,7 +4565,7 @@
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B1" s="99" t="str">
-        <f>Thesis!C8</f>
+        <f>Thesis!C16</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="114">
@@ -6849,7 +6876,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H87"/>
+  <dimension ref="B1:H89"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -7390,7 +7417,7 @@
       </c>
       <c r="G31" s="226">
         <f>C31+C40</f>
-        <v>1715502</v>
+        <v>2034922</v>
       </c>
       <c r="H31" s="223"/>
     </row>
@@ -7529,7 +7556,8 @@
         <v>217</v>
       </c>
       <c r="C40" s="90">
-        <v>0</v>
+        <f>SUM(C36:C39)</f>
+        <v>319420</v>
       </c>
       <c r="F40" s="234" t="s">
         <v>150</v>
@@ -7549,7 +7577,7 @@
       </c>
       <c r="C41" s="22">
         <f>C42-C40</f>
-        <v>473357</v>
+        <v>153937</v>
       </c>
       <c r="F41" s="225" t="s">
         <v>203</v>
@@ -7574,11 +7602,11 @@
         <v>204</v>
       </c>
       <c r="G42" s="237">
-        <f>C80</f>
+        <f>C82</f>
         <v>925726</v>
       </c>
       <c r="H42" s="238">
-        <f>D80</f>
+        <f>D82</f>
         <v>92572.6</v>
       </c>
     </row>
@@ -7597,13 +7625,13 @@
       <c r="B45" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="C45" s="278" t="s">
+      <c r="C45" s="277" t="s">
         <v>148</v>
       </c>
       <c r="D45" s="217" t="s">
         <v>302</v>
       </c>
-      <c r="F45" s="316" t="s">
+      <c r="F45" s="307" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7619,7 +7647,7 @@
         <f>H29</f>
         <v>3446088.45</v>
       </c>
-      <c r="F46" s="303"/>
+      <c r="F46" s="302"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7634,23 +7662,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>5.8696003638854428</v>
       </c>
-      <c r="F47" s="303"/>
+      <c r="F47" s="302"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="303"/>
+      <c r="F48" s="302"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="169" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="279" t="s">
+      <c r="C49" s="278" t="s">
         <v>62</v>
       </c>
       <c r="D49" s="232" t="s">
         <v>106</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="303"/>
+      <c r="F49" s="302"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7658,13 +7686,13 @@
       </c>
       <c r="C50" s="105">
         <f>G31/Normalized_FCF!C8</f>
-        <v>1.2266425127543255</v>
+        <v>1.4550387206421544</v>
       </c>
       <c r="D50" s="105">
         <f>G31/Normalized_FCF!G8</f>
-        <v>0.91407005535565566</v>
-      </c>
-      <c r="F50" s="303"/>
+        <v>1.0842664509772892</v>
+      </c>
+      <c r="F50" s="302"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
@@ -7675,22 +7703,22 @@
         <f>G29/G32</f>
         <v>0.76485172952944758</v>
       </c>
-      <c r="F51" s="303"/>
+      <c r="F51" s="302"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="303"/>
+      <c r="F52" s="302"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="169" t="s">
         <v>154</v>
       </c>
-      <c r="C53" s="279" t="s">
+      <c r="C53" s="278" t="s">
         <v>62</v>
       </c>
       <c r="D53" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="F53" s="303"/>
+      <c r="F53" s="302"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7704,7 +7732,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.13472770763839131</v>
       </c>
-      <c r="F54" s="303"/>
+      <c r="F54" s="302"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7718,22 +7746,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>2.1854036242131779E-4</v>
       </c>
-      <c r="F55" s="303"/>
+      <c r="F55" s="302"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="303"/>
+      <c r="F56" s="302"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="169" t="s">
         <v>187</v>
       </c>
-      <c r="C57" s="279" t="s">
+      <c r="C57" s="278" t="s">
         <v>62</v>
       </c>
       <c r="D57" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="F57" s="303"/>
+      <c r="F57" s="302"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7755,22 +7783,22 @@
         <f>G39/G32</f>
         <v>0.14965749507062509</v>
       </c>
-      <c r="F59" s="303"/>
+      <c r="F59" s="302"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="303"/>
+      <c r="F60" s="302"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="169" t="s">
         <v>305</v>
       </c>
-      <c r="C61" s="279" t="s">
+      <c r="C61" s="278" t="s">
         <v>149</v>
       </c>
       <c r="D61" s="232" t="s">
         <v>106</v>
       </c>
-      <c r="F61" s="303"/>
+      <c r="F61" s="302"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7784,7 +7812,7 @@
         <f>G28/G29</f>
         <v>-2.0915594459950692E-3</v>
       </c>
-      <c r="F62" s="303" t="s">
+      <c r="F62" s="302" t="s">
         <v>303</v>
       </c>
     </row>
@@ -7803,13 +7831,13 @@
       <c r="B65" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="C65" s="278" t="s">
+      <c r="C65" s="277" t="s">
         <v>148</v>
       </c>
       <c r="D65" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="F65" s="316" t="s">
+      <c r="F65" s="307" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7822,7 +7850,7 @@
         <v>1998219</v>
       </c>
       <c r="D66" s="199">
-        <f>C66+D74</f>
+        <f>C66+D75</f>
         <v>1116785.5502773244</v>
       </c>
       <c r="F66" s="5" t="s">
@@ -7837,7 +7865,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="303"/>
+      <c r="F67" s="302"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="115" t="s">
@@ -7847,7 +7875,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="303"/>
+      <c r="F68" s="302"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="115" t="s">
@@ -7857,7 +7885,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="303"/>
+      <c r="F69" s="302"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="89" t="s">
@@ -7867,22 +7895,22 @@
         <f>SUM(C66:C69)</f>
         <v>1998219</v>
       </c>
-      <c r="F70" s="303"/>
+      <c r="F70" s="302"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="303"/>
+      <c r="F71" s="302"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="306" t="s">
+      <c r="B72" s="305" t="s">
         <v>372</v>
       </c>
-      <c r="C72" s="278" t="s">
+      <c r="C72" s="277" t="s">
         <v>106</v>
       </c>
       <c r="D72" s="217" t="s">
         <v>62</v>
       </c>
-      <c r="F72" s="303"/>
+      <c r="F72" s="302"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="115" t="s">
@@ -7896,180 +7924,202 @@
         <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
         <v>-881433.44972267561</v>
       </c>
-      <c r="F73" s="303" t="s">
+      <c r="F73" s="302" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="89" t="s">
+      <c r="B74" s="308" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="317">
+        <f>-$C$66/C73</f>
+        <v>1.7829051253573729</v>
+      </c>
+      <c r="D74" s="317">
+        <f>-$C$66/D73</f>
+        <v>2.2670106298197523</v>
+      </c>
+      <c r="F74" s="302"/>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="89" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="198">
-        <f>C73*1</f>
-        <v>-1120765.75</v>
-      </c>
-      <c r="D74" s="198">
-        <f>D73*1</f>
+      <c r="C75" s="318"/>
+      <c r="D75" s="319">
+        <f>MIN(D73*D76,-G5)</f>
         <v>-881433.44972267561</v>
       </c>
-      <c r="F74" s="303" t="s">
+      <c r="F75" s="302" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F75" s="303"/>
-    </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="16" t="s">
+      <c r="B76" s="320" t="s">
+        <v>378</v>
+      </c>
+      <c r="C76" s="321"/>
+      <c r="D76" s="322">
+        <f>IF(D74&lt;=3,1,IF(D74&gt;10,5,2))</f>
+        <v>1</v>
+      </c>
+      <c r="F76" s="302"/>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F77" s="302"/>
+    </row>
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C76" s="278" t="s">
+      <c r="C78" s="277" t="s">
         <v>148</v>
       </c>
-      <c r="D76" s="218" t="s">
+      <c r="D78" s="218" t="s">
         <v>37</v>
       </c>
-      <c r="F76" s="303"/>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="115" t="s">
-        <v>190</v>
-      </c>
-      <c r="C77" s="21">
-        <f>G7+G17</f>
-        <v>0</v>
-      </c>
-      <c r="D77" s="199">
-        <f>G7*H7+G17*H17</f>
-        <v>0</v>
-      </c>
-      <c r="F77" s="303"/>
-    </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="115" t="s">
-        <v>194</v>
-      </c>
-      <c r="C78" s="21">
-        <f>G19</f>
-        <v>0</v>
-      </c>
-      <c r="D78" s="199">
-        <f>G19*H19</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="303"/>
+      <c r="F78" s="302"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="115" t="s">
+        <v>190</v>
+      </c>
+      <c r="C79" s="21">
+        <f>G7+G17</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="199">
+        <f>G7*H7+G17*H17</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="302"/>
+    </row>
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B80" s="115" t="s">
+        <v>194</v>
+      </c>
+      <c r="C80" s="21">
+        <f>G19</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="199">
+        <f>G19*H19</f>
+        <v>0</v>
+      </c>
+      <c r="F80" s="302"/>
+    </row>
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B81" s="115" t="s">
         <v>192</v>
       </c>
-      <c r="C79" s="21">
+      <c r="C81" s="21">
         <f>G9+G21</f>
         <v>925726</v>
       </c>
-      <c r="D79" s="199">
+      <c r="D81" s="199">
         <f>G9*H9+G21*H21</f>
         <v>92572.6</v>
       </c>
-      <c r="F79" s="303"/>
-    </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="89" t="s">
+      <c r="F81" s="302"/>
+    </row>
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B82" s="89" t="s">
         <v>201</v>
       </c>
-      <c r="C80" s="90">
-        <f>SUM(C77:C79)</f>
+      <c r="C82" s="90">
+        <f>SUM(C79:C81)</f>
         <v>925726</v>
       </c>
-      <c r="D80" s="90">
-        <f>SUM(D77:D79)</f>
+      <c r="D82" s="90">
+        <f>SUM(D79:D81)</f>
         <v>92572.6</v>
       </c>
-      <c r="F80" s="303"/>
-    </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="88" t="s">
+      <c r="F82" s="302"/>
+    </row>
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B84" s="88" t="s">
         <v>332</v>
       </c>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="38"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-    </row>
-    <row r="83" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="16" t="s">
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="38"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="38"/>
+      <c r="H84" s="38"/>
+    </row>
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="D83" s="288" t="s">
+      <c r="D85" s="287" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="285" t="s">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B86" s="284" t="s">
         <v>330</v>
       </c>
-      <c r="C84" s="199">
+      <c r="C86" s="199">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1715502</v>
-      </c>
-      <c r="D84" s="263">
-        <f>C84*$H$1/Common_Shares</f>
-        <v>-2.9219537773170638</v>
-      </c>
-      <c r="E84" s="287" t="str">
+        <v>-2034922</v>
+      </c>
+      <c r="D86" s="263">
+        <f>C86*$H$1/Common_Shares</f>
+        <v>-3.4660105464438944</v>
+      </c>
+      <c r="E86" s="286" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="285" t="s">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B87" s="284" t="s">
         <v>331</v>
       </c>
-      <c r="C85" s="199">
+      <c r="C87" s="199">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>1116785.5502773244</v>
       </c>
-      <c r="D85" s="263">
-        <f>C85*$H$1/Common_Shares</f>
+      <c r="D87" s="263">
+        <f>C87*$H$1/Common_Shares</f>
         <v>1.9021812606956703</v>
       </c>
-      <c r="E85" s="287" t="str">
+      <c r="E87" s="286" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="286" t="s">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="285" t="s">
         <v>201</v>
       </c>
-      <c r="C86" s="199">
+      <c r="C88" s="199">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>92572.6</v>
       </c>
-      <c r="D86" s="263">
-        <f>C86*$H$1/Common_Shares</f>
+      <c r="D88" s="263">
+        <f>C88*$H$1/Common_Shares</f>
         <v>0.15767562978420405</v>
       </c>
-      <c r="E86" s="287" t="str">
+      <c r="E88" s="286" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="89" t="s">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B89" s="89" t="s">
         <v>335</v>
       </c>
-      <c r="C87" s="198">
-        <f>SUM(C84:C86)</f>
-        <v>-506143.84972267563</v>
-      </c>
-      <c r="D87" s="289">
-        <f>SUM(D84:D86)</f>
-        <v>-0.86209688683718955</v>
-      </c>
-      <c r="E87" s="287" t="str">
+      <c r="C89" s="198">
+        <f>SUM(C86:C88)</f>
+        <v>-825563.84972267563</v>
+      </c>
+      <c r="D89" s="288">
+        <f>SUM(D86:D88)</f>
+        <v>-1.40615365596402</v>
+      </c>
+      <c r="E89" s="286" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8103,7 +8153,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3"/>
       <c r="B1" s="99" t="str">
-        <f>Thesis!C8</f>
+        <f>Thesis!C16</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="54" t="s">
@@ -8646,7 +8696,7 @@
       </c>
       <c r="C12" s="205">
         <f>C49</f>
-        <v>-30619.000000000007</v>
+        <v>-30619</v>
       </c>
       <c r="E12" s="18"/>
       <c r="G12" s="205">
@@ -9910,7 +9960,7 @@
       </c>
       <c r="C47" s="205">
         <f>-BS!G31*Normalized_FCF!C53</f>
-        <v>-59596.000000000007</v>
+        <v>-59596</v>
       </c>
       <c r="G47" s="205">
         <f>Data!C51</f>
@@ -10018,7 +10068,7 @@
       </c>
       <c r="C49" s="195">
         <f>C47+C48</f>
-        <v>-30619.000000000007</v>
+        <v>-30619</v>
       </c>
       <c r="G49" s="195">
         <f t="shared" ref="G49:Q49" si="19">IF(G4="","",G47+G48)</f>
@@ -10111,14 +10161,14 @@
       </c>
       <c r="C53" s="91">
         <f>Normalized_FCF!G53</f>
-        <v>3.4739685526452319E-2</v>
+        <v>2.9286626219579916E-2</v>
       </c>
       <c r="E53" s="73" t="s">
         <v>86</v>
       </c>
       <c r="G53" s="24">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>3.4739685526452319E-2</v>
+        <v>2.9286626219579916E-2</v>
       </c>
       <c r="H53" s="181"/>
       <c r="I53" s="181"/>
@@ -10203,7 +10253,7 @@
         <v>179</v>
       </c>
       <c r="C57" s="205">
-        <f>BS!$C77*C65</f>
+        <f>BS!$C79*C65</f>
         <v>0</v>
       </c>
       <c r="G57" s="205">
@@ -10311,7 +10361,7 @@
         <v>170</v>
       </c>
       <c r="C59" s="205">
-        <f>BS!$C79*C67</f>
+        <f>BS!$C81*C67</f>
         <v>0</v>
       </c>
       <c r="G59" s="205">
@@ -10593,7 +10643,7 @@
         <v>0</v>
       </c>
       <c r="G67" s="24">
-        <f>IFERROR(G59/BS!$C$79,0)</f>
+        <f>IFERROR(G59/BS!$C$81,0)</f>
         <v>0</v>
       </c>
       <c r="H67" s="187"/>
@@ -11089,7 +11139,7 @@
       </c>
       <c r="C79" s="84">
         <f>ABS(C12/C$4)</f>
-        <v>2.5567530880774266E-3</v>
+        <v>2.5567530880774257E-3</v>
       </c>
       <c r="D79" s="28"/>
       <c r="E79" s="73"/>
@@ -13564,10 +13614,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="313" t="s">
+      <c r="E6" s="314" t="s">
         <v>268</v>
       </c>
-      <c r="F6" s="313"/>
+      <c r="F6" s="314"/>
       <c r="H6" s="131"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13576,14 +13626,14 @@
       </c>
       <c r="C7" s="240">
         <f>BS!G31</f>
-        <v>1715502</v>
+        <v>2034922</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="313"/>
-      <c r="F7" s="313"/>
+      <c r="E7" s="314"/>
+      <c r="F7" s="314"/>
       <c r="H7" s="131"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13598,8 +13648,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="313"/>
-      <c r="F8" s="313"/>
+      <c r="E8" s="314"/>
+      <c r="F8" s="314"/>
       <c r="H8" s="131"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13614,8 +13664,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="313"/>
-      <c r="F9" s="313"/>
+      <c r="E9" s="314"/>
+      <c r="F9" s="314"/>
       <c r="H9" s="131"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -13624,7 +13674,7 @@
       </c>
       <c r="C10" s="246">
         <f>C6-C7+C8+C9</f>
-        <v>10893152.844676431</v>
+        <v>10573732.844676431</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13641,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D9</f>
+        <f>Thesis!D17</f>
         <v>HKD</v>
       </c>
       <c r="H11" s="131"/>
@@ -13652,7 +13702,7 @@
       </c>
       <c r="C12" s="122">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13705,7 +13755,7 @@
       </c>
       <c r="C18" s="151">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>18.991218721398649</v>
+        <v>18.44716195227182</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14641,23 +14691,23 @@
       </c>
       <c r="B65" s="135">
         <f>C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="C65" s="135">
         <f>C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="D65" s="135">
         <f>C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="E65" s="152">
         <f>C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="F65" s="135">
         <f>C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="H65" s="131"/>
     </row>
@@ -14668,23 +14718,23 @@
       </c>
       <c r="B66" s="135">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>16.153330023684582</v>
+        <v>15.609273254557753</v>
       </c>
       <c r="C66" s="135">
         <f t="shared" si="4"/>
-        <v>17.020407869144801</v>
+        <v>16.476351100017972</v>
       </c>
       <c r="D66" s="135">
         <f t="shared" si="4"/>
-        <v>19.200628307862797</v>
+        <v>18.656571538735964</v>
       </c>
       <c r="E66" s="135">
         <f t="shared" si="4"/>
-        <v>20.209039117679229</v>
+        <v>19.664982348552396</v>
       </c>
       <c r="F66" s="135">
         <f t="shared" si="4"/>
-        <v>21.266165072953562</v>
+        <v>20.722108303826733</v>
       </c>
       <c r="H66" s="131"/>
     </row>
@@ -14695,23 +14745,23 @@
       </c>
       <c r="B67" s="135">
         <f t="shared" si="4"/>
-        <v>14.404837788606434</v>
+        <v>13.860781019479603</v>
       </c>
       <c r="C67" s="135">
         <f t="shared" si="4"/>
-        <v>15.788051232759992</v>
+        <v>15.243994463633163</v>
       </c>
       <c r="D67" s="135">
         <f t="shared" si="4"/>
-        <v>19.855017686388827</v>
+        <v>19.310960917261998</v>
       </c>
       <c r="E67" s="135">
         <f t="shared" si="4"/>
-        <v>22.058187046471733</v>
+        <v>21.514130277344904</v>
       </c>
       <c r="F67" s="135">
         <f t="shared" si="4"/>
-        <v>24.612070022963707</v>
+        <v>24.068013253836877</v>
       </c>
       <c r="H67" s="131"/>
     </row>
@@ -14722,23 +14772,23 @@
       </c>
       <c r="B68" s="135">
         <f t="shared" si="4"/>
-        <v>12.755351305649558</v>
+        <v>12.211294536522727</v>
       </c>
       <c r="C68" s="135">
         <f t="shared" si="4"/>
-        <v>14.551270774645824</v>
+        <v>14.007214005518993</v>
       </c>
       <c r="D68" s="135">
         <f t="shared" si="4"/>
-        <v>20.6293952554506</v>
+        <v>20.085338486323771</v>
       </c>
       <c r="E68" s="135">
         <f t="shared" si="4"/>
-        <v>24.4249405135686</v>
+        <v>23.880883744441768</v>
       </c>
       <c r="F68" s="135">
         <f t="shared" si="4"/>
-        <v>29.262570581362741</v>
+        <v>28.718513812235905</v>
       </c>
       <c r="H68" s="131"/>
     </row>
@@ -14749,23 +14799,23 @@
       </c>
       <c r="B69" s="135">
         <f t="shared" si="4"/>
-        <v>11.463513680849275</v>
+        <v>10.919456911722445</v>
       </c>
       <c r="C69" s="135">
         <f t="shared" si="4"/>
-        <v>13.528265851333558</v>
+        <v>12.984209082206728</v>
       </c>
       <c r="D69" s="135">
         <f t="shared" si="4"/>
-        <v>21.383171614638439</v>
+        <v>20.839114845511606</v>
       </c>
       <c r="E69" s="135">
         <f t="shared" si="4"/>
-        <v>26.929475480275087</v>
+        <v>26.385418711148258</v>
       </c>
       <c r="F69" s="135">
         <f t="shared" si="4"/>
-        <v>34.649460626220339</v>
+        <v>34.105403857093513</v>
       </c>
       <c r="H69" s="131"/>
     </row>
@@ -14776,23 +14826,23 @@
       </c>
       <c r="B70" s="135">
         <f t="shared" si="4"/>
-        <v>10.529761426813623</v>
+        <v>9.9857046576867923</v>
       </c>
       <c r="C70" s="135">
         <f t="shared" si="4"/>
-        <v>12.753154981180069</v>
+        <v>12.209098212053238</v>
       </c>
       <c r="D70" s="135">
         <f t="shared" si="4"/>
-        <v>22.052816079447464</v>
+        <v>21.508759310320631</v>
       </c>
       <c r="E70" s="135">
         <f t="shared" si="4"/>
-        <v>29.358799120093057</v>
+        <v>28.814742350966224</v>
       </c>
       <c r="F70" s="135">
         <f t="shared" si="4"/>
-        <v>40.408467220499077</v>
+        <v>39.864410451372244</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14802,23 +14852,23 @@
       </c>
       <c r="B71" s="135">
         <f t="shared" si="4"/>
-        <v>9.8825581728319776</v>
+        <v>9.3385014037051466</v>
       </c>
       <c r="C71" s="135">
         <f t="shared" si="4"/>
-        <v>12.193952008985075</v>
+        <v>11.649895239858246</v>
       </c>
       <c r="D71" s="135">
         <f t="shared" si="4"/>
-        <v>22.617017395652937</v>
+        <v>22.072960626526108</v>
       </c>
       <c r="E71" s="135">
         <f t="shared" si="4"/>
-        <v>31.602573014542486</v>
+        <v>31.058516245415653</v>
       </c>
       <c r="F71" s="135">
         <f t="shared" si="4"/>
-        <v>46.307633823574882</v>
+        <v>45.763577054448049</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14853,7 +14903,7 @@
       </c>
       <c r="E74" s="146">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>24.612070022963707</v>
+        <v>24.068013253836877</v>
       </c>
       <c r="F74" s="153">
         <f>Scenarios!C58</f>
@@ -14875,7 +14925,7 @@
       </c>
       <c r="E75" s="146">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>20.209039117679229</v>
+        <v>19.664982348552396</v>
       </c>
       <c r="F75" s="153">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -14898,7 +14948,7 @@
       </c>
       <c r="E76" s="146">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>19.200628307862797</v>
+        <v>18.656571538735964</v>
       </c>
       <c r="F76" s="153">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -14921,7 +14971,7 @@
       </c>
       <c r="E77" s="146">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>17.020407869144801</v>
+        <v>16.476351100017972</v>
       </c>
       <c r="F77" s="153">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -14944,7 +14994,7 @@
       </c>
       <c r="E78" s="146">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>14.404837788606434</v>
+        <v>13.860781019479603</v>
       </c>
       <c r="F78" s="153">
         <f>Scenarios!C52</f>
@@ -15031,19 +15081,19 @@
       <c r="D2" s="38"/>
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
-      <c r="H2" s="296" t="s">
+      <c r="H2" s="295" t="s">
         <v>340</v>
       </c>
-      <c r="I2" s="297"/>
+      <c r="I2" s="296"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="171" t="s">
         <v>160</v>
       </c>
-      <c r="H3" s="295">
-        <v>0</v>
-      </c>
-      <c r="I3" s="282">
+      <c r="H3" s="294">
+        <v>0</v>
+      </c>
+      <c r="I3" s="281">
         <f>-Market_Price</f>
         <v>-15.38</v>
       </c>
@@ -15060,19 +15110,19 @@
         <v>162</v>
       </c>
       <c r="F4" s="167"/>
-      <c r="H4" s="295">
+      <c r="H4" s="294">
         <v>1</v>
       </c>
-      <c r="I4" s="282">
+      <c r="I4" s="281">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>1.3599999999999999</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="H5" s="295">
+      <c r="H5" s="294">
         <v>2</v>
       </c>
-      <c r="I5" s="282">
+      <c r="I5" s="281">
         <f t="shared" si="0"/>
         <v>1.3599999999999999</v>
       </c>
@@ -15089,12 +15139,12 @@
         <v>313</v>
       </c>
       <c r="F6" s="110"/>
-      <c r="H6" s="295">
+      <c r="H6" s="294">
         <v>3</v>
       </c>
-      <c r="I6" s="282">
+      <c r="I6" s="281">
         <f t="shared" si="0"/>
-        <v>20.347953883030584</v>
+        <v>19.803897113903751</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15109,15 +15159,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="315" t="str">
+      <c r="E7" s="316" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="315"/>
-      <c r="H7" s="295">
+      <c r="F7" s="316"/>
+      <c r="H7" s="294">
         <v>4</v>
       </c>
-      <c r="I7" s="282" t="str">
+      <c r="I7" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15134,12 +15184,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="315"/>
-      <c r="F8" s="315"/>
-      <c r="H8" s="295">
+      <c r="E8" s="316"/>
+      <c r="F8" s="316"/>
+      <c r="H8" s="294">
         <v>5</v>
       </c>
-      <c r="I8" s="282" t="str">
+      <c r="I8" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15156,23 +15206,23 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="315"/>
-      <c r="F9" s="315"/>
-      <c r="H9" s="295">
+      <c r="E9" s="316"/>
+      <c r="F9" s="316"/>
+      <c r="H9" s="294">
         <v>6</v>
       </c>
-      <c r="I9" s="282" t="str">
+      <c r="I9" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="315"/>
-      <c r="F10" s="315"/>
-      <c r="H10" s="295">
+      <c r="E10" s="316"/>
+      <c r="F10" s="316"/>
+      <c r="H10" s="294">
         <v>7</v>
       </c>
-      <c r="I10" s="282" t="str">
+      <c r="I10" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15181,12 +15231,12 @@
       <c r="B11" s="171" t="s">
         <v>310</v>
       </c>
-      <c r="E11" s="315"/>
-      <c r="F11" s="315"/>
-      <c r="H11" s="295">
+      <c r="E11" s="316"/>
+      <c r="F11" s="316"/>
+      <c r="H11" s="294">
         <v>8</v>
       </c>
-      <c r="I11" s="282" t="str">
+      <c r="I11" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15200,12 +15250,12 @@
         <v>0.20035451325595277</v>
       </c>
       <c r="D12" s="170"/>
-      <c r="E12" s="315"/>
-      <c r="F12" s="315"/>
-      <c r="H12" s="295">
+      <c r="E12" s="316"/>
+      <c r="F12" s="316"/>
+      <c r="H12" s="294">
         <v>9</v>
       </c>
-      <c r="I12" s="282" t="str">
+      <c r="I12" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15218,12 +15268,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="315"/>
-      <c r="F13" s="315"/>
-      <c r="H13" s="295">
+      <c r="E13" s="316"/>
+      <c r="F13" s="316"/>
+      <c r="H13" s="294">
         <v>10</v>
       </c>
-      <c r="I13" s="282" t="str">
+      <c r="I13" s="281" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15236,8 +15286,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.3908780398304268E-2</v>
       </c>
-      <c r="E14" s="315"/>
-      <c r="F14" s="315"/>
+      <c r="E14" s="316"/>
+      <c r="F14" s="316"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="37" t="s">
@@ -15287,7 +15337,7 @@
       </c>
       <c r="C22" s="172">
         <f>Valuation_Model!C12</f>
-        <v>18.553921301982985</v>
+        <v>18.009864532856156</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15312,8 +15362,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="175"/>
-      <c r="E25" s="314"/>
-      <c r="F25" s="314"/>
+      <c r="E25" s="315"/>
+      <c r="F25" s="315"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="129" t="s">
@@ -15323,8 +15373,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="176"/>
-      <c r="E26" s="314"/>
-      <c r="F26" s="314"/>
+      <c r="E26" s="315"/>
+      <c r="F26" s="315"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="110" t="s">
@@ -15332,14 +15382,14 @@
       </c>
       <c r="C27" s="172">
         <f>Valuation_Model!E76</f>
-        <v>19.200628307862797</v>
+        <v>18.656571538735964</v>
       </c>
       <c r="D27" s="172" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="314"/>
-      <c r="F27" s="314"/>
+      <c r="E27" s="315"/>
+      <c r="F27" s="315"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="110" t="s">
@@ -15349,8 +15399,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="177"/>
-      <c r="E28" s="314"/>
-      <c r="F28" s="314"/>
+      <c r="E28" s="315"/>
+      <c r="F28" s="315"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="171" t="s">
@@ -15370,8 +15420,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="175"/>
-      <c r="E31" s="314"/>
-      <c r="F31" s="314"/>
+      <c r="E31" s="315"/>
+      <c r="F31" s="315"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="129" t="s">
@@ -15381,8 +15431,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="176"/>
-      <c r="E32" s="314"/>
-      <c r="F32" s="314"/>
+      <c r="E32" s="315"/>
+      <c r="F32" s="315"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="110" t="s">
@@ -15390,14 +15440,14 @@
       </c>
       <c r="C33" s="172">
         <f>Valuation_Model!E77</f>
-        <v>17.020407869144801</v>
+        <v>16.476351100017972</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="314"/>
-      <c r="F33" s="314"/>
+      <c r="E33" s="315"/>
+      <c r="F33" s="315"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="110" t="s">
@@ -15407,8 +15457,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="177"/>
-      <c r="E34" s="314"/>
-      <c r="F34" s="314"/>
+      <c r="E34" s="315"/>
+      <c r="F34" s="315"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="171" t="s">
@@ -15428,8 +15478,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="175"/>
-      <c r="E37" s="314"/>
-      <c r="F37" s="314"/>
+      <c r="E37" s="315"/>
+      <c r="F37" s="315"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="129" t="s">
@@ -15439,8 +15489,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="176"/>
-      <c r="E38" s="314"/>
-      <c r="F38" s="314"/>
+      <c r="E38" s="315"/>
+      <c r="F38" s="315"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="110" t="s">
@@ -15448,14 +15498,14 @@
       </c>
       <c r="C39" s="172">
         <f>Valuation_Model!E75</f>
-        <v>20.209039117679229</v>
+        <v>19.664982348552396</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="314"/>
-      <c r="F39" s="314"/>
+      <c r="E39" s="315"/>
+      <c r="F39" s="315"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="110" t="s">
@@ -15466,8 +15516,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="177"/>
-      <c r="E40" s="314"/>
-      <c r="F40" s="314"/>
+      <c r="E40" s="315"/>
+      <c r="F40" s="315"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="110" t="s">
@@ -15475,7 +15525,7 @@
       </c>
       <c r="C42" s="166">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>18.966266382082484</v>
+        <v>18.422209612955651</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15529,8 +15579,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="175"/>
-      <c r="E49" s="314"/>
-      <c r="F49" s="314"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="315"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="129" t="s">
@@ -15540,8 +15590,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="176"/>
-      <c r="E50" s="314"/>
-      <c r="F50" s="314"/>
+      <c r="E50" s="315"/>
+      <c r="F50" s="315"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="110" t="s">
@@ -15549,14 +15599,14 @@
       </c>
       <c r="C51" s="172">
         <f>Valuation_Model!E78</f>
-        <v>14.404837788606434</v>
+        <v>13.860781019479603</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="314"/>
-      <c r="F51" s="314"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="110" t="s">
@@ -15566,8 +15616,8 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="177"/>
-      <c r="E52" s="314"/>
-      <c r="F52" s="314"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="171" t="s">
@@ -15587,8 +15637,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="175"/>
-      <c r="E55" s="314"/>
-      <c r="F55" s="314"/>
+      <c r="E55" s="315"/>
+      <c r="F55" s="315"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="129" t="s">
@@ -15598,8 +15648,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="176"/>
-      <c r="E56" s="314"/>
-      <c r="F56" s="314"/>
+      <c r="E56" s="315"/>
+      <c r="F56" s="315"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="110" t="s">
@@ -15607,14 +15657,14 @@
       </c>
       <c r="C57" s="172">
         <f>Valuation_Model!E74</f>
-        <v>24.612070022963707</v>
+        <v>24.068013253836877</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="314"/>
-      <c r="F57" s="314"/>
+      <c r="E57" s="315"/>
+      <c r="F57" s="315"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="110" t="s">
@@ -15624,8 +15674,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="177"/>
-      <c r="E58" s="314"/>
-      <c r="F58" s="314"/>
+      <c r="E58" s="315"/>
+      <c r="F58" s="315"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="110" t="s">
@@ -15633,7 +15683,7 @@
       </c>
       <c r="C60" s="166">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>18.987953883030585</v>
+        <v>18.443897113903752</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -15642,7 +15692,7 @@
       <c r="E60" s="110" t="s">
         <v>341</v>
       </c>
-      <c r="F60" s="292">
+      <c r="F60" s="291">
         <v>3</v>
       </c>
     </row>
@@ -15659,7 +15709,7 @@
       <c r="B63" s="119" t="s">
         <v>349</v>
       </c>
-      <c r="E63" s="302" t="s">
+      <c r="E63" s="301" t="s">
         <v>359</v>
       </c>
     </row>
@@ -15671,7 +15721,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="161"/>
-      <c r="E64" s="301" t="s">
+      <c r="E64" s="300" t="s">
         <v>360</v>
       </c>
     </row>
@@ -15683,7 +15733,7 @@
         <v>6.9371044268871293E-3</v>
       </c>
       <c r="D65" s="162"/>
-      <c r="E65" s="301" t="s">
+      <c r="E65" s="300" t="s">
         <v>361</v>
       </c>
     </row>
@@ -15693,13 +15743,13 @@
       </c>
       <c r="C66" s="172">
         <f>Valuation_Model!C18</f>
-        <v>18.991218721398649</v>
+        <v>18.44716195227182</v>
       </c>
       <c r="D66" s="172" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="301" t="s">
+      <c r="E66" s="300" t="s">
         <v>362</v>
       </c>
     </row>
@@ -15707,7 +15757,7 @@
       <c r="B68" s="119" t="s">
         <v>336</v>
       </c>
-      <c r="E68" s="302" t="s">
+      <c r="E68" s="301" t="s">
         <v>363</v>
       </c>
     </row>
@@ -15715,7 +15765,7 @@
       <c r="B69" s="110" t="s">
         <v>350</v>
       </c>
-      <c r="C69" s="291" t="str">
+      <c r="C69" s="290" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -15725,11 +15775,11 @@
       <c r="B70" s="110" t="s">
         <v>338</v>
       </c>
-      <c r="C70" s="291" t="str">
+      <c r="C70" s="290" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="301" t="s">
+      <c r="E70" s="300" t="s">
         <v>339</v>
       </c>
     </row>
@@ -15737,23 +15787,23 @@
       <c r="B71" s="110" t="s">
         <v>337</v>
       </c>
-      <c r="C71" s="291" t="str">
+      <c r="C71" s="290" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="301"/>
+      <c r="E71" s="300"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="110" t="s">
         <v>328</v>
       </c>
-      <c r="C72" s="290" t="str">
+      <c r="C72" s="289" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="145" t="str">
-        <f>"Non-FCF Value is "&amp;ROUND(BS!D87/C60*100,0)&amp;"% of Expected Equity Value"</f>
-        <v>Non-FCF Value is -5% of Expected Equity Value</v>
+        <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of Expected Equity Value"</f>
+        <v>Non-FCF Value is -8% of Expected Equity Value</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -15773,10 +15823,10 @@
       <c r="F75" s="268"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B76" s="294" t="s">
+      <c r="B76" s="293" t="s">
         <v>342</v>
       </c>
-      <c r="C76" s="293">
+      <c r="C76" s="292">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -15829,7 +15879,7 @@
       </c>
       <c r="C82" s="127">
         <f>C60/(1+C80)^C76</f>
-        <v>10.988399237864922</v>
+        <v>10.673551570546152</v>
       </c>
       <c r="D82" s="127"/>
     </row>
@@ -15839,7 +15889,7 @@
       </c>
       <c r="C83" s="122">
         <f>C81+C82</f>
-        <v>13.853214052679736</v>
+        <v>13.538366385360966</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -15848,9 +15898,9 @@
       <c r="E83" s="157" t="s">
         <v>138</v>
       </c>
-      <c r="F83" s="280">
+      <c r="F83" s="279">
         <f>(C83/C60-1)</f>
-        <v>-0.27042091327911499</v>
+        <v>-0.26597040193012134</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
@@ -15865,7 +15915,7 @@
       <c r="B86" s="159" t="s">
         <v>345</v>
       </c>
-      <c r="C86" s="284">
+      <c r="C86" s="283">
         <f>Market_Price</f>
         <v>15.38</v>
       </c>
@@ -15878,9 +15928,9 @@
       <c r="B87" s="110" t="s">
         <v>343</v>
       </c>
-      <c r="C87" s="283">
+      <c r="C87" s="282">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15562262672344218</v>
+        <v>0.14601322135335382</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00613B6C-7BD7-4CB4-BC0C-8DE975331C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D834CD90-9932-4821-9D06-48F0032984E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -118,10 +118,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-  </si>
-  <si>
-    <t>Capitalization:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ST AR</t>
@@ -1532,10 +1528,6 @@
   </si>
   <si>
     <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Buy Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3328,20 +3320,20 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3647,22 +3639,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="293" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="294" t="s">
         <v>356</v>
-      </c>
-      <c r="F1" s="294" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="254" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3686,24 +3678,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="50">
         <v>15.38</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3719,7 +3711,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C8" s="287">
         <v>6</v>
@@ -3729,7 +3721,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3739,17 +3731,15 @@
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>25</v>
+      <c r="B10" s="4" t="str">
+        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
+        <v>Capitalization (HKD):</v>
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
         <v>9029.7187329999997</v>
       </c>
-      <c r="D10" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -3757,24 +3747,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="330" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="330"/>
-      <c r="D12" s="330"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="330"/>
+      <c r="B12" s="329" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="329"/>
+      <c r="D12" s="329"/>
+      <c r="E12" s="329"/>
+      <c r="F12" s="329"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3787,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3807,16 +3797,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C19" s="256">
         <v>0.2</v>
@@ -3824,15 +3814,16 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
-        <v>288</v>
+      <c r="B20" s="2" t="str">
+        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
+        <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
         <f>C123</f>
         <v>13.538366385360966</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E20" s="289">
         <f>Scenarios!C76</f>
@@ -3841,16 +3832,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
         <v>0.14601322135335382</v>
       </c>
-      <c r="D21" s="5" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3859,7 +3847,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="254" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3868,26 +3856,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="330" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="330"/>
-      <c r="D25" s="330"/>
-      <c r="E25" s="330"/>
-      <c r="F25" s="330"/>
+      <c r="B25" s="329" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="329"/>
+      <c r="D25" s="329"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="331" t="s">
-        <v>257</v>
-      </c>
-      <c r="C26" s="331"/>
-      <c r="D26" s="331"/>
-      <c r="E26" s="331"/>
-      <c r="F26" s="331"/>
+      <c r="B26" s="333" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="333"/>
+      <c r="D26" s="333"/>
+      <c r="E26" s="333"/>
+      <c r="F26" s="333"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3895,17 +3883,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="329" t="s">
-        <v>239</v>
-      </c>
-      <c r="C29" s="329"/>
-      <c r="D29" s="329"/>
-      <c r="E29" s="329"/>
-      <c r="F29" s="329"/>
+      <c r="B29" s="331" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="331"/>
+      <c r="D29" s="331"/>
+      <c r="E29" s="331"/>
+      <c r="F29" s="331"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="192">
         <f>Normalized_FCF!C8</f>
@@ -3921,17 +3909,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="329" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="329"/>
-      <c r="D32" s="329"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
+      <c r="B32" s="331" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" s="331"/>
+      <c r="D32" s="331"/>
+      <c r="E32" s="331"/>
+      <c r="F32" s="331"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C33" s="192">
         <f>Normalized_FCF!C9</f>
@@ -3944,7 +3932,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C34" s="192">
         <f>Normalized_FCF!C10</f>
@@ -3956,17 +3944,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="329" t="s">
-        <v>244</v>
-      </c>
-      <c r="C36" s="329"/>
-      <c r="D36" s="329"/>
-      <c r="E36" s="329"/>
-      <c r="F36" s="329"/>
+      <c r="B36" s="331" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="331"/>
+      <c r="D36" s="331"/>
+      <c r="E36" s="331"/>
+      <c r="F36" s="331"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C37" s="192">
         <f>Normalized_FCF!C11</f>
@@ -3978,17 +3966,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="329" t="s">
-        <v>248</v>
-      </c>
-      <c r="C39" s="329"/>
-      <c r="D39" s="329"/>
-      <c r="E39" s="329"/>
-      <c r="F39" s="329"/>
+      <c r="B39" s="331" t="s">
+        <v>247</v>
+      </c>
+      <c r="C39" s="331"/>
+      <c r="D39" s="331"/>
+      <c r="E39" s="331"/>
+      <c r="F39" s="331"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C40" s="192">
         <f>Normalized_FCF!C12</f>
@@ -4001,12 +3989,12 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C43" s="192">
         <f>Normalized_FCF!C15</f>
@@ -4018,17 +4006,17 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="329" t="s">
-        <v>249</v>
-      </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="329"/>
-      <c r="F45" s="329"/>
+      <c r="B45" s="331" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" s="331"/>
+      <c r="D45" s="331"/>
+      <c r="E45" s="331"/>
+      <c r="F45" s="331"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C46" s="192">
         <f>Normalized_FCF!C14</f>
@@ -4040,17 +4028,17 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="329" t="s">
-        <v>252</v>
-      </c>
-      <c r="C48" s="333"/>
-      <c r="D48" s="333"/>
-      <c r="E48" s="333"/>
-      <c r="F48" s="333"/>
+      <c r="B48" s="331" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" s="332"/>
+      <c r="D48" s="332"/>
+      <c r="E48" s="332"/>
+      <c r="F48" s="332"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C49" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4063,7 +4051,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C50" s="1">
         <f>Normalized_FCF!C18</f>
@@ -4075,17 +4063,17 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="330" t="s">
-        <v>273</v>
-      </c>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="330"/>
-      <c r="F52" s="330"/>
+      <c r="B52" s="329" t="s">
+        <v>272</v>
+      </c>
+      <c r="C52" s="329"/>
+      <c r="D52" s="329"/>
+      <c r="E52" s="329"/>
+      <c r="F52" s="329"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C53" s="192">
         <f>Normalized_FCF!G19</f>
@@ -4098,7 +4086,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B54" s="47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54" s="192">
         <f>Normalized_FCF!C19</f>
@@ -4111,7 +4099,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B55" s="261" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
@@ -4120,7 +4108,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="261" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
@@ -4129,7 +4117,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="254" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" s="36"/>
@@ -4142,31 +4130,31 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="329" t="s">
-        <v>309</v>
-      </c>
-      <c r="C60" s="329"/>
-      <c r="D60" s="329"/>
-      <c r="E60" s="329"/>
-      <c r="F60" s="329"/>
+      <c r="B60" s="331" t="s">
+        <v>307</v>
+      </c>
+      <c r="C60" s="331"/>
+      <c r="D60" s="331"/>
+      <c r="E60" s="331"/>
+      <c r="F60" s="331"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="331" t="s">
-        <v>264</v>
-      </c>
-      <c r="C61" s="331"/>
-      <c r="D61" s="331"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="331"/>
+      <c r="B61" s="333" t="s">
+        <v>263</v>
+      </c>
+      <c r="C61" s="333"/>
+      <c r="D61" s="333"/>
+      <c r="E61" s="333"/>
+      <c r="F61" s="333"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C64" s="322">
         <v>0.08</v>
@@ -4174,31 +4162,31 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C65" s="271">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="296" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C66" s="271">
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D66" s="296" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C67" s="271">
         <f>SUM(C64:C66)</f>
@@ -4209,26 +4197,26 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="330" t="s">
-        <v>317</v>
-      </c>
-      <c r="C69" s="330"/>
-      <c r="D69" s="330"/>
-      <c r="E69" s="330"/>
-      <c r="F69" s="330"/>
+      <c r="B69" s="329" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" s="329"/>
+      <c r="D69" s="329"/>
+      <c r="E69" s="329"/>
+      <c r="F69" s="329"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="330" t="s">
-        <v>263</v>
-      </c>
-      <c r="C70" s="330"/>
-      <c r="D70" s="330"/>
-      <c r="E70" s="330"/>
-      <c r="F70" s="330"/>
+      <c r="B70" s="329" t="s">
+        <v>262</v>
+      </c>
+      <c r="C70" s="329"/>
+      <c r="D70" s="329"/>
+      <c r="E70" s="329"/>
+      <c r="F70" s="329"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C71" s="271">
         <v>0</v>
@@ -4236,7 +4224,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="47" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4249,7 +4237,7 @@
     </row>
     <row r="75" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A75" s="254" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B75" s="36"/>
       <c r="C75" s="36"/>
@@ -4261,27 +4249,27 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="330" t="s">
-        <v>266</v>
-      </c>
-      <c r="C77" s="330"/>
-      <c r="D77" s="330"/>
-      <c r="E77" s="330"/>
-      <c r="F77" s="330"/>
+      <c r="B77" s="329" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77" s="329"/>
+      <c r="D77" s="329"/>
+      <c r="E77" s="329"/>
+      <c r="F77" s="329"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B80" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C81" s="192">
         <f>Valuation_Model!C7</f>
@@ -4294,7 +4282,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
@@ -4307,12 +4295,12 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C85" s="192">
         <f>BS!C66</f>
@@ -4325,7 +4313,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C86" s="192">
         <f>Valuation_Model!C8</f>
@@ -4338,7 +4326,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4351,12 +4339,12 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C90" s="192">
         <f>Valuation_Model!C9</f>
@@ -4369,7 +4357,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4381,17 +4369,17 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="330" t="s">
-        <v>272</v>
-      </c>
-      <c r="C93" s="330"/>
-      <c r="D93" s="330"/>
-      <c r="E93" s="330"/>
-      <c r="F93" s="330"/>
+      <c r="B93" s="329" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" s="329"/>
+      <c r="D93" s="329"/>
+      <c r="E93" s="329"/>
+      <c r="F93" s="329"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
@@ -4404,7 +4392,7 @@
     </row>
     <row r="97" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A97" s="254" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
@@ -4413,29 +4401,29 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="329" t="s">
-        <v>376</v>
-      </c>
-      <c r="C99" s="329"/>
-      <c r="D99" s="329"/>
-      <c r="E99" s="329"/>
-      <c r="F99" s="329"/>
+      <c r="B99" s="331" t="s">
+        <v>374</v>
+      </c>
+      <c r="C99" s="331"/>
+      <c r="D99" s="331"/>
+      <c r="E99" s="331"/>
+      <c r="F99" s="331"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="267" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D101" s="267" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E101" s="267" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F101" s="267" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4550,7 +4538,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B108" s="242" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
@@ -4563,7 +4551,7 @@
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="334" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C110" s="334"/>
       <c r="D110" s="334"/>
@@ -4572,7 +4560,7 @@
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B112" s="36"/>
       <c r="C112" s="36"/>
@@ -4581,22 +4569,22 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="332" t="s">
-        <v>280</v>
-      </c>
-      <c r="C114" s="332"/>
-      <c r="D114" s="332"/>
-      <c r="E114" s="332"/>
-      <c r="F114" s="332"/>
+      <c r="B114" s="330" t="s">
+        <v>279</v>
+      </c>
+      <c r="C114" s="330"/>
+      <c r="D114" s="330"/>
+      <c r="E114" s="330"/>
+      <c r="F114" s="330"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C116" s="258">
         <f>E20</f>
@@ -4605,7 +4593,7 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C117" s="257">
         <f>C19</f>
@@ -4614,7 +4602,7 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B118" s="243" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C118" s="244">
         <f>Scenarios!C77</f>
@@ -4627,7 +4615,7 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B120" s="241" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
@@ -4652,7 +4640,7 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B123" s="82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
@@ -4665,7 +4653,7 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B124" s="245" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
@@ -4674,6 +4662,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4687,12 +4681,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4776,7 +4764,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4792,7 +4780,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="109">
         <v>1000</v>
@@ -4826,7 +4814,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="194">
         <v>11151623</v>
@@ -4852,7 +4840,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="194">
         <v>2297566</v>
@@ -4878,7 +4866,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="195">
         <v>2043459</v>
@@ -4904,7 +4892,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="194"/>
       <c r="D8" s="185"/>
@@ -4920,7 +4908,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C9" s="194">
         <v>639</v>
@@ -4940,7 +4928,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4956,7 +4944,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -4972,7 +4960,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="194">
         <v>59596</v>
@@ -4998,7 +4986,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" s="194">
         <v>28977</v>
@@ -5024,7 +5012,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="194">
         <v>327166</v>
@@ -5050,7 +5038,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="196">
         <v>1767305</v>
@@ -5076,7 +5064,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="194">
         <v>-9467</v>
@@ -5102,13 +5090,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="185">
         <v>463424</v>
@@ -5132,7 +5120,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="185">
         <v>676387</v>
@@ -5156,7 +5144,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="185">
         <v>626583</v>
@@ -5209,13 +5197,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="187"/>
       <c r="D25" s="185">
@@ -5237,7 +5225,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="187"/>
       <c r="D26" s="185">
@@ -5259,7 +5247,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="186">
         <v>3990166</v>
@@ -5283,7 +5271,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="186">
         <v>12863898</v>
@@ -5307,7 +5295,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C29" s="185"/>
       <c r="D29" s="185"/>
@@ -5323,13 +5311,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="185">
         <v>1095356</v>
@@ -5353,7 +5341,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5369,7 +5357,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
@@ -5423,7 +5411,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="187">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5472,7 +5460,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="188">
         <f>IF(C36="","",C36+C37)</f>
@@ -5521,7 +5509,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="187">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5570,7 +5558,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="189">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5619,7 +5607,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="189">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5668,7 +5656,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="187">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5717,7 +5705,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="190">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5766,7 +5754,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C44" s="191">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5815,7 +5803,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="192">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5864,7 +5852,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="187">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5913,7 +5901,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="190">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5962,7 +5950,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="187">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6011,12 +5999,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" s="187">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6065,7 +6053,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="187">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6114,12 +6102,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="179" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C55" s="192">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6168,7 +6156,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C56" s="192">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6217,7 +6205,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>
@@ -6266,7 +6254,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="192">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6315,13 +6303,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" s="187">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6370,7 +6358,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" s="187">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6419,7 +6407,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" s="187">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6468,7 +6456,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6517,7 +6505,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6772,7 +6760,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6788,7 +6776,7 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="9"/>
     </row>
@@ -6843,7 +6831,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6877,7 +6865,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6911,7 +6899,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6960,7 +6948,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -7052,7 +7040,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7068,7 +7056,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7079,27 +7067,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="210" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="211" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="210" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="211" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>191</v>
-      </c>
       <c r="G3" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H3" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="19">
         <v>265773</v>
@@ -7109,7 +7097,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" s="19">
         <v>1998219</v>
@@ -7120,7 +7108,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -7130,7 +7118,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -7151,7 +7139,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7162,7 +7150,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -7172,7 +7160,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7183,7 +7171,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7193,7 +7181,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7204,7 +7192,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="19">
         <v>366595</v>
@@ -7214,7 +7202,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7249,7 +7237,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7260,7 +7248,7 @@
         <v>5058769.8</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7278,27 +7266,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G14" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="19">
         <v>103050</v>
@@ -7307,7 +7295,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7318,7 +7306,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -7327,7 +7315,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -7338,7 +7326,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -7347,7 +7335,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -7358,7 +7346,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7367,7 +7355,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -7378,7 +7366,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="19">
         <v>2522337</v>
@@ -7387,7 +7375,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7407,7 +7395,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7427,7 +7415,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G21" s="19">
         <v>925726</v>
@@ -7462,7 +7450,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7473,7 +7461,7 @@
         <v>459552.95</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7486,19 +7474,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G26" s="213" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H26" s="214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7509,7 +7497,7 @@
         <v>1427805</v>
       </c>
       <c r="F27" s="215" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7528,7 +7516,7 @@
         <v>287697</v>
       </c>
       <c r="F28" s="217" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G28" s="185">
         <v>-26962</v>
@@ -7543,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7572,14 +7560,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1715502</v>
       </c>
       <c r="F31" s="218" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G31" s="219">
         <f>C31+C40</f>
@@ -7596,7 +7584,7 @@
         <v>1801307</v>
       </c>
       <c r="F32" s="220" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" s="221">
         <f>G35+G40</f>
@@ -7622,24 +7610,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G34" s="225" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H34" s="226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F35" s="227" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="221">
         <f>C12+C24</f>
@@ -7658,7 +7646,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="218" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G36" s="219">
         <f>C4+C15</f>
@@ -7674,7 +7662,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="218" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G37" s="219">
         <f>C6</f>
@@ -7690,7 +7678,7 @@
         <v>319420</v>
       </c>
       <c r="F38" s="218" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G38" s="219">
         <f>C7+C17</f>
@@ -7706,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="218" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G39" s="219">
         <f>C7+C17+C19+C20</f>
@@ -7719,14 +7707,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>319420</v>
       </c>
       <c r="F40" s="227" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G40" s="221">
         <f>G12+G24</f>
@@ -7746,7 +7734,7 @@
         <v>153937</v>
       </c>
       <c r="F41" s="218" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G41" s="219">
         <f>C70</f>
@@ -7765,7 +7753,7 @@
         <v>473357</v>
       </c>
       <c r="F42" s="229" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G42" s="230">
         <f>C82</f>
@@ -7778,7 +7766,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7789,21 +7777,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C45" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D45" s="210" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F45" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C46" s="192">
         <f>G29</f>
@@ -7835,20 +7823,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C49" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="292"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7862,7 +7850,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C51" s="209"/>
       <c r="D51" s="94">
@@ -7876,19 +7864,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F53" s="292"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7902,7 +7890,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7919,19 +7907,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C57" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F57" s="292"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7942,7 +7930,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7956,19 +7944,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C61" s="269" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D61" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F61" s="292"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7979,12 +7967,12 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="292" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7995,21 +7983,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C65" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D65" s="211" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F65" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8020,12 +8008,12 @@
         <v>1116785.5502773244</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8035,7 +8023,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8045,7 +8033,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8055,7 +8043,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8068,19 +8056,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="295" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C72" s="268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D72" s="210" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F72" s="292"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C73" s="192">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8093,7 +8081,7 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="298" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C74" s="299">
         <f>-$C$66/C73</f>
@@ -8104,12 +8092,12 @@
         <v>2.2670106298197523</v>
       </c>
       <c r="F74" s="292" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C75" s="304"/>
       <c r="D75" s="303">
@@ -8117,12 +8105,12 @@
         <v>-881433.44972267561</v>
       </c>
       <c r="F75" s="292" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="300" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C76" s="301"/>
       <c r="D76" s="302">
@@ -8130,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="292" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8138,19 +8126,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C78" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D78" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F78" s="292"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8164,7 +8152,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8178,7 +8166,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8192,7 +8180,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8206,7 +8194,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8217,15 +8205,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D85" s="278" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="275" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8242,7 +8230,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="275" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8259,7 +8247,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="276" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8276,7 +8264,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
@@ -8324,7 +8312,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8377,12 +8365,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8400,7 +8388,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8471,7 +8459,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="198">
         <f>C25</f>
@@ -8526,7 +8514,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="188">
         <f>C4+C5</f>
@@ -8581,7 +8569,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="198">
         <f>C35</f>
@@ -8636,7 +8624,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C8" s="199">
         <f>C6+C7</f>
@@ -8693,7 +8681,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="198">
         <f>BS!$G$39*BS!D58</f>
@@ -8748,7 +8736,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="198">
         <f>-C4*C77</f>
@@ -8803,7 +8791,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C11" s="200">
         <f>C62</f>
@@ -8860,7 +8848,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="198">
         <f>C49</f>
@@ -8915,7 +8903,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="188">
         <f>SUM(C8:C12)</f>
@@ -8970,7 +8958,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="198">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9025,7 +9013,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" s="198">
         <f>-C4*C82</f>
@@ -9082,7 +9070,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" s="201">
         <f>SUM(C13:C15)</f>
@@ -9139,7 +9127,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="198">
         <f>-C4*C84</f>
@@ -9147,7 +9135,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="312" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9165,7 +9153,7 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="198">
         <f>-C4*C85</f>
@@ -9173,7 +9161,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="312" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9191,7 +9179,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="188">
         <f>SUM(C16:C18)</f>
@@ -9267,12 +9255,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9290,7 +9278,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9311,7 +9299,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="204">
         <f>-C4*C28</f>
@@ -9368,7 +9356,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="198">
         <f>-C4*C29</f>
@@ -9425,7 +9413,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="188">
         <f>C23+C24</f>
@@ -9486,14 +9474,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E27" s="313"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
@@ -9501,7 +9489,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9561,7 +9549,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9612,7 +9600,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9671,21 +9659,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="313"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" s="205">
         <f>AVERAGE(G33:J33)</f>
         <v>-302359.25</v>
       </c>
       <c r="E33" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9735,7 +9723,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="205">
         <f>AVERAGE(G34:J34)</f>
@@ -9743,7 +9731,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9794,7 +9782,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="188">
         <f>C33+C34</f>
@@ -9855,7 +9843,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E37" s="313"/>
     </row>
@@ -9978,7 +9966,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -10037,21 +10025,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E42" s="313"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C43" s="307">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="310" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10105,12 +10093,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10128,14 +10116,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="313"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="198">
         <f>-BS!G31*Normalized_FCF!C53</f>
@@ -10190,7 +10178,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" s="198">
         <f>BS!$C$66*C52</f>
@@ -10245,7 +10233,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="188">
         <f>C47+C48</f>
@@ -10304,24 +10292,24 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E51" s="313"/>
       <c r="G51" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52" s="89">
         <f>G52</f>
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E52" s="310" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10341,14 +10329,14 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="84">
         <f>Normalized_FCF!G53</f>
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E53" s="310" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10368,7 +10356,7 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" s="42">
         <f>-C8/C47</f>
@@ -10427,17 +10415,17 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E56" s="313"/>
       <c r="G56" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" s="198">
         <f>BS!$C79*C65</f>
@@ -10492,7 +10480,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="198">
         <f>BS!$C68*C66</f>
@@ -10547,7 +10535,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="198">
         <f>BS!$C81*C67</f>
@@ -10602,7 +10590,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C60" s="188">
         <f>SUM(C57:C59)</f>
@@ -10657,13 +10645,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C61" s="308">
         <v>0</v>
       </c>
       <c r="E61" s="311" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -10713,7 +10701,7 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C62" s="188">
         <f>C60+C61</f>
@@ -10772,17 +10760,17 @@
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E64" s="313"/>
       <c r="G64" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" s="181">
         <f>G65</f>
@@ -10807,7 +10795,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C66" s="181">
         <f>G66</f>
@@ -10832,7 +10820,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C67" s="181">
         <f>G67</f>
@@ -10857,7 +10845,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C68" s="72">
         <f>C60/BS!C70</f>
@@ -10887,12 +10875,12 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="10"/>
       <c r="B70" s="54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C70" s="54"/>
       <c r="D70" s="56"/>
       <c r="E70" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F70" s="56"/>
       <c r="G70" s="37"/>
@@ -10910,7 +10898,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10"/>
       <c r="B71" s="73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
@@ -10931,7 +10919,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C72" s="79">
         <f>ABS(C5/C$4)</f>
@@ -10988,7 +10976,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C73" s="80">
         <f>ABS(C6/C$4)</f>
@@ -11045,7 +11033,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11102,7 +11090,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C75" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11159,7 +11147,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C76" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11216,7 +11204,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C77" s="90">
         <f>MAX(AVERAGE(G77:J77),C76)</f>
@@ -11224,7 +11212,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="311" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
@@ -11275,7 +11263,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11332,7 +11320,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11389,7 +11377,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C80" s="80">
         <f>C13/C4</f>
@@ -11446,7 +11434,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C81" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11561,7 +11549,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10"/>
       <c r="B83" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C83" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11618,7 +11606,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C84" s="309">
         <v>0</v>
@@ -11644,7 +11632,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C85" s="309">
         <v>0</v>
@@ -11668,7 +11656,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C86" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11729,7 +11717,7 @@
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E88" s="313"/>
     </row>
@@ -11848,7 +11836,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C91" s="23">
         <f>C89/(C19*$C$3/Common_Shares)</f>
@@ -11903,7 +11891,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
@@ -11962,7 +11950,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
       <c r="B94" s="162" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
@@ -11983,7 +11971,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C95" s="79">
         <f>C4/G4-1</f>
@@ -12040,7 +12028,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C96" s="79">
         <f>C13/G13-1</f>
@@ -12100,12 +12088,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="3"/>
       <c r="B98" s="54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C98" s="54"/>
       <c r="D98" s="56"/>
       <c r="E98" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="37"/>
@@ -12123,11 +12111,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10"/>
       <c r="B99" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" s="313"/>
       <c r="G99" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12190,7 +12178,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C101" s="207">
         <f>BS!C4</f>
@@ -12247,7 +12235,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="207">
         <f>BS!C6+BS!C7</f>
@@ -12304,7 +12292,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C103" s="206">
         <f>BS!G30</f>
@@ -12361,7 +12349,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C104" s="206">
         <f>BS!G27</f>
@@ -12422,14 +12410,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
       <c r="B106" s="93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
       <c r="E106" s="314"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -12445,7 +12433,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C107" s="97">
         <f>C101/C$4</f>
@@ -12502,7 +12490,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12559,7 +12547,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C109" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12590,7 +12578,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
       <c r="B111" s="93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
@@ -12644,7 +12632,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C112" s="23">
         <f>C80</f>
@@ -12698,7 +12686,7 @@
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C113" s="42">
         <f>C4/C100</f>
@@ -12752,7 +12740,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C114" s="15">
         <f>C100/C104</f>
@@ -12809,7 +12797,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C115" s="105">
         <f>C8/C104</f>
@@ -12885,12 +12873,12 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A117" s="10"/>
       <c r="B117" s="54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C117" s="54"/>
       <c r="D117" s="56"/>
       <c r="E117" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F117" s="56"/>
       <c r="G117" s="37"/>
@@ -12908,7 +12896,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="10"/>
       <c r="B118" s="183" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
@@ -12987,7 +12975,7 @@
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
       <c r="B120" s="27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13756,32 +13744,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13792,7 +13780,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C71</f>
@@ -13802,7 +13790,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="234" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="235">
         <f>Thesis!C67</f>
@@ -13813,7 +13801,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="239">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13824,14 +13812,14 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="335" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F6" s="335"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="233">
         <f>BS!G31</f>
@@ -13847,7 +13835,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C8" s="208">
         <f>BS!D66</f>
@@ -13863,7 +13851,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="234" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" s="236">
         <f>BS!H42</f>
@@ -13879,7 +13867,7 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C10" s="239">
         <f>C6-C7+C8+C9</f>
@@ -13893,7 +13881,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
@@ -13907,7 +13895,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -13924,7 +13912,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13934,13 +13922,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="166">
         <f>Scenarios!C65</f>
@@ -13950,7 +13938,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="167">
         <f>Scenarios!C64</f>
@@ -13960,7 +13948,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -13977,19 +13965,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>115</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>116</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14655,7 +14643,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14678,7 +14666,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14692,7 +14680,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14863,7 +14851,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15082,19 +15070,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C73" s="176" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D73" s="176" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" s="177" t="s">
         <v>118</v>
       </c>
-      <c r="E73" s="177" t="s">
-        <v>119</v>
-      </c>
       <c r="F73" s="177" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15219,20 +15207,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C80" s="160" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="160" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="160" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15284,20 +15272,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="285" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I2" s="286"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H3" s="284">
         <v>0</v>
@@ -15309,14 +15297,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4" s="160"/>
       <c r="H4" s="284">
@@ -15338,14 +15326,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="164" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="284">
@@ -15358,7 +15346,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15383,7 +15371,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15405,7 +15393,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="208">
         <f>Normalized_FCF!C19</f>
@@ -15438,7 +15426,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="164" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E11" s="337"/>
       <c r="F11" s="337"/>
@@ -15452,7 +15440,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="163">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15471,7 +15459,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="163">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15489,7 +15477,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15500,7 +15488,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15509,21 +15497,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17" s="164" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="154">
         <v>5</v>
       </c>
       <c r="E18" s="337" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F18" s="338"/>
     </row>
@@ -15533,14 +15521,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E20" s="338"/>
       <c r="F20" s="338"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
@@ -15555,7 +15543,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
@@ -15570,16 +15558,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E24" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F24" s="164"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C25" s="171">
         <f>C18</f>
@@ -15591,7 +15579,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" s="169">
         <v>0.02</v>
@@ -15602,7 +15590,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
@@ -15617,7 +15605,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C28" s="170">
         <v>0.6</v>
@@ -15628,16 +15616,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F30" s="164"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C31" s="171">
         <f>C18</f>
@@ -15649,7 +15637,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" s="169">
         <v>-0.05</v>
@@ -15660,7 +15648,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
@@ -15675,7 +15663,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="170">
         <v>0.2</v>
@@ -15686,16 +15674,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E36" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F36" s="164"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C37" s="171">
         <f>C18</f>
@@ -15707,7 +15695,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C38" s="169">
         <v>0.05</v>
@@ -15718,7 +15706,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
@@ -15733,7 +15721,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="172">
         <f>1-C28-C34</f>
@@ -15745,7 +15733,7 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15758,7 +15746,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15767,12 +15755,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" s="154">
         <v>10</v>
@@ -15787,16 +15775,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="164" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F48" s="164"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C49" s="171">
         <f>C46</f>
@@ -15808,7 +15796,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C50" s="169">
         <v>-0.08</v>
@@ -15819,7 +15807,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
@@ -15834,7 +15822,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="170">
         <v>0.02</v>
@@ -15845,16 +15833,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E54" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F54" s="164"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C55" s="171">
         <f>C46</f>
@@ -15866,7 +15854,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="169">
         <v>0.08</v>
@@ -15877,7 +15865,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
@@ -15892,7 +15880,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C58" s="170">
         <v>0.02</v>
@@ -15903,7 +15891,7 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15914,7 +15902,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F60" s="324">
         <v>3</v>
@@ -15922,7 +15910,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15931,39 +15919,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E63" s="291" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C64" s="171">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="290" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65" s="155">
         <v>6.9371044268871302E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="290" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
@@ -15974,20 +15962,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="290" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E68" s="291" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C69" s="281" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -15997,19 +15985,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C70" s="281" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="290" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C71" s="281" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16019,7 +16007,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C72" s="280" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -16032,7 +16020,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16041,16 +16029,16 @@
     </row>
     <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B75" s="112" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E75" s="325" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F75" s="323"/>
     </row>
     <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B76" s="283" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C76" s="282">
         <f>F60</f>
@@ -16058,15 +16046,15 @@
       </c>
       <c r="D76" s="138"/>
       <c r="E76" s="326" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F76" s="323" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B77" s="103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="178">
         <f>Normalized_FCF!C89</f>
@@ -16077,28 +16065,28 @@
         <v>HKD</v>
       </c>
       <c r="E77" s="327" t="s">
+        <v>368</v>
+      </c>
+      <c r="F77" s="323" t="s">
         <v>370</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E78" s="328" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F78" s="323" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C80" s="172">
         <f>Thesis!C117</f>
@@ -16107,7 +16095,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16119,7 +16107,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16129,7 +16117,7 @@
     </row>
     <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16140,7 +16128,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
@@ -16152,12 +16140,12 @@
     </row>
     <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
@@ -16170,7 +16158,7 @@
     </row>
     <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D834CD90-9932-4821-9D06-48F0032984E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C793385-F9A2-4EBB-A168-3D8B638FAE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3692,7 +3692,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>15.38</v>
+        <v>15.1</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>9029.7187329999997</v>
+        <v>8865.3285350000006</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14601322135335382</v>
+        <v>0.15361989461854253</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>0.11361779174212065</v>
+        <v>0.11572461172144474</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>8.8426527958387513E-2</v>
+        <v>9.0066225165562924E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -11895,28 +11895,28 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>8.8426527958387513E-2</v>
+        <v>9.0066225165562924E-2</v>
       </c>
       <c r="E92" s="313"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>8.8426527958387513E-2</v>
+        <v>9.0066225165562924E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
-        <v>7.1521456436931086E-2</v>
+        <v>7.2847682119205309E-2</v>
       </c>
       <c r="I92" s="23">
         <f t="shared" si="38"/>
-        <v>7.1521456436931086E-2</v>
+        <v>7.2847682119205309E-2</v>
       </c>
       <c r="J92" s="23">
         <f t="shared" si="38"/>
-        <v>6.5019505851755519E-2</v>
+        <v>6.6225165562913912E-2</v>
       </c>
       <c r="K92" s="23">
         <f t="shared" si="38"/>
-        <v>6.5019505851755519E-2</v>
+        <v>6.6225165562913912E-2</v>
       </c>
       <c r="L92" s="23" t="str">
         <f t="shared" si="38"/>
@@ -12979,30 +12979,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11361779174212065</v>
+        <v>0.11572461172144474</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="310"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>0.1447070544096426</v>
+        <v>0.14739036402783465</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>0.15060834564313999</v>
+        <v>0.15340108317824458</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>0.12977768573425619</v>
+        <v>0.13218415937701061</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>0.12361769319797482</v>
+        <v>0.12590994181356641</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>0.10658106065727441</v>
+        <v>0.10855739820588613</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-15.38</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>15.38</v>
+        <v>15.1</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16149,7 +16149,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>15.38</v>
+        <v>15.1</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16162,7 +16162,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14601322135335382</v>
+        <v>0.15361989461854253</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C793385-F9A2-4EBB-A168-3D8B638FAE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E258883B-0C5D-433E-A1A8-D2A0B045AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E258883B-0C5D-433E-A1A8-D2A0B045AC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19098A12-D83B-4777-82BA-0B2D008FAE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1986,7 +1986,7 @@
     <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="192" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2410,13 +2410,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <i/>
       <u/>
       <sz val="10"/>
@@ -2632,7 +2626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3234,9 +3228,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3304,21 +3295,27 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3645,10 +3642,10 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="293" t="s">
+      <c r="E1" s="292" t="s">
         <v>354</v>
       </c>
-      <c r="F1" s="294" t="s">
+      <c r="F1" s="293" t="s">
         <v>356</v>
       </c>
     </row>
@@ -3747,13 +3744,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="329" t="s">
+      <c r="B12" s="332" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="329"/>
-      <c r="D12" s="329"/>
-      <c r="E12" s="329"/>
-      <c r="F12" s="329"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="332"/>
+      <c r="F12" s="332"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3819,15 +3816,15 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
-        <f>C123</f>
-        <v>13.538366385360966</v>
+        <f ca="1">C123</f>
+        <v>86.958503954899456</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E20" s="289">
-        <f>Scenarios!C76</f>
-        <v>3</v>
+      <c r="E20" s="323">
+        <f ca="1">Scenarios!C76</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3836,7 +3833,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15361989461854253</v>
+        <v>1.162487831816041</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3856,22 +3853,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="329" t="s">
+      <c r="B25" s="332" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
+      <c r="C25" s="332"/>
+      <c r="D25" s="332"/>
+      <c r="E25" s="332"/>
+      <c r="F25" s="332"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="333" t="s">
+      <c r="B26" s="336" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="333"/>
-      <c r="D26" s="333"/>
-      <c r="E26" s="333"/>
-      <c r="F26" s="333"/>
+      <c r="C26" s="336"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3883,13 +3880,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="331" t="s">
+      <c r="B29" s="334" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="331"/>
-      <c r="D29" s="331"/>
-      <c r="E29" s="331"/>
-      <c r="F29" s="331"/>
+      <c r="C29" s="334"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3909,13 +3906,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="334" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="331"/>
-      <c r="D32" s="331"/>
-      <c r="E32" s="331"/>
-      <c r="F32" s="331"/>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3944,13 +3941,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="331" t="s">
+      <c r="B36" s="334" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="331"/>
-      <c r="D36" s="331"/>
-      <c r="E36" s="331"/>
-      <c r="F36" s="331"/>
+      <c r="C36" s="334"/>
+      <c r="D36" s="334"/>
+      <c r="E36" s="334"/>
+      <c r="F36" s="334"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3966,13 +3963,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="331" t="s">
+      <c r="B39" s="334" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
+      <c r="C39" s="334"/>
+      <c r="D39" s="334"/>
+      <c r="E39" s="334"/>
+      <c r="F39" s="334"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4006,13 +4003,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="331" t="s">
+      <c r="B45" s="334" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="331"/>
-      <c r="D45" s="331"/>
-      <c r="E45" s="331"/>
-      <c r="F45" s="331"/>
+      <c r="C45" s="334"/>
+      <c r="D45" s="334"/>
+      <c r="E45" s="334"/>
+      <c r="F45" s="334"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4028,13 +4025,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="331" t="s">
+      <c r="B48" s="334" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="332"/>
-      <c r="D48" s="332"/>
-      <c r="E48" s="332"/>
-      <c r="F48" s="332"/>
+      <c r="C48" s="335"/>
+      <c r="D48" s="335"/>
+      <c r="E48" s="335"/>
+      <c r="F48" s="335"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4063,13 +4060,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="329" t="s">
+      <c r="B52" s="332" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="329"/>
-      <c r="D52" s="329"/>
-      <c r="E52" s="329"/>
-      <c r="F52" s="329"/>
+      <c r="C52" s="332"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4130,22 +4127,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="334" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="331"/>
-      <c r="D60" s="331"/>
-      <c r="E60" s="331"/>
-      <c r="F60" s="331"/>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="333" t="s">
+      <c r="B61" s="336" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="333"/>
-      <c r="D61" s="333"/>
-      <c r="E61" s="333"/>
-      <c r="F61" s="333"/>
+      <c r="C61" s="336"/>
+      <c r="D61" s="336"/>
+      <c r="E61" s="336"/>
+      <c r="F61" s="336"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4156,7 +4153,7 @@
       <c r="B64" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C64" s="322">
+      <c r="C64" s="321">
         <v>0.08</v>
       </c>
     </row>
@@ -4168,7 +4165,7 @@
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D65" s="296" t="s">
+      <c r="D65" s="295" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4180,7 +4177,7 @@
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D66" s="296" t="s">
+      <c r="D66" s="295" t="s">
         <v>362</v>
       </c>
     </row>
@@ -4197,22 +4194,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="329" t="s">
+      <c r="B69" s="332" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="329"/>
-      <c r="D69" s="329"/>
-      <c r="E69" s="329"/>
-      <c r="F69" s="329"/>
+      <c r="C69" s="332"/>
+      <c r="D69" s="332"/>
+      <c r="E69" s="332"/>
+      <c r="F69" s="332"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="329" t="s">
+      <c r="B70" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="329"/>
-      <c r="D70" s="329"/>
-      <c r="E70" s="329"/>
-      <c r="F70" s="329"/>
+      <c r="C70" s="332"/>
+      <c r="D70" s="332"/>
+      <c r="E70" s="332"/>
+      <c r="F70" s="332"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4249,13 +4246,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="329" t="s">
+      <c r="B77" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="329"/>
-      <c r="D77" s="329"/>
-      <c r="E77" s="329"/>
-      <c r="F77" s="329"/>
+      <c r="C77" s="332"/>
+      <c r="D77" s="332"/>
+      <c r="E77" s="332"/>
+      <c r="F77" s="332"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4369,13 +4366,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="329" t="s">
+      <c r="B93" s="332" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="329"/>
-      <c r="D93" s="329"/>
-      <c r="E93" s="329"/>
-      <c r="F93" s="329"/>
+      <c r="C93" s="332"/>
+      <c r="D93" s="332"/>
+      <c r="E93" s="332"/>
+      <c r="F93" s="332"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4401,13 +4398,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="334" t="s">
         <v>374</v>
       </c>
-      <c r="C99" s="331"/>
-      <c r="D99" s="331"/>
-      <c r="E99" s="331"/>
-      <c r="F99" s="331"/>
+      <c r="C99" s="334"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4550,13 +4547,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="334" t="s">
+      <c r="B110" s="337" t="s">
         <v>375</v>
       </c>
-      <c r="C110" s="334"/>
-      <c r="D110" s="334"/>
-      <c r="E110" s="334"/>
-      <c r="F110" s="334"/>
+      <c r="C110" s="337"/>
+      <c r="D110" s="337"/>
+      <c r="E110" s="337"/>
+      <c r="F110" s="337"/>
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
@@ -4569,13 +4566,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="330" t="s">
+      <c r="B114" s="333" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="330"/>
-      <c r="D114" s="330"/>
-      <c r="E114" s="330"/>
-      <c r="F114" s="330"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4587,7 +4584,7 @@
         <v>280</v>
       </c>
       <c r="C116" s="258">
-        <f>E20</f>
+        <f ca="1">E20</f>
         <v>3</v>
       </c>
     </row>
@@ -4620,22 +4617,22 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B121" s="243" t="str">
-        <f>"PV("&amp;C116&amp;" yrs of Dividends)"</f>
+        <f ca="1">"PV("&amp;C116&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C121" s="247">
-        <f>Scenarios!C81</f>
-        <v>2.8648148148148147</v>
+        <f ca="1">Scenarios!C81</f>
+        <v>1.2217592592592592</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B122" s="243" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
+        <f ca="1">"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C122" s="247">
-        <f>Scenarios!C82</f>
-        <v>10.673551570546152</v>
+        <f ca="1">Scenarios!C82</f>
+        <v>85.736744695640198</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4643,8 +4640,8 @@
         <v>275</v>
       </c>
       <c r="C123" s="246">
-        <f>Scenarios!C83</f>
-        <v>13.538366385360966</v>
+        <f ca="1">Scenarios!C83</f>
+        <v>86.958503954899456</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4656,8 +4653,8 @@
         <v>277</v>
       </c>
       <c r="C124" s="158">
-        <f>Scenarios!F83</f>
-        <v>-0.26597040193012134</v>
+        <f ca="1">Scenarios!F83</f>
+        <v>-0.41304969665133007</v>
       </c>
     </row>
   </sheetData>
@@ -7092,7 +7089,7 @@
       <c r="C4" s="19">
         <v>265773</v>
       </c>
-      <c r="D4" s="305">
+      <c r="D4" s="304">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7102,7 +7099,7 @@
       <c r="G4" s="19">
         <v>1998219</v>
       </c>
-      <c r="H4" s="305">
+      <c r="H4" s="304">
         <v>0.9</v>
       </c>
     </row>
@@ -7113,7 +7110,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="305">
+      <c r="D5" s="304">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7123,7 +7120,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="305">
+      <c r="H5" s="304">
         <v>0.7</v>
       </c>
     </row>
@@ -7134,7 +7131,7 @@
       <c r="C6" s="19">
         <v>9672256</v>
       </c>
-      <c r="D6" s="305">
+      <c r="D6" s="304">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7144,7 +7141,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="305">
+      <c r="H6" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7155,7 +7152,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="305">
+      <c r="D7" s="304">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7165,7 +7162,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="305">
+      <c r="H7" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7176,7 +7173,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="305">
+      <c r="D8" s="304">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7186,7 +7183,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="305">
+      <c r="H8" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7197,7 +7194,7 @@
       <c r="C9" s="19">
         <v>366595</v>
       </c>
-      <c r="D9" s="305">
+      <c r="D9" s="304">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7207,7 +7204,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="305">
+      <c r="H9" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7218,10 +7215,10 @@
       <c r="C10" s="19">
         <v>29465</v>
       </c>
-      <c r="D10" s="305">
+      <c r="D10" s="304">
         <v>0.9</v>
       </c>
-      <c r="H10" s="306"/>
+      <c r="H10" s="305"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7230,10 +7227,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="305">
+      <c r="D11" s="304">
         <v>0.05</v>
       </c>
-      <c r="H11" s="306"/>
+      <c r="H11" s="305"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7291,7 +7288,7 @@
       <c r="C15" s="19">
         <v>103050</v>
       </c>
-      <c r="D15" s="305">
+      <c r="D15" s="304">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7300,7 +7297,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="305">
+      <c r="H15" s="304">
         <v>0.8</v>
       </c>
     </row>
@@ -7311,7 +7308,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="305">
+      <c r="D16" s="304">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7320,7 +7317,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="305">
+      <c r="H16" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7331,7 +7328,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="305">
+      <c r="D17" s="304">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7340,7 +7337,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="305">
+      <c r="H17" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7351,7 +7348,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="305">
+      <c r="D18" s="304">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7360,7 +7357,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="305">
+      <c r="H18" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7371,7 +7368,7 @@
       <c r="C19" s="19">
         <v>2522337</v>
       </c>
-      <c r="D19" s="305">
+      <c r="D19" s="304">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7380,7 +7377,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="305">
+      <c r="H19" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7391,7 +7388,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="305">
+      <c r="D20" s="304">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7400,7 +7397,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="305">
+      <c r="H20" s="304">
         <v>0.2</v>
       </c>
     </row>
@@ -7411,7 +7408,7 @@
       <c r="C21" s="19">
         <v>538321</v>
       </c>
-      <c r="D21" s="305">
+      <c r="D21" s="304">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7420,7 +7417,7 @@
       <c r="G21" s="19">
         <v>925726</v>
       </c>
-      <c r="H21" s="305">
+      <c r="H21" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7431,10 +7428,10 @@
       <c r="C22" s="19">
         <v>154648</v>
       </c>
-      <c r="D22" s="305">
+      <c r="D22" s="304">
         <v>0.9</v>
       </c>
-      <c r="H22" s="306"/>
+      <c r="H22" s="305"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7443,10 +7440,10 @@
       <c r="C23" s="19">
         <v>277674</v>
       </c>
-      <c r="D23" s="305">
-        <v>0</v>
-      </c>
-      <c r="H23" s="306"/>
+      <c r="D23" s="304">
+        <v>0</v>
+      </c>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7785,7 +7782,7 @@
       <c r="D45" s="210" t="s">
         <v>292</v>
       </c>
-      <c r="F45" s="297" t="s">
+      <c r="F45" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7801,7 +7798,7 @@
         <f>H29</f>
         <v>3446088.45</v>
       </c>
-      <c r="F46" s="292"/>
+      <c r="F46" s="291"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7816,10 +7813,10 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>5.8696003638854428</v>
       </c>
-      <c r="F47" s="292"/>
+      <c r="F47" s="291"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="292"/>
+      <c r="F48" s="291"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
@@ -7832,7 +7829,7 @@
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="292"/>
+      <c r="F49" s="291"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7846,7 +7843,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.0842664509772892</v>
       </c>
-      <c r="F50" s="292"/>
+      <c r="F50" s="291"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
@@ -7857,10 +7854,10 @@
         <f>G29/G32</f>
         <v>0.76485172952944758</v>
       </c>
-      <c r="F51" s="292"/>
+      <c r="F51" s="291"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="292"/>
+      <c r="F52" s="291"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
@@ -7872,7 +7869,7 @@
       <c r="D53" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="292"/>
+      <c r="F53" s="291"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7886,7 +7883,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.13472770763839131</v>
       </c>
-      <c r="F54" s="292"/>
+      <c r="F54" s="291"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7900,10 +7897,10 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>2.1854036242131779E-4</v>
       </c>
-      <c r="F55" s="292"/>
+      <c r="F55" s="291"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="292"/>
+      <c r="F56" s="291"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
@@ -7915,7 +7912,7 @@
       <c r="D57" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="292"/>
+      <c r="F57" s="291"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7937,10 +7934,10 @@
         <f>G39/G32</f>
         <v>0.14965749507062509</v>
       </c>
-      <c r="F59" s="292"/>
+      <c r="F59" s="291"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="292"/>
+      <c r="F60" s="291"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
@@ -7952,7 +7949,7 @@
       <c r="D61" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="292"/>
+      <c r="F61" s="291"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7966,7 +7963,7 @@
         <f>G28/G29</f>
         <v>-2.0915594459950692E-3</v>
       </c>
-      <c r="F62" s="292" t="s">
+      <c r="F62" s="291" t="s">
         <v>293</v>
       </c>
     </row>
@@ -7991,7 +7988,7 @@
       <c r="D65" s="211" t="s">
         <v>318</v>
       </c>
-      <c r="F65" s="297" t="s">
+      <c r="F65" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8019,7 +8016,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="292"/>
+      <c r="F67" s="291"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -8029,7 +8026,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="292"/>
+      <c r="F68" s="291"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -8039,7 +8036,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="292"/>
+      <c r="F69" s="291"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -8049,13 +8046,13 @@
         <f>SUM(C66:C69)</f>
         <v>1998219</v>
       </c>
-      <c r="F70" s="292"/>
+      <c r="F70" s="291"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="292"/>
+      <c r="F71" s="291"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="295" t="s">
+      <c r="B72" s="294" t="s">
         <v>359</v>
       </c>
       <c r="C72" s="268" t="s">
@@ -8064,7 +8061,7 @@
       <c r="D72" s="210" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="292"/>
+      <c r="F72" s="291"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
@@ -8080,18 +8077,18 @@
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="298" t="s">
+      <c r="B74" s="297" t="s">
         <v>364</v>
       </c>
-      <c r="C74" s="299">
+      <c r="C74" s="298">
         <f>-$C$66/C73</f>
         <v>1.7829051253573729</v>
       </c>
-      <c r="D74" s="299">
+      <c r="D74" s="298">
         <f>-$C$66/D73</f>
         <v>2.2670106298197523</v>
       </c>
-      <c r="F74" s="292" t="s">
+      <c r="F74" s="291" t="s">
         <v>360</v>
       </c>
     </row>
@@ -8099,30 +8096,30 @@
       <c r="B75" s="82" t="s">
         <v>361</v>
       </c>
-      <c r="C75" s="304"/>
-      <c r="D75" s="303">
+      <c r="C75" s="303"/>
+      <c r="D75" s="302">
         <f>MIN(D73*D76,-G5)</f>
         <v>-881433.44972267561</v>
       </c>
-      <c r="F75" s="292" t="s">
+      <c r="F75" s="291" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="300" t="s">
+      <c r="B76" s="299" t="s">
         <v>365</v>
       </c>
-      <c r="C76" s="301"/>
-      <c r="D76" s="302">
+      <c r="C76" s="300"/>
+      <c r="D76" s="301">
         <f>IF(D74&lt;=3,1,IF(D74&gt;10,5,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="292" t="s">
+      <c r="F76" s="291" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="292"/>
+      <c r="F77" s="291"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
@@ -8134,7 +8131,7 @@
       <c r="D78" s="211" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="292"/>
+      <c r="F78" s="291"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8148,7 +8145,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="292"/>
+      <c r="F79" s="291"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8162,7 +8159,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="292"/>
+      <c r="F80" s="291"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8176,7 +8173,7 @@
         <f>G9*H9+G21*H21</f>
         <v>92572.6</v>
       </c>
-      <c r="F81" s="292"/>
+      <c r="F81" s="291"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8190,7 +8187,7 @@
         <f>SUM(D79:D81)</f>
         <v>92572.6</v>
       </c>
-      <c r="F82" s="292"/>
+      <c r="F82" s="291"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8395,7 +8392,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="313"/>
+      <c r="E3" s="312"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8409,7 +8406,7 @@
         <v>11975736</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="311"/>
+      <c r="E4" s="310"/>
       <c r="F4" s="57"/>
       <c r="G4" s="187">
         <f>Data!C36</f>
@@ -8465,7 +8462,7 @@
         <f>C25</f>
         <v>-10274842.146672107</v>
       </c>
-      <c r="E5" s="313"/>
+      <c r="E5" s="312"/>
       <c r="G5" s="187">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-13195082</v>
@@ -8520,7 +8517,7 @@
         <f>C4+C5</f>
         <v>1700893.8533278927</v>
       </c>
-      <c r="E6" s="313"/>
+      <c r="E6" s="312"/>
       <c r="G6" s="188">
         <f>IF(G4="","",G4+G5)</f>
         <v>2130880</v>
@@ -8575,7 +8572,7 @@
         <f>C35</f>
         <v>-302359.25</v>
       </c>
-      <c r="E7" s="313"/>
+      <c r="E7" s="312"/>
       <c r="G7" s="198">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-254107</v>
@@ -8631,7 +8628,7 @@
         <v>1398534.6033278927</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="319"/>
+      <c r="E8" s="318"/>
       <c r="F8" s="60"/>
       <c r="G8" s="188">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8687,7 +8684,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>463424</v>
       </c>
-      <c r="E9" s="313"/>
+      <c r="E9" s="312"/>
       <c r="G9" s="198">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>463424</v>
@@ -8742,7 +8739,7 @@
         <f>-C4*C77</f>
         <v>-463424.00000000006</v>
       </c>
-      <c r="E10" s="313"/>
+      <c r="E10" s="312"/>
       <c r="G10" s="198">
         <f>Data!C62</f>
         <v>-676387</v>
@@ -8798,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="173"/>
-      <c r="E11" s="312"/>
+      <c r="E11" s="311"/>
       <c r="F11" s="173"/>
       <c r="G11" s="190">
         <f>G60</f>
@@ -8854,7 +8851,7 @@
         <f>C49</f>
         <v>-30619</v>
       </c>
-      <c r="E12" s="313"/>
+      <c r="E12" s="312"/>
       <c r="G12" s="198">
         <f t="shared" ref="G12:Q12" si="6">G49</f>
         <v>-30619</v>
@@ -8909,7 +8906,7 @@
         <f>SUM(C8:C12)</f>
         <v>1367915.6033278927</v>
       </c>
-      <c r="E13" s="313"/>
+      <c r="E13" s="312"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1633830</v>
@@ -8964,7 +8961,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-341978.90083197318</v>
       </c>
-      <c r="E14" s="313"/>
+      <c r="E14" s="312"/>
       <c r="G14" s="198">
         <f>Data!C46</f>
         <v>-327166</v>
@@ -9020,7 +9017,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="320"/>
+      <c r="E15" s="319"/>
       <c r="F15" s="61"/>
       <c r="G15" s="187">
         <f>Data!C48</f>
@@ -9077,7 +9074,7 @@
         <v>1025936.7024959195</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="321"/>
+      <c r="E16" s="320"/>
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -9134,7 +9131,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="312" t="s">
+      <c r="E17" s="311" t="s">
         <v>378</v>
       </c>
       <c r="F17" s="59"/>
@@ -9160,7 +9157,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="312" t="s">
+      <c r="E18" s="311" t="s">
         <v>379</v>
       </c>
       <c r="F18" s="59"/>
@@ -9186,7 +9183,7 @@
         <v>1025936.7024959195</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="310"/>
+      <c r="E19" s="309"/>
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",SUM(G16:G18))</f>
@@ -9282,7 +9279,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="310"/>
+      <c r="E22" s="309"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9306,7 +9303,7 @@
         <v>-8638608.2360938303</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="312"/>
+      <c r="E23" s="311"/>
       <c r="F23" s="59"/>
       <c r="G23" s="187">
         <f>Data!C37</f>
@@ -9363,7 +9360,7 @@
         <v>-1636233.9105782772</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="310"/>
+      <c r="E24" s="309"/>
       <c r="F24" s="27"/>
       <c r="G24" s="187">
         <f>Data!C40</f>
@@ -9420,7 +9417,7 @@
         <v>-10274842.146672107</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="318"/>
+      <c r="E25" s="317"/>
       <c r="F25" s="9"/>
       <c r="G25" s="188">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9469,14 +9466,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="313"/>
+      <c r="E26" s="312"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="313"/>
+      <c r="E27" s="312"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9488,7 +9485,7 @@
         <v>0.72134257435984139</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="311" t="s">
+      <c r="E28" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F28" s="26"/>
@@ -9548,7 +9545,7 @@
         <v>0.13662908990130354</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="311" t="s">
+      <c r="E29" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F29" s="26"/>
@@ -9606,7 +9603,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.85797166426114502</v>
       </c>
-      <c r="E30" s="313"/>
+      <c r="E30" s="312"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.86096272455849754</v>
@@ -9654,14 +9651,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="313"/>
+      <c r="E31" s="312"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="313"/>
+      <c r="E32" s="312"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
@@ -9672,7 +9669,7 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-302359.25</v>
       </c>
-      <c r="E33" s="311" t="s">
+      <c r="E33" s="310" t="s">
         <v>380</v>
       </c>
       <c r="G33" s="198">
@@ -9730,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="311" t="s">
+      <c r="E34" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F34" s="59"/>
@@ -9789,7 +9786,7 @@
         <v>-302359.25</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="312"/>
+      <c r="E35" s="311"/>
       <c r="F35" s="59"/>
       <c r="G35" s="188">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9838,14 +9835,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="313"/>
+      <c r="E36" s="312"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="313"/>
+      <c r="E37" s="312"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9858,7 +9855,7 @@
         <v>2.5247654924924864E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="310"/>
+      <c r="E38" s="309"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9916,7 +9913,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="310"/>
+      <c r="E39" s="309"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9972,7 +9969,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>2.5247654924924864E-2</v>
       </c>
-      <c r="E40" s="313"/>
+      <c r="E40" s="312"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>1.6580166386945237E-2</v>
@@ -10020,25 +10017,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="313"/>
+      <c r="E41" s="312"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="313"/>
+      <c r="E42" s="312"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="307">
+      <c r="C43" s="306">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="310" t="s">
+      <c r="E43" s="309" t="s">
         <v>381</v>
       </c>
       <c r="F43" s="27"/>
@@ -10118,7 +10115,7 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="313"/>
+      <c r="E46" s="312"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
@@ -10129,7 +10126,7 @@
         <f>-BS!G31*Normalized_FCF!C53</f>
         <v>-59596</v>
       </c>
-      <c r="E47" s="313"/>
+      <c r="E47" s="312"/>
       <c r="G47" s="198">
         <f>Data!C51</f>
         <v>-59596</v>
@@ -10184,7 +10181,7 @@
         <f>BS!$C$66*C52</f>
         <v>28977</v>
       </c>
-      <c r="E48" s="313"/>
+      <c r="E48" s="312"/>
       <c r="G48" s="198">
         <f>Data!C52</f>
         <v>28977</v>
@@ -10239,7 +10236,7 @@
         <f>C47+C48</f>
         <v>-30619</v>
       </c>
-      <c r="E49" s="313"/>
+      <c r="E49" s="312"/>
       <c r="G49" s="188">
         <f t="shared" ref="G49:Q49" si="19">IF(G4="","",G47+G48)</f>
         <v>-30619</v>
@@ -10287,14 +10284,14 @@
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
-      <c r="E50" s="313"/>
+      <c r="E50" s="312"/>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="313"/>
+      <c r="E51" s="312"/>
       <c r="G51" s="100" t="s">
         <v>224</v>
       </c>
@@ -10308,7 +10305,7 @@
         <f>G52</f>
         <v>1.4501413508729523E-2</v>
       </c>
-      <c r="E52" s="310" t="s">
+      <c r="E52" s="309" t="s">
         <v>382</v>
       </c>
       <c r="G52" s="6">
@@ -10335,7 +10332,7 @@
         <f>Normalized_FCF!G53</f>
         <v>2.9286626219579916E-2</v>
       </c>
-      <c r="E53" s="310" t="s">
+      <c r="E53" s="309" t="s">
         <v>383</v>
       </c>
       <c r="G53" s="23">
@@ -10362,7 +10359,7 @@
         <f>-C8/C47</f>
         <v>23.466920654538772</v>
       </c>
-      <c r="E54" s="313"/>
+      <c r="E54" s="312"/>
       <c r="G54" s="42">
         <f>IF(G4="","",-G8/G47)</f>
         <v>31.4915933955299</v>
@@ -10410,14 +10407,14 @@
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
-      <c r="E55" s="313"/>
+      <c r="E55" s="312"/>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="313"/>
+      <c r="E56" s="312"/>
       <c r="G56" s="100" t="s">
         <v>224</v>
       </c>
@@ -10431,7 +10428,7 @@
         <f>BS!$C79*C65</f>
         <v>0</v>
       </c>
-      <c r="E57" s="313"/>
+      <c r="E57" s="312"/>
       <c r="G57" s="198">
         <f>Data!C56</f>
         <v>0</v>
@@ -10486,7 +10483,7 @@
         <f>BS!$C68*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="313"/>
+      <c r="E58" s="312"/>
       <c r="G58" s="198">
         <f>Data!C55</f>
         <v>639</v>
@@ -10541,7 +10538,7 @@
         <f>BS!$C81*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="313"/>
+      <c r="E59" s="312"/>
       <c r="G59" s="198">
         <f>Data!C57</f>
         <v>0</v>
@@ -10596,7 +10593,7 @@
         <f>SUM(C57:C59)</f>
         <v>0</v>
       </c>
-      <c r="E60" s="313"/>
+      <c r="E60" s="312"/>
       <c r="G60" s="188">
         <f t="shared" ref="G60:Q60" si="21">IF(G4="","",SUM(G57:G59))</f>
         <v>639</v>
@@ -10647,10 +10644,10 @@
       <c r="B61" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="308">
-        <v>0</v>
-      </c>
-      <c r="E61" s="311" t="s">
+      <c r="C61" s="307">
+        <v>0</v>
+      </c>
+      <c r="E61" s="310" t="s">
         <v>384</v>
       </c>
       <c r="G61" s="198">
@@ -10707,7 +10704,7 @@
         <f>C60+C61</f>
         <v>0</v>
       </c>
-      <c r="E62" s="313"/>
+      <c r="E62" s="312"/>
       <c r="G62" s="188">
         <f t="shared" ref="G62:Q62" si="22">IF(G4="","",G60+G61)</f>
         <v>248317</v>
@@ -10755,14 +10752,14 @@
     </row>
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
-      <c r="E63" s="313"/>
+      <c r="E63" s="312"/>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="313"/>
+      <c r="E64" s="312"/>
       <c r="G64" s="100" t="s">
         <v>224</v>
       </c>
@@ -10776,7 +10773,7 @@
         <f>G65</f>
         <v>0</v>
       </c>
-      <c r="E65" s="313"/>
+      <c r="E65" s="312"/>
       <c r="G65" s="23">
         <f>IFERROR(G57/BS!$C$67,0)</f>
         <v>0</v>
@@ -10801,7 +10798,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="313"/>
+      <c r="E66" s="312"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$68,0)</f>
         <v>0</v>
@@ -10826,7 +10823,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="313"/>
+      <c r="E67" s="312"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$81,0)</f>
         <v>0</v>
@@ -10852,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="9"/>
-      <c r="E68" s="318"/>
+      <c r="E68" s="317"/>
       <c r="F68" s="9"/>
       <c r="G68" s="72">
         <f>G60/BS!C70</f>
@@ -10902,7 +10899,7 @@
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
-      <c r="E71" s="310"/>
+      <c r="E71" s="309"/>
       <c r="F71" s="27"/>
       <c r="G71" s="100"/>
       <c r="H71" s="12"/>
@@ -10926,7 +10923,7 @@
         <v>0.85797166426114502</v>
       </c>
       <c r="D72" s="27"/>
-      <c r="E72" s="310"/>
+      <c r="E72" s="309"/>
       <c r="F72" s="27"/>
       <c r="G72" s="6">
         <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G5/G$4))</f>
@@ -10983,7 +10980,7 @@
         <v>0.14202833573885504</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="310"/>
+      <c r="E73" s="309"/>
       <c r="F73" s="27"/>
       <c r="G73" s="66">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11040,7 +11037,7 @@
         <v>2.5247654924924864E-2</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="310"/>
+      <c r="E74" s="309"/>
       <c r="F74" s="27"/>
       <c r="G74" s="6">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11097,7 +11094,7 @@
         <v>0.11678068081393016</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="310"/>
+      <c r="E75" s="309"/>
       <c r="F75" s="27"/>
       <c r="G75" s="66">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11154,7 +11151,7 @@
         <v>3.8696911822371505E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="310"/>
+      <c r="E76" s="309"/>
       <c r="F76" s="27"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",G9/G$4)</f>
@@ -11211,7 +11208,7 @@
         <v>3.8696911822371505E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="311" t="s">
+      <c r="E77" s="310" t="s">
         <v>385</v>
       </c>
       <c r="F77" s="27"/>
@@ -11270,7 +11267,7 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="310"/>
+      <c r="E78" s="309"/>
       <c r="F78" s="27"/>
       <c r="G78" s="66">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",G11/G$4)</f>
@@ -11327,7 +11324,7 @@
         <v>2.5567530880774257E-3</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="310"/>
+      <c r="E79" s="309"/>
       <c r="F79" s="27"/>
       <c r="G79" s="6">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11384,7 +11381,7 @@
         <v>0.11422392772585273</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="310"/>
+      <c r="E80" s="309"/>
       <c r="F80" s="27"/>
       <c r="G80" s="66">
         <f>IF(G$4="","",G13/G$4)</f>
@@ -11441,7 +11438,7 @@
         <v>2.8555981931463182E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="310"/>
+      <c r="E81" s="309"/>
       <c r="F81" s="27"/>
       <c r="G81" s="6">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11494,12 +11491,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C82" s="309">
+      <c r="C82" s="308">
         <f>MIN(BS!C62,MAX(G82:K82))</f>
         <v>0</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="310"/>
+      <c r="E82" s="309"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",-G15/G$4)</f>
@@ -11556,7 +11553,7 @@
         <v>8.5667945794389549E-2</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="310"/>
+      <c r="E83" s="309"/>
       <c r="F83" s="27"/>
       <c r="G83" s="66">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11608,11 +11605,11 @@
       <c r="B84" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C84" s="309">
+      <c r="C84" s="308">
         <v>0</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="312" t="str">
+      <c r="E84" s="311" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11634,10 +11631,10 @@
       <c r="B85" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C85" s="309">
-        <v>0</v>
-      </c>
-      <c r="E85" s="312" t="str">
+      <c r="C85" s="308">
+        <v>0</v>
+      </c>
+      <c r="E85" s="311" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11663,7 +11660,7 @@
         <v>8.5667945794389549E-2</v>
       </c>
       <c r="D86" s="77"/>
-      <c r="E86" s="310"/>
+      <c r="E86" s="309"/>
       <c r="F86" s="77"/>
       <c r="G86" s="66">
         <f t="shared" ref="G86:Q86" si="35">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11712,14 +11709,14 @@
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
-      <c r="E87" s="313"/>
+      <c r="E87" s="312"/>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E88" s="313"/>
+      <c r="E88" s="312"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
@@ -11731,7 +11728,7 @@
         <f>G89</f>
         <v>1.36</v>
       </c>
-      <c r="E89" s="313"/>
+      <c r="E89" s="312"/>
       <c r="G89" s="116">
         <f>Data!C64</f>
         <v>1.36</v>
@@ -11787,7 +11784,7 @@
         <f>C89*Common_Shares/$C$3</f>
         <v>798466.67599999998</v>
       </c>
-      <c r="E90" s="313"/>
+      <c r="E90" s="312"/>
       <c r="G90" s="76">
         <f t="shared" ref="G90:Q90" si="36">IF(G$4="","",G89*Common_Shares/$C$3)</f>
         <v>798466.67599999998</v>
@@ -11842,7 +11839,7 @@
         <f>C89/(C19*$C$3/Common_Shares)</f>
         <v>0.77828064251671092</v>
       </c>
-      <c r="E91" s="313"/>
+      <c r="E91" s="312"/>
       <c r="G91" s="175">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G89/(G19*$C$3/Common_Shares))</f>
         <v>0.61107268280139349</v>
@@ -11897,7 +11894,7 @@
         <f>C89/Market_Price</f>
         <v>9.0066225165562924E-2</v>
       </c>
-      <c r="E92" s="313"/>
+      <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
         <v>9.0066225165562924E-2</v>
@@ -11945,7 +11942,7 @@
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
-      <c r="E93" s="313"/>
+      <c r="E93" s="312"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
@@ -11954,7 +11951,7 @@
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
-      <c r="E94" s="310"/>
+      <c r="E94" s="309"/>
       <c r="F94" s="27"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
@@ -11978,7 +11975,7 @@
         <v>-0.2185980886550547</v>
       </c>
       <c r="D95" s="27"/>
-      <c r="E95" s="310"/>
+      <c r="E95" s="309"/>
       <c r="F95" s="27"/>
       <c r="G95" s="6">
         <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
@@ -12035,7 +12032,7 @@
         <v>-0.16275524177674994</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="310"/>
+      <c r="E96" s="309"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G13/H13-1)</f>
@@ -12113,7 +12110,7 @@
       <c r="B99" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="313"/>
+      <c r="E99" s="312"/>
       <c r="G99" s="100" t="s">
         <v>224</v>
       </c>
@@ -12128,7 +12125,7 @@
         <v>16854064</v>
       </c>
       <c r="D100" s="26"/>
-      <c r="E100" s="314"/>
+      <c r="E100" s="313"/>
       <c r="F100" s="26"/>
       <c r="G100" s="187">
         <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
@@ -12185,7 +12182,7 @@
         <v>265773</v>
       </c>
       <c r="D101" s="91"/>
-      <c r="E101" s="315"/>
+      <c r="E101" s="314"/>
       <c r="F101" s="91"/>
       <c r="G101" s="189">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12242,7 +12239,7 @@
         <v>9672256</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="315"/>
+      <c r="E102" s="314"/>
       <c r="F102" s="91"/>
       <c r="G102" s="189">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12299,7 +12296,7 @@
         <v>3990166</v>
       </c>
       <c r="D103" s="26"/>
-      <c r="E103" s="314"/>
+      <c r="E103" s="313"/>
       <c r="F103" s="26"/>
       <c r="G103" s="187">
         <f>Data!C78</f>
@@ -12356,7 +12353,7 @@
         <v>12863898</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="314"/>
+      <c r="E104" s="313"/>
       <c r="F104" s="26"/>
       <c r="G104" s="187">
         <f>Data!C79</f>
@@ -12405,7 +12402,7 @@
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
-      <c r="E105" s="313"/>
+      <c r="E105" s="312"/>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
@@ -12414,7 +12411,7 @@
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
-      <c r="E106" s="314"/>
+      <c r="E106" s="313"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
         <v>224</v>
@@ -12440,7 +12437,7 @@
         <v>2.2192623484686036E-2</v>
       </c>
       <c r="D107" s="26"/>
-      <c r="E107" s="314"/>
+      <c r="E107" s="313"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97">
         <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
@@ -12497,7 +12494,7 @@
         <v>0.80765441055146836</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="314"/>
+      <c r="E108" s="313"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12554,7 +12551,7 @@
         <v>0</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="314"/>
+      <c r="E109" s="313"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12573,7 +12570,7 @@
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
-      <c r="E110" s="313"/>
+      <c r="E110" s="312"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
@@ -12582,7 +12579,7 @@
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
-      <c r="E111" s="316"/>
+      <c r="E111" s="315"/>
       <c r="F111" s="55"/>
       <c r="G111" s="23" t="str">
         <f>IFERROR(IF(#REF!*G113*(1/#REF!)=G115,"","Error"),"")</f>
@@ -12638,7 +12635,7 @@
         <f>C80</f>
         <v>0.11422392772585273</v>
       </c>
-      <c r="E112" s="313"/>
+      <c r="E112" s="312"/>
       <c r="G112" s="23">
         <f t="shared" ref="G112:Q112" si="44">G80</f>
         <v>0.10660537981237328</v>
@@ -12692,7 +12689,7 @@
         <f>C4/C100</f>
         <v>0.71055479556740742</v>
       </c>
-      <c r="E113" s="313"/>
+      <c r="E113" s="312"/>
       <c r="G113" s="42">
         <f t="shared" ref="G113:Q113" si="45">IF(G4="","",G4/G100)</f>
         <v>0.90933332162498015</v>
@@ -12747,7 +12744,7 @@
         <v>1.3101832741522048</v>
       </c>
       <c r="D114" s="11"/>
-      <c r="E114" s="317"/>
+      <c r="E114" s="316"/>
       <c r="F114" s="11"/>
       <c r="G114" s="15">
         <f t="shared" ref="G114:Q114" si="46">IF(G$4="","",G100/G104)</f>
@@ -12804,7 +12801,7 @@
         <v>0.10871779326358874</v>
       </c>
       <c r="D115" s="106"/>
-      <c r="E115" s="316"/>
+      <c r="E115" s="315"/>
       <c r="F115" s="106"/>
       <c r="G115" s="105">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G8/G104)</f>
@@ -12900,7 +12897,7 @@
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
-      <c r="E118" s="310"/>
+      <c r="E118" s="309"/>
       <c r="F118" s="27"/>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
@@ -12925,7 +12922,7 @@
         <v>1.7474416369938157</v>
       </c>
       <c r="D119" s="27"/>
-      <c r="E119" s="310"/>
+      <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -12982,7 +12979,7 @@
         <v>0.11572461172144474</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="310"/>
+      <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
@@ -13811,10 +13808,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="335" t="s">
+      <c r="E6" s="338" t="s">
         <v>259</v>
       </c>
-      <c r="F6" s="335"/>
+      <c r="F6" s="338"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13829,8 +13826,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
+      <c r="E7" s="338"/>
+      <c r="F7" s="338"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13845,8 +13842,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="335"/>
-      <c r="F8" s="335"/>
+      <c r="E8" s="338"/>
+      <c r="F8" s="338"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13861,8 +13858,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
+      <c r="E9" s="338"/>
+      <c r="F9" s="338"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15259,7 +15256,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I90"/>
+  <dimension ref="B2:I92"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -15311,8 +15308,8 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.36</v>
+        <f t="shared" ref="I4:I13" ca="1" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15320,8 +15317,8 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" si="0"/>
-        <v>1.36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15340,8 +15337,8 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" si="0"/>
-        <v>19.803897113903751</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>148.73309483406626</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15356,16 +15353,16 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="337" t="str">
+      <c r="E7" s="340" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="337"/>
+      <c r="F7" s="340"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15381,13 +15378,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
+      <c r="E8" s="340"/>
+      <c r="F8" s="340"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15403,24 +15400,24 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
+      <c r="E9" s="340"/>
+      <c r="F9" s="340"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="337"/>
-      <c r="F10" s="337"/>
+      <c r="E10" s="340"/>
+      <c r="F10" s="340"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15428,13 +15425,13 @@
       <c r="B11" s="164" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="337"/>
-      <c r="F11" s="337"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15447,13 +15444,13 @@
         <v>0.20035451325595277</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15465,13 +15462,13 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="337"/>
-      <c r="F13" s="337"/>
+      <c r="E13" s="340"/>
+      <c r="F13" s="340"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15483,8 +15480,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>5.3908780398304268E-2</v>
       </c>
-      <c r="E14" s="337"/>
-      <c r="F14" s="337"/>
+      <c r="E14" s="340"/>
+      <c r="F14" s="340"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15510,21 +15507,21 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="337" t="s">
+      <c r="E18" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="F18" s="338"/>
+      <c r="F18" s="341"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="338"/>
-      <c r="F19" s="338"/>
+      <c r="E19" s="341"/>
+      <c r="F19" s="341"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
         <v>337</v>
       </c>
-      <c r="E20" s="338"/>
-      <c r="F20" s="338"/>
+      <c r="E20" s="341"/>
+      <c r="F20" s="341"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15538,8 +15535,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="338"/>
-      <c r="F21" s="338"/>
+      <c r="E21" s="341"/>
+      <c r="F21" s="341"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15553,8 +15550,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="338"/>
-      <c r="F22" s="338"/>
+      <c r="E22" s="341"/>
+      <c r="F22" s="341"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
@@ -15574,8 +15571,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15585,8 +15582,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15600,8 +15597,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="336"/>
-      <c r="F27" s="336"/>
+      <c r="E27" s="339"/>
+      <c r="F27" s="339"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15611,8 +15608,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="336"/>
-      <c r="F28" s="336"/>
+      <c r="E28" s="339"/>
+      <c r="F28" s="339"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
@@ -15632,8 +15629,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
+      <c r="E31" s="339"/>
+      <c r="F31" s="339"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15643,8 +15640,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15658,8 +15655,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="336"/>
-      <c r="F33" s="336"/>
+      <c r="E33" s="339"/>
+      <c r="F33" s="339"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15669,8 +15666,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="336"/>
-      <c r="F34" s="336"/>
+      <c r="E34" s="339"/>
+      <c r="F34" s="339"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
@@ -15690,8 +15687,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="336"/>
-      <c r="F37" s="336"/>
+      <c r="E37" s="339"/>
+      <c r="F37" s="339"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15701,8 +15698,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="336"/>
-      <c r="F38" s="336"/>
+      <c r="E38" s="339"/>
+      <c r="F38" s="339"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15716,8 +15713,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="336"/>
-      <c r="F39" s="336"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15728,8 +15725,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="336"/>
-      <c r="F40" s="336"/>
+      <c r="E40" s="339"/>
+      <c r="F40" s="339"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15791,8 +15788,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="336"/>
+      <c r="E49" s="339"/>
+      <c r="F49" s="339"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15802,8 +15799,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="336"/>
-      <c r="F50" s="336"/>
+      <c r="E50" s="339"/>
+      <c r="F50" s="339"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15817,8 +15814,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="336"/>
-      <c r="F51" s="336"/>
+      <c r="E51" s="339"/>
+      <c r="F51" s="339"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15828,8 +15825,8 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="336"/>
-      <c r="F52" s="336"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
@@ -15849,8 +15846,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="336"/>
-      <c r="F55" s="336"/>
+      <c r="E55" s="339"/>
+      <c r="F55" s="339"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15860,8 +15857,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="336"/>
-      <c r="F56" s="336"/>
+      <c r="E56" s="339"/>
+      <c r="F56" s="339"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15875,8 +15872,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="336"/>
-      <c r="F57" s="336"/>
+      <c r="E57" s="339"/>
+      <c r="F57" s="339"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15886,8 +15883,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="336"/>
-      <c r="F58" s="336"/>
+      <c r="E58" s="339"/>
+      <c r="F58" s="339"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15904,7 +15901,8 @@
       <c r="E60" s="103" t="s">
         <v>330</v>
       </c>
-      <c r="F60" s="324">
+      <c r="F60" s="322">
+        <f ca="1">Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -15921,7 +15919,7 @@
       <c r="B63" s="112" t="s">
         <v>338</v>
       </c>
-      <c r="E63" s="291" t="s">
+      <c r="E63" s="290" t="s">
         <v>348</v>
       </c>
     </row>
@@ -15933,7 +15931,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="290" t="s">
+      <c r="E64" s="289" t="s">
         <v>349</v>
       </c>
     </row>
@@ -15945,7 +15943,7 @@
         <v>6.9371044268871302E-3</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="290" t="s">
+      <c r="E65" s="289" t="s">
         <v>350</v>
       </c>
     </row>
@@ -15961,7 +15959,7 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="290" t="s">
+      <c r="E66" s="289" t="s">
         <v>351</v>
       </c>
     </row>
@@ -15969,7 +15967,7 @@
       <c r="B68" s="112" t="s">
         <v>325</v>
       </c>
-      <c r="E68" s="291" t="s">
+      <c r="E68" s="290" t="s">
         <v>352</v>
       </c>
     </row>
@@ -15991,7 +15989,7 @@
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="290" t="s">
+      <c r="E70" s="289" t="s">
         <v>328</v>
       </c>
     </row>
@@ -16003,7 +16001,7 @@
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="290"/>
+      <c r="E71" s="289"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
@@ -16027,32 +16025,22 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
         <v>130</v>
       </c>
-      <c r="E75" s="325" t="s">
-        <v>367</v>
-      </c>
-      <c r="F75" s="323"/>
-    </row>
-    <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="283" t="s">
         <v>331</v>
       </c>
       <c r="C76" s="282">
-        <f>F60</f>
+        <f ca="1">F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
-      <c r="E76" s="326" t="s">
-        <v>368</v>
-      </c>
-      <c r="F76" s="323" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
@@ -16064,20 +16052,6 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E77" s="327" t="s">
-        <v>368</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E78" s="328" t="s">
-        <v>368</v>
-      </c>
-      <c r="F78" s="323" t="s">
-        <v>371</v>
-      </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
@@ -16093,35 +16067,35 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
         <v>126</v>
       </c>
       <c r="C81" s="120">
-        <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.8648148148148147</v>
+        <f ca="1">PV(C80, C76, -C77, 0)</f>
+        <v>1.2217592592592592</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
       <c r="F81" s="103"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
         <v>127</v>
       </c>
       <c r="C82" s="120">
-        <f>C60/(1+C80)^C76</f>
-        <v>10.673551570546152</v>
+        <f ca="1">C60/(1+C80)^C76</f>
+        <v>85.736744695640198</v>
       </c>
       <c r="D82" s="120"/>
     </row>
-    <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
         <v>106</v>
       </c>
       <c r="C83" s="115">
-        <f>C81+C82</f>
-        <v>13.538366385360966</v>
+        <f ca="1">C81+C82</f>
+        <v>86.958503954899456</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16131,19 +16105,19 @@
         <v>131</v>
       </c>
       <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.26597040193012134</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <f ca="1">(C83/C60-1)</f>
+        <v>-0.41304969665133007</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E84" s="124"/>
     </row>
-    <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
         <v>334</v>
       </c>
@@ -16156,20 +16130,55 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
         <v>332</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15361989461854253</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+        <v>1.162487831816041</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="103"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C90" s="121"/>
+    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E89" s="331" t="s">
+        <v>367</v>
+      </c>
+      <c r="F89" s="328"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="327"/>
+    </row>
+    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E90" s="324" t="s">
+        <v>368</v>
+      </c>
+      <c r="F90" s="329" t="s">
+        <v>369</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="327"/>
+    </row>
+    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E91" s="325" t="s">
+        <v>368</v>
+      </c>
+      <c r="F91" s="329" t="s">
+        <v>370</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="327"/>
+    </row>
+    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E92" s="326" t="s">
+        <v>368</v>
+      </c>
+      <c r="F92" s="330" t="s">
+        <v>371</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="327"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19098A12-D83B-4777-82BA-0B2D008FAE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBC34D5-3D8B-4476-8899-4D6F10AE5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3317,20 +3317,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3744,13 +3744,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="332" t="s">
+      <c r="B12" s="333" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="332"/>
-      <c r="D12" s="332"/>
-      <c r="E12" s="332"/>
-      <c r="F12" s="332"/>
+      <c r="C12" s="333"/>
+      <c r="D12" s="333"/>
+      <c r="E12" s="333"/>
+      <c r="F12" s="333"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3816,15 +3816,14 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
-        <f ca="1">C123</f>
-        <v>86.958503954899456</v>
+        <f>C123</f>
+        <v>13.538366385360966</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
       </c>
       <c r="E20" s="323">
-        <f ca="1">Scenarios!C76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3833,7 +3832,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>1.162487831816041</v>
+        <v>0.15361989461854253</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3853,22 +3852,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="332" t="s">
+      <c r="B25" s="333" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="332"/>
-      <c r="D25" s="332"/>
-      <c r="E25" s="332"/>
-      <c r="F25" s="332"/>
+      <c r="C25" s="333"/>
+      <c r="D25" s="333"/>
+      <c r="E25" s="333"/>
+      <c r="F25" s="333"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="336" t="s">
+      <c r="B26" s="334" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="336"/>
-      <c r="D26" s="336"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="334"/>
+      <c r="E26" s="334"/>
+      <c r="F26" s="334"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3880,13 +3879,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="334" t="s">
+      <c r="B29" s="332" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="334"/>
-      <c r="D29" s="334"/>
-      <c r="E29" s="334"/>
-      <c r="F29" s="334"/>
+      <c r="C29" s="332"/>
+      <c r="D29" s="332"/>
+      <c r="E29" s="332"/>
+      <c r="F29" s="332"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3906,13 +3905,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="334" t="s">
+      <c r="B32" s="332" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="334"/>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="332"/>
+      <c r="E32" s="332"/>
+      <c r="F32" s="332"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3941,13 +3940,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="334" t="s">
+      <c r="B36" s="332" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="334"/>
-      <c r="D36" s="334"/>
-      <c r="E36" s="334"/>
-      <c r="F36" s="334"/>
+      <c r="C36" s="332"/>
+      <c r="D36" s="332"/>
+      <c r="E36" s="332"/>
+      <c r="F36" s="332"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3963,13 +3962,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="334" t="s">
+      <c r="B39" s="332" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="334"/>
-      <c r="D39" s="334"/>
-      <c r="E39" s="334"/>
-      <c r="F39" s="334"/>
+      <c r="C39" s="332"/>
+      <c r="D39" s="332"/>
+      <c r="E39" s="332"/>
+      <c r="F39" s="332"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4003,13 +4002,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="334" t="s">
+      <c r="B45" s="332" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="334"/>
-      <c r="D45" s="334"/>
-      <c r="E45" s="334"/>
-      <c r="F45" s="334"/>
+      <c r="C45" s="332"/>
+      <c r="D45" s="332"/>
+      <c r="E45" s="332"/>
+      <c r="F45" s="332"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4025,13 +4024,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="334" t="s">
+      <c r="B48" s="332" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="335"/>
-      <c r="D48" s="335"/>
-      <c r="E48" s="335"/>
-      <c r="F48" s="335"/>
+      <c r="C48" s="336"/>
+      <c r="D48" s="336"/>
+      <c r="E48" s="336"/>
+      <c r="F48" s="336"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4060,13 +4059,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="332" t="s">
+      <c r="B52" s="333" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="332"/>
-      <c r="D52" s="332"/>
-      <c r="E52" s="332"/>
-      <c r="F52" s="332"/>
+      <c r="C52" s="333"/>
+      <c r="D52" s="333"/>
+      <c r="E52" s="333"/>
+      <c r="F52" s="333"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4127,22 +4126,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="334" t="s">
+      <c r="B60" s="332" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="334"/>
-      <c r="D60" s="334"/>
-      <c r="E60" s="334"/>
-      <c r="F60" s="334"/>
+      <c r="C60" s="332"/>
+      <c r="D60" s="332"/>
+      <c r="E60" s="332"/>
+      <c r="F60" s="332"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="336" t="s">
+      <c r="B61" s="334" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="336"/>
-      <c r="D61" s="336"/>
-      <c r="E61" s="336"/>
-      <c r="F61" s="336"/>
+      <c r="C61" s="334"/>
+      <c r="D61" s="334"/>
+      <c r="E61" s="334"/>
+      <c r="F61" s="334"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4194,22 +4193,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="332" t="s">
+      <c r="B69" s="333" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="332"/>
-      <c r="D69" s="332"/>
-      <c r="E69" s="332"/>
-      <c r="F69" s="332"/>
+      <c r="C69" s="333"/>
+      <c r="D69" s="333"/>
+      <c r="E69" s="333"/>
+      <c r="F69" s="333"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="332" t="s">
+      <c r="B70" s="333" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="332"/>
-      <c r="D70" s="332"/>
-      <c r="E70" s="332"/>
-      <c r="F70" s="332"/>
+      <c r="C70" s="333"/>
+      <c r="D70" s="333"/>
+      <c r="E70" s="333"/>
+      <c r="F70" s="333"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4246,13 +4245,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="332" t="s">
+      <c r="B77" s="333" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="332"/>
-      <c r="D77" s="332"/>
-      <c r="E77" s="332"/>
-      <c r="F77" s="332"/>
+      <c r="C77" s="333"/>
+      <c r="D77" s="333"/>
+      <c r="E77" s="333"/>
+      <c r="F77" s="333"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4366,13 +4365,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="332" t="s">
+      <c r="B93" s="333" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="332"/>
-      <c r="D93" s="332"/>
-      <c r="E93" s="332"/>
-      <c r="F93" s="332"/>
+      <c r="C93" s="333"/>
+      <c r="D93" s="333"/>
+      <c r="E93" s="333"/>
+      <c r="F93" s="333"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4398,13 +4397,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="334" t="s">
+      <c r="B99" s="332" t="s">
         <v>374</v>
       </c>
-      <c r="C99" s="334"/>
-      <c r="D99" s="334"/>
-      <c r="E99" s="334"/>
-      <c r="F99" s="334"/>
+      <c r="C99" s="332"/>
+      <c r="D99" s="332"/>
+      <c r="E99" s="332"/>
+      <c r="F99" s="332"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4566,13 +4565,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="333" t="s">
+      <c r="B114" s="335" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="333"/>
-      <c r="D114" s="333"/>
-      <c r="E114" s="333"/>
-      <c r="F114" s="333"/>
+      <c r="C114" s="335"/>
+      <c r="D114" s="335"/>
+      <c r="E114" s="335"/>
+      <c r="F114" s="335"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4584,7 +4583,7 @@
         <v>280</v>
       </c>
       <c r="C116" s="258">
-        <f ca="1">E20</f>
+        <f>E20</f>
         <v>3</v>
       </c>
     </row>
@@ -4617,22 +4616,22 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B121" s="243" t="str">
-        <f ca="1">"PV("&amp;C116&amp;" yrs of Dividends)"</f>
+        <f>"PV("&amp;C116&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C121" s="247">
-        <f ca="1">Scenarios!C81</f>
-        <v>1.2217592592592592</v>
+        <f>Scenarios!C81</f>
+        <v>2.8648148148148147</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B122" s="243" t="str">
-        <f ca="1">"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
+        <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C122" s="247">
-        <f ca="1">Scenarios!C82</f>
-        <v>85.736744695640198</v>
+        <f>Scenarios!C82</f>
+        <v>10.673551570546152</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4640,8 +4639,8 @@
         <v>275</v>
       </c>
       <c r="C123" s="246">
-        <f ca="1">Scenarios!C83</f>
-        <v>86.958503954899456</v>
+        <f>Scenarios!C83</f>
+        <v>13.538366385360966</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4653,18 +4652,12 @@
         <v>277</v>
       </c>
       <c r="C124" s="158">
-        <f ca="1">Scenarios!F83</f>
-        <v>-0.41304969665133007</v>
+        <f>Scenarios!F83</f>
+        <v>-0.26597040193012134</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4678,6 +4671,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -15308,8 +15307,8 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" ca="1" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.57999999999999996</v>
+        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <v>1.36</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -15317,8 +15316,8 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" ca="1" si="0"/>
-        <v>0.57999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>1.36</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -15337,8 +15336,8 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" ca="1" si="0"/>
-        <v>148.73309483406626</v>
+        <f t="shared" si="0"/>
+        <v>19.803897113903751</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15362,7 +15361,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15384,7 +15383,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15406,7 +15405,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15417,7 +15416,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15431,7 +15430,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15450,7 +15449,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15468,7 +15467,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15902,7 +15901,7 @@
         <v>330</v>
       </c>
       <c r="F60" s="322">
-        <f ca="1">Thesis!E20</f>
+        <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -16035,7 +16034,7 @@
         <v>331</v>
       </c>
       <c r="C76" s="282">
-        <f ca="1">F60</f>
+        <f>F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
@@ -16072,8 +16071,8 @@
         <v>126</v>
       </c>
       <c r="C81" s="120">
-        <f ca="1">PV(C80, C76, -C77, 0)</f>
-        <v>1.2217592592592592</v>
+        <f>PV(C80, C76, -C77, 0)</f>
+        <v>2.8648148148148147</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16084,8 +16083,8 @@
         <v>127</v>
       </c>
       <c r="C82" s="120">
-        <f ca="1">C60/(1+C80)^C76</f>
-        <v>85.736744695640198</v>
+        <f>C60/(1+C80)^C76</f>
+        <v>10.673551570546152</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16094,8 +16093,8 @@
         <v>106</v>
       </c>
       <c r="C83" s="115">
-        <f ca="1">C81+C82</f>
-        <v>86.958503954899456</v>
+        <f>C81+C82</f>
+        <v>13.538366385360966</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16105,8 +16104,8 @@
         <v>131</v>
       </c>
       <c r="F83" s="270">
-        <f ca="1">(C83/C60-1)</f>
-        <v>-0.41304969665133007</v>
+        <f>(C83/C60-1)</f>
+        <v>-0.26597040193012134</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16136,7 +16135,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>1.162487831816041</v>
+        <v>0.15361989461854253</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBC34D5-3D8B-4476-8899-4D6F10AE5173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F47554-CF36-4864-88DC-32637283ADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F47554-CF36-4864-88DC-32637283ADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE814515-5CFA-4AA8-BEEB-0EB8D12E6156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1928,6 +1928,31 @@
   </si>
   <si>
     <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Prompt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I need to categorize the balance sheet items from the provided financial statements into the exact structure below. Follow these steps:
+1.	Identify Line Items: Extract all assets, liabilities, and equity line items from the text. Preserve their exact wording (e.g., ‘Trade Receivables’ vs. ‘Accounts Receivable’).
+2.	Map to Categories: Classify each item into the pre-defined structure below. Use the descriptions to resolve ambiguities.
+3.	Flag Uncertainties: Note items that don’t fit cleanly or require assumptions.
+4.	Format Output: Provide a table with columns: PDF Line Item | Category | Subcategory | Amount. 
+STRUCTURE TO FOLLOW (use exact names):
+•	ST Operating Assets: ST AR, Operating ST Financial Assets, Inventory, Prepayments and Contract Assets, ST DTA, Other ST Assets, Operating ST Assets
+•	LT Operating Assets: LT AR, Operating LT Financial Assets, PP&amp;E &amp; Right of Use Assets, Biological assets, Intangible assets, LT DTA, Other assets &amp; Goodwill
+•	ST Non-Operating Assets: Cash and cash equivalents, Restricted cash, Securities with stable income, Other Securities, Properties with stable income, Other Properties
+•	LT Non-Operating Assets: LT Deposits, Securities with stable income, Other Securities, JV or associate with stable income, Other JV or associate, Properties with stable income, Other Properties
+•	ST Liabilities: ST Borrowing, ST Lease liabilities, ST SH Loan, ST Financial Liabilities, ST Interest-bearing Debt, Other ST liabilities
+•	LT Liabilities: LT Borrowing, LT Lease liabilities, LT SH Loan, LT Financial Liabilities, LT Interest-bearing Debt, Other LT liabilities
+•	Equity: Minority Interest (NCI), Common Equity
+EXAMPLE:
+•	If the PDF says “Property, Plant, and Equipment – $50M”, map to:
+PP&amp;E &amp; Right of Use Assets | LT Operating Assets | PP&amp;E &amp; Right of Use Assets | \$50,000,000
+•	If the PDF says “Marketable Securities – $10M”, map to:
+Other Securities | ST Non-Operating Assets | Other Securities | \$10,000,000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3678,10 +3703,10 @@
         <v>353</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -7022,7 +7047,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H89"/>
+  <dimension ref="B1:H93"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -8275,7 +8300,38 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="91" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="81" t="s">
+        <v>376</v>
+      </c>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
+      <c r="H91" s="37"/>
+    </row>
+    <row r="92" spans="2:8" ht="212" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="332" t="s">
+        <v>377</v>
+      </c>
+      <c r="C92" s="332"/>
+      <c r="D92" s="332"/>
+      <c r="E92" s="332"/>
+      <c r="F92" s="332"/>
+      <c r="G92" s="332"/>
+      <c r="H92" s="332"/>
+    </row>
+    <row r="93" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="str">
+        <f>"Please find the financial statement text below. The output should use a scaling factor of "&amp;H1</f>
+        <v>Please find the financial statement text below. The output should use a scaling factor of 1000</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B92:H92"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="71" orientation="portrait" r:id="rId1"/>
@@ -9131,7 +9187,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="311" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9157,7 +9213,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="311" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9485,7 +9541,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9545,7 +9601,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9669,7 +9725,7 @@
         <v>-302359.25</v>
       </c>
       <c r="E33" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9727,7 +9783,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -10035,7 +10091,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="309" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10305,7 +10361,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E52" s="309" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10332,7 +10388,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E53" s="309" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10647,7 +10703,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="310" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -11208,7 +11264,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="310" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE814515-5CFA-4AA8-BEEB-0EB8D12E6156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713708FB-1C68-415D-8E82-D914BFB0521E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="387">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1646,10 +1646,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3342,20 +3338,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3668,10 +3664,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="292" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F1" s="293" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3700,13 +3696,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>378</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3714,7 +3710,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>15.1</v>
+        <v>14.86</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3733,7 +3729,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C8" s="287">
         <v>6</v>
@@ -3759,7 +3755,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8865.3285350000006</v>
+        <v>8724.4226510000008</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3769,24 +3765,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="333" t="s">
+      <c r="B12" s="332" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="333"/>
-      <c r="D12" s="333"/>
-      <c r="E12" s="333"/>
-      <c r="F12" s="333"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="332"/>
+      <c r="F12" s="332"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3822,7 +3818,7 @@
         <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3842,10 +3838,10 @@
       </c>
       <c r="C20" s="259">
         <f>C123</f>
-        <v>13.538366385360966</v>
+        <v>14.964393533646771</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E20" s="323">
         <v>3</v>
@@ -3853,11 +3849,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15361989461854253</v>
+        <v>0.20302018521144283</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3877,22 +3873,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="333" t="s">
+      <c r="B25" s="332" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="333"/>
-      <c r="D25" s="333"/>
-      <c r="E25" s="333"/>
-      <c r="F25" s="333"/>
+      <c r="C25" s="332"/>
+      <c r="D25" s="332"/>
+      <c r="E25" s="332"/>
+      <c r="F25" s="332"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="334" t="s">
+      <c r="B26" s="336" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="334"/>
-      <c r="D26" s="334"/>
-      <c r="E26" s="334"/>
-      <c r="F26" s="334"/>
+      <c r="C26" s="336"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3904,13 +3900,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="332" t="s">
+      <c r="B29" s="334" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="332"/>
-      <c r="D29" s="332"/>
-      <c r="E29" s="332"/>
-      <c r="F29" s="332"/>
+      <c r="C29" s="334"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3930,13 +3926,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="332" t="s">
+      <c r="B32" s="334" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="332"/>
-      <c r="D32" s="332"/>
-      <c r="E32" s="332"/>
-      <c r="F32" s="332"/>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3965,13 +3961,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="332" t="s">
+      <c r="B36" s="334" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="332"/>
-      <c r="D36" s="332"/>
-      <c r="E36" s="332"/>
-      <c r="F36" s="332"/>
+      <c r="C36" s="334"/>
+      <c r="D36" s="334"/>
+      <c r="E36" s="334"/>
+      <c r="F36" s="334"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3987,13 +3983,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="332" t="s">
+      <c r="B39" s="334" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="332"/>
-      <c r="D39" s="332"/>
-      <c r="E39" s="332"/>
-      <c r="F39" s="332"/>
+      <c r="C39" s="334"/>
+      <c r="D39" s="334"/>
+      <c r="E39" s="334"/>
+      <c r="F39" s="334"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4027,13 +4023,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="332" t="s">
+      <c r="B45" s="334" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="332"/>
-      <c r="D45" s="332"/>
-      <c r="E45" s="332"/>
-      <c r="F45" s="332"/>
+      <c r="C45" s="334"/>
+      <c r="D45" s="334"/>
+      <c r="E45" s="334"/>
+      <c r="F45" s="334"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4049,13 +4045,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="332" t="s">
+      <c r="B48" s="334" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="336"/>
-      <c r="D48" s="336"/>
-      <c r="E48" s="336"/>
-      <c r="F48" s="336"/>
+      <c r="C48" s="335"/>
+      <c r="D48" s="335"/>
+      <c r="E48" s="335"/>
+      <c r="F48" s="335"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4084,13 +4080,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="333" t="s">
+      <c r="B52" s="332" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="333"/>
-      <c r="D52" s="333"/>
-      <c r="E52" s="333"/>
-      <c r="F52" s="333"/>
+      <c r="C52" s="332"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4124,16 +4120,16 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>0.11572461172144474</v>
+        <v>0.11759364986499432</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="261" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>9.0066225165562924E-2</v>
+        <v>9.1520861372812928E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4151,22 +4147,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="332" t="s">
+      <c r="B60" s="334" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="332"/>
-      <c r="D60" s="332"/>
-      <c r="E60" s="332"/>
-      <c r="F60" s="332"/>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="334" t="s">
+      <c r="B61" s="336" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="334"/>
-      <c r="D61" s="334"/>
-      <c r="E61" s="334"/>
-      <c r="F61" s="334"/>
+      <c r="C61" s="336"/>
+      <c r="D61" s="336"/>
+      <c r="E61" s="336"/>
+      <c r="F61" s="336"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4175,7 +4171,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C64" s="321">
         <v>0.08</v>
@@ -4183,26 +4179,26 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C65" s="271">
         <f>IF(D65="Y",1%,0)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D65" s="295" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C66" s="271">
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D66" s="295" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
@@ -4211,29 +4207,29 @@
       </c>
       <c r="C67" s="271">
         <f>SUM(C64:C66)</f>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="333" t="s">
-        <v>315</v>
-      </c>
-      <c r="C69" s="333"/>
-      <c r="D69" s="333"/>
-      <c r="E69" s="333"/>
-      <c r="F69" s="333"/>
+      <c r="B69" s="332" t="s">
+        <v>314</v>
+      </c>
+      <c r="C69" s="332"/>
+      <c r="D69" s="332"/>
+      <c r="E69" s="332"/>
+      <c r="F69" s="332"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="333" t="s">
+      <c r="B70" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="333"/>
-      <c r="D70" s="333"/>
-      <c r="E70" s="333"/>
-      <c r="F70" s="333"/>
+      <c r="C70" s="332"/>
+      <c r="D70" s="332"/>
+      <c r="E70" s="332"/>
+      <c r="F70" s="332"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4249,7 +4245,7 @@
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>19.416018188820175</v>
+        <v>21.843020462422693</v>
       </c>
       <c r="D73" s="1" t="str">
         <f>Market_currency</f>
@@ -4270,13 +4266,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="333" t="s">
+      <c r="B77" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="333"/>
-      <c r="D77" s="333"/>
-      <c r="E77" s="333"/>
-      <c r="F77" s="333"/>
+      <c r="C77" s="332"/>
+      <c r="D77" s="332"/>
+      <c r="E77" s="332"/>
+      <c r="F77" s="332"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4390,13 +4386,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="333" t="s">
+      <c r="B93" s="332" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="333"/>
-      <c r="D93" s="333"/>
-      <c r="E93" s="333"/>
-      <c r="F93" s="333"/>
+      <c r="C93" s="332"/>
+      <c r="D93" s="332"/>
+      <c r="E93" s="332"/>
+      <c r="F93" s="332"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4404,7 +4400,7 @@
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4422,13 +4418,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="332" t="s">
-        <v>374</v>
-      </c>
-      <c r="C99" s="332"/>
-      <c r="D99" s="332"/>
-      <c r="E99" s="332"/>
-      <c r="F99" s="332"/>
+      <c r="B99" s="334" t="s">
+        <v>373</v>
+      </c>
+      <c r="C99" s="334"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4462,7 +4458,7 @@
       </c>
       <c r="E102" s="265" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>24.07 HKD</v>
+        <v>27 HKD</v>
       </c>
       <c r="F102" s="266">
         <f>Valuation_Model!F74</f>
@@ -4484,7 +4480,7 @@
       </c>
       <c r="E103" s="252" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>19.66 HKD</v>
+        <v>22.24 HKD</v>
       </c>
       <c r="F103" s="253">
         <f>Valuation_Model!F75</f>
@@ -4506,7 +4502,7 @@
       </c>
       <c r="E104" s="252" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>18.66 HKD</v>
+        <v>21.14 HKD</v>
       </c>
       <c r="F104" s="253">
         <f>Valuation_Model!F76</f>
@@ -4528,7 +4524,7 @@
       </c>
       <c r="E105" s="252" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>16.48 HKD</v>
+        <v>18.76 HKD</v>
       </c>
       <c r="F105" s="253">
         <f>Valuation_Model!F77</f>
@@ -4550,7 +4546,7 @@
       </c>
       <c r="E106" s="252" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>13.86 HKD</v>
+        <v>15.93 HKD</v>
       </c>
       <c r="F106" s="253">
         <f>Valuation_Model!F78</f>
@@ -4563,7 +4559,7 @@
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
-        <v>18.443897113903752</v>
+        <v>20.908072026141618</v>
       </c>
       <c r="D108" s="243" t="str">
         <f>Market_currency</f>
@@ -4572,7 +4568,7 @@
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="337" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C110" s="337"/>
       <c r="D110" s="337"/>
@@ -4590,13 +4586,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="335" t="s">
+      <c r="B114" s="333" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="335"/>
-      <c r="D114" s="335"/>
-      <c r="E114" s="335"/>
-      <c r="F114" s="335"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4656,7 +4652,7 @@
       </c>
       <c r="C122" s="247">
         <f>Scenarios!C82</f>
-        <v>10.673551570546152</v>
+        <v>12.099578718831955</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4665,7 +4661,7 @@
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
-        <v>13.538366385360966</v>
+        <v>14.964393533646771</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4678,11 +4674,17 @@
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
-        <v>-0.26597040193012134</v>
+        <v>-0.28427673699724165</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4696,12 +4698,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8010,7 +8006,7 @@
         <v>141</v>
       </c>
       <c r="D65" s="211" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F65" s="296" t="s">
         <v>63</v>
@@ -8077,7 +8073,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="294" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C72" s="268" t="s">
         <v>100</v>
@@ -8089,7 +8085,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C73" s="192">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8102,7 +8098,7 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="297" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C74" s="298">
         <f>-$C$66/C73</f>
@@ -8113,12 +8109,12 @@
         <v>2.2670106298197523</v>
       </c>
       <c r="F74" s="291" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C75" s="303"/>
       <c r="D75" s="302">
@@ -8126,12 +8122,12 @@
         <v>-881433.44972267561</v>
       </c>
       <c r="F75" s="291" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="299" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C76" s="300"/>
       <c r="D76" s="301">
@@ -8139,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="291" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8215,7 +8211,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8226,15 +8222,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="D85" s="278" t="s">
         <v>322</v>
-      </c>
-      <c r="D85" s="278" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="275" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8251,7 +8247,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="275" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8285,7 +8281,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
@@ -8302,7 +8298,7 @@
     </row>
     <row r="91" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B91" s="81" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C91" s="37"/>
       <c r="D91" s="37"/>
@@ -8312,15 +8308,15 @@
       <c r="H91" s="37"/>
     </row>
     <row r="92" spans="2:8" ht="212" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="332" t="s">
-        <v>377</v>
-      </c>
-      <c r="C92" s="332"/>
-      <c r="D92" s="332"/>
-      <c r="E92" s="332"/>
-      <c r="F92" s="332"/>
-      <c r="G92" s="332"/>
-      <c r="H92" s="332"/>
+      <c r="B92" s="334" t="s">
+        <v>376</v>
+      </c>
+      <c r="C92" s="334"/>
+      <c r="D92" s="334"/>
+      <c r="E92" s="334"/>
+      <c r="F92" s="334"/>
+      <c r="G92" s="334"/>
+      <c r="H92" s="334"/>
     </row>
     <row r="93" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="str">
@@ -9187,7 +9183,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="311" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9213,7 +9209,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="311" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9541,7 +9537,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="310" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9601,7 +9597,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="310" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9725,7 +9721,7 @@
         <v>-302359.25</v>
       </c>
       <c r="E33" s="310" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9783,7 +9779,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="310" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -10091,7 +10087,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="309" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10361,7 +10357,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E52" s="309" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10388,7 +10384,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E53" s="309" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10703,7 +10699,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="310" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -11264,7 +11260,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="310" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
@@ -11943,32 +11939,32 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>9.0066225165562924E-2</v>
+        <v>9.1520861372812928E-2</v>
       </c>
       <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>9.0066225165562924E-2</v>
+        <v>9.1520861372812928E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
-        <v>7.2847682119205309E-2</v>
+        <v>7.4024226110363398E-2</v>
       </c>
       <c r="I92" s="23">
         <f t="shared" si="38"/>
-        <v>7.2847682119205309E-2</v>
+        <v>7.4024226110363398E-2</v>
       </c>
       <c r="J92" s="23">
         <f t="shared" si="38"/>
-        <v>6.6225165562913912E-2</v>
+        <v>6.7294751009421269E-2</v>
       </c>
       <c r="K92" s="23">
         <f t="shared" si="38"/>
-        <v>6.6225165562913912E-2</v>
+        <v>6.7294751009421269E-2</v>
       </c>
       <c r="L92" s="23" t="str">
         <f t="shared" si="38"/>
@@ -13031,30 +13027,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11572461172144474</v>
+        <v>0.11759364986499432</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>0.14739036402783465</v>
+        <v>0.14977082751146051</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>0.15340108317824458</v>
+        <v>0.15587862422553789</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>0.13218415937701061</v>
+        <v>0.13431903139925036</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>0.12590994181356641</v>
+        <v>0.12794348057771554</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>0.10855739820588613</v>
+        <v>0.11031068054568509</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -13846,7 +13842,7 @@
       </c>
       <c r="C5" s="235">
         <f>Thesis!C67</f>
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E5" s="152"/>
       <c r="H5" s="124"/>
@@ -13857,7 +13853,7 @@
       </c>
       <c r="C6" s="239">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>11399296.694399107</v>
+        <v>12824208.781198993</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -13923,7 +13919,7 @@
       </c>
       <c r="C10" s="239">
         <f>C6-C7+C8+C9</f>
-        <v>10573732.844676431</v>
+        <v>11998644.931476317</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13951,7 +13947,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14004,7 +14000,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>18.44716195227182</v>
+        <v>20.910971233890763</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14047,11 +14043,11 @@
       </c>
       <c r="E21" s="128">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.9174311926605504</v>
+        <v>0.92592592592592582</v>
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>947755.7179234036</v>
+        <v>956531.23383010167</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14069,11 +14065,11 @@
       </c>
       <c r="E22" s="128">
         <f t="shared" si="0"/>
-        <v>0.84167999326655996</v>
+        <v>0.85733882030178321</v>
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>875532.47551359411</v>
+        <v>891821.10267292627</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14091,11 +14087,11 @@
       </c>
       <c r="E23" s="128">
         <f t="shared" si="0"/>
-        <v>0.77218348006106419</v>
+        <v>0.79383224102016958</v>
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>808812.96855537884</v>
+        <v>831488.66554839804</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14113,11 +14109,11 @@
       </c>
       <c r="E24" s="128">
         <f t="shared" si="0"/>
-        <v>0.7084252110651964</v>
+        <v>0.73502985279645328</v>
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>747177.78768813564</v>
+        <v>775237.76782507426</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14135,11 +14131,11 @@
       </c>
       <c r="E25" s="128">
         <f t="shared" si="0"/>
-        <v>0.64993138629834524</v>
+        <v>0.68058319703375303</v>
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>690239.48442823731</v>
+        <v>722792.28997791081</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14157,11 +14153,11 @@
       </c>
       <c r="E26" s="128">
         <f t="shared" si="0"/>
-        <v>0.5962673268792158</v>
+        <v>0.63016962688310452</v>
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>637640.13560667587</v>
+        <v>673894.79219670035</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14179,11 +14175,11 @@
       </c>
       <c r="E27" s="128">
         <f t="shared" si="0"/>
-        <v>0.54703424484331731</v>
+        <v>0.58349039526213387</v>
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>589049.09340748074</v>
+        <v>628305.25068787439</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14201,11 +14197,11 @@
       </c>
       <c r="E28" s="128">
         <f t="shared" si="0"/>
-        <v>0.50186627967276809</v>
+        <v>0.54026888450197574</v>
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>544160.90686331317</v>
+        <v>585799.87946653471</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14223,11 +14219,11 @@
       </c>
       <c r="E29" s="128">
         <f t="shared" si="0"/>
-        <v>0.46042777951630098</v>
+        <v>0.50024896713145905</v>
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>502693.40174243454</v>
+        <v>546170.03185523336</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14245,11 +14241,11 @@
       </c>
       <c r="E30" s="128">
         <f t="shared" si="0"/>
-        <v>0.42241080689568894</v>
+        <v>0.46319348808468425</v>
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>464385.90675690724</v>
+        <v>509221.1762972679</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14699,7 +14695,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>11478374.805961223</v>
+        <v>12913171.656706374</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14707,11 +14703,11 @@
       </c>
       <c r="E51" s="128">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.42241080689568894</v>
+        <v>0.46319348808468425</v>
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>4848589.5636372278</v>
+        <v>5981297.0219061058</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -14722,7 +14718,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>11656037.442122787</v>
+        <v>13102559.212264128</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14743,7 +14739,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>11656037.442122787</v>
+        <v>13102559.212264128</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -14773,19 +14769,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>9989890.7102685813</v>
+        <v>11282726.428198345</v>
       </c>
       <c r="C56" s="127">
-        <v>10498958.919899363</v>
+        <v>11840565.304262523</v>
       </c>
       <c r="D56" s="127">
-        <v>11778983.45420114</v>
+        <v>13237984.887774194</v>
       </c>
       <c r="E56" s="127">
-        <v>12371029.356669225</v>
+        <v>13882054.1124526</v>
       </c>
       <c r="F56" s="127">
-        <v>12991676.303449536</v>
+        <v>14555859.805155281</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14794,19 +14790,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>8963337.1933901533</v>
+        <v>10177077.841397041</v>
       </c>
       <c r="C57" s="127">
-        <v>9775432.6646782458</v>
+        <v>11061100.638071539</v>
       </c>
       <c r="D57" s="127">
-        <v>12163180.595290394</v>
+        <v>13652142.016756626</v>
       </c>
       <c r="E57" s="127">
-        <v>13456678.621474545</v>
+        <v>15052693.18286407</v>
       </c>
       <c r="F57" s="127">
-        <v>14956083.364954349</v>
+        <v>16674664.222032182</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14815,19 +14811,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>7994910.7307772804</v>
+        <v>9086029.4174918626</v>
       </c>
       <c r="C58" s="127">
-        <v>9049309.1489928197</v>
+        <v>10242858.129900236</v>
       </c>
       <c r="D58" s="127">
-        <v>12617823.744950479</v>
+        <v>14164776.298883488</v>
       </c>
       <c r="E58" s="127">
-        <v>14846218.161021832</v>
+        <v>16619945.945723236</v>
       </c>
       <c r="F58" s="127">
-        <v>17686428.749219801</v>
+        <v>19755194.013744399</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14836,19 +14832,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>7236462.72033168</v>
+        <v>8191614.6291523315</v>
       </c>
       <c r="C59" s="127">
-        <v>8448694.9279275406</v>
+        <v>9534439.4308413006</v>
       </c>
       <c r="D59" s="127">
-        <v>13060371.762574079</v>
+        <v>14687068.422470205</v>
       </c>
       <c r="E59" s="127">
-        <v>16316650.300574701</v>
+        <v>18355891.124841124</v>
       </c>
       <c r="F59" s="127">
-        <v>20849114.181642551</v>
+        <v>23490257.935730524</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14857,19 +14853,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>6688249.4420321546</v>
+        <v>7514770.1645255014</v>
       </c>
       <c r="C60" s="127">
-        <v>7993621.2514400966</v>
+        <v>8972499.0159606077</v>
       </c>
       <c r="D60" s="127">
-        <v>13453525.284572506</v>
+        <v>15172829.079400806</v>
       </c>
       <c r="E60" s="127">
-        <v>17742925.279702403</v>
+        <v>20118710.16775756</v>
       </c>
       <c r="F60" s="127">
-        <v>24230272.161345363</v>
+        <v>27670786.788666163</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14878,19 +14874,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>6308271.3310739864</v>
+        <v>7023564.9469353091</v>
       </c>
       <c r="C61" s="127">
-        <v>7665308.796721085</v>
+        <v>8548026.0081255715</v>
       </c>
       <c r="D61" s="127">
-        <v>13784772.306297071</v>
+        <v>15601337.552094221</v>
       </c>
       <c r="E61" s="127">
-        <v>19060262.54675873</v>
+        <v>21823437.068809107</v>
       </c>
       <c r="F61" s="127">
-        <v>27693719.182468999</v>
+        <v>32154491.58847386</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -14940,23 +14936,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14967,23 +14963,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>15.609273254557753</v>
+        <v>17.811314528456176</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>16.476351100017972</v>
+        <v>18.761461722134779</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>18.656571538735964</v>
+        <v>21.1416369889306</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>19.664982348552396</v>
+        <v>22.238657280310463</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>20.722108303826733</v>
+        <v>23.386326644129532</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -14994,23 +14990,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>13.860781019479603</v>
+        <v>15.928102463072781</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>15.243994463633163</v>
+        <v>17.433827172211824</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>19.310960917261998</v>
+        <v>21.847056153369351</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>21.514130277344904</v>
+        <v>24.232565333850321</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>24.068013253836877</v>
+        <v>26.995211139332419</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15021,23 +15017,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>12.211294536522727</v>
+        <v>14.069758337874697</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>14.007214005518993</v>
+        <v>16.040143697921188</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>20.085338486323771</v>
+        <v>22.720207963768175</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>23.880883744441768</v>
+        <v>26.902011437933524</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>28.718513812235905</v>
+        <v>32.242168392096481</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15048,23 +15044,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>10.919456911722445</v>
+        <v>12.546333317515096</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>12.984209082206728</v>
+        <v>14.833519226695104</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>20.839114845511606</v>
+        <v>23.609809633353613</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>26.385418711148258</v>
+        <v>29.858785357951604</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>34.105403857093513</v>
+        <v>38.603970439175441</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15075,23 +15071,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>9.9857046576867923</v>
+        <v>11.393488121139626</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>12.209098212053238</v>
+        <v>13.876386027265573</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>21.508759310320631</v>
+        <v>24.437188550073259</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>28.814742350966224</v>
+        <v>32.861332578051694</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>39.864410451372244</v>
+        <v>45.72451712056565</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15101,23 +15097,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>9.3385014037051466</v>
+        <v>10.556835677146257</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>11.649895239858246</v>
+        <v>13.153396191863036</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>22.072960626526108</v>
+        <v>25.167051849794795</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>31.058516245415653</v>
+        <v>35.764933511085623</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>45.763577054448049</v>
+        <v>53.361452650907644</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15152,7 +15148,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>24.068013253836877</v>
+        <v>26.995211139332419</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15174,7 +15170,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>19.664982348552396</v>
+        <v>22.238657280310463</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15197,7 +15193,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>18.656571538735964</v>
+        <v>21.1416369889306</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15220,7 +15216,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>16.476351100017972</v>
+        <v>18.761461722134779</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15243,7 +15239,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>13.860781019479603</v>
+        <v>15.928102463072781</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15259,7 +15255,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C80" s="160" t="s">
         <v>110</v>
@@ -15331,7 +15327,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I2" s="286"/>
     </row>
@@ -15344,7 +15340,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-15.1</v>
+        <v>-14.86</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15393,7 +15389,7 @@
       </c>
       <c r="I6" s="272">
         <f t="shared" si="0"/>
-        <v>19.803897113903751</v>
+        <v>22.268072026141617</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15552,7 +15548,7 @@
         <v>156</v>
       </c>
       <c r="E17" s="164" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15563,7 +15559,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="340" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F18" s="341"/>
     </row>
@@ -15573,7 +15569,7 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E20" s="341"/>
       <c r="F20" s="341"/>
@@ -15584,7 +15580,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>15.1</v>
+        <v>14.86</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -15599,7 +15595,7 @@
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
-        <v>18.009864532856156</v>
+        <v>20.436866806458671</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15646,7 +15642,7 @@
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
-        <v>18.656571538735964</v>
+        <v>21.1416369889306</v>
       </c>
       <c r="D27" s="165" t="str">
         <f>Market_currency</f>
@@ -15704,7 +15700,7 @@
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
-        <v>16.476351100017972</v>
+        <v>18.761461722134779</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15762,7 +15758,7 @@
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
-        <v>19.664982348552396</v>
+        <v>22.238657280310463</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15789,7 +15785,7 @@
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>18.422209612955651</v>
+        <v>20.885005993847411</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15863,7 +15859,7 @@
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
-        <v>13.860781019479603</v>
+        <v>15.928102463072781</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15885,7 +15881,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E54" s="164" t="s">
         <v>154</v>
@@ -15921,7 +15917,7 @@
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
-        <v>24.068013253836877</v>
+        <v>26.995211139332419</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15947,14 +15943,14 @@
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>18.443897113903752</v>
+        <v>20.908072026141618</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F60" s="322">
         <f>Thesis!E20</f>
@@ -15963,7 +15959,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15972,10 +15968,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E63" s="290" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -15987,7 +15983,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -15999,7 +15995,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="289" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16008,27 +16004,27 @@
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
-        <v>18.44716195227182</v>
+        <v>20.910971233890763</v>
       </c>
       <c r="D66" s="165" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="289" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E68" s="290" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C69" s="281" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16038,19 +16034,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C70" s="281" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="289" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C71" s="281" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16060,7 +16056,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C72" s="280" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -16068,7 +16064,7 @@
       </c>
       <c r="E72" s="138" t="str">
         <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of the Expected Equity Value"</f>
-        <v>Non-FCF Value is -8% of the Expected Equity Value</v>
+        <v>Non-FCF Value is -7% of the Expected Equity Value</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16087,7 +16083,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C76" s="282">
         <f>F60</f>
@@ -16110,12 +16106,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C80" s="172">
         <f>Thesis!C117</f>
@@ -16140,7 +16136,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>10.673551570546152</v>
+        <v>12.099578718831955</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16150,7 +16146,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>13.538366385360966</v>
+        <v>14.964393533646771</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16161,7 +16157,7 @@
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
-        <v>-0.26597040193012134</v>
+        <v>-0.28427673699724165</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16169,16 +16165,16 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>15.1</v>
+        <v>14.86</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16187,11 +16183,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15361989461854253</v>
+        <v>0.20302018521144283</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16199,7 +16195,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="331" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F89" s="328"/>
       <c r="G89" s="2"/>
@@ -16207,30 +16203,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="324" t="s">
+        <v>367</v>
+      </c>
+      <c r="F90" s="329" t="s">
         <v>368</v>
-      </c>
-      <c r="F90" s="329" t="s">
-        <v>369</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="327"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="325" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F91" s="329" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="327"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="326" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F92" s="330" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="327"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF946FE-B847-473A-9B1B-CA05A27242BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B420D5DA-B7C3-4E00-8E1C-A4C4A8CD0767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="391">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1986,6 +1986,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Operating Interest Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Non-FCF Value is of the Expected Value, at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>六福珠宝</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2022,7 +2030,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2455,13 +2463,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3365,15 +3366,17 @@
     <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3735,10 +3738,10 @@
         <v>347</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3746,7 +3749,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>14.86</v>
+        <v>14.96</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3791,7 +3794,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8724.4226510000008</v>
+        <v>8783.1334360000001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3822,7 +3825,7 @@
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v>Low Growth Asset Play</v>
+        <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="E15" s="5"/>
     </row>
@@ -3889,7 +3892,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19796385260234528</v>
+        <v>0.1950811274187132</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4156,7 +4159,7 @@
       </c>
       <c r="C56" s="192">
         <f>Normalized_FCF!G19</f>
-        <v>1337283</v>
+        <v>1290469.0309348544</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4182,7 +4185,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>0.11620144005527505</v>
+        <v>0.11542469246132268</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4191,7 +4194,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>9.1520861372812928E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -8203,7 +8206,7 @@
         <v>359</v>
       </c>
       <c r="C76" s="300"/>
-      <c r="D76" s="339">
+      <c r="D76" s="337">
         <f>IF(D74&lt;=3,1,IF(D74&gt;12,IF(D74&gt;24,12,6),2))</f>
         <v>1</v>
       </c>
@@ -8946,48 +8949,48 @@
       </c>
       <c r="E12" s="311"/>
       <c r="G12" s="198">
-        <f t="shared" ref="G12:Q12" si="6">G50</f>
-        <v>0</v>
+        <f>G50</f>
+        <v>-46813.969065145531</v>
       </c>
       <c r="H12" s="198">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="H12:Q12" si="6">H50</f>
+        <v>-6151.2467226747285</v>
       </c>
       <c r="I12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15431.271041651278</v>
       </c>
       <c r="J12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-883.53783318135538</v>
       </c>
       <c r="K12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="198">
+        <v>-43026.571729677475</v>
+      </c>
+      <c r="L12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="198">
+        <v/>
+      </c>
+      <c r="M12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="198">
+        <v/>
+      </c>
+      <c r="N12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="198">
+        <v/>
+      </c>
+      <c r="O12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="198">
+        <v/>
+      </c>
+      <c r="P12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="198">
+        <v/>
+      </c>
+      <c r="Q12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -9002,23 +9005,23 @@
       <c r="E13" s="311"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>1664449</v>
+        <v>1617635.0309348544</v>
       </c>
       <c r="H13" s="188">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1628253</v>
+        <v>1622101.7532773253</v>
       </c>
       <c r="I13" s="188">
         <f t="shared" si="7"/>
-        <v>1398905</v>
+        <v>1414336.2710416513</v>
       </c>
       <c r="J13" s="188">
         <f t="shared" si="7"/>
-        <v>1319786</v>
+        <v>1318902.4621668186</v>
       </c>
       <c r="K13" s="188">
         <f t="shared" si="7"/>
-        <v>1204768</v>
+        <v>1161741.4282703225</v>
       </c>
       <c r="L13" s="188" t="str">
         <f t="shared" si="7"/>
@@ -9171,23 +9174,23 @@
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>1337283</v>
+        <v>1290469.0309348544</v>
       </c>
       <c r="H16" s="188">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1347589</v>
+        <v>1341437.7532773253</v>
       </c>
       <c r="I16" s="188">
         <f t="shared" si="8"/>
-        <v>1107609</v>
+        <v>1123040.2710416513</v>
       </c>
       <c r="J16" s="188">
         <f t="shared" si="8"/>
-        <v>1081684</v>
+        <v>1080800.4621668186</v>
       </c>
       <c r="K16" s="188">
         <f t="shared" si="8"/>
-        <v>980022</v>
+        <v>936995.4282703225</v>
       </c>
       <c r="L16" s="188" t="str">
         <f t="shared" si="8"/>
@@ -9279,23 +9282,23 @@
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>1337283</v>
+        <v>1290469.0309348544</v>
       </c>
       <c r="H19" s="190">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1347589</v>
+        <v>1341437.7532773253</v>
       </c>
       <c r="I19" s="190">
         <f t="shared" si="9"/>
-        <v>1107609</v>
+        <v>1123040.2710416513</v>
       </c>
       <c r="J19" s="190">
         <f t="shared" si="9"/>
-        <v>1081684</v>
+        <v>1080800.4621668186</v>
       </c>
       <c r="K19" s="190">
         <f t="shared" si="9"/>
-        <v>980022</v>
+        <v>936995.4282703225</v>
       </c>
       <c r="L19" s="190" t="str">
         <f t="shared" si="9"/>
@@ -10133,23 +10136,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.17426435966106535</v>
+        <v>0.17872083028130542</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20579421311928575</v>
+        <v>0.20672662114033497</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20532368705223597</v>
+        <v>0.20311442616937492</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.25196649730496301</v>
+        <v>0.25220409972307367</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18543736221413584</v>
+        <v>0.19230527083175997</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10267,78 +10270,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>71</v>
+        <v>386</v>
       </c>
       <c r="C48" s="198">
         <f>BS!D75*C53</f>
         <v>12782.030934854472</v>
       </c>
       <c r="E48" s="311"/>
-      <c r="G48" s="333"/>
-      <c r="H48" s="333"/>
-      <c r="I48" s="333"/>
-      <c r="J48" s="333"/>
-      <c r="K48" s="333"/>
-      <c r="L48" s="333"/>
-      <c r="M48" s="333"/>
-      <c r="N48" s="333"/>
-      <c r="O48" s="333"/>
-      <c r="P48" s="333"/>
-      <c r="Q48" s="333"/>
+      <c r="G48" s="338">
+        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <v>12782.030934854472</v>
+      </c>
+      <c r="H48" s="338">
+        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <v>14611.753277325271</v>
+      </c>
+      <c r="I48" s="338">
+        <f t="shared" si="19"/>
+        <v>38528.271041651278</v>
+      </c>
+      <c r="J48" s="338">
+        <f t="shared" si="19"/>
+        <v>27965.462166818645</v>
+      </c>
+      <c r="K48" s="338">
+        <f t="shared" si="19"/>
+        <v>20048.428270322525</v>
+      </c>
+      <c r="L48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="M48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="N48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="O48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="P48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Q48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="334" t="s">
+      <c r="B49" s="333" t="s">
         <v>381</v>
       </c>
-      <c r="C49" s="335">
+      <c r="C49" s="334">
         <f>BS!$C$66*C53</f>
         <v>28977</v>
       </c>
-      <c r="D49" s="336"/>
-      <c r="E49" s="337"/>
-      <c r="F49" s="336"/>
-      <c r="G49" s="335">
+      <c r="D49" s="335"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="335"/>
+      <c r="G49" s="334">
         <f>Data!C52</f>
         <v>28977</v>
       </c>
-      <c r="H49" s="335">
+      <c r="H49" s="334">
         <f>Data!D52</f>
         <v>33125</v>
       </c>
-      <c r="I49" s="335">
+      <c r="I49" s="334">
         <f>Data!E52</f>
         <v>87344</v>
       </c>
-      <c r="J49" s="335">
+      <c r="J49" s="334">
         <f>Data!F52</f>
         <v>63398</v>
       </c>
-      <c r="K49" s="335">
+      <c r="K49" s="334">
         <f>Data!G52</f>
         <v>45450</v>
       </c>
-      <c r="L49" s="335" t="str">
+      <c r="L49" s="334" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="335" t="str">
+      <c r="M49" s="334" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="335" t="str">
+      <c r="N49" s="334" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="335" t="str">
+      <c r="O49" s="334" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="335" t="str">
+      <c r="P49" s="334" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="335" t="str">
+      <c r="Q49" s="334" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10353,17 +10389,50 @@
         <v>-46813.969065145531</v>
       </c>
       <c r="E50" s="311"/>
-      <c r="G50" s="338"/>
-      <c r="H50" s="338"/>
-      <c r="I50" s="338"/>
-      <c r="J50" s="338"/>
-      <c r="K50" s="338"/>
-      <c r="L50" s="338"/>
-      <c r="M50" s="338"/>
-      <c r="N50" s="338"/>
-      <c r="O50" s="338"/>
-      <c r="P50" s="338"/>
-      <c r="Q50" s="338"/>
+      <c r="G50" s="188">
+        <f>IF(G$4="","",(G47+G48))</f>
+        <v>-46813.969065145531</v>
+      </c>
+      <c r="H50" s="188">
+        <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
+        <v>-6151.2467226747285</v>
+      </c>
+      <c r="I50" s="188">
+        <f t="shared" si="20"/>
+        <v>15431.271041651278</v>
+      </c>
+      <c r="J50" s="188">
+        <f t="shared" si="20"/>
+        <v>-883.53783318135538</v>
+      </c>
+      <c r="K50" s="188">
+        <f t="shared" si="20"/>
+        <v>-43026.571729677475</v>
+      </c>
+      <c r="L50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="M50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="N50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="O50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="P50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Q50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
@@ -10444,47 +10513,47 @@
       </c>
       <c r="E55" s="311"/>
       <c r="G55" s="42">
-        <f t="shared" ref="G55:Q55" si="19">IF(G4="","",-G8/G47)</f>
+        <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>31.4915933955299</v>
       </c>
       <c r="H55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>65.639936425372056</v>
       </c>
       <c r="I55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>61.424254232151362</v>
       </c>
       <c r="J55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>32.508405837290724</v>
       </c>
       <c r="K55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>19.100562822037258</v>
       </c>
       <c r="L55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="M55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -10678,47 +10747,47 @@
       </c>
       <c r="E61" s="311"/>
       <c r="G61" s="188">
-        <f t="shared" ref="G61:Q61" si="20">IF(G4="","",SUM(G58:G60))</f>
+        <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
       <c r="H61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>927</v>
       </c>
       <c r="I61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="M61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="N61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="O61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="P61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -10789,47 +10858,47 @@
       </c>
       <c r="E63" s="311"/>
       <c r="G63" s="188">
-        <f t="shared" ref="G63:Q63" si="21">IF(G4="","",G61+G62)</f>
+        <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>248317</v>
       </c>
       <c r="H63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>190177</v>
       </c>
       <c r="I63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>200697</v>
       </c>
       <c r="J63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>281254</v>
       </c>
       <c r="K63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-97419</v>
       </c>
       <c r="L63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="O63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -11009,47 +11078,47 @@
       <c r="E73" s="308"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:Q73" si="22">IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.86096272455849754</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.85703537297697319</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.85154513157189637</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.86234342793721264</v>
       </c>
       <c r="K73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.8773412774748568</v>
       </c>
       <c r="L73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="P73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -11066,47 +11135,47 @@
       <c r="E74" s="308"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
-        <f t="shared" ref="G74:Q74" si="23">IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.13903727544150246</v>
       </c>
       <c r="H74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.14296462702302684</v>
       </c>
       <c r="I74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.14845486842810363</v>
       </c>
       <c r="J74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.13765657206278739</v>
       </c>
       <c r="K74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.12265872252514316</v>
       </c>
       <c r="L74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -11123,47 +11192,47 @@
       <c r="E75" s="308"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
-        <f t="shared" ref="G75:Q75" si="24">IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
         <v>1.6580166386945237E-2</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2.9181044602016856E-2</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>2.7587615842589962E-2</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>3.1822067442433898E-2</v>
       </c>
       <c r="K75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1.5413524096227349E-2</v>
       </c>
       <c r="L75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Q75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -11180,47 +11249,47 @@
       <c r="E76" s="308"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
-        <f t="shared" ref="G76:Q76" si="25">IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
         <v>0.12245710905455723</v>
       </c>
       <c r="H76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.11378358242100998</v>
       </c>
       <c r="I76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.12086725258551366</v>
       </c>
       <c r="J76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.10583450462035347</v>
       </c>
       <c r="K76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.10724519842891581</v>
       </c>
       <c r="L76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="N76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -11237,47 +11306,47 @@
       <c r="E77" s="308"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
-        <f t="shared" ref="G77:Q77" si="26">IF(G$4="","",G9/G$4)</f>
+        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
         <v>3.0237840861147901E-2</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3.1034299661942499E-2</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3.7116997107550703E-2</v>
       </c>
       <c r="J77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>5.8782113530297636E-2</v>
       </c>
       <c r="K77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="M77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="N77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="O77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -11292,51 +11361,51 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="309" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
-        <f t="shared" ref="G78:Q78" si="27">IF(G$4="","",-G10/G$4)</f>
+        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
         <v>4.413341231043115E-2</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8.9565367523571013E-3</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>3.8804791663312119E-2</v>
       </c>
       <c r="J78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1.5679014505150749E-2</v>
       </c>
       <c r="K78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11353,47 +11422,47 @@
       <c r="E79" s="308"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
-        <f t="shared" ref="G79:Q79" si="28">IF(G$4="","",G11/G$4)</f>
+        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
         <v>4.1693956960091643E-5</v>
       </c>
       <c r="H79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.7392893078253488E-5</v>
       </c>
       <c r="I79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="M79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="O79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="P79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -11410,47 +11479,47 @@
       <c r="E80" s="308"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
-        <f t="shared" ref="G80:Q80" si="29">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>0</v>
+        <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
+        <v>3.0545533823681365E-3</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>5.1355208188341142E-4</v>
       </c>
       <c r="I80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>1.3146643406480138E-3</v>
       </c>
       <c r="J80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>9.970707948422618E-5</v>
       </c>
       <c r="K80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>3.8301093844335509E-3</v>
       </c>
       <c r="L80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="M80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="O80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="P80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Q80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11467,47 +11536,47 @@
       <c r="E81" s="308"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
-        <f t="shared" ref="G81:Q81" si="30">IF(G$4="","",G13/G$4)</f>
-        <v>0.10860323156223407</v>
+        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
+        <v>0.10554867817986593</v>
       </c>
       <c r="H81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.13593873822367364</v>
+        <f t="shared" si="32"/>
+        <v>0.13542518614179022</v>
       </c>
       <c r="I81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.11917945802975224</v>
+        <f t="shared" si="32"/>
+        <v>0.12049412237040026</v>
       </c>
       <c r="J81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.14893760364550038</v>
+        <f t="shared" si="32"/>
+        <v>0.14883789656601612</v>
       </c>
       <c r="K81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.10724519842891581</v>
+        <f t="shared" si="32"/>
+        <v>0.10341508904448225</v>
       </c>
       <c r="L81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="N81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="O81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="P81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Q81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11524,47 +11593,47 @@
       <c r="E82" s="308"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
-        <f t="shared" ref="G82:Q82" si="31">IF(G$4="","",ABS(G14/G$4))</f>
+        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
         <v>2.134717546604905E-2</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.3431929819757211E-2</v>
       </c>
       <c r="I82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.4816909944731565E-2</v>
       </c>
       <c r="J82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2.6666749423196391E-2</v>
       </c>
       <c r="K82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>1.9887266706789732E-2</v>
       </c>
       <c r="L82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="N82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="P82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Q82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -11582,47 +11651,47 @@
       <c r="E83" s="308"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
-        <f t="shared" ref="G83:Q83" si="32">IF(G$4="","",-G15/G$4)</f>
+        <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="I83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2.0301681405792693E-4</v>
       </c>
       <c r="K83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.1901613447523543E-4</v>
       </c>
       <c r="L83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="P83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -11639,47 +11708,47 @@
       <c r="E84" s="308"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
-        <f t="shared" ref="G84:Q84" si="33">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.7256056096185017E-2</v>
+        <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
+        <v>8.4201502713816878E-2</v>
       </c>
       <c r="H84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.11250680840391643</v>
+        <f t="shared" si="35"/>
+        <v>0.11199325632203302</v>
       </c>
       <c r="I84" s="66">
-        <f t="shared" si="33"/>
-        <v>9.4362548085020675E-2</v>
+        <f t="shared" si="35"/>
+        <v>9.5677212425668692E-2</v>
       </c>
       <c r="J84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.12206783740824605</v>
+        <f t="shared" si="35"/>
+        <v>0.12196813032876182</v>
       </c>
       <c r="K84" s="66">
-        <f t="shared" si="33"/>
-        <v>8.7238915587650845E-2</v>
+        <f t="shared" si="35"/>
+        <v>8.3408806203217292E-2</v>
       </c>
       <c r="L84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="P84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -11746,47 +11815,47 @@
       <c r="E87" s="308"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
-        <f t="shared" ref="G87:Q87" si="34">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.7256056096185017E-2</v>
+        <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
+        <v>8.4201502713816878E-2</v>
       </c>
       <c r="H87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.11250680840391643</v>
+        <f t="shared" si="36"/>
+        <v>0.11199325632203302</v>
       </c>
       <c r="I87" s="66">
-        <f t="shared" si="34"/>
-        <v>9.4362548085020675E-2</v>
+        <f t="shared" si="36"/>
+        <v>9.5677212425668692E-2</v>
       </c>
       <c r="J87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.12206783740824605</v>
+        <f t="shared" si="36"/>
+        <v>0.12196813032876182</v>
       </c>
       <c r="K87" s="66">
-        <f t="shared" si="34"/>
-        <v>8.7238915587650845E-2</v>
+        <f t="shared" si="36"/>
+        <v>8.3408806203217292E-2</v>
       </c>
       <c r="L87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="M87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="O87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="P87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -11869,47 +11938,47 @@
       </c>
       <c r="E91" s="311"/>
       <c r="G91" s="76">
-        <f t="shared" ref="G91:Q91" si="35">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>798466.67599999998</v>
       </c>
       <c r="H91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>645818.63500000001</v>
       </c>
       <c r="I91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>645818.63500000001</v>
       </c>
       <c r="J91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>587107.85</v>
       </c>
       <c r="K91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>587107.85</v>
       </c>
       <c r="L91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="O91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Q91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -11924,47 +11993,47 @@
       </c>
       <c r="E92" s="311"/>
       <c r="G92" s="175">
-        <f t="shared" ref="G92:Q92" si="36">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.59708130291045358</v>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <v>0.61874144738023407</v>
       </c>
       <c r="H92" s="175">
-        <f t="shared" si="36"/>
-        <v>0.47924006132433561</v>
+        <f t="shared" si="38"/>
+        <v>0.48143764660132177</v>
       </c>
       <c r="I92" s="175">
-        <f t="shared" si="36"/>
-        <v>0.58307456421896187</v>
+        <f t="shared" si="38"/>
+        <v>0.57506275745658275</v>
       </c>
       <c r="J92" s="175">
-        <f t="shared" si="36"/>
-        <v>0.54277205727365851</v>
+        <f t="shared" si="38"/>
+        <v>0.54321576512185232</v>
       </c>
       <c r="K92" s="175">
-        <f t="shared" si="36"/>
-        <v>0.59907619420788516</v>
+        <f t="shared" si="38"/>
+        <v>0.62658560787622086</v>
       </c>
       <c r="L92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -11975,51 +12044,51 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.1520861372812928E-2</v>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="E93" s="311"/>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="37">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.1520861372812928E-2</v>
+        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+        <v>9.0909090909090912E-2</v>
       </c>
       <c r="H93" s="23">
-        <f t="shared" si="37"/>
-        <v>7.4024226110363398E-2</v>
+        <f t="shared" si="39"/>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="I93" s="23">
-        <f t="shared" si="37"/>
-        <v>7.4024226110363398E-2</v>
+        <f t="shared" si="39"/>
+        <v>7.3529411764705885E-2</v>
       </c>
       <c r="J93" s="23">
-        <f t="shared" si="37"/>
-        <v>6.7294751009421269E-2</v>
+        <f t="shared" si="39"/>
+        <v>6.6844919786096246E-2</v>
       </c>
       <c r="K93" s="23">
-        <f t="shared" si="37"/>
-        <v>6.7294751009421269E-2</v>
+        <f t="shared" si="39"/>
+        <v>6.6844919786096246E-2</v>
       </c>
       <c r="L93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="O93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12061,47 +12130,47 @@
       <c r="E96" s="308"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="38">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
         <v>0.27952593137796744</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>2.0450249505806095E-2</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>0.32460887665346139</v>
       </c>
       <c r="J96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.21118785490642455</v>
       </c>
       <c r="K96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="N96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="O96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -12112,53 +12181,53 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.18788702191371009</v>
+        <v>-0.16438466748487235</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="308"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="39">IF(H5="","",G13/H13-1)</f>
-        <v>2.2229960577379471E-2</v>
+        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <v>-2.7536634699063534E-3</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="39"/>
-        <v>0.16394823093776911</v>
+        <f t="shared" si="41"/>
+        <v>0.14689963517845439</v>
       </c>
       <c r="I97" s="6">
-        <f t="shared" si="39"/>
-        <v>5.9948355263656383E-2</v>
+        <f t="shared" si="41"/>
+        <v>7.2358503841174926E-2</v>
       </c>
       <c r="J97" s="6">
-        <f t="shared" si="39"/>
-        <v>9.5469003160774557E-2</v>
+        <f t="shared" si="41"/>
+        <v>0.13528056250045917</v>
       </c>
       <c r="K97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="N97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="O97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="P97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="Q97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -12211,47 +12280,47 @@
       <c r="E101" s="312"/>
       <c r="F101" s="26"/>
       <c r="G101" s="187">
-        <f t="shared" ref="G101:Q101" si="40">IF(G$4="","",G105+G104)</f>
+        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>16854064</v>
       </c>
       <c r="H101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>14687373</v>
       </c>
       <c r="I101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>15987114</v>
       </c>
       <c r="J101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>14270996</v>
       </c>
       <c r="K101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="O101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="P101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Q101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -12523,47 +12592,47 @@
       <c r="E108" s="312"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
-        <f t="shared" ref="G108:Q108" si="41">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>1.3951685381968192E-2</v>
       </c>
       <c r="H108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1.5671518179732512E-2</v>
       </c>
       <c r="I108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>2.3627760663558588E-2</v>
       </c>
       <c r="J108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K108" s="97" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#VALUE!</v>
       </c>
       <c r="L108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12580,47 +12649,47 @@
       <c r="E109" s="312"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
-        <f t="shared" ref="G109:Q109" si="42">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
         <v>0.57762188109301071</v>
       </c>
       <c r="H109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.73212708397270831</v>
       </c>
       <c r="I109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0.62376357824373097</v>
       </c>
       <c r="J109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K109" s="97" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
       <c r="L109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="M109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="N109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="O109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="P109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -12720,47 +12789,47 @@
       </c>
       <c r="E113" s="311"/>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="43">G81</f>
-        <v>0.10860323156223407</v>
+        <f t="shared" ref="G113:Q113" si="45">G81</f>
+        <v>0.10554867817986593</v>
       </c>
       <c r="H113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.13593873822367364</v>
+        <f t="shared" si="45"/>
+        <v>0.13542518614179022</v>
       </c>
       <c r="I113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.11917945802975224</v>
+        <f t="shared" si="45"/>
+        <v>0.12049412237040026</v>
       </c>
       <c r="J113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.14893760364550038</v>
+        <f t="shared" si="45"/>
+        <v>0.14883789656601612</v>
       </c>
       <c r="K113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.10724519842891581</v>
+        <f t="shared" si="45"/>
+        <v>0.10341508904448225</v>
       </c>
       <c r="L113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="M113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="N113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="O113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="P113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -12774,47 +12843,47 @@
       </c>
       <c r="E114" s="311"/>
       <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="44">IF(G4="","",G4/G101)</f>
+        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>0.90933332162498015</v>
       </c>
       <c r="H114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.81551983462257005</v>
       </c>
       <c r="I114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.73420399704411943</v>
       </c>
       <c r="J114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>0.62093318504188499</v>
       </c>
       <c r="K114" s="42" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="N114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="O114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="P114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="Q114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -12830,47 +12899,47 @@
       <c r="E115" s="315"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="45">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.3101832741522048</v>
       </c>
       <c r="H115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.2018200397317982</v>
       </c>
       <c r="I115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.3235978755027102</v>
       </c>
       <c r="J115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.2602184485223888</v>
       </c>
       <c r="K115" s="15" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="M115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="N115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="O115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="Q115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -12887,47 +12956,47 @@
       <c r="E116" s="314"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="46">IF(G$4="","",G8/G105)</f>
+        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
         <v>0.14589458032083277</v>
       </c>
       <c r="H116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.11152020850765841</v>
       </c>
       <c r="I116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>0.1174576902086082</v>
       </c>
       <c r="J116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>8.2816712209154458E-2</v>
       </c>
       <c r="K116" s="105" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="M116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="O116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="P116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Q116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -13008,47 +13077,47 @@
       <c r="E120" s="308"/>
       <c r="F120" s="27"/>
       <c r="G120" s="182">
-        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.2777467547061412</v>
+        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>2.198010179790399</v>
       </c>
       <c r="H120" s="182">
-        <f t="shared" si="47"/>
-        <v>2.295300599370286</v>
+        <f t="shared" si="49"/>
+        <v>2.2848233987628088</v>
       </c>
       <c r="I120" s="182">
-        <f t="shared" si="47"/>
-        <v>1.8865511677283824</v>
+        <f t="shared" si="49"/>
+        <v>1.9128347049722658</v>
       </c>
       <c r="J120" s="182">
-        <f t="shared" si="47"/>
-        <v>1.8423940337367317</v>
+        <f t="shared" si="49"/>
+        <v>1.8408891350487284</v>
       </c>
       <c r="K120" s="182">
-        <f t="shared" si="47"/>
-        <v>1.6692367509649206</v>
+        <f t="shared" si="49"/>
+        <v>1.5959511157452972</v>
       </c>
       <c r="L120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="M120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="N120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="O120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="P120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="Q120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
@@ -13059,53 +13128,53 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11620144005527505</v>
+        <v>0.11542469246132268</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="308"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
-        <f t="shared" ref="G121" si="48">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.15328040072046711</v>
+        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
+        <v>0.14692581415711223</v>
       </c>
       <c r="H121" s="79">
-        <f t="shared" ref="H121" si="49">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.15446168232639879</v>
+        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
+        <v>0.15272883681569577</v>
       </c>
       <c r="I121" s="79">
-        <f t="shared" ref="I121" si="50">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12695499109881442</v>
+        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
+        <v>0.12786328241793221</v>
       </c>
       <c r="J121" s="79">
-        <f t="shared" ref="J121" si="51">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.12398344776155665</v>
+        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
+        <v>0.12305408656742836</v>
       </c>
       <c r="K121" s="79">
-        <f t="shared" ref="K121" si="52">IF(K$4="","",K120/Market_Price)</f>
-        <v>0.11233087153195967</v>
+        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
+        <v>0.10668122431452522</v>
       </c>
       <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="53">IF(L$4="","",L120/Market_Price)</f>
+        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
         <v/>
       </c>
       <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="54">IF(M$4="","",M120/Market_Price)</f>
+        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
         <v/>
       </c>
       <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="55">IF(N$4="","",N120/Market_Price)</f>
+        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
         <v/>
       </c>
       <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="56">IF(O$4="","",O120/Market_Price)</f>
+        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
         <v/>
       </c>
       <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="57">IF(P$4="","",P120/Market_Price)</f>
+        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
         <v/>
       </c>
       <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="58">IF(Q$4="","",Q120/Market_Price)</f>
+        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -15372,7 +15441,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-14.86</v>
+        <v>-14.96</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15455,7 +15524,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>1337283</v>
+        <v>1290469.0309348544</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15561,7 +15630,7 @@
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>7.3266661710982284E-2</v>
+        <v>6.0882669786354038E-2</v>
       </c>
       <c r="E14" s="348"/>
       <c r="F14" s="348"/>
@@ -15612,7 +15681,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>14.86</v>
+        <v>14.96</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16091,12 +16160,15 @@
         <v>311</v>
       </c>
       <c r="C72" s="280" t="str">
-        <f>IF(E72&gt;50%,"Y","N")</f>
-        <v>Y</v>
-      </c>
-      <c r="E72" s="138" t="str">
-        <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of the Expected Equity Value"</f>
-        <v>Non-FCF Value is -7% of the Expected Equity Value</v>
+        <f>IF(F72&gt;50%,"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="E72" s="138" t="s">
+        <v>387</v>
+      </c>
+      <c r="F72" s="339">
+        <f>BS!D89/C60</f>
+        <v>-6.8238022613097041E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16206,7 +16278,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>14.86</v>
+        <v>14.96</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16219,7 +16291,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19796385260234528</v>
+        <v>0.1950811274187132</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B420D5DA-B7C3-4E00-8E1C-A4C4A8CD0767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87898A2C-E248-4137-9D38-84757BAB4D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2670,7 +2670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="350">
+  <cellXfs count="348">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3013,7 +3013,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3235,9 +3234,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3377,20 +3373,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3702,15 +3698,15 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="292" t="s">
+      <c r="E1" s="290" t="s">
         <v>348</v>
       </c>
-      <c r="F1" s="293" t="s">
+      <c r="F1" s="291" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="253" t="s">
         <v>281</v>
       </c>
       <c r="B2" s="36"/>
@@ -3770,7 +3766,7 @@
       <c r="B8" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C8" s="287">
+      <c r="C8" s="285">
         <v>6</v>
       </c>
       <c r="D8" s="5"/>
@@ -3804,13 +3800,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="339" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3865,7 +3861,7 @@
       <c r="B19" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="255">
         <v>0.2</v>
       </c>
       <c r="E19" s="5"/>
@@ -3875,14 +3871,14 @@
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="259">
+      <c r="C20" s="258">
         <f>C127</f>
         <v>14.789930718256866</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E20" s="322">
+      <c r="E20" s="320">
         <v>3</v>
       </c>
     </row>
@@ -3890,7 +3886,7 @@
       <c r="B21" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="C21" s="288">
+      <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
         <v>0.1950811274187132</v>
       </c>
@@ -3902,7 +3898,7 @@
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A23" s="254" t="s">
+      <c r="A23" s="253" t="s">
         <v>235</v>
       </c>
       <c r="B23" s="36"/>
@@ -3912,25 +3908,25 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="339" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="344" t="s">
+      <c r="B26" s="340" t="s">
         <v>378</v>
       </c>
-      <c r="C26" s="344"/>
-      <c r="D26" s="344"/>
-      <c r="E26" s="344"/>
-      <c r="F26" s="344"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="241" t="s">
+      <c r="B28" s="240" t="s">
         <v>237</v>
       </c>
       <c r="C28" s="111">
@@ -3939,19 +3935,19 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="342" t="s">
+      <c r="B29" s="338" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="342"/>
-      <c r="D29" s="342"/>
-      <c r="E29" s="342"/>
-      <c r="F29" s="342"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C30" s="192">
+      <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
         <v>1398534.6033278927</v>
       </c>
@@ -3965,19 +3961,19 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="342" t="s">
+      <c r="B32" s="338" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="342"/>
-      <c r="D32" s="342"/>
-      <c r="E32" s="342"/>
-      <c r="F32" s="342"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="192">
+      <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
         <v>463424</v>
       </c>
@@ -3990,7 +3986,7 @@
       <c r="B34" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="C34" s="192">
+      <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
         <v>-463424.00000000006</v>
       </c>
@@ -4000,19 +3996,19 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="342" t="s">
+      <c r="B36" s="338" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="342"/>
-      <c r="D36" s="342"/>
-      <c r="E36" s="342"/>
-      <c r="F36" s="342"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="192">
+      <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4022,19 +4018,19 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="342" t="s">
+      <c r="B39" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="342"/>
-      <c r="D39" s="342"/>
-      <c r="E39" s="342"/>
-      <c r="F39" s="342"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
         <v>379</v>
       </c>
-      <c r="C40" s="332">
+      <c r="C40" s="330">
         <f>Normalized_FCF!C48</f>
         <v>12782.030934854472</v>
       </c>
@@ -4042,14 +4038,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="331"/>
-      <c r="F40" s="331"/>
+      <c r="E40" s="329"/>
+      <c r="F40" s="329"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
         <v>380</v>
       </c>
-      <c r="C41" s="332">
+      <c r="C41" s="330">
         <f>Normalized_FCF!C47</f>
         <v>-59596</v>
       </c>
@@ -4057,14 +4053,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="331"/>
-      <c r="F41" s="331"/>
+      <c r="E41" s="329"/>
+      <c r="F41" s="329"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="192">
+      <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
         <v>-46813.969065145531</v>
       </c>
@@ -4082,7 +4078,7 @@
       <c r="B45" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
@@ -4092,19 +4088,19 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="342" t="s">
+      <c r="B47" s="338" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="342"/>
-      <c r="D47" s="342"/>
-      <c r="E47" s="342"/>
-      <c r="F47" s="342"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="C48" s="192">
+      <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
         <v>-337930.15856568678</v>
       </c>
@@ -4114,13 +4110,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="342" t="s">
+      <c r="B50" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4136,28 +4132,28 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="339" t="s">
         <v>382</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="339" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
         <v>1290469.0309348544</v>
       </c>
@@ -4170,7 +4166,7 @@
       <c r="B57" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
         <v>1013790.4756970603</v>
       </c>
@@ -4180,7 +4176,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="260" t="s">
         <v>284</v>
       </c>
       <c r="C58" s="94">
@@ -4189,7 +4185,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="261" t="s">
+      <c r="B59" s="260" t="s">
         <v>339</v>
       </c>
       <c r="C59" s="94">
@@ -4198,7 +4194,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A61" s="254" t="s">
+      <c r="A61" s="253" t="s">
         <v>302</v>
       </c>
       <c r="B61" s="36"/>
@@ -4208,29 +4204,29 @@
       <c r="F61" s="36"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="240"/>
+      <c r="A62" s="239"/>
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="338" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="344" t="s">
+      <c r="B64" s="340" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="344"/>
-      <c r="D64" s="344"/>
-      <c r="E64" s="344"/>
-      <c r="F64" s="344"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B66" s="241" t="s">
+      <c r="B66" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4238,7 +4234,7 @@
       <c r="B67" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C67" s="320">
+      <c r="C67" s="318">
         <v>0.08</v>
       </c>
     </row>
@@ -4246,11 +4242,11 @@
       <c r="B68" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C68" s="271">
+      <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="295" t="s">
+      <c r="D68" s="293" t="s">
         <v>356</v>
       </c>
     </row>
@@ -4258,11 +4254,11 @@
       <c r="B69" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C69" s="271">
+      <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="295" t="s">
+      <c r="D69" s="293" t="s">
         <v>356</v>
       </c>
     </row>
@@ -4270,7 +4266,7 @@
       <c r="B70" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="C70" s="271">
+      <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
         <v>0.08</v>
       </c>
@@ -4279,28 +4275,28 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="340" t="s">
+      <c r="B72" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C72" s="340"/>
-      <c r="D72" s="340"/>
-      <c r="E72" s="340"/>
-      <c r="F72" s="340"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C75" s="271">
+      <c r="C75" s="269">
         <v>0</v>
       </c>
     </row>
@@ -4308,7 +4304,7 @@
       <c r="B76" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C76" s="255">
+      <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
         <v>21.584417490267342</v>
       </c>
@@ -4318,7 +4314,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="254" t="s">
+      <c r="A78" s="253" t="s">
         <v>260</v>
       </c>
       <c r="B78" s="36"/>
@@ -4328,16 +4324,16 @@
       <c r="F78" s="36"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="240"/>
+      <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="340" t="s">
+      <c r="B80" s="339" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="340"/>
-      <c r="D80" s="340"/>
-      <c r="E80" s="340"/>
-      <c r="F80" s="340"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4345,24 +4341,24 @@
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="241" t="s">
+      <c r="B83" s="240" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="340" t="s">
+      <c r="B84" s="339" t="s">
         <v>385</v>
       </c>
-      <c r="C84" s="340"/>
-      <c r="D84" s="340"/>
-      <c r="E84" s="340"/>
-      <c r="F84" s="340"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="C85" s="192">
+      <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
         <v>2034922</v>
       </c>
@@ -4375,7 +4371,7 @@
       <c r="B86" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="C86" s="255">
+      <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
         <v>3.4660105464438944</v>
       </c>
@@ -4393,7 +4389,7 @@
       <c r="B89" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C89" s="192">
+      <c r="C89" s="191">
         <f>BS!C66</f>
         <v>1998219</v>
       </c>
@@ -4406,7 +4402,7 @@
       <c r="B90" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C90" s="192">
+      <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
         <v>1116785.5502773244</v>
       </c>
@@ -4419,7 +4415,7 @@
       <c r="B91" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="C91" s="255">
+      <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
         <v>1.9021812606956703</v>
       </c>
@@ -4437,7 +4433,7 @@
       <c r="B94" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C94" s="192">
+      <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
         <v>92572.6</v>
       </c>
@@ -4450,7 +4446,7 @@
       <c r="B95" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="C95" s="255">
+      <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>0.15767562978420405</v>
       </c>
@@ -4460,19 +4456,19 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="340" t="s">
+      <c r="B97" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="340"/>
-      <c r="D97" s="340"/>
-      <c r="E97" s="340"/>
-      <c r="F97" s="340"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="C99" s="255">
+      <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
         <v>20.178263834303323</v>
       </c>
@@ -4482,7 +4478,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="254" t="s">
+      <c r="A101" s="253" t="s">
         <v>277</v>
       </c>
       <c r="B101" s="36"/>
@@ -4492,165 +4488,165 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="342" t="s">
+      <c r="B103" s="338" t="s">
         <v>368</v>
       </c>
-      <c r="C103" s="342"/>
-      <c r="D103" s="342"/>
-      <c r="E103" s="342"/>
-      <c r="F103" s="342"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="267" t="s">
+      <c r="B105" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="267" t="s">
+      <c r="C105" s="266" t="s">
         <v>137</v>
       </c>
-      <c r="D105" s="267" t="s">
+      <c r="D105" s="266" t="s">
         <v>117</v>
       </c>
-      <c r="E105" s="267" t="s">
+      <c r="E105" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="F105" s="267" t="s">
+      <c r="F105" s="266" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="262" t="str">
+      <c r="B106" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="263">
+      <c r="C106" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D106" s="264">
+      <c r="D106" s="263">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E106" s="265" t="str">
+      <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>24.79 HKD</v>
       </c>
-      <c r="F106" s="266">
+      <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="249" t="str">
+      <c r="B107" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="250">
+      <c r="C107" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.05</v>
       </c>
-      <c r="D107" s="251">
+      <c r="D107" s="250">
         <f>Valuation_Model!D75</f>
         <v>5</v>
       </c>
-      <c r="E107" s="252" t="str">
+      <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.96 HKD</v>
       </c>
-      <c r="F107" s="253">
+      <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.192</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="249" t="str">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="250">
+      <c r="C108" s="249">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D108" s="251">
+      <c r="D108" s="250">
         <f>Valuation_Model!D76</f>
         <v>5</v>
       </c>
-      <c r="E108" s="252" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>20.87 HKD</v>
       </c>
-      <c r="F108" s="253">
+      <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.57599999999999996</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="249" t="str">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="250">
+      <c r="C109" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D109" s="251">
+      <c r="D109" s="250">
         <f>Valuation_Model!D77</f>
         <v>5</v>
       </c>
-      <c r="E109" s="252" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>18.52 HKD</v>
       </c>
-      <c r="F109" s="253">
+      <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.192</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="249" t="str">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="250">
+      <c r="C110" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.08</v>
       </c>
-      <c r="D110" s="251">
+      <c r="D110" s="250">
         <f>Valuation_Model!D78</f>
         <v>10</v>
       </c>
-      <c r="E110" s="252" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.72 HKD</v>
       </c>
-      <c r="F110" s="253">
+      <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="242" t="s">
+      <c r="B112" s="241" t="s">
         <v>269</v>
       </c>
-      <c r="C112" s="248">
+      <c r="C112" s="247">
         <f>Scenarios!C60</f>
         <v>20.606600281147866</v>
       </c>
-      <c r="D112" s="243" t="str">
+      <c r="D112" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="345" t="s">
+      <c r="B114" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C114" s="345"/>
-      <c r="D114" s="345"/>
-      <c r="E114" s="345"/>
-      <c r="F114" s="345"/>
+      <c r="C114" s="343"/>
+      <c r="D114" s="343"/>
+      <c r="E114" s="343"/>
+      <c r="F114" s="343"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="254" t="s">
+      <c r="A116" s="253" t="s">
         <v>299</v>
       </c>
       <c r="B116" s="36"/>
@@ -4669,7 +4665,7 @@
       <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="241" t="s">
+      <c r="B119" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4677,7 +4673,7 @@
       <c r="B120" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="258">
+      <c r="C120" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
@@ -4686,45 +4682,45 @@
       <c r="B121" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C121" s="257">
+      <c r="C121" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="243" t="s">
+      <c r="B122" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="244">
+      <c r="C122" s="243">
         <f>Scenarios!C77</f>
         <v>1.36</v>
       </c>
-      <c r="D122" s="243" t="str">
+      <c r="D122" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="241" t="s">
+      <c r="B124" s="240" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="243" t="str">
+      <c r="B125" s="242" t="str">
         <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="247">
+      <c r="C125" s="246">
         <f>Scenarios!C81</f>
         <v>2.8648148148148147</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="243" t="str">
+      <c r="B126" s="242" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="247">
+      <c r="C126" s="246">
         <f>Scenarios!C82</f>
         <v>11.925115903442052</v>
       </c>
@@ -4733,7 +4729,7 @@
       <c r="B127" s="82" t="s">
         <v>271</v>
       </c>
-      <c r="C127" s="246">
+      <c r="C127" s="245">
         <f>Scenarios!C83</f>
         <v>14.789930718256866</v>
       </c>
@@ -4743,22 +4739,16 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="245" t="s">
+      <c r="B128" s="244" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="158">
+      <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>-0.28227215957658158</v>
+        <v>0.28227215957658158</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4774,6 +4764,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4883,303 +4879,303 @@
       <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="194">
+      <c r="C4" s="193">
         <v>15325962</v>
       </c>
-      <c r="D4" s="185">
+      <c r="D4" s="184">
         <v>11977844</v>
       </c>
-      <c r="E4" s="185">
+      <c r="E4" s="184">
         <v>11737803</v>
       </c>
-      <c r="F4" s="185">
+      <c r="F4" s="184">
         <v>8861335</v>
       </c>
-      <c r="G4" s="185">
+      <c r="G4" s="184">
         <v>11233771</v>
       </c>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="194">
+      <c r="C5" s="193">
         <v>11151623</v>
       </c>
-      <c r="D5" s="185">
+      <c r="D5" s="184">
         <v>8747447</v>
       </c>
-      <c r="E5" s="185">
+      <c r="E5" s="184">
         <v>8503976</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="184">
         <v>6229020</v>
       </c>
-      <c r="G5" s="185">
+      <c r="G5" s="184">
         <v>7910751</v>
       </c>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="185"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="194">
+      <c r="C6" s="193">
         <v>2297566</v>
       </c>
-      <c r="D6" s="185">
+      <c r="D6" s="184">
         <v>1867515</v>
       </c>
-      <c r="E6" s="185">
+      <c r="E6" s="184">
         <v>1815111</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="184">
         <v>1694480</v>
       </c>
-      <c r="G6" s="185">
+      <c r="G6" s="184">
         <v>2118252</v>
       </c>
-      <c r="H6" s="185"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="185"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="185"/>
-      <c r="M6" s="185"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="195">
+      <c r="C7" s="194">
         <v>2043459</v>
       </c>
-      <c r="D7" s="193">
+      <c r="D7" s="192">
         <v>1517989</v>
       </c>
-      <c r="E7" s="193">
+      <c r="E7" s="192">
         <v>1491293</v>
       </c>
-      <c r="F7" s="193">
+      <c r="F7" s="192">
         <v>1412494</v>
       </c>
-      <c r="G7" s="193">
+      <c r="G7" s="192">
         <v>1945100</v>
       </c>
-      <c r="H7" s="193"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
-      <c r="L7" s="193"/>
-      <c r="M7" s="193"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="194"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="185"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="185"/>
-      <c r="J8" s="185"/>
-      <c r="K8" s="185"/>
-      <c r="L8" s="185"/>
-      <c r="M8" s="185"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="194">
+      <c r="C9" s="193">
         <v>639</v>
       </c>
-      <c r="D9" s="185">
+      <c r="D9" s="184">
         <v>927</v>
       </c>
-      <c r="E9" s="185"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="185"/>
-      <c r="H9" s="185"/>
-      <c r="I9" s="185"/>
-      <c r="J9" s="185"/>
-      <c r="K9" s="185"/>
-      <c r="L9" s="185"/>
-      <c r="M9" s="185"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="184"/>
+      <c r="M9" s="184"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="194"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="185"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="185"/>
+      <c r="C10" s="193"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="184"/>
+      <c r="L10" s="184"/>
+      <c r="M10" s="184"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="194"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
+      <c r="C11" s="193"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="194">
+      <c r="C12" s="193">
         <v>59596</v>
       </c>
-      <c r="D12" s="185">
+      <c r="D12" s="184">
         <v>20763</v>
       </c>
-      <c r="E12" s="185">
+      <c r="E12" s="184">
         <v>23097</v>
       </c>
-      <c r="F12" s="185">
+      <c r="F12" s="184">
         <v>28849</v>
       </c>
-      <c r="G12" s="185">
+      <c r="G12" s="184">
         <v>63075</v>
       </c>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="184"/>
+      <c r="J12" s="184"/>
+      <c r="K12" s="184"/>
+      <c r="L12" s="184"/>
+      <c r="M12" s="184"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="194">
+      <c r="C13" s="193">
         <v>28977</v>
       </c>
-      <c r="D13" s="185">
+      <c r="D13" s="184">
         <v>33125</v>
       </c>
-      <c r="E13" s="185">
+      <c r="E13" s="184">
         <v>87344</v>
       </c>
-      <c r="F13" s="185">
+      <c r="F13" s="184">
         <v>63398</v>
       </c>
-      <c r="G13" s="185">
+      <c r="G13" s="184">
         <v>45450</v>
       </c>
-      <c r="H13" s="185"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="185"/>
-      <c r="K13" s="185"/>
-      <c r="L13" s="185"/>
-      <c r="M13" s="185"/>
+      <c r="H13" s="184"/>
+      <c r="I13" s="184"/>
+      <c r="J13" s="184"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="184"/>
+      <c r="M13" s="184"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="194">
+      <c r="C14" s="193">
         <v>327166</v>
       </c>
-      <c r="D14" s="185">
+      <c r="D14" s="184">
         <v>280664</v>
       </c>
-      <c r="E14" s="185">
+      <c r="E14" s="184">
         <v>291296</v>
       </c>
-      <c r="F14" s="185">
+      <c r="F14" s="184">
         <v>236303</v>
       </c>
-      <c r="G14" s="185">
+      <c r="G14" s="184">
         <v>223409</v>
       </c>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="185"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="185"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="184"/>
+      <c r="K14" s="184"/>
+      <c r="L14" s="184"/>
+      <c r="M14" s="184"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="196">
+      <c r="C15" s="195">
         <v>1767305</v>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="185">
         <v>1284757</v>
       </c>
-      <c r="E15" s="186">
+      <c r="E15" s="185">
         <v>1392364</v>
       </c>
-      <c r="F15" s="186">
+      <c r="F15" s="185">
         <v>1017335</v>
       </c>
-      <c r="G15" s="186">
+      <c r="G15" s="185">
         <v>866315</v>
       </c>
-      <c r="H15" s="186"/>
-      <c r="I15" s="186"/>
-      <c r="J15" s="186"/>
-      <c r="K15" s="186"/>
-      <c r="L15" s="186"/>
-      <c r="M15" s="186"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="185"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="194">
+      <c r="C16" s="193">
         <v>-9467</v>
       </c>
-      <c r="D16" s="185">
+      <c r="D16" s="184">
         <v>-30</v>
       </c>
-      <c r="E16" s="185">
+      <c r="E16" s="184">
         <v>-27</v>
       </c>
-      <c r="F16" s="185">
+      <c r="F16" s="184">
         <v>1799</v>
       </c>
-      <c r="G16" s="185">
+      <c r="G16" s="184">
         <v>1337</v>
       </c>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="185"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="185"/>
+      <c r="H16" s="184"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="184"/>
+      <c r="K16" s="184"/>
+      <c r="L16" s="184"/>
+      <c r="M16" s="184"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
@@ -5191,73 +5187,73 @@
       <c r="B19" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="185">
+      <c r="C19" s="184">
         <v>463424</v>
       </c>
-      <c r="D19" s="185">
+      <c r="D19" s="184">
         <v>371724</v>
       </c>
-      <c r="E19" s="185">
+      <c r="E19" s="184">
         <v>435672</v>
       </c>
-      <c r="F19" s="185">
+      <c r="F19" s="184">
         <v>520888</v>
       </c>
-      <c r="G19" s="185"/>
-      <c r="H19" s="185"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="185"/>
-      <c r="M19" s="185"/>
+      <c r="G19" s="184"/>
+      <c r="H19" s="184"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="184"/>
+      <c r="L19" s="184"/>
+      <c r="M19" s="184"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="185">
+      <c r="C20" s="184">
         <v>676387</v>
       </c>
-      <c r="D20" s="185">
+      <c r="D20" s="184">
         <v>107280</v>
       </c>
-      <c r="E20" s="185">
+      <c r="E20" s="184">
         <v>455483</v>
       </c>
-      <c r="F20" s="185">
+      <c r="F20" s="184">
         <v>138937</v>
       </c>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="185"/>
-      <c r="L20" s="185"/>
-      <c r="M20" s="185"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="184"/>
+      <c r="K20" s="184"/>
+      <c r="L20" s="184"/>
+      <c r="M20" s="184"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="185">
+      <c r="C21" s="184">
         <v>626583</v>
       </c>
-      <c r="D21" s="185">
+      <c r="D21" s="184">
         <v>352099</v>
       </c>
-      <c r="E21" s="185">
+      <c r="E21" s="184">
         <v>1045251</v>
       </c>
-      <c r="F21" s="185">
+      <c r="F21" s="184">
         <v>-818677</v>
       </c>
-      <c r="G21" s="185"/>
-      <c r="H21" s="185"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="185"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="185"/>
+      <c r="G21" s="184"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="184"/>
+      <c r="L21" s="184"/>
+      <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="24" t="str">
@@ -5298,109 +5294,109 @@
       <c r="B25" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="187"/>
-      <c r="D25" s="185">
+      <c r="C25" s="186"/>
+      <c r="D25" s="184">
         <v>213823</v>
       </c>
-      <c r="E25" s="185">
+      <c r="E25" s="184">
         <v>187711</v>
       </c>
-      <c r="F25" s="185">
+      <c r="F25" s="184">
         <v>277338</v>
       </c>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
+      <c r="G25" s="184"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="184"/>
+      <c r="M25" s="184"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="187"/>
-      <c r="D26" s="185">
+      <c r="C26" s="186"/>
+      <c r="D26" s="184">
         <v>8852611</v>
       </c>
-      <c r="E26" s="185">
+      <c r="E26" s="184">
         <v>8769304</v>
       </c>
-      <c r="F26" s="185">
+      <c r="F26" s="184">
         <v>7321614</v>
       </c>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="185"/>
+      <c r="G26" s="184"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="184"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="184"/>
+      <c r="M26" s="184"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="186">
+      <c r="C27" s="185">
         <v>3990166</v>
       </c>
-      <c r="D27" s="186">
+      <c r="D27" s="185">
         <v>2466431</v>
       </c>
-      <c r="E27" s="186">
+      <c r="E27" s="185">
         <v>3908586</v>
       </c>
-      <c r="F27" s="186">
+      <c r="F27" s="185">
         <v>2946772</v>
       </c>
-      <c r="G27" s="186"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="186"/>
-      <c r="K27" s="186"/>
-      <c r="L27" s="186"/>
-      <c r="M27" s="186"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="185"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="186">
+      <c r="C28" s="185">
         <v>12863898</v>
       </c>
-      <c r="D28" s="186">
+      <c r="D28" s="185">
         <v>12220942</v>
       </c>
-      <c r="E28" s="186">
+      <c r="E28" s="185">
         <v>12078528</v>
       </c>
-      <c r="F28" s="186">
+      <c r="F28" s="185">
         <v>11324224</v>
       </c>
-      <c r="G28" s="186"/>
-      <c r="H28" s="186"/>
-      <c r="I28" s="186"/>
-      <c r="J28" s="186"/>
-      <c r="K28" s="186"/>
-      <c r="L28" s="186"/>
-      <c r="M28" s="186"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="185"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="186"/>
-      <c r="H29" s="186"/>
-      <c r="I29" s="186"/>
-      <c r="J29" s="186"/>
-      <c r="K29" s="186"/>
-      <c r="L29" s="186"/>
-      <c r="M29" s="186"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
@@ -5412,25 +5408,25 @@
       <c r="B32" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="185">
+      <c r="C32" s="184">
         <v>1095356</v>
       </c>
-      <c r="D32" s="185">
+      <c r="D32" s="184">
         <v>1099308</v>
       </c>
-      <c r="E32" s="185">
+      <c r="E32" s="184">
         <v>1107736</v>
       </c>
-      <c r="F32" s="185">
+      <c r="F32" s="184">
         <v>1122325</v>
       </c>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="185"/>
+      <c r="G32" s="184"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="184"/>
+      <c r="J32" s="184"/>
+      <c r="K32" s="184"/>
+      <c r="L32" s="184"/>
+      <c r="M32" s="184"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
@@ -5457,47 +5453,47 @@
       <c r="B36" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="187">
+      <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>15325962</v>
       </c>
-      <c r="D36" s="187">
+      <c r="D36" s="186">
         <f t="shared" si="1"/>
         <v>11977844</v>
       </c>
-      <c r="E36" s="187">
+      <c r="E36" s="186">
         <f t="shared" si="1"/>
         <v>11737803</v>
       </c>
-      <c r="F36" s="187">
+      <c r="F36" s="186">
         <f t="shared" si="1"/>
         <v>8861335</v>
       </c>
-      <c r="G36" s="187">
+      <c r="G36" s="186">
         <f t="shared" si="1"/>
         <v>11233771</v>
       </c>
-      <c r="H36" s="187" t="str">
+      <c r="H36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I36" s="187" t="str">
+      <c r="I36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J36" s="187" t="str">
+      <c r="J36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="187" t="str">
+      <c r="K36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L36" s="187" t="str">
+      <c r="L36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="187" t="str">
+      <c r="M36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5506,47 +5502,47 @@
       <c r="B37" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="187">
+      <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-11151623</v>
       </c>
-      <c r="D37" s="187">
+      <c r="D37" s="186">
         <f t="shared" si="2"/>
         <v>-8747447</v>
       </c>
-      <c r="E37" s="187">
+      <c r="E37" s="186">
         <f t="shared" si="2"/>
         <v>-8503976</v>
       </c>
-      <c r="F37" s="187">
+      <c r="F37" s="186">
         <f t="shared" si="2"/>
         <v>-6229020</v>
       </c>
-      <c r="G37" s="187">
+      <c r="G37" s="186">
         <f t="shared" si="2"/>
         <v>-7910751</v>
       </c>
-      <c r="H37" s="187" t="str">
+      <c r="H37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I37" s="187" t="str">
+      <c r="I37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="187" t="str">
+      <c r="J37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="187" t="str">
+      <c r="K37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="187" t="str">
+      <c r="L37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="187" t="str">
+      <c r="M37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5555,47 +5551,47 @@
       <c r="B38" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
         <v>4174339</v>
       </c>
-      <c r="D38" s="188">
+      <c r="D38" s="187">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>3230397</v>
       </c>
-      <c r="E38" s="188">
+      <c r="E38" s="187">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>3233827</v>
       </c>
-      <c r="F38" s="188">
+      <c r="F38" s="187">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>2632315</v>
       </c>
-      <c r="G38" s="188">
+      <c r="G38" s="187">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>3323020</v>
       </c>
-      <c r="H38" s="188" t="str">
+      <c r="H38" s="187" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v/>
       </c>
-      <c r="I38" s="188" t="str">
+      <c r="I38" s="187" t="str">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v/>
       </c>
-      <c r="J38" s="188" t="str">
+      <c r="J38" s="187" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
-      <c r="K38" s="188" t="str">
+      <c r="K38" s="187" t="str">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
-      <c r="L38" s="188" t="str">
+      <c r="L38" s="187" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="188" t="str">
+      <c r="M38" s="187" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -5604,47 +5600,47 @@
       <c r="B39" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="187">
+      <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-2297566</v>
       </c>
-      <c r="D39" s="187">
+      <c r="D39" s="186">
         <f t="shared" si="13"/>
         <v>-1867515</v>
       </c>
-      <c r="E39" s="187">
+      <c r="E39" s="186">
         <f t="shared" si="13"/>
         <v>-1815111</v>
       </c>
-      <c r="F39" s="187">
+      <c r="F39" s="186">
         <f t="shared" si="13"/>
         <v>-1694480</v>
       </c>
-      <c r="G39" s="187">
+      <c r="G39" s="186">
         <f t="shared" si="13"/>
         <v>-2118252</v>
       </c>
-      <c r="H39" s="187" t="str">
+      <c r="H39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I39" s="187" t="str">
+      <c r="I39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J39" s="187" t="str">
+      <c r="J39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K39" s="187" t="str">
+      <c r="K39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L39" s="187" t="str">
+      <c r="L39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="187" t="str">
+      <c r="M39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -5653,47 +5649,47 @@
       <c r="B40" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="189">
+      <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-2043459</v>
       </c>
-      <c r="D40" s="189">
+      <c r="D40" s="188">
         <f t="shared" si="14"/>
         <v>-1517989</v>
       </c>
-      <c r="E40" s="189">
+      <c r="E40" s="188">
         <f t="shared" si="14"/>
         <v>-1491293</v>
       </c>
-      <c r="F40" s="189">
+      <c r="F40" s="188">
         <f t="shared" si="14"/>
         <v>-1412494</v>
       </c>
-      <c r="G40" s="189">
+      <c r="G40" s="188">
         <f t="shared" si="14"/>
         <v>-1945100</v>
       </c>
-      <c r="H40" s="189" t="str">
+      <c r="H40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I40" s="189" t="str">
+      <c r="I40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J40" s="189" t="str">
+      <c r="J40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K40" s="189" t="str">
+      <c r="K40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L40" s="189" t="str">
+      <c r="L40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="189" t="str">
+      <c r="M40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -5702,47 +5698,47 @@
       <c r="B41" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="189">
+      <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-254107</v>
       </c>
-      <c r="D41" s="189">
+      <c r="D41" s="188">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-349526</v>
       </c>
-      <c r="E41" s="189">
+      <c r="E41" s="188">
         <f t="shared" si="15"/>
         <v>-323818</v>
       </c>
-      <c r="F41" s="189">
+      <c r="F41" s="188">
         <f t="shared" si="15"/>
         <v>-281986</v>
       </c>
-      <c r="G41" s="189">
+      <c r="G41" s="188">
         <f t="shared" si="15"/>
         <v>-173152</v>
       </c>
-      <c r="H41" s="189" t="str">
+      <c r="H41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I41" s="189" t="str">
+      <c r="I41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J41" s="189" t="str">
+      <c r="J41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K41" s="189" t="str">
+      <c r="K41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="L41" s="189" t="str">
+      <c r="L41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="189" t="str">
+      <c r="M41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -5751,47 +5747,47 @@
       <c r="B42" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="187">
+      <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="187">
+      <c r="D42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="187">
+      <c r="E42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="187">
+      <c r="F42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="187" t="str">
+      <c r="H42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="I42" s="187" t="str">
+      <c r="I42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="J42" s="187" t="str">
+      <c r="J42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="K42" s="187" t="str">
+      <c r="K42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="L42" s="187" t="str">
+      <c r="L42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="187" t="str">
+      <c r="M42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -5800,47 +5796,47 @@
       <c r="B43" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="C43" s="190">
+      <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>1876773</v>
       </c>
-      <c r="D43" s="190">
+      <c r="D43" s="189">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>1362882</v>
       </c>
-      <c r="E43" s="190">
+      <c r="E43" s="189">
         <f t="shared" si="17"/>
         <v>1418716</v>
       </c>
-      <c r="F43" s="190">
+      <c r="F43" s="189">
         <f t="shared" si="17"/>
         <v>937835</v>
       </c>
-      <c r="G43" s="190">
+      <c r="G43" s="189">
         <f t="shared" si="17"/>
         <v>1204768</v>
       </c>
-      <c r="H43" s="190" t="str">
+      <c r="H43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I43" s="190" t="str">
+      <c r="I43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="J43" s="190" t="str">
+      <c r="J43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="K43" s="190" t="str">
+      <c r="K43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="L43" s="190" t="str">
+      <c r="L43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="190" t="str">
+      <c r="M43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -5849,47 +5845,47 @@
       <c r="B44" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C44" s="191">
+      <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
         <v>248317</v>
       </c>
-      <c r="D44" s="191">
+      <c r="D44" s="190">
         <f t="shared" si="18"/>
         <v>190177</v>
       </c>
-      <c r="E44" s="191">
+      <c r="E44" s="190">
         <f t="shared" si="18"/>
         <v>200697</v>
       </c>
-      <c r="F44" s="191">
+      <c r="F44" s="190">
         <f t="shared" si="18"/>
         <v>281254</v>
       </c>
-      <c r="G44" s="191">
+      <c r="G44" s="190">
         <f t="shared" si="18"/>
         <v>-97419</v>
       </c>
-      <c r="H44" s="191" t="str">
+      <c r="H44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="I44" s="191" t="str">
+      <c r="I44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J44" s="191" t="str">
+      <c r="J44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="K44" s="191" t="str">
+      <c r="K44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L44" s="191" t="str">
+      <c r="L44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M44" s="191" t="str">
+      <c r="M44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
@@ -5898,47 +5894,47 @@
       <c r="B45" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
         <v>-30619</v>
       </c>
-      <c r="D45" s="192">
+      <c r="D45" s="191">
         <f t="shared" si="19"/>
         <v>12362</v>
       </c>
-      <c r="E45" s="192">
+      <c r="E45" s="191">
         <f t="shared" si="19"/>
         <v>64247</v>
       </c>
-      <c r="F45" s="192">
+      <c r="F45" s="191">
         <f t="shared" si="19"/>
         <v>34549</v>
       </c>
-      <c r="G45" s="192">
+      <c r="G45" s="191">
         <f t="shared" si="19"/>
         <v>-17625</v>
       </c>
-      <c r="H45" s="192" t="str">
+      <c r="H45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I45" s="192" t="str">
+      <c r="I45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J45" s="192" t="str">
+      <c r="J45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K45" s="192" t="str">
+      <c r="K45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L45" s="192" t="str">
+      <c r="L45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M45" s="192" t="str">
+      <c r="M45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -5947,47 +5943,47 @@
       <c r="B46" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="187">
+      <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-327166</v>
       </c>
-      <c r="D46" s="187">
+      <c r="D46" s="186">
         <f t="shared" si="20"/>
         <v>-280664</v>
       </c>
-      <c r="E46" s="187">
+      <c r="E46" s="186">
         <f t="shared" si="20"/>
         <v>-291296</v>
       </c>
-      <c r="F46" s="187">
+      <c r="F46" s="186">
         <f t="shared" si="20"/>
         <v>-236303</v>
       </c>
-      <c r="G46" s="187">
+      <c r="G46" s="186">
         <f t="shared" si="20"/>
         <v>-223409</v>
       </c>
-      <c r="H46" s="187" t="str">
+      <c r="H46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I46" s="187" t="str">
+      <c r="I46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J46" s="187" t="str">
+      <c r="J46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K46" s="187" t="str">
+      <c r="K46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L46" s="187" t="str">
+      <c r="L46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="187" t="str">
+      <c r="M46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -5996,47 +5992,47 @@
       <c r="B47" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="190">
+      <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>1767305</v>
       </c>
-      <c r="D47" s="190">
+      <c r="D47" s="189">
         <f t="shared" si="21"/>
         <v>1284757</v>
       </c>
-      <c r="E47" s="190">
+      <c r="E47" s="189">
         <f t="shared" si="21"/>
         <v>1392364</v>
       </c>
-      <c r="F47" s="190">
+      <c r="F47" s="189">
         <f t="shared" si="21"/>
         <v>1017335</v>
       </c>
-      <c r="G47" s="190">
+      <c r="G47" s="189">
         <f t="shared" si="21"/>
         <v>866315</v>
       </c>
-      <c r="H47" s="190" t="str">
+      <c r="H47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I47" s="190" t="str">
+      <c r="I47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="J47" s="190" t="str">
+      <c r="J47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="K47" s="190" t="str">
+      <c r="K47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="L47" s="190" t="str">
+      <c r="L47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="190" t="str">
+      <c r="M47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -6045,47 +6041,47 @@
       <c r="B48" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="187">
+      <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="187">
+      <c r="D48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="187">
+      <c r="E48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="187">
+      <c r="F48" s="186">
         <f t="shared" si="22"/>
         <v>-1799</v>
       </c>
-      <c r="G48" s="187">
+      <c r="G48" s="186">
         <f t="shared" si="22"/>
         <v>-1337</v>
       </c>
-      <c r="H48" s="187" t="str">
+      <c r="H48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I48" s="187" t="str">
+      <c r="I48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J48" s="187" t="str">
+      <c r="J48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K48" s="187" t="str">
+      <c r="K48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L48" s="187" t="str">
+      <c r="L48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="187" t="str">
+      <c r="M48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6099,47 +6095,47 @@
       <c r="B51" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="187">
+      <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-59596</v>
       </c>
-      <c r="D51" s="187">
+      <c r="D51" s="186">
         <f t="shared" si="23"/>
         <v>-20763</v>
       </c>
-      <c r="E51" s="187">
+      <c r="E51" s="186">
         <f t="shared" si="23"/>
         <v>-23097</v>
       </c>
-      <c r="F51" s="187">
+      <c r="F51" s="186">
         <f t="shared" si="23"/>
         <v>-28849</v>
       </c>
-      <c r="G51" s="187">
+      <c r="G51" s="186">
         <f t="shared" si="23"/>
         <v>-63075</v>
       </c>
-      <c r="H51" s="187" t="str">
+      <c r="H51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I51" s="187" t="str">
+      <c r="I51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J51" s="187" t="str">
+      <c r="J51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K51" s="187" t="str">
+      <c r="K51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L51" s="187" t="str">
+      <c r="L51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="187" t="str">
+      <c r="M51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -6148,53 +6144,53 @@
       <c r="B52" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="187">
+      <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>28977</v>
       </c>
-      <c r="D52" s="187">
+      <c r="D52" s="186">
         <f t="shared" si="24"/>
         <v>33125</v>
       </c>
-      <c r="E52" s="187">
+      <c r="E52" s="186">
         <f t="shared" si="24"/>
         <v>87344</v>
       </c>
-      <c r="F52" s="187">
+      <c r="F52" s="186">
         <f t="shared" si="24"/>
         <v>63398</v>
       </c>
-      <c r="G52" s="187">
+      <c r="G52" s="186">
         <f t="shared" si="24"/>
         <v>45450</v>
       </c>
-      <c r="H52" s="187" t="str">
+      <c r="H52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="I52" s="187" t="str">
+      <c r="I52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="J52" s="187" t="str">
+      <c r="J52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K52" s="187" t="str">
+      <c r="K52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="L52" s="187" t="str">
+      <c r="L52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="187" t="str">
+      <c r="M52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B54" s="179" t="s">
+      <c r="B54" s="178" t="s">
         <v>173</v>
       </c>
     </row>
@@ -6202,47 +6198,47 @@
       <c r="B55" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C55" s="192">
+      <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>639</v>
       </c>
-      <c r="D55" s="192">
+      <c r="D55" s="191">
         <f t="shared" si="25"/>
         <v>927</v>
       </c>
-      <c r="E55" s="192">
+      <c r="E55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="F55" s="192">
+      <c r="F55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="G55" s="192">
+      <c r="G55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H55" s="192" t="str">
+      <c r="H55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I55" s="192" t="str">
+      <c r="I55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="J55" s="192" t="str">
+      <c r="J55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="K55" s="192" t="str">
+      <c r="K55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="L55" s="192" t="str">
+      <c r="L55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M55" s="192" t="str">
+      <c r="M55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
@@ -6251,47 +6247,47 @@
       <c r="B56" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="192">
+      <c r="D56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="192">
+      <c r="E56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F56" s="192">
+      <c r="F56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="G56" s="192">
+      <c r="G56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H56" s="192" t="str">
+      <c r="H56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="I56" s="192" t="str">
+      <c r="I56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="J56" s="192" t="str">
+      <c r="J56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="K56" s="192" t="str">
+      <c r="K56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="L56" s="192" t="str">
+      <c r="L56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M56" s="192" t="str">
+      <c r="M56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
@@ -6300,47 +6296,47 @@
       <c r="B57" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="192">
+      <c r="D57" s="191">
         <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="192">
+      <c r="E57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F57" s="192">
+      <c r="F57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G57" s="192">
+      <c r="G57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H57" s="192" t="str">
+      <c r="H57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="I57" s="192" t="str">
+      <c r="I57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="J57" s="192" t="str">
+      <c r="J57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="K57" s="192" t="str">
+      <c r="K57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="L57" s="192" t="str">
+      <c r="L57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="M57" s="192" t="str">
+      <c r="M57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -6349,47 +6345,47 @@
       <c r="B58" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="192">
+      <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
         <v>247678</v>
       </c>
-      <c r="D58" s="192">
+      <c r="D58" s="191">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>189250</v>
       </c>
-      <c r="E58" s="192">
+      <c r="E58" s="191">
         <f t="shared" si="28"/>
         <v>200697</v>
       </c>
-      <c r="F58" s="192">
+      <c r="F58" s="191">
         <f t="shared" si="28"/>
         <v>281254</v>
       </c>
-      <c r="G58" s="192">
+      <c r="G58" s="191">
         <f t="shared" si="28"/>
         <v>-97419</v>
       </c>
-      <c r="H58" s="192" t="str">
+      <c r="H58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="I58" s="192" t="str">
+      <c r="I58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="J58" s="192" t="str">
+      <c r="J58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="K58" s="192" t="str">
+      <c r="K58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="L58" s="192" t="str">
+      <c r="L58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="M58" s="192" t="str">
+      <c r="M58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
@@ -6404,47 +6400,47 @@
       <c r="B61" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="187">
+      <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
         <v>-463424</v>
       </c>
-      <c r="D61" s="187">
+      <c r="D61" s="186">
         <f t="shared" si="29"/>
         <v>-371724</v>
       </c>
-      <c r="E61" s="187">
+      <c r="E61" s="186">
         <f t="shared" si="29"/>
         <v>-435672</v>
       </c>
-      <c r="F61" s="187">
+      <c r="F61" s="186">
         <f t="shared" si="29"/>
         <v>-520888</v>
       </c>
-      <c r="G61" s="187">
+      <c r="G61" s="186">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="187" t="str">
+      <c r="H61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="I61" s="187" t="str">
+      <c r="I61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="J61" s="187" t="str">
+      <c r="J61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="K61" s="187" t="str">
+      <c r="K61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="L61" s="187" t="str">
+      <c r="L61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="187" t="str">
+      <c r="M61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -6453,47 +6449,47 @@
       <c r="B62" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="187">
+      <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
         <v>-676387</v>
       </c>
-      <c r="D62" s="187">
+      <c r="D62" s="186">
         <f t="shared" si="30"/>
         <v>-107280</v>
       </c>
-      <c r="E62" s="187">
+      <c r="E62" s="186">
         <f t="shared" si="30"/>
         <v>-455483</v>
       </c>
-      <c r="F62" s="187">
+      <c r="F62" s="186">
         <f t="shared" si="30"/>
         <v>-138937</v>
       </c>
-      <c r="G62" s="187">
+      <c r="G62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="187" t="str">
+      <c r="H62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I62" s="187" t="str">
+      <c r="I62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="J62" s="187" t="str">
+      <c r="J62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K62" s="187" t="str">
+      <c r="K62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L62" s="187" t="str">
+      <c r="L62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="187" t="str">
+      <c r="M62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -6502,47 +6498,47 @@
       <c r="B63" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C63" s="187">
+      <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
         <v>-626583</v>
       </c>
-      <c r="D63" s="187">
+      <c r="D63" s="186">
         <f t="shared" si="31"/>
         <v>-352099</v>
       </c>
-      <c r="E63" s="187">
+      <c r="E63" s="186">
         <f t="shared" si="31"/>
         <v>-1045251</v>
       </c>
-      <c r="F63" s="187">
+      <c r="F63" s="186">
         <f t="shared" si="31"/>
         <v>818677</v>
       </c>
-      <c r="G63" s="187">
+      <c r="G63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="187" t="str">
+      <c r="H63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="I63" s="187" t="str">
+      <c r="I63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="J63" s="187" t="str">
+      <c r="J63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K63" s="187" t="str">
+      <c r="K63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L63" s="187" t="str">
+      <c r="L63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="187" t="str">
+      <c r="M63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7162,19 +7158,19 @@
       <c r="B3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="211" t="s">
+      <c r="D3" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="210" t="s">
+      <c r="G3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="211" t="s">
+      <c r="H3" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7185,7 +7181,7 @@
       <c r="C4" s="19">
         <v>265773</v>
       </c>
-      <c r="D4" s="303">
+      <c r="D4" s="301">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7195,7 +7191,7 @@
       <c r="G4" s="19">
         <v>1998219</v>
       </c>
-      <c r="H4" s="303">
+      <c r="H4" s="301">
         <v>0.9</v>
       </c>
     </row>
@@ -7206,7 +7202,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="303">
+      <c r="D5" s="301">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7216,7 +7212,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="303">
+      <c r="H5" s="301">
         <v>0.7</v>
       </c>
     </row>
@@ -7227,7 +7223,7 @@
       <c r="C6" s="19">
         <v>9672256</v>
       </c>
-      <c r="D6" s="303">
+      <c r="D6" s="301">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7237,7 +7233,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="303">
+      <c r="H6" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7248,7 +7244,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="303">
+      <c r="D7" s="301">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7258,7 +7254,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="303">
+      <c r="H7" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7269,7 +7265,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="303">
+      <c r="D8" s="301">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7279,7 +7275,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="303">
+      <c r="H8" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7290,7 +7286,7 @@
       <c r="C9" s="19">
         <v>366595</v>
       </c>
-      <c r="D9" s="303">
+      <c r="D9" s="301">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7300,7 +7296,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="303">
+      <c r="H9" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7311,10 +7307,10 @@
       <c r="C10" s="19">
         <v>29465</v>
       </c>
-      <c r="D10" s="303">
+      <c r="D10" s="301">
         <v>0.9</v>
       </c>
-      <c r="H10" s="304"/>
+      <c r="H10" s="302"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7323,10 +7319,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="303">
+      <c r="D11" s="301">
         <v>0.05</v>
       </c>
-      <c r="H11" s="304"/>
+      <c r="H11" s="302"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7361,19 +7357,19 @@
       <c r="B14" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="210" t="s">
+      <c r="C14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="211" t="s">
+      <c r="D14" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="210" t="s">
+      <c r="G14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="211" t="s">
+      <c r="H14" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7384,7 +7380,7 @@
       <c r="C15" s="19">
         <v>103050</v>
       </c>
-      <c r="D15" s="303">
+      <c r="D15" s="301">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7393,7 +7389,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="303">
+      <c r="H15" s="301">
         <v>0.8</v>
       </c>
     </row>
@@ -7404,7 +7400,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="303">
+      <c r="D16" s="301">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7413,7 +7409,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="303">
+      <c r="H16" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7424,7 +7420,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="303">
+      <c r="D17" s="301">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7433,7 +7429,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="303">
+      <c r="H17" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7444,7 +7440,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="303">
+      <c r="D18" s="301">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7453,7 +7449,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="303">
+      <c r="H18" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7464,7 +7460,7 @@
       <c r="C19" s="19">
         <v>2522337</v>
       </c>
-      <c r="D19" s="303">
+      <c r="D19" s="301">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7473,7 +7469,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="303">
+      <c r="H19" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7484,7 +7480,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="303">
+      <c r="D20" s="301">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7493,7 +7489,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="303">
+      <c r="H20" s="301">
         <v>0.2</v>
       </c>
     </row>
@@ -7504,7 +7500,7 @@
       <c r="C21" s="19">
         <v>538321</v>
       </c>
-      <c r="D21" s="303">
+      <c r="D21" s="301">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7513,7 +7509,7 @@
       <c r="G21" s="19">
         <v>925726</v>
       </c>
-      <c r="H21" s="303">
+      <c r="H21" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7524,10 +7520,10 @@
       <c r="C22" s="19">
         <v>154648</v>
       </c>
-      <c r="D22" s="303">
+      <c r="D22" s="301">
         <v>0.9</v>
       </c>
-      <c r="H22" s="304"/>
+      <c r="H22" s="302"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7536,10 +7532,10 @@
       <c r="C23" s="19">
         <v>277674</v>
       </c>
-      <c r="D23" s="303">
-        <v>0</v>
-      </c>
-      <c r="H23" s="304"/>
+      <c r="D23" s="301">
+        <v>0</v>
+      </c>
+      <c r="H23" s="302"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7569,16 +7565,16 @@
       <c r="B26" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="210" t="s">
+      <c r="C26" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F26" s="212" t="s">
+      <c r="F26" s="211" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="213" t="s">
+      <c r="G26" s="212" t="s">
         <v>141</v>
       </c>
-      <c r="H26" s="214" t="s">
+      <c r="H26" s="213" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7589,14 +7585,14 @@
       <c r="C27" s="19">
         <v>1427805</v>
       </c>
-      <c r="F27" s="215" t="s">
+      <c r="F27" s="214" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
         <v>12863898</v>
       </c>
-      <c r="H27" s="216">
+      <c r="H27" s="215">
         <f>H32-G30</f>
         <v>3419126.45</v>
       </c>
@@ -7608,13 +7604,13 @@
       <c r="C28" s="19">
         <v>287697</v>
       </c>
-      <c r="F28" s="217" t="s">
+      <c r="F28" s="216" t="s">
         <v>251</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="184">
         <v>-26962</v>
       </c>
-      <c r="H28" s="216"/>
+      <c r="H28" s="215"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
@@ -7623,14 +7619,14 @@
       <c r="C29" s="19">
         <v>0</v>
       </c>
-      <c r="F29" s="218" t="s">
+      <c r="F29" s="217" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
         <v>12890860</v>
       </c>
-      <c r="H29" s="216">
+      <c r="H29" s="215">
         <f>H27-G28</f>
         <v>3446088.45</v>
       </c>
@@ -7642,14 +7638,14 @@
       <c r="C30" s="19">
         <v>0</v>
       </c>
-      <c r="F30" s="215" t="s">
+      <c r="F30" s="214" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
         <v>3990166</v>
       </c>
-      <c r="H30" s="216"/>
+      <c r="H30" s="215"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
@@ -7659,14 +7655,14 @@
         <f>SUM(C27:C30)</f>
         <v>1715502</v>
       </c>
-      <c r="F31" s="218" t="s">
+      <c r="F31" s="217" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="219">
+      <c r="G31" s="218">
         <f>C31+C40</f>
         <v>2034922</v>
       </c>
-      <c r="H31" s="216"/>
+      <c r="H31" s="215"/>
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
@@ -7676,14 +7672,14 @@
         <f>C33-C31</f>
         <v>1801307</v>
       </c>
-      <c r="F32" s="220" t="s">
+      <c r="F32" s="219" t="s">
         <v>79</v>
       </c>
-      <c r="G32" s="221">
+      <c r="G32" s="220">
         <f>G35+G40</f>
         <v>16854064</v>
       </c>
-      <c r="H32" s="216">
+      <c r="H32" s="215">
         <f>H35+H40</f>
         <v>7409292.4500000002</v>
       </c>
@@ -7695,20 +7691,20 @@
       <c r="C33" s="86">
         <v>3516809</v>
       </c>
-      <c r="F33" s="222"/>
+      <c r="F33" s="221"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="223"/>
+      <c r="H33" s="222"/>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
-      <c r="F34" s="224" t="s">
+      <c r="F34" s="223" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="225" t="s">
+      <c r="G34" s="224" t="s">
         <v>141</v>
       </c>
-      <c r="H34" s="226" t="s">
+      <c r="H34" s="225" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7716,17 +7712,17 @@
       <c r="B35" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C35" s="210" t="s">
+      <c r="C35" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="227" t="s">
+      <c r="F35" s="226" t="s">
         <v>32</v>
       </c>
-      <c r="G35" s="221">
+      <c r="G35" s="220">
         <f>C12+C24</f>
         <v>13930119</v>
       </c>
-      <c r="H35" s="228">
+      <c r="H35" s="227">
         <f>D12+D24</f>
         <v>5518322.75</v>
       </c>
@@ -7738,14 +7734,14 @@
       <c r="C36" s="19">
         <v>0</v>
       </c>
-      <c r="F36" s="218" t="s">
+      <c r="F36" s="217" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="219">
+      <c r="G36" s="218">
         <f>C4+C15</f>
         <v>368823</v>
       </c>
-      <c r="H36" s="223"/>
+      <c r="H36" s="222"/>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
@@ -7754,14 +7750,14 @@
       <c r="C37" s="19">
         <v>0</v>
       </c>
-      <c r="F37" s="218" t="s">
+      <c r="F37" s="217" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="219">
+      <c r="G37" s="218">
         <f>C6</f>
         <v>9672256</v>
       </c>
-      <c r="H37" s="223"/>
+      <c r="H37" s="222"/>
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
@@ -7770,14 +7766,14 @@
       <c r="C38" s="19">
         <v>319420</v>
       </c>
-      <c r="F38" s="218" t="s">
+      <c r="F38" s="217" t="s">
         <v>204</v>
       </c>
-      <c r="G38" s="219">
+      <c r="G38" s="218">
         <f>C7+C17</f>
         <v>0</v>
       </c>
-      <c r="H38" s="223"/>
+      <c r="H38" s="222"/>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
@@ -7786,14 +7782,14 @@
       <c r="C39" s="19">
         <v>0</v>
       </c>
-      <c r="F39" s="218" t="s">
+      <c r="F39" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="G39" s="219">
+      <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
         <v>2522337</v>
       </c>
-      <c r="H39" s="216">
+      <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
         <v>252233.7</v>
       </c>
@@ -7806,14 +7802,14 @@
         <f>SUM(C36:C39)</f>
         <v>319420</v>
       </c>
-      <c r="F40" s="227" t="s">
+      <c r="F40" s="226" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="221">
+      <c r="G40" s="220">
         <f>G12+G24</f>
         <v>2923945</v>
       </c>
-      <c r="H40" s="228">
+      <c r="H40" s="227">
         <f>H12+H24</f>
         <v>1890969.7000000002</v>
       </c>
@@ -7826,14 +7822,14 @@
         <f>C42-C40</f>
         <v>153937</v>
       </c>
-      <c r="F41" s="218" t="s">
+      <c r="F41" s="217" t="s">
         <v>196</v>
       </c>
-      <c r="G41" s="219">
+      <c r="G41" s="218">
         <f>C70</f>
         <v>1998219</v>
       </c>
-      <c r="H41" s="228">
+      <c r="H41" s="227">
         <f>H40-H42</f>
         <v>1798397.1</v>
       </c>
@@ -7845,14 +7841,14 @@
       <c r="C42" s="86">
         <v>473357</v>
       </c>
-      <c r="F42" s="229" t="s">
+      <c r="F42" s="228" t="s">
         <v>197</v>
       </c>
-      <c r="G42" s="230">
+      <c r="G42" s="229">
         <f>C82</f>
         <v>925726</v>
       </c>
-      <c r="H42" s="231">
+      <c r="H42" s="230">
         <f>D82</f>
         <v>92572.6</v>
       </c>
@@ -7872,13 +7868,13 @@
       <c r="B45" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="268" t="s">
+      <c r="C45" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D45" s="210" t="s">
+      <c r="D45" s="209" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="296" t="s">
+      <c r="F45" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7886,15 +7882,15 @@
       <c r="B46" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="192">
+      <c r="C46" s="191">
         <f>G29</f>
         <v>12890860</v>
       </c>
-      <c r="D46" s="192">
+      <c r="D46" s="191">
         <f>H29</f>
         <v>3446088.45</v>
       </c>
-      <c r="F46" s="291"/>
+      <c r="F46" s="289"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7909,23 +7905,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>5.8696003638854428</v>
       </c>
-      <c r="F47" s="291"/>
+      <c r="F47" s="289"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="291"/>
+      <c r="F48" s="289"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="162" t="s">
+      <c r="B49" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="C49" s="269" t="s">
+      <c r="C49" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="225" t="s">
+      <c r="D49" s="224" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="291"/>
+      <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7939,33 +7935,33 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.0842664509772892</v>
       </c>
-      <c r="F50" s="291"/>
+      <c r="F50" s="289"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C51" s="209"/>
+      <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
         <v>0.76485172952944758</v>
       </c>
-      <c r="F51" s="291"/>
+      <c r="F51" s="289"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="291"/>
+      <c r="F52" s="289"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="161" t="s">
         <v>147</v>
       </c>
-      <c r="C53" s="269" t="s">
+      <c r="C53" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="225" t="s">
+      <c r="D53" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="291"/>
+      <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7979,7 +7975,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.13472770763839131</v>
       </c>
-      <c r="F54" s="291"/>
+      <c r="F54" s="289"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7993,22 +7989,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>2.1854036242131779E-4</v>
       </c>
-      <c r="F55" s="291"/>
+      <c r="F55" s="289"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="291"/>
+      <c r="F56" s="289"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="162" t="s">
+      <c r="B57" s="161" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="269" t="s">
+      <c r="C57" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="225" t="s">
+      <c r="D57" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="291"/>
+      <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -8030,22 +8026,22 @@
         <f>G39/G32</f>
         <v>0.14965749507062509</v>
       </c>
-      <c r="F59" s="291"/>
+      <c r="F59" s="289"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="291"/>
+      <c r="F60" s="289"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="162" t="s">
+      <c r="B61" s="161" t="s">
         <v>291</v>
       </c>
-      <c r="C61" s="269" t="s">
+      <c r="C61" s="268" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="291"/>
+      <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -8059,7 +8055,7 @@
         <f>G28/G29</f>
         <v>-2.0915594459950692E-3</v>
       </c>
-      <c r="F62" s="291" t="s">
+      <c r="F62" s="289" t="s">
         <v>289</v>
       </c>
     </row>
@@ -8078,13 +8074,13 @@
       <c r="B65" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="268" t="s">
+      <c r="C65" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="211" t="s">
+      <c r="D65" s="210" t="s">
         <v>312</v>
       </c>
-      <c r="F65" s="296" t="s">
+      <c r="F65" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8096,7 +8092,7 @@
         <f>G4+G5+G15</f>
         <v>1998219</v>
       </c>
-      <c r="D66" s="192">
+      <c r="D66" s="191">
         <f>C66-D75</f>
         <v>1116785.5502773244</v>
       </c>
@@ -8112,7 +8108,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="291"/>
+      <c r="F67" s="289"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -8122,7 +8118,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="291"/>
+      <c r="F68" s="289"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -8132,7 +8128,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="291"/>
+      <c r="F69" s="289"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -8142,49 +8138,49 @@
         <f>SUM(C66:C69)</f>
         <v>1998219</v>
       </c>
-      <c r="F70" s="291"/>
+      <c r="F70" s="289"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="291"/>
+      <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="294" t="s">
+      <c r="B72" s="292" t="s">
         <v>353</v>
       </c>
-      <c r="C72" s="268" t="s">
+      <c r="C72" s="267" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="210" t="s">
+      <c r="D72" s="209" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="291"/>
+      <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
         <v>352</v>
       </c>
-      <c r="C73" s="192">
+      <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
         <v>-1120765.75</v>
       </c>
-      <c r="D73" s="192">
+      <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
         <v>-881433.44972267561</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="297" t="s">
+      <c r="B74" s="295" t="s">
         <v>358</v>
       </c>
-      <c r="C74" s="298">
+      <c r="C74" s="296">
         <f>-$C$66/C73</f>
         <v>1.7829051253573729</v>
       </c>
-      <c r="D74" s="298">
+      <c r="D74" s="296">
         <f>-$C$66/D73</f>
         <v>2.2670106298197523</v>
       </c>
-      <c r="F74" s="291" t="s">
+      <c r="F74" s="289" t="s">
         <v>354</v>
       </c>
     </row>
@@ -8192,42 +8188,42 @@
       <c r="B75" s="82" t="s">
         <v>355</v>
       </c>
-      <c r="C75" s="302"/>
-      <c r="D75" s="301">
+      <c r="C75" s="300"/>
+      <c r="D75" s="299">
         <f>MAX(-D73*D76,G5)</f>
         <v>881433.44972267561</v>
       </c>
-      <c r="F75" s="291" t="s">
+      <c r="F75" s="289" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="299" t="s">
+      <c r="B76" s="297" t="s">
         <v>359</v>
       </c>
-      <c r="C76" s="300"/>
-      <c r="D76" s="337">
+      <c r="C76" s="298"/>
+      <c r="D76" s="335">
         <f>IF(D74&lt;=3,1,IF(D74&gt;12,IF(D74&gt;24,12,6),2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="291" t="s">
+      <c r="F76" s="289" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="291"/>
+      <c r="F77" s="289"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D78" s="211" t="s">
+      <c r="D78" s="210" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="291"/>
+      <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8237,11 +8233,11 @@
         <f>G7+G17</f>
         <v>0</v>
       </c>
-      <c r="D79" s="192">
+      <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="291"/>
+      <c r="F79" s="289"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8251,11 +8247,11 @@
         <f>G19</f>
         <v>0</v>
       </c>
-      <c r="D80" s="192">
+      <c r="D80" s="191">
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="291"/>
+      <c r="F80" s="289"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8265,11 +8261,11 @@
         <f>G9+G21</f>
         <v>925726</v>
       </c>
-      <c r="D81" s="192">
+      <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
         <v>92572.6</v>
       </c>
-      <c r="F81" s="291"/>
+      <c r="F81" s="289"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8283,7 +8279,7 @@
         <f>SUM(D79:D81)</f>
         <v>92572.6</v>
       </c>
-      <c r="F82" s="291"/>
+      <c r="F82" s="289"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8300,57 +8296,57 @@
       <c r="B85" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="D85" s="278" t="s">
+      <c r="D85" s="276" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="275" t="s">
+      <c r="B86" s="273" t="s">
         <v>313</v>
       </c>
-      <c r="C86" s="192">
+      <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-2034922</v>
       </c>
-      <c r="D86" s="255">
+      <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
         <v>-3.4660105464438944</v>
       </c>
-      <c r="E86" s="277" t="str">
+      <c r="E86" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="275" t="s">
+      <c r="B87" s="273" t="s">
         <v>314</v>
       </c>
-      <c r="C87" s="192">
+      <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>1116785.5502773244</v>
       </c>
-      <c r="D87" s="255">
+      <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
         <v>1.9021812606956703</v>
       </c>
-      <c r="E87" s="277" t="str">
+      <c r="E87" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="276" t="s">
+      <c r="B88" s="274" t="s">
         <v>194</v>
       </c>
-      <c r="C88" s="192">
+      <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>92572.6</v>
       </c>
-      <c r="D88" s="255">
+      <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
         <v>0.15767562978420405</v>
       </c>
-      <c r="E88" s="277" t="str">
+      <c r="E88" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8359,15 +8355,15 @@
       <c r="B89" s="82" t="s">
         <v>318</v>
       </c>
-      <c r="C89" s="191">
+      <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
         <v>-825563.84972267563</v>
       </c>
-      <c r="D89" s="279">
+      <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
         <v>-1.40615365596402</v>
       </c>
-      <c r="E89" s="277" t="str">
+      <c r="E89" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8488,7 +8484,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="311"/>
+      <c r="E3" s="309"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8497,54 +8493,54 @@
       <c r="B4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="197">
+      <c r="C4" s="196">
         <f>AVERAGE(G4:J4)</f>
         <v>11975736</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="309"/>
+      <c r="E4" s="307"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="187">
+      <c r="G4" s="186">
         <f>Data!C36</f>
         <v>15325962</v>
       </c>
-      <c r="H4" s="187">
+      <c r="H4" s="186">
         <f>Data!D36</f>
         <v>11977844</v>
       </c>
-      <c r="I4" s="187">
+      <c r="I4" s="186">
         <f>Data!E36</f>
         <v>11737803</v>
       </c>
-      <c r="J4" s="187">
+      <c r="J4" s="186">
         <f>Data!F36</f>
         <v>8861335</v>
       </c>
-      <c r="K4" s="187">
+      <c r="K4" s="186">
         <f>Data!G36</f>
         <v>11233771</v>
       </c>
-      <c r="L4" s="187" t="str">
+      <c r="L4" s="186" t="str">
         <f>Data!H36</f>
         <v/>
       </c>
-      <c r="M4" s="187" t="str">
+      <c r="M4" s="186" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N4" s="187" t="str">
+      <c r="N4" s="186" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O4" s="187" t="str">
+      <c r="O4" s="186" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P4" s="187" t="str">
+      <c r="P4" s="186" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="187" t="str">
+      <c r="Q4" s="186" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -8554,52 +8550,52 @@
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="198">
+      <c r="C5" s="197">
         <f>C25</f>
         <v>-10274842.146672107</v>
       </c>
-      <c r="E5" s="311"/>
-      <c r="G5" s="187">
+      <c r="E5" s="309"/>
+      <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-13195082</v>
       </c>
-      <c r="H5" s="187">
+      <c r="H5" s="186">
         <f t="shared" si="1"/>
         <v>-10265436</v>
       </c>
-      <c r="I5" s="187">
+      <c r="I5" s="186">
         <f t="shared" si="1"/>
         <v>-9995269</v>
       </c>
-      <c r="J5" s="187">
+      <c r="J5" s="186">
         <f t="shared" si="1"/>
         <v>-7641514</v>
       </c>
-      <c r="K5" s="187">
+      <c r="K5" s="186">
         <f t="shared" si="1"/>
         <v>-9855851</v>
       </c>
-      <c r="L5" s="187" t="str">
+      <c r="L5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M5" s="187" t="str">
+      <c r="M5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N5" s="187" t="str">
+      <c r="N5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O5" s="187" t="str">
+      <c r="O5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="187" t="str">
+      <c r="P5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="187" t="str">
+      <c r="Q5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8609,52 +8605,52 @@
       <c r="B6" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="188">
+      <c r="C6" s="187">
         <f>C4+C5</f>
         <v>1700893.8533278927</v>
       </c>
-      <c r="E6" s="311"/>
-      <c r="G6" s="188">
+      <c r="E6" s="309"/>
+      <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>2130880</v>
       </c>
-      <c r="H6" s="188">
+      <c r="H6" s="187">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>1712408</v>
       </c>
-      <c r="I6" s="188">
+      <c r="I6" s="187">
         <f t="shared" si="2"/>
         <v>1742534</v>
       </c>
-      <c r="J6" s="188">
+      <c r="J6" s="187">
         <f t="shared" si="2"/>
         <v>1219821</v>
       </c>
-      <c r="K6" s="188">
+      <c r="K6" s="187">
         <f t="shared" si="2"/>
         <v>1377920</v>
       </c>
-      <c r="L6" s="188" t="str">
+      <c r="L6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M6" s="188" t="str">
+      <c r="M6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="N6" s="188" t="str">
+      <c r="N6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="188" t="str">
+      <c r="O6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" s="188" t="str">
+      <c r="P6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="188" t="str">
+      <c r="Q6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8664,52 +8660,52 @@
       <c r="B7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="198">
+      <c r="C7" s="197">
         <f>C35</f>
         <v>-302359.25</v>
       </c>
-      <c r="E7" s="311"/>
-      <c r="G7" s="198">
+      <c r="E7" s="309"/>
+      <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-254107</v>
       </c>
-      <c r="H7" s="198">
+      <c r="H7" s="197">
         <f t="shared" si="3"/>
         <v>-349526</v>
       </c>
-      <c r="I7" s="198">
+      <c r="I7" s="197">
         <f t="shared" si="3"/>
         <v>-323818</v>
       </c>
-      <c r="J7" s="198">
+      <c r="J7" s="197">
         <f t="shared" si="3"/>
         <v>-281986</v>
       </c>
-      <c r="K7" s="198">
+      <c r="K7" s="197">
         <f t="shared" si="3"/>
         <v>-173152</v>
       </c>
-      <c r="L7" s="198" t="str">
+      <c r="L7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M7" s="198" t="str">
+      <c r="M7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="N7" s="198" t="str">
+      <c r="N7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O7" s="198" t="str">
+      <c r="O7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P7" s="198" t="str">
+      <c r="P7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="198" t="str">
+      <c r="Q7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -8719,54 +8715,54 @@
       <c r="B8" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="199">
+      <c r="C8" s="198">
         <f>C6+C7</f>
         <v>1398534.6033278927</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="317"/>
+      <c r="E8" s="315"/>
       <c r="F8" s="60"/>
-      <c r="G8" s="188">
+      <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
         <v>1876773</v>
       </c>
-      <c r="H8" s="188">
+      <c r="H8" s="187">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>1362882</v>
       </c>
-      <c r="I8" s="188">
+      <c r="I8" s="187">
         <f t="shared" si="4"/>
         <v>1418716</v>
       </c>
-      <c r="J8" s="188">
+      <c r="J8" s="187">
         <f t="shared" si="4"/>
         <v>937835</v>
       </c>
-      <c r="K8" s="188">
+      <c r="K8" s="187">
         <f t="shared" si="4"/>
         <v>1204768</v>
       </c>
-      <c r="L8" s="188" t="str">
+      <c r="L8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="188" t="str">
+      <c r="M8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="188" t="str">
+      <c r="N8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O8" s="188" t="str">
+      <c r="O8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P8" s="188" t="str">
+      <c r="P8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="188" t="str">
+      <c r="Q8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -8776,52 +8772,52 @@
       <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="198">
+      <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>463424</v>
       </c>
-      <c r="E9" s="311"/>
-      <c r="G9" s="198">
+      <c r="E9" s="309"/>
+      <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>463424</v>
       </c>
-      <c r="H9" s="198">
+      <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>371724</v>
       </c>
-      <c r="I9" s="198">
+      <c r="I9" s="197">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>435672</v>
       </c>
-      <c r="J9" s="198">
+      <c r="J9" s="197">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>520888</v>
       </c>
-      <c r="K9" s="198">
+      <c r="K9" s="197">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="198" t="str">
+      <c r="L9" s="197" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v/>
       </c>
-      <c r="M9" s="198" t="str">
+      <c r="M9" s="197" t="str">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v/>
       </c>
-      <c r="N9" s="198" t="str">
+      <c r="N9" s="197" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v/>
       </c>
-      <c r="O9" s="198" t="str">
+      <c r="O9" s="197" t="str">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v/>
       </c>
-      <c r="P9" s="198" t="str">
+      <c r="P9" s="197" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="198" t="str">
+      <c r="Q9" s="197" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -8831,52 +8827,52 @@
       <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="198">
+      <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-463424.00000000006</v>
       </c>
-      <c r="E10" s="311"/>
-      <c r="G10" s="198">
+      <c r="E10" s="309"/>
+      <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-676387</v>
       </c>
-      <c r="H10" s="198">
+      <c r="H10" s="197">
         <f>Data!D62</f>
         <v>-107280</v>
       </c>
-      <c r="I10" s="198">
+      <c r="I10" s="197">
         <f>Data!E62</f>
         <v>-455483</v>
       </c>
-      <c r="J10" s="198">
+      <c r="J10" s="197">
         <f>Data!F62</f>
         <v>-138937</v>
       </c>
-      <c r="K10" s="198">
+      <c r="K10" s="197">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="198" t="str">
+      <c r="L10" s="197" t="str">
         <f>Data!H62</f>
         <v/>
       </c>
-      <c r="M10" s="198" t="str">
+      <c r="M10" s="197" t="str">
         <f>Data!I62</f>
         <v/>
       </c>
-      <c r="N10" s="198" t="str">
+      <c r="N10" s="197" t="str">
         <f>Data!J62</f>
         <v/>
       </c>
-      <c r="O10" s="198" t="str">
+      <c r="O10" s="197" t="str">
         <f>Data!K62</f>
         <v/>
       </c>
-      <c r="P10" s="198" t="str">
+      <c r="P10" s="197" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="198" t="str">
+      <c r="Q10" s="197" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -8886,54 +8882,54 @@
       <c r="B11" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="200">
+      <c r="C11" s="199">
         <f>C63</f>
         <v>0</v>
       </c>
-      <c r="D11" s="173"/>
-      <c r="E11" s="310"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="190">
+      <c r="D11" s="172"/>
+      <c r="E11" s="308"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="189">
         <f>G61</f>
         <v>639</v>
       </c>
-      <c r="H11" s="190">
+      <c r="H11" s="189">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>927</v>
       </c>
-      <c r="I11" s="190">
+      <c r="I11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="190">
+      <c r="J11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="190">
+      <c r="K11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="190" t="str">
+      <c r="L11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="M11" s="190" t="str">
+      <c r="M11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="190" t="str">
+      <c r="N11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O11" s="190" t="str">
+      <c r="O11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P11" s="190" t="str">
+      <c r="P11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="190" t="str">
+      <c r="Q11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -8943,52 +8939,52 @@
       <c r="B12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="198">
+      <c r="C12" s="197">
         <f>C50</f>
         <v>-46813.969065145531</v>
       </c>
-      <c r="E12" s="311"/>
-      <c r="G12" s="198">
+      <c r="E12" s="309"/>
+      <c r="G12" s="197">
         <f>G50</f>
         <v>-46813.969065145531</v>
       </c>
-      <c r="H12" s="198">
+      <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-6151.2467226747285</v>
       </c>
-      <c r="I12" s="198">
+      <c r="I12" s="197">
         <f t="shared" si="6"/>
         <v>15431.271041651278</v>
       </c>
-      <c r="J12" s="198">
+      <c r="J12" s="197">
         <f t="shared" si="6"/>
         <v>-883.53783318135538</v>
       </c>
-      <c r="K12" s="198">
+      <c r="K12" s="197">
         <f t="shared" si="6"/>
         <v>-43026.571729677475</v>
       </c>
-      <c r="L12" s="198" t="str">
+      <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M12" s="198" t="str">
+      <c r="M12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="N12" s="198" t="str">
+      <c r="N12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O12" s="198" t="str">
+      <c r="O12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P12" s="198" t="str">
+      <c r="P12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="198" t="str">
+      <c r="Q12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8998,52 +8994,52 @@
       <c r="B13" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="188">
+      <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
         <v>1351720.6342627471</v>
       </c>
-      <c r="E13" s="311"/>
-      <c r="G13" s="188">
+      <c r="E13" s="309"/>
+      <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1617635.0309348544</v>
       </c>
-      <c r="H13" s="188">
+      <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>1622101.7532773253</v>
       </c>
-      <c r="I13" s="188">
+      <c r="I13" s="187">
         <f t="shared" si="7"/>
         <v>1414336.2710416513</v>
       </c>
-      <c r="J13" s="188">
+      <c r="J13" s="187">
         <f t="shared" si="7"/>
         <v>1318902.4621668186</v>
       </c>
-      <c r="K13" s="188">
+      <c r="K13" s="187">
         <f t="shared" si="7"/>
         <v>1161741.4282703225</v>
       </c>
-      <c r="L13" s="188" t="str">
+      <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M13" s="188" t="str">
+      <c r="M13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N13" s="188" t="str">
+      <c r="N13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O13" s="188" t="str">
+      <c r="O13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P13" s="188" t="str">
+      <c r="P13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="188" t="str">
+      <c r="Q13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9053,52 +9049,52 @@
       <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="198">
+      <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-337930.15856568678</v>
       </c>
-      <c r="E14" s="311"/>
-      <c r="G14" s="198">
+      <c r="E14" s="309"/>
+      <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-327166</v>
       </c>
-      <c r="H14" s="198">
+      <c r="H14" s="197">
         <f>Data!D46</f>
         <v>-280664</v>
       </c>
-      <c r="I14" s="198">
+      <c r="I14" s="197">
         <f>Data!E46</f>
         <v>-291296</v>
       </c>
-      <c r="J14" s="198">
+      <c r="J14" s="197">
         <f>Data!F46</f>
         <v>-236303</v>
       </c>
-      <c r="K14" s="198">
+      <c r="K14" s="197">
         <f>Data!G46</f>
         <v>-223409</v>
       </c>
-      <c r="L14" s="198" t="str">
+      <c r="L14" s="197" t="str">
         <f>Data!H46</f>
         <v/>
       </c>
-      <c r="M14" s="198" t="str">
+      <c r="M14" s="197" t="str">
         <f>Data!I46</f>
         <v/>
       </c>
-      <c r="N14" s="198" t="str">
+      <c r="N14" s="197" t="str">
         <f>Data!J46</f>
         <v/>
       </c>
-      <c r="O14" s="198" t="str">
+      <c r="O14" s="197" t="str">
         <f>Data!K46</f>
         <v/>
       </c>
-      <c r="P14" s="198" t="str">
+      <c r="P14" s="197" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="198" t="str">
+      <c r="Q14" s="197" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -9108,54 +9104,54 @@
       <c r="B15" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="198">
+      <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="318"/>
+      <c r="E15" s="316"/>
       <c r="F15" s="61"/>
-      <c r="G15" s="187">
+      <c r="G15" s="186">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="187">
+      <c r="H15" s="186">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="187">
+      <c r="I15" s="186">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="187">
+      <c r="J15" s="186">
         <f>Data!F48</f>
         <v>-1799</v>
       </c>
-      <c r="K15" s="187">
+      <c r="K15" s="186">
         <f>Data!G48</f>
         <v>-1337</v>
       </c>
-      <c r="L15" s="187" t="str">
+      <c r="L15" s="186" t="str">
         <f>Data!H48</f>
         <v/>
       </c>
-      <c r="M15" s="187" t="str">
+      <c r="M15" s="186" t="str">
         <f>Data!I48</f>
         <v/>
       </c>
-      <c r="N15" s="187" t="str">
+      <c r="N15" s="186" t="str">
         <f>Data!J48</f>
         <v/>
       </c>
-      <c r="O15" s="187" t="str">
+      <c r="O15" s="186" t="str">
         <f>Data!K48</f>
         <v/>
       </c>
-      <c r="P15" s="187" t="str">
+      <c r="P15" s="186" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="187" t="str">
+      <c r="Q15" s="186" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -9165,54 +9161,54 @@
       <c r="B16" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="201">
+      <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
         <v>1013790.4756970603</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="319"/>
+      <c r="E16" s="317"/>
       <c r="F16" s="62"/>
-      <c r="G16" s="188">
+      <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>1290469.0309348544</v>
       </c>
-      <c r="H16" s="188">
+      <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>1341437.7532773253</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="187">
         <f t="shared" si="8"/>
         <v>1123040.2710416513</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="187">
         <f t="shared" si="8"/>
         <v>1080800.4621668186</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="187">
         <f t="shared" si="8"/>
         <v>936995.4282703225</v>
       </c>
-      <c r="L16" s="188" t="str">
+      <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M16" s="188" t="str">
+      <c r="M16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N16" s="188" t="str">
+      <c r="N16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O16" s="188" t="str">
+      <c r="O16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P16" s="188" t="str">
+      <c r="P16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="188" t="str">
+      <c r="Q16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -9222,105 +9218,105 @@
       <c r="B17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="198">
+      <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="310" t="s">
+      <c r="E17" s="308" t="s">
         <v>370</v>
       </c>
       <c r="F17" s="59"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="202"/>
-      <c r="N17" s="202"/>
-      <c r="O17" s="202"/>
-      <c r="P17" s="202"/>
-      <c r="Q17" s="202"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="201"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="201"/>
+      <c r="K17" s="201"/>
+      <c r="L17" s="201"/>
+      <c r="M17" s="201"/>
+      <c r="N17" s="201"/>
+      <c r="O17" s="201"/>
+      <c r="P17" s="201"/>
+      <c r="Q17" s="201"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="198">
+      <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="310" t="s">
+      <c r="E18" s="308" t="s">
         <v>371</v>
       </c>
       <c r="F18" s="59"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="203"/>
-      <c r="I18" s="203"/>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="203"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="203"/>
-      <c r="O18" s="203"/>
-      <c r="P18" s="203"/>
-      <c r="Q18" s="203"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="202"/>
+      <c r="J18" s="202"/>
+      <c r="K18" s="202"/>
+      <c r="L18" s="202"/>
+      <c r="M18" s="202"/>
+      <c r="N18" s="202"/>
+      <c r="O18" s="202"/>
+      <c r="P18" s="202"/>
+      <c r="Q18" s="202"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="188">
+      <c r="C19" s="187">
         <f>C16+C17</f>
         <v>1013790.4756970603</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="308"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="190">
+      <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
         <v>1290469.0309348544</v>
       </c>
-      <c r="H19" s="190">
+      <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>1341437.7532773253</v>
       </c>
-      <c r="I19" s="190">
+      <c r="I19" s="189">
         <f t="shared" si="9"/>
         <v>1123040.2710416513</v>
       </c>
-      <c r="J19" s="190">
+      <c r="J19" s="189">
         <f t="shared" si="9"/>
         <v>1080800.4621668186</v>
       </c>
-      <c r="K19" s="190">
+      <c r="K19" s="189">
         <f t="shared" si="9"/>
         <v>936995.4282703225</v>
       </c>
-      <c r="L19" s="190" t="str">
+      <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M19" s="190" t="str">
+      <c r="M19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="N19" s="190" t="str">
+      <c r="N19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O19" s="190" t="str">
+      <c r="O19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P19" s="190" t="str">
+      <c r="P19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="190" t="str">
+      <c r="Q19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -9374,7 +9370,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="308"/>
+      <c r="E22" s="306"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9393,54 +9389,54 @@
       <c r="B23" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="204">
+      <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-8638608.2360938303</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="310"/>
+      <c r="E23" s="308"/>
       <c r="F23" s="59"/>
-      <c r="G23" s="187">
+      <c r="G23" s="186">
         <f>Data!C37</f>
         <v>-11151623</v>
       </c>
-      <c r="H23" s="187">
+      <c r="H23" s="186">
         <f>Data!D37</f>
         <v>-8747447</v>
       </c>
-      <c r="I23" s="187">
+      <c r="I23" s="186">
         <f>Data!E37</f>
         <v>-8503976</v>
       </c>
-      <c r="J23" s="187">
+      <c r="J23" s="186">
         <f>Data!F37</f>
         <v>-6229020</v>
       </c>
-      <c r="K23" s="187">
+      <c r="K23" s="186">
         <f>Data!G37</f>
         <v>-7910751</v>
       </c>
-      <c r="L23" s="187" t="str">
+      <c r="L23" s="186" t="str">
         <f>Data!H37</f>
         <v/>
       </c>
-      <c r="M23" s="187" t="str">
+      <c r="M23" s="186" t="str">
         <f>Data!I37</f>
         <v/>
       </c>
-      <c r="N23" s="187" t="str">
+      <c r="N23" s="186" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O23" s="187" t="str">
+      <c r="O23" s="186" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P23" s="187" t="str">
+      <c r="P23" s="186" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="187" t="str">
+      <c r="Q23" s="186" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -9450,54 +9446,54 @@
       <c r="B24" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="198">
+      <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>-1636233.9105782772</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="308"/>
+      <c r="E24" s="306"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="187">
+      <c r="G24" s="186">
         <f>Data!C40</f>
         <v>-2043459</v>
       </c>
-      <c r="H24" s="187">
+      <c r="H24" s="186">
         <f>Data!D40</f>
         <v>-1517989</v>
       </c>
-      <c r="I24" s="187">
+      <c r="I24" s="186">
         <f>Data!E40</f>
         <v>-1491293</v>
       </c>
-      <c r="J24" s="187">
+      <c r="J24" s="186">
         <f>Data!F40</f>
         <v>-1412494</v>
       </c>
-      <c r="K24" s="187">
+      <c r="K24" s="186">
         <f>Data!G40</f>
         <v>-1945100</v>
       </c>
-      <c r="L24" s="187" t="str">
+      <c r="L24" s="186" t="str">
         <f>Data!H40</f>
         <v/>
       </c>
-      <c r="M24" s="187" t="str">
+      <c r="M24" s="186" t="str">
         <f>Data!I40</f>
         <v/>
       </c>
-      <c r="N24" s="187" t="str">
+      <c r="N24" s="186" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O24" s="187" t="str">
+      <c r="O24" s="186" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P24" s="187" t="str">
+      <c r="P24" s="186" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="187" t="str">
+      <c r="Q24" s="186" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -9507,68 +9503,68 @@
       <c r="B25" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="188">
+      <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-10274842.146672107</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="316"/>
+      <c r="E25" s="314"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="188">
+      <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-13195082</v>
       </c>
-      <c r="H25" s="188">
+      <c r="H25" s="187">
         <f t="shared" si="10"/>
         <v>-10265436</v>
       </c>
-      <c r="I25" s="188">
+      <c r="I25" s="187">
         <f t="shared" si="10"/>
         <v>-9995269</v>
       </c>
-      <c r="J25" s="188">
+      <c r="J25" s="187">
         <f t="shared" si="10"/>
         <v>-7641514</v>
       </c>
-      <c r="K25" s="188">
+      <c r="K25" s="187">
         <f t="shared" si="10"/>
         <v>-9855851</v>
       </c>
-      <c r="L25" s="188" t="str">
+      <c r="L25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M25" s="188" t="str">
+      <c r="M25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N25" s="188" t="str">
+      <c r="N25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O25" s="188" t="str">
+      <c r="O25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P25" s="188" t="str">
+      <c r="P25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="188" t="str">
+      <c r="Q25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="311"/>
+      <c r="E26" s="309"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="311"/>
+      <c r="E27" s="309"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9580,7 +9576,7 @@
         <v>0.72134257435984139</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="309" t="s">
+      <c r="E28" s="307" t="s">
         <v>372</v>
       </c>
       <c r="F28" s="26"/>
@@ -9640,7 +9636,7 @@
         <v>0.13662908990130354</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="309" t="s">
+      <c r="E29" s="307" t="s">
         <v>372</v>
       </c>
       <c r="F29" s="26"/>
@@ -9698,7 +9694,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.85797166426114502</v>
       </c>
-      <c r="E30" s="311"/>
+      <c r="E30" s="309"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.86096272455849754</v>
@@ -9746,68 +9742,68 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="311"/>
+      <c r="E31" s="309"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="311"/>
+      <c r="E32" s="309"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="205">
+      <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
         <v>-302359.25</v>
       </c>
-      <c r="E33" s="309" t="s">
+      <c r="E33" s="307" t="s">
         <v>372</v>
       </c>
-      <c r="G33" s="198">
+      <c r="G33" s="197">
         <f>Data!C41</f>
         <v>-254107</v>
       </c>
-      <c r="H33" s="198">
+      <c r="H33" s="197">
         <f>Data!D41</f>
         <v>-349526</v>
       </c>
-      <c r="I33" s="198">
+      <c r="I33" s="197">
         <f>Data!E41</f>
         <v>-323818</v>
       </c>
-      <c r="J33" s="198">
+      <c r="J33" s="197">
         <f>Data!F41</f>
         <v>-281986</v>
       </c>
-      <c r="K33" s="198">
+      <c r="K33" s="197">
         <f>Data!G41</f>
         <v>-173152</v>
       </c>
-      <c r="L33" s="198" t="str">
+      <c r="L33" s="197" t="str">
         <f>Data!H41</f>
         <v/>
       </c>
-      <c r="M33" s="198" t="str">
+      <c r="M33" s="197" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N33" s="198" t="str">
+      <c r="N33" s="197" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O33" s="198" t="str">
+      <c r="O33" s="197" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P33" s="198" t="str">
+      <c r="P33" s="197" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="198" t="str">
+      <c r="Q33" s="197" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -9817,56 +9813,56 @@
       <c r="B34" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="205">
+      <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="309" t="s">
+      <c r="E34" s="307" t="s">
         <v>372</v>
       </c>
       <c r="F34" s="59"/>
-      <c r="G34" s="187">
+      <c r="G34" s="186">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="187">
+      <c r="H34" s="186">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="187">
+      <c r="I34" s="186">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="187">
+      <c r="J34" s="186">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="187">
+      <c r="K34" s="186">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="187" t="str">
+      <c r="L34" s="186" t="str">
         <f>Data!H42</f>
         <v/>
       </c>
-      <c r="M34" s="187" t="str">
+      <c r="M34" s="186" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N34" s="187" t="str">
+      <c r="N34" s="186" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O34" s="187" t="str">
+      <c r="O34" s="186" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P34" s="187" t="str">
+      <c r="P34" s="186" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="187" t="str">
+      <c r="Q34" s="186" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -9876,68 +9872,68 @@
       <c r="B35" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-302359.25</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="310"/>
+      <c r="E35" s="308"/>
       <c r="F35" s="59"/>
-      <c r="G35" s="188">
+      <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-254107</v>
       </c>
-      <c r="H35" s="188">
+      <c r="H35" s="187">
         <f t="shared" si="14"/>
         <v>-349526</v>
       </c>
-      <c r="I35" s="188">
+      <c r="I35" s="187">
         <f t="shared" si="14"/>
         <v>-323818</v>
       </c>
-      <c r="J35" s="188">
+      <c r="J35" s="187">
         <f t="shared" si="14"/>
         <v>-281986</v>
       </c>
-      <c r="K35" s="188">
+      <c r="K35" s="187">
         <f t="shared" si="14"/>
         <v>-173152</v>
       </c>
-      <c r="L35" s="188" t="str">
+      <c r="L35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M35" s="188" t="str">
+      <c r="M35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="N35" s="188" t="str">
+      <c r="N35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O35" s="188" t="str">
+      <c r="O35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P35" s="188" t="str">
+      <c r="P35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="188" t="str">
+      <c r="Q35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="311"/>
+      <c r="E36" s="309"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="311"/>
+      <c r="E37" s="309"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9950,7 +9946,7 @@
         <v>2.5247654924924864E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="308"/>
+      <c r="E38" s="306"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -10008,7 +10004,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="308"/>
+      <c r="E39" s="306"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -10064,7 +10060,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>2.5247654924924864E-2</v>
       </c>
-      <c r="E40" s="311"/>
+      <c r="E40" s="309"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>1.6580166386945237E-2</v>
@@ -10112,25 +10108,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="311"/>
+      <c r="E41" s="309"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="311"/>
+      <c r="E42" s="309"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="305">
+      <c r="C43" s="303">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="308" t="s">
+      <c r="E43" s="306" t="s">
         <v>373</v>
       </c>
       <c r="F43" s="27"/>
@@ -10210,59 +10206,59 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="311"/>
+      <c r="E46" s="309"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="198">
+      <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-59596</v>
       </c>
-      <c r="E47" s="311"/>
-      <c r="G47" s="198">
+      <c r="E47" s="309"/>
+      <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-59596</v>
       </c>
-      <c r="H47" s="198">
+      <c r="H47" s="197">
         <f>Data!D51</f>
         <v>-20763</v>
       </c>
-      <c r="I47" s="198">
+      <c r="I47" s="197">
         <f>Data!E51</f>
         <v>-23097</v>
       </c>
-      <c r="J47" s="198">
+      <c r="J47" s="197">
         <f>Data!F51</f>
         <v>-28849</v>
       </c>
-      <c r="K47" s="198">
+      <c r="K47" s="197">
         <f>Data!G51</f>
         <v>-63075</v>
       </c>
-      <c r="L47" s="198" t="str">
+      <c r="L47" s="197" t="str">
         <f>Data!H51</f>
         <v/>
       </c>
-      <c r="M47" s="198" t="str">
+      <c r="M47" s="197" t="str">
         <f>Data!I51</f>
         <v/>
       </c>
-      <c r="N47" s="198" t="str">
+      <c r="N47" s="197" t="str">
         <f>Data!J51</f>
         <v/>
       </c>
-      <c r="O47" s="198" t="str">
+      <c r="O47" s="197" t="str">
         <f>Data!K51</f>
         <v/>
       </c>
-      <c r="P47" s="198" t="str">
+      <c r="P47" s="197" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="198" t="str">
+      <c r="Q47" s="197" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -10272,109 +10268,109 @@
       <c r="B48" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C48" s="198">
+      <c r="C48" s="197">
         <f>BS!D75*C53</f>
         <v>12782.030934854472</v>
       </c>
-      <c r="E48" s="311"/>
-      <c r="G48" s="338">
+      <c r="E48" s="309"/>
+      <c r="G48" s="336">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>12782.030934854472</v>
       </c>
-      <c r="H48" s="338">
+      <c r="H48" s="336">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>14611.753277325271</v>
       </c>
-      <c r="I48" s="338">
+      <c r="I48" s="336">
         <f t="shared" si="19"/>
         <v>38528.271041651278</v>
       </c>
-      <c r="J48" s="338">
+      <c r="J48" s="336">
         <f t="shared" si="19"/>
         <v>27965.462166818645</v>
       </c>
-      <c r="K48" s="338">
+      <c r="K48" s="336">
         <f t="shared" si="19"/>
         <v>20048.428270322525</v>
       </c>
-      <c r="L48" s="338" t="str">
+      <c r="L48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="338" t="str">
+      <c r="M48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="338" t="str">
+      <c r="N48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="338" t="str">
+      <c r="O48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="338" t="str">
+      <c r="P48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="338" t="str">
+      <c r="Q48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="333" t="s">
+      <c r="B49" s="331" t="s">
         <v>381</v>
       </c>
-      <c r="C49" s="334">
+      <c r="C49" s="332">
         <f>BS!$C$66*C53</f>
         <v>28977</v>
       </c>
-      <c r="D49" s="335"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="335"/>
-      <c r="G49" s="334">
+      <c r="D49" s="333"/>
+      <c r="E49" s="334"/>
+      <c r="F49" s="333"/>
+      <c r="G49" s="332">
         <f>Data!C52</f>
         <v>28977</v>
       </c>
-      <c r="H49" s="334">
+      <c r="H49" s="332">
         <f>Data!D52</f>
         <v>33125</v>
       </c>
-      <c r="I49" s="334">
+      <c r="I49" s="332">
         <f>Data!E52</f>
         <v>87344</v>
       </c>
-      <c r="J49" s="334">
+      <c r="J49" s="332">
         <f>Data!F52</f>
         <v>63398</v>
       </c>
-      <c r="K49" s="334">
+      <c r="K49" s="332">
         <f>Data!G52</f>
         <v>45450</v>
       </c>
-      <c r="L49" s="334" t="str">
+      <c r="L49" s="332" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="334" t="str">
+      <c r="M49" s="332" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="334" t="str">
+      <c r="N49" s="332" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="334" t="str">
+      <c r="O49" s="332" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="334" t="str">
+      <c r="P49" s="332" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="334" t="str">
+      <c r="Q49" s="332" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10384,66 +10380,66 @@
       <c r="B50" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="188">
+      <c r="C50" s="187">
         <f>C47+C48</f>
         <v>-46813.969065145531</v>
       </c>
-      <c r="E50" s="311"/>
-      <c r="G50" s="188">
+      <c r="E50" s="309"/>
+      <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-46813.969065145531</v>
       </c>
-      <c r="H50" s="188">
+      <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-6151.2467226747285</v>
       </c>
-      <c r="I50" s="188">
+      <c r="I50" s="187">
         <f t="shared" si="20"/>
         <v>15431.271041651278</v>
       </c>
-      <c r="J50" s="188">
+      <c r="J50" s="187">
         <f t="shared" si="20"/>
         <v>-883.53783318135538</v>
       </c>
-      <c r="K50" s="188">
+      <c r="K50" s="187">
         <f t="shared" si="20"/>
         <v>-43026.571729677475</v>
       </c>
-      <c r="L50" s="188" t="str">
+      <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M50" s="188" t="str">
+      <c r="M50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="N50" s="188" t="str">
+      <c r="N50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O50" s="188" t="str">
+      <c r="O50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="P50" s="188" t="str">
+      <c r="P50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="188" t="str">
+      <c r="Q50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="311"/>
+      <c r="E51" s="309"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="311"/>
+      <c r="E52" s="309"/>
       <c r="G52" s="100" t="s">
         <v>224</v>
       </c>
@@ -10457,23 +10453,23 @@
         <f>G53</f>
         <v>1.4501413508729523E-2</v>
       </c>
-      <c r="E53" s="308" t="s">
+      <c r="E53" s="306" t="s">
         <v>374</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
         <v>1.4501413508729523E-2</v>
       </c>
-      <c r="H53" s="174"/>
-      <c r="I53" s="174"/>
-      <c r="J53" s="174"/>
-      <c r="K53" s="174"/>
-      <c r="L53" s="174"/>
-      <c r="M53" s="174"/>
-      <c r="N53" s="174"/>
-      <c r="O53" s="174"/>
-      <c r="P53" s="174"/>
-      <c r="Q53" s="174"/>
+      <c r="H53" s="173"/>
+      <c r="I53" s="173"/>
+      <c r="J53" s="173"/>
+      <c r="K53" s="173"/>
+      <c r="L53" s="173"/>
+      <c r="M53" s="173"/>
+      <c r="N53" s="173"/>
+      <c r="O53" s="173"/>
+      <c r="P53" s="173"/>
+      <c r="Q53" s="173"/>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
@@ -10484,23 +10480,23 @@
         <f>G54</f>
         <v>2.9286626219579916E-2</v>
       </c>
-      <c r="E54" s="308" t="s">
+      <c r="E54" s="306" t="s">
         <v>375</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
         <v>2.9286626219579916E-2</v>
       </c>
-      <c r="H54" s="174"/>
-      <c r="I54" s="174"/>
-      <c r="J54" s="174"/>
-      <c r="K54" s="174"/>
-      <c r="L54" s="174"/>
-      <c r="M54" s="174"/>
-      <c r="N54" s="174"/>
-      <c r="O54" s="174"/>
-      <c r="P54" s="174"/>
-      <c r="Q54" s="174"/>
+      <c r="H54" s="173"/>
+      <c r="I54" s="173"/>
+      <c r="J54" s="173"/>
+      <c r="K54" s="173"/>
+      <c r="L54" s="173"/>
+      <c r="M54" s="173"/>
+      <c r="N54" s="173"/>
+      <c r="O54" s="173"/>
+      <c r="P54" s="173"/>
+      <c r="Q54" s="173"/>
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
@@ -10511,7 +10507,7 @@
         <f>-C8/C47</f>
         <v>23.466920654538772</v>
       </c>
-      <c r="E55" s="311"/>
+      <c r="E55" s="309"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>31.4915933955299</v>
@@ -10559,14 +10555,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="311"/>
+      <c r="E56" s="309"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E57" s="311"/>
+      <c r="E57" s="309"/>
       <c r="G57" s="100" t="s">
         <v>224</v>
       </c>
@@ -10576,52 +10572,52 @@
       <c r="B58" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C58" s="198">
+      <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="311"/>
-      <c r="G58" s="198">
+      <c r="E58" s="309"/>
+      <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="198">
+      <c r="H58" s="197">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="198">
+      <c r="I58" s="197">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="198">
+      <c r="J58" s="197">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="198">
+      <c r="K58" s="197">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="198" t="str">
+      <c r="L58" s="197" t="str">
         <f>Data!H56</f>
         <v/>
       </c>
-      <c r="M58" s="198" t="str">
+      <c r="M58" s="197" t="str">
         <f>Data!I56</f>
         <v/>
       </c>
-      <c r="N58" s="198" t="str">
+      <c r="N58" s="197" t="str">
         <f>Data!J56</f>
         <v/>
       </c>
-      <c r="O58" s="198" t="str">
+      <c r="O58" s="197" t="str">
         <f>Data!K56</f>
         <v/>
       </c>
-      <c r="P58" s="198" t="str">
+      <c r="P58" s="197" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="198" t="str">
+      <c r="Q58" s="197" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -10631,52 +10627,52 @@
       <c r="B59" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="198">
+      <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="311"/>
-      <c r="G59" s="198">
+      <c r="E59" s="309"/>
+      <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
       </c>
-      <c r="H59" s="198">
+      <c r="H59" s="197">
         <f>Data!D55</f>
         <v>927</v>
       </c>
-      <c r="I59" s="198">
+      <c r="I59" s="197">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="198">
+      <c r="J59" s="197">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="198">
+      <c r="K59" s="197">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="198" t="str">
+      <c r="L59" s="197" t="str">
         <f>Data!H55</f>
         <v/>
       </c>
-      <c r="M59" s="198" t="str">
+      <c r="M59" s="197" t="str">
         <f>Data!I55</f>
         <v/>
       </c>
-      <c r="N59" s="198" t="str">
+      <c r="N59" s="197" t="str">
         <f>Data!J55</f>
         <v/>
       </c>
-      <c r="O59" s="198" t="str">
+      <c r="O59" s="197" t="str">
         <f>Data!K55</f>
         <v/>
       </c>
-      <c r="P59" s="198" t="str">
+      <c r="P59" s="197" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="198" t="str">
+      <c r="Q59" s="197" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -10686,52 +10682,52 @@
       <c r="B60" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="198">
+      <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="311"/>
-      <c r="G60" s="198">
+      <c r="E60" s="309"/>
+      <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="198">
+      <c r="H60" s="197">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="198">
+      <c r="I60" s="197">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="198">
+      <c r="J60" s="197">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="198">
+      <c r="K60" s="197">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="198" t="str">
+      <c r="L60" s="197" t="str">
         <f>Data!H57</f>
         <v/>
       </c>
-      <c r="M60" s="198" t="str">
+      <c r="M60" s="197" t="str">
         <f>Data!I57</f>
         <v/>
       </c>
-      <c r="N60" s="198" t="str">
+      <c r="N60" s="197" t="str">
         <f>Data!J57</f>
         <v/>
       </c>
-      <c r="O60" s="198" t="str">
+      <c r="O60" s="197" t="str">
         <f>Data!K57</f>
         <v/>
       </c>
-      <c r="P60" s="198" t="str">
+      <c r="P60" s="197" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="198" t="str">
+      <c r="Q60" s="197" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -10741,52 +10737,52 @@
       <c r="B61" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="188">
+      <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="311"/>
-      <c r="G61" s="188">
+      <c r="E61" s="309"/>
+      <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
-      <c r="H61" s="188">
+      <c r="H61" s="187">
         <f t="shared" si="22"/>
         <v>927</v>
       </c>
-      <c r="I61" s="188">
+      <c r="I61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="188">
+      <c r="J61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="188">
+      <c r="K61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="188" t="str">
+      <c r="L61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M61" s="188" t="str">
+      <c r="M61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="N61" s="188" t="str">
+      <c r="N61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="O61" s="188" t="str">
+      <c r="O61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="P61" s="188" t="str">
+      <c r="P61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="188" t="str">
+      <c r="Q61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -10796,53 +10792,53 @@
       <c r="B62" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C62" s="306">
-        <v>0</v>
-      </c>
-      <c r="E62" s="309" t="s">
+      <c r="C62" s="304">
+        <v>0</v>
+      </c>
+      <c r="E62" s="307" t="s">
         <v>376</v>
       </c>
-      <c r="G62" s="198">
+      <c r="G62" s="197">
         <f>Data!C58</f>
         <v>247678</v>
       </c>
-      <c r="H62" s="198">
+      <c r="H62" s="197">
         <f>Data!D58</f>
         <v>189250</v>
       </c>
-      <c r="I62" s="198">
+      <c r="I62" s="197">
         <f>Data!E58</f>
         <v>200697</v>
       </c>
-      <c r="J62" s="198">
+      <c r="J62" s="197">
         <f>Data!F58</f>
         <v>281254</v>
       </c>
-      <c r="K62" s="198">
+      <c r="K62" s="197">
         <f>Data!G58</f>
         <v>-97419</v>
       </c>
-      <c r="L62" s="198" t="str">
+      <c r="L62" s="197" t="str">
         <f>Data!H58</f>
         <v/>
       </c>
-      <c r="M62" s="198" t="str">
+      <c r="M62" s="197" t="str">
         <f>Data!I58</f>
         <v/>
       </c>
-      <c r="N62" s="198" t="str">
+      <c r="N62" s="197" t="str">
         <f>Data!J58</f>
         <v/>
       </c>
-      <c r="O62" s="198" t="str">
+      <c r="O62" s="197" t="str">
         <f>Data!K58</f>
         <v/>
       </c>
-      <c r="P62" s="198" t="str">
+      <c r="P62" s="197" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="198" t="str">
+      <c r="Q62" s="197" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -10852,66 +10848,66 @@
       <c r="B63" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="C63" s="188">
+      <c r="C63" s="187">
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="311"/>
-      <c r="G63" s="188">
+      <c r="E63" s="309"/>
+      <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>248317</v>
       </c>
-      <c r="H63" s="188">
+      <c r="H63" s="187">
         <f t="shared" si="23"/>
         <v>190177</v>
       </c>
-      <c r="I63" s="188">
+      <c r="I63" s="187">
         <f t="shared" si="23"/>
         <v>200697</v>
       </c>
-      <c r="J63" s="188">
+      <c r="J63" s="187">
         <f t="shared" si="23"/>
         <v>281254</v>
       </c>
-      <c r="K63" s="188">
+      <c r="K63" s="187">
         <f t="shared" si="23"/>
         <v>-97419</v>
       </c>
-      <c r="L63" s="188" t="str">
+      <c r="L63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M63" s="188" t="str">
+      <c r="M63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="N63" s="188" t="str">
+      <c r="N63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="O63" s="188" t="str">
+      <c r="O63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="P63" s="188" t="str">
+      <c r="P63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="188" t="str">
+      <c r="Q63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="311"/>
+      <c r="E64" s="309"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="311"/>
+      <c r="E65" s="309"/>
       <c r="G65" s="100" t="s">
         <v>224</v>
       </c>
@@ -10921,75 +10917,75 @@
       <c r="B66" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C66" s="181">
+      <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="311"/>
+      <c r="E66" s="309"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="180"/>
-      <c r="I66" s="180"/>
-      <c r="J66" s="180"/>
-      <c r="K66" s="180"/>
-      <c r="L66" s="180"/>
-      <c r="M66" s="180"/>
-      <c r="N66" s="180"/>
-      <c r="O66" s="180"/>
-      <c r="P66" s="180"/>
-      <c r="Q66" s="180"/>
+      <c r="H66" s="179"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="179"/>
+      <c r="K66" s="179"/>
+      <c r="L66" s="179"/>
+      <c r="M66" s="179"/>
+      <c r="N66" s="179"/>
+      <c r="O66" s="179"/>
+      <c r="P66" s="179"/>
+      <c r="Q66" s="179"/>
     </row>
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="181">
+      <c r="C67" s="180">
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="311"/>
+      <c r="E67" s="309"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
       </c>
-      <c r="H67" s="180"/>
-      <c r="I67" s="180"/>
-      <c r="J67" s="180"/>
-      <c r="K67" s="180"/>
-      <c r="L67" s="180"/>
-      <c r="M67" s="180"/>
-      <c r="N67" s="180"/>
-      <c r="O67" s="180"/>
-      <c r="P67" s="180"/>
-      <c r="Q67" s="180"/>
+      <c r="H67" s="179"/>
+      <c r="I67" s="179"/>
+      <c r="J67" s="179"/>
+      <c r="K67" s="179"/>
+      <c r="L67" s="179"/>
+      <c r="M67" s="179"/>
+      <c r="N67" s="179"/>
+      <c r="O67" s="179"/>
+      <c r="P67" s="179"/>
+      <c r="Q67" s="179"/>
     </row>
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="C68" s="181">
+      <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="311"/>
+      <c r="E68" s="309"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="180"/>
-      <c r="I68" s="180"/>
-      <c r="J68" s="180"/>
-      <c r="K68" s="180"/>
-      <c r="L68" s="180"/>
-      <c r="M68" s="180"/>
-      <c r="N68" s="180"/>
-      <c r="O68" s="180"/>
-      <c r="P68" s="180"/>
-      <c r="Q68" s="180"/>
+      <c r="H68" s="179"/>
+      <c r="I68" s="179"/>
+      <c r="J68" s="179"/>
+      <c r="K68" s="179"/>
+      <c r="L68" s="179"/>
+      <c r="M68" s="179"/>
+      <c r="N68" s="179"/>
+      <c r="O68" s="179"/>
+      <c r="P68" s="179"/>
+      <c r="Q68" s="179"/>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
@@ -11001,22 +10997,22 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="316"/>
+      <c r="E69" s="314"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
         <v>3.197847683362034E-4</v>
       </c>
-      <c r="H69" s="180"/>
-      <c r="I69" s="180"/>
-      <c r="J69" s="180"/>
-      <c r="K69" s="180"/>
-      <c r="L69" s="180"/>
-      <c r="M69" s="180"/>
-      <c r="N69" s="180"/>
-      <c r="O69" s="180"/>
-      <c r="P69" s="180"/>
-      <c r="Q69" s="180"/>
+      <c r="H69" s="179"/>
+      <c r="I69" s="179"/>
+      <c r="J69" s="179"/>
+      <c r="K69" s="179"/>
+      <c r="L69" s="179"/>
+      <c r="M69" s="179"/>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="10"/>
@@ -11051,7 +11047,7 @@
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="308"/>
+      <c r="E72" s="306"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -11075,7 +11071,7 @@
         <v>0.85797166426114502</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="308"/>
+      <c r="E73" s="306"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11132,7 +11128,7 @@
         <v>0.14202833573885504</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="308"/>
+      <c r="E74" s="306"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11189,7 +11185,7 @@
         <v>2.5247654924924864E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="308"/>
+      <c r="E75" s="306"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11246,7 +11242,7 @@
         <v>0.11678068081393016</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="308"/>
+      <c r="E76" s="306"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11303,7 +11299,7 @@
         <v>3.8696911822371505E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="308"/>
+      <c r="E77" s="306"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11360,7 +11356,7 @@
         <v>3.8696911822371505E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="309" t="s">
+      <c r="E78" s="307" t="s">
         <v>390</v>
       </c>
       <c r="F78" s="27"/>
@@ -11419,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="308"/>
+      <c r="E79" s="306"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11476,7 +11472,7 @@
         <v>3.9090682247124959E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="308"/>
+      <c r="E80" s="306"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11533,7 +11529,7 @@
         <v>0.11287161258921766</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="308"/>
+      <c r="E81" s="306"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -11590,7 +11586,7 @@
         <v>2.8217903147304414E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="308"/>
+      <c r="E82" s="306"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11643,12 +11639,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="307">
+      <c r="C83" s="305">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="308"/>
+      <c r="E83" s="306"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11705,7 +11701,7 @@
         <v>8.465370944191325E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="308"/>
+      <c r="E84" s="306"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11757,26 +11753,26 @@
       <c r="B85" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C85" s="307">
+      <c r="C85" s="305">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="310" t="str">
+      <c r="E85" s="308" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="260"/>
-      <c r="H85" s="260"/>
-      <c r="I85" s="260"/>
-      <c r="J85" s="260"/>
-      <c r="K85" s="260"/>
-      <c r="L85" s="260"/>
-      <c r="M85" s="260"/>
-      <c r="N85" s="260"/>
-      <c r="O85" s="260"/>
-      <c r="P85" s="260"/>
-      <c r="Q85" s="260"/>
+      <c r="G85" s="259"/>
+      <c r="H85" s="259"/>
+      <c r="I85" s="259"/>
+      <c r="J85" s="259"/>
+      <c r="K85" s="259"/>
+      <c r="L85" s="259"/>
+      <c r="M85" s="259"/>
+      <c r="N85" s="259"/>
+      <c r="O85" s="259"/>
+      <c r="P85" s="259"/>
+      <c r="Q85" s="259"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
@@ -11786,21 +11782,21 @@
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="310" t="str">
+      <c r="E86" s="308" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
-      <c r="G86" s="174"/>
-      <c r="H86" s="174"/>
-      <c r="I86" s="174"/>
-      <c r="J86" s="174"/>
-      <c r="K86" s="174"/>
-      <c r="L86" s="174"/>
-      <c r="M86" s="174"/>
-      <c r="N86" s="174"/>
-      <c r="O86" s="174"/>
-      <c r="P86" s="174"/>
-      <c r="Q86" s="174"/>
+      <c r="G86" s="173"/>
+      <c r="H86" s="173"/>
+      <c r="I86" s="173"/>
+      <c r="J86" s="173"/>
+      <c r="K86" s="173"/>
+      <c r="L86" s="173"/>
+      <c r="M86" s="173"/>
+      <c r="N86" s="173"/>
+      <c r="O86" s="173"/>
+      <c r="P86" s="173"/>
+      <c r="Q86" s="173"/>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
@@ -11812,7 +11808,7 @@
         <v>8.465370944191325E-2</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="308"/>
+      <c r="E87" s="306"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11861,14 +11857,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="311"/>
+      <c r="E88" s="309"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E89" s="311"/>
+      <c r="E89" s="309"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11880,7 +11876,7 @@
         <f>G90</f>
         <v>1.36</v>
       </c>
-      <c r="E90" s="311"/>
+      <c r="E90" s="309"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>1.36</v>
@@ -11936,7 +11932,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>798466.67599999998</v>
       </c>
-      <c r="E91" s="311"/>
+      <c r="E91" s="309"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>798466.67599999998</v>
@@ -11991,48 +11987,48 @@
         <f>C90/(C19*$C$3/Common_Shares)</f>
         <v>0.7876052252818726</v>
       </c>
-      <c r="E92" s="311"/>
-      <c r="G92" s="175">
+      <c r="E92" s="309"/>
+      <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
         <v>0.61874144738023407</v>
       </c>
-      <c r="H92" s="175">
+      <c r="H92" s="174">
         <f t="shared" si="38"/>
         <v>0.48143764660132177</v>
       </c>
-      <c r="I92" s="175">
+      <c r="I92" s="174">
         <f t="shared" si="38"/>
         <v>0.57506275745658275</v>
       </c>
-      <c r="J92" s="175">
+      <c r="J92" s="174">
         <f t="shared" si="38"/>
         <v>0.54321576512185232</v>
       </c>
-      <c r="K92" s="175">
+      <c r="K92" s="174">
         <f t="shared" si="38"/>
         <v>0.62658560787622086</v>
       </c>
-      <c r="L92" s="175" t="str">
+      <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="M92" s="175" t="str">
+      <c r="M92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="N92" s="175" t="str">
+      <c r="N92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="O92" s="175" t="str">
+      <c r="O92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="P92" s="175" t="str">
+      <c r="P92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="Q92" s="175" t="str">
+      <c r="Q92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
@@ -12046,7 +12042,7 @@
         <f>C90/Market_Price</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="E93" s="311"/>
+      <c r="E93" s="309"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>9.0909090909090912E-2</v>
@@ -12094,16 +12090,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="311"/>
+      <c r="E94" s="309"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
-      <c r="B95" s="162" t="s">
+      <c r="B95" s="161" t="s">
         <v>89</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="308"/>
+      <c r="E95" s="306"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12127,7 +12123,7 @@
         <v>-0.2185980886550547</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="308"/>
+      <c r="E96" s="306"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12184,7 +12180,7 @@
         <v>-0.16438466748487235</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="308"/>
+      <c r="E97" s="306"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -12262,7 +12258,7 @@
       <c r="B100" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E100" s="311"/>
+      <c r="E100" s="309"/>
       <c r="G100" s="100" t="s">
         <v>224</v>
       </c>
@@ -12272,54 +12268,54 @@
       <c r="B101" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C101" s="206">
+      <c r="C101" s="205">
         <f>BS!G32</f>
         <v>16854064</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="312"/>
+      <c r="E101" s="310"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="187">
+      <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>16854064</v>
       </c>
-      <c r="H101" s="187">
+      <c r="H101" s="186">
         <f t="shared" si="42"/>
         <v>14687373</v>
       </c>
-      <c r="I101" s="187">
+      <c r="I101" s="186">
         <f t="shared" si="42"/>
         <v>15987114</v>
       </c>
-      <c r="J101" s="187">
+      <c r="J101" s="186">
         <f t="shared" si="42"/>
         <v>14270996</v>
       </c>
-      <c r="K101" s="187">
+      <c r="K101" s="186">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="L101" s="187" t="str">
+      <c r="L101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M101" s="187" t="str">
+      <c r="M101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="N101" s="187" t="str">
+      <c r="N101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="187" t="str">
+      <c r="O101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="187" t="str">
+      <c r="P101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="187" t="str">
+      <c r="Q101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -12329,54 +12325,54 @@
       <c r="B102" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="C102" s="207">
+      <c r="C102" s="206">
         <f>BS!C4</f>
         <v>265773</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="313"/>
+      <c r="E102" s="311"/>
       <c r="F102" s="91"/>
-      <c r="G102" s="189">
+      <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
         <v>213823</v>
       </c>
-      <c r="H102" s="189">
+      <c r="H102" s="188">
         <f>IF(H$4="","",Data!E76)</f>
         <v>187711</v>
       </c>
-      <c r="I102" s="189">
+      <c r="I102" s="188">
         <f>IF(I$4="","",Data!F76)</f>
         <v>277338</v>
       </c>
-      <c r="J102" s="189">
+      <c r="J102" s="188">
         <f>IF(J$4="","",Data!G76)</f>
         <v>0</v>
       </c>
-      <c r="K102" s="189" t="str">
+      <c r="K102" s="188" t="str">
         <f>IF(K$4="","",Data!H76)</f>
         <v/>
       </c>
-      <c r="L102" s="189" t="str">
+      <c r="L102" s="188" t="str">
         <f>IF(L$4="","",Data!I76)</f>
         <v/>
       </c>
-      <c r="M102" s="189" t="str">
+      <c r="M102" s="188" t="str">
         <f>IF(M$4="","",Data!J76)</f>
         <v/>
       </c>
-      <c r="N102" s="189" t="str">
+      <c r="N102" s="188" t="str">
         <f>IF(N$4="","",Data!K76)</f>
         <v/>
       </c>
-      <c r="O102" s="189" t="str">
+      <c r="O102" s="188" t="str">
         <f>IF(O$4="","",Data!L76)</f>
         <v/>
       </c>
-      <c r="P102" s="189" t="str">
+      <c r="P102" s="188" t="str">
         <f>IF(P$4="","",Data!M76)</f>
         <v/>
       </c>
-      <c r="Q102" s="189" t="str">
+      <c r="Q102" s="188" t="str">
         <f>IF(Q$4="","",Data!N76)</f>
         <v/>
       </c>
@@ -12386,54 +12382,54 @@
       <c r="B103" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="C103" s="207">
+      <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>9672256</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="313"/>
+      <c r="E103" s="311"/>
       <c r="F103" s="91"/>
-      <c r="G103" s="189">
+      <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
         <v>8852611</v>
       </c>
-      <c r="H103" s="189">
+      <c r="H103" s="188">
         <f>IF(H$4="","",Data!E77)</f>
         <v>8769304</v>
       </c>
-      <c r="I103" s="189">
+      <c r="I103" s="188">
         <f>IF(I$4="","",Data!F77)</f>
         <v>7321614</v>
       </c>
-      <c r="J103" s="189">
+      <c r="J103" s="188">
         <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
-      <c r="K103" s="189" t="str">
+      <c r="K103" s="188" t="str">
         <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
-      <c r="L103" s="189" t="str">
+      <c r="L103" s="188" t="str">
         <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
-      <c r="M103" s="189" t="str">
+      <c r="M103" s="188" t="str">
         <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
-      <c r="N103" s="189" t="str">
+      <c r="N103" s="188" t="str">
         <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
-      <c r="O103" s="189" t="str">
+      <c r="O103" s="188" t="str">
         <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
-      <c r="P103" s="189" t="str">
+      <c r="P103" s="188" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q103" s="189" t="str">
+      <c r="Q103" s="188" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -12443,54 +12439,54 @@
       <c r="B104" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C104" s="206">
+      <c r="C104" s="205">
         <f>BS!G30</f>
         <v>3990166</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="312"/>
+      <c r="E104" s="310"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="187">
+      <c r="G104" s="186">
         <f>Data!C78</f>
         <v>3990166</v>
       </c>
-      <c r="H104" s="187">
+      <c r="H104" s="186">
         <f>Data!D78</f>
         <v>2466431</v>
       </c>
-      <c r="I104" s="187">
+      <c r="I104" s="186">
         <f>Data!E78</f>
         <v>3908586</v>
       </c>
-      <c r="J104" s="187">
+      <c r="J104" s="186">
         <f>Data!F78</f>
         <v>2946772</v>
       </c>
-      <c r="K104" s="187">
+      <c r="K104" s="186">
         <f>Data!G78</f>
         <v>0</v>
       </c>
-      <c r="L104" s="187" t="str">
+      <c r="L104" s="186" t="str">
         <f>Data!H78</f>
         <v/>
       </c>
-      <c r="M104" s="187" t="str">
+      <c r="M104" s="186" t="str">
         <f>Data!I78</f>
         <v/>
       </c>
-      <c r="N104" s="187" t="str">
+      <c r="N104" s="186" t="str">
         <f>Data!J78</f>
         <v/>
       </c>
-      <c r="O104" s="187" t="str">
+      <c r="O104" s="186" t="str">
         <f>Data!K78</f>
         <v/>
       </c>
-      <c r="P104" s="187" t="str">
+      <c r="P104" s="186" t="str">
         <f>Data!L78</f>
         <v/>
       </c>
-      <c r="Q104" s="187" t="str">
+      <c r="Q104" s="186" t="str">
         <f>Data!M78</f>
         <v/>
       </c>
@@ -12500,61 +12496,61 @@
       <c r="B105" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C105" s="206">
+      <c r="C105" s="205">
         <f>BS!G27</f>
         <v>12863898</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="312"/>
+      <c r="E105" s="310"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="187">
+      <c r="G105" s="186">
         <f>Data!C79</f>
         <v>12863898</v>
       </c>
-      <c r="H105" s="187">
+      <c r="H105" s="186">
         <f>Data!D79</f>
         <v>12220942</v>
       </c>
-      <c r="I105" s="187">
+      <c r="I105" s="186">
         <f>Data!E79</f>
         <v>12078528</v>
       </c>
-      <c r="J105" s="187">
+      <c r="J105" s="186">
         <f>Data!F79</f>
         <v>11324224</v>
       </c>
-      <c r="K105" s="187">
+      <c r="K105" s="186">
         <f>Data!G79</f>
         <v>0</v>
       </c>
-      <c r="L105" s="187" t="str">
+      <c r="L105" s="186" t="str">
         <f>Data!H79</f>
         <v/>
       </c>
-      <c r="M105" s="187" t="str">
+      <c r="M105" s="186" t="str">
         <f>Data!I79</f>
         <v/>
       </c>
-      <c r="N105" s="187" t="str">
+      <c r="N105" s="186" t="str">
         <f>Data!J79</f>
         <v/>
       </c>
-      <c r="O105" s="187" t="str">
+      <c r="O105" s="186" t="str">
         <f>Data!K79</f>
         <v/>
       </c>
-      <c r="P105" s="187" t="str">
+      <c r="P105" s="186" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q105" s="187" t="str">
+      <c r="Q105" s="186" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="311"/>
+      <c r="E106" s="309"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
@@ -12563,7 +12559,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="312"/>
+      <c r="E107" s="310"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
         <v>224</v>
@@ -12589,7 +12585,7 @@
         <v>2.2192623484686036E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="312"/>
+      <c r="E108" s="310"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12646,7 +12642,7 @@
         <v>0.80765441055146836</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="312"/>
+      <c r="E109" s="310"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12703,26 +12699,26 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="312"/>
+      <c r="E110" s="310"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
         <v>0</v>
       </c>
-      <c r="H110" s="232"/>
-      <c r="I110" s="232"/>
-      <c r="J110" s="232"/>
-      <c r="K110" s="232"/>
-      <c r="L110" s="232"/>
-      <c r="M110" s="232"/>
-      <c r="N110" s="232"/>
-      <c r="O110" s="232"/>
-      <c r="P110" s="232"/>
-      <c r="Q110" s="232"/>
+      <c r="H110" s="231"/>
+      <c r="I110" s="231"/>
+      <c r="J110" s="231"/>
+      <c r="K110" s="231"/>
+      <c r="L110" s="231"/>
+      <c r="M110" s="231"/>
+      <c r="N110" s="231"/>
+      <c r="O110" s="231"/>
+      <c r="P110" s="231"/>
+      <c r="Q110" s="231"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="311"/>
+      <c r="E111" s="309"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
@@ -12731,7 +12727,7 @@
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="314"/>
+      <c r="E112" s="312"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12787,7 +12783,7 @@
         <f>C81</f>
         <v>0.11287161258921766</v>
       </c>
-      <c r="E113" s="311"/>
+      <c r="E113" s="309"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
         <v>0.10554867817986593</v>
@@ -12841,7 +12837,7 @@
         <f>C4/C101</f>
         <v>0.71055479556740742</v>
       </c>
-      <c r="E114" s="311"/>
+      <c r="E114" s="309"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>0.90933332162498015</v>
@@ -12896,7 +12892,7 @@
         <v>1.3101832741522048</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="315"/>
+      <c r="E115" s="313"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12953,7 +12949,7 @@
         <v>0.10871779326358874</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="314"/>
+      <c r="E116" s="312"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -13044,12 +13040,12 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
-      <c r="B119" s="183" t="s">
+      <c r="B119" s="182" t="s">
         <v>175</v>
       </c>
-      <c r="C119" s="184"/>
+      <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="308"/>
+      <c r="E119" s="306"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -13069,54 +13065,54 @@
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="182">
+      <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
         <v>1.7267533992213873</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="308"/>
+      <c r="E120" s="306"/>
       <c r="F120" s="27"/>
-      <c r="G120" s="182">
+      <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>2.198010179790399</v>
       </c>
-      <c r="H120" s="182">
+      <c r="H120" s="181">
         <f t="shared" si="49"/>
         <v>2.2848233987628088</v>
       </c>
-      <c r="I120" s="182">
+      <c r="I120" s="181">
         <f t="shared" si="49"/>
         <v>1.9128347049722658</v>
       </c>
-      <c r="J120" s="182">
+      <c r="J120" s="181">
         <f t="shared" si="49"/>
         <v>1.8408891350487284</v>
       </c>
-      <c r="K120" s="182">
+      <c r="K120" s="181">
         <f t="shared" si="49"/>
         <v>1.5959511157452972</v>
       </c>
-      <c r="L120" s="182" t="str">
+      <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="182" t="str">
+      <c r="M120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="182" t="str">
+      <c r="N120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="182" t="str">
+      <c r="O120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="182" t="str">
+      <c r="P120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="182" t="str">
+      <c r="Q120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
@@ -13131,7 +13127,7 @@
         <v>0.11542469246132268</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="308"/>
+      <c r="E121" s="306"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
@@ -13938,10 +13934,10 @@
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="234" t="s">
+      <c r="B5" s="233" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="235">
+      <c r="C5" s="234">
         <f>Thesis!C70</f>
         <v>0.08</v>
       </c>
@@ -13952,7 +13948,7 @@
       <c r="B6" s="153" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="239">
+      <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>12672380.946213255</v>
       </c>
@@ -13960,17 +13956,17 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="346" t="s">
+      <c r="E6" s="344" t="s">
         <v>256</v>
       </c>
-      <c r="F6" s="346"/>
+      <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="233">
+      <c r="C7" s="232">
         <f>BS!G31</f>
         <v>2034922</v>
       </c>
@@ -13978,15 +13974,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346"/>
-      <c r="F7" s="346"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="208">
+      <c r="C8" s="207">
         <f>BS!D66</f>
         <v>1116785.5502773244</v>
       </c>
@@ -13994,15 +13990,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="234" t="s">
+      <c r="B9" s="233" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="235">
         <f>BS!H42</f>
         <v>92572.6</v>
       </c>
@@ -14010,15 +14006,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="239">
+      <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
         <v>11846817.096490579</v>
       </c>
@@ -14029,10 +14025,10 @@
       <c r="H10" s="124"/>
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="236" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="237">
         <f>Exchange_Rate</f>
         <v>1</v>
       </c>
@@ -14079,7 +14075,7 @@
       <c r="B16" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="166">
+      <c r="C16" s="165">
         <f>Scenarios!C65</f>
         <v>6.4006284479398504E-3</v>
       </c>
@@ -14089,7 +14085,7 @@
       <c r="B17" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="167">
+      <c r="C17" s="166">
         <f>Scenarios!C64</f>
         <v>10</v>
       </c>
@@ -15218,19 +15214,19 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B73" s="176" t="s">
+      <c r="B73" s="175" t="s">
         <v>122</v>
       </c>
-      <c r="C73" s="176" t="s">
+      <c r="C73" s="175" t="s">
         <v>137</v>
       </c>
-      <c r="D73" s="176" t="s">
+      <c r="D73" s="175" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="177" t="s">
+      <c r="E73" s="176" t="s">
         <v>118</v>
       </c>
-      <c r="F73" s="177" t="s">
+      <c r="F73" s="176" t="s">
         <v>124</v>
       </c>
     </row>
@@ -15348,27 +15344,27 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B79" s="160"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="160"/>
-      <c r="E79" s="160"/>
-      <c r="F79" s="161"/>
+      <c r="B79" s="159"/>
+      <c r="C79" s="159"/>
+      <c r="D79" s="159"/>
+      <c r="E79" s="159"/>
+      <c r="F79" s="160"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B80" s="160" t="s">
+      <c r="B80" s="159" t="s">
         <v>341</v>
       </c>
-      <c r="C80" s="160" t="s">
+      <c r="C80" s="159" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C81" s="160" t="s">
+      <c r="C81" s="159" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C82" s="160" t="s">
+      <c r="C82" s="159" t="s">
         <v>108</v>
       </c>
     </row>
@@ -15427,19 +15423,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="285" t="s">
+      <c r="H2" s="283" t="s">
         <v>323</v>
       </c>
-      <c r="I2" s="286"/>
+      <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="284">
-        <v>0</v>
-      </c>
-      <c r="I3" s="272">
+      <c r="H3" s="282">
+        <v>0</v>
+      </c>
+      <c r="I3" s="270">
         <f>-Market_Price</f>
         <v>-14.96</v>
       </c>
@@ -15452,29 +15448,29 @@
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="159" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="160"/>
-      <c r="H4" s="284">
+      <c r="F4" s="159"/>
+      <c r="H4" s="282">
         <v>1</v>
       </c>
-      <c r="I4" s="272">
+      <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>1.36</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="H5" s="284">
+      <c r="H5" s="282">
         <v>2</v>
       </c>
-      <c r="I5" s="272">
+      <c r="I5" s="270">
         <f t="shared" si="0"/>
         <v>1.36</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B6" s="164" t="s">
+      <c r="B6" s="163" t="s">
         <v>100</v>
       </c>
       <c r="C6" s="110">
@@ -15485,10 +15481,10 @@
         <v>298</v>
       </c>
       <c r="F6" s="103"/>
-      <c r="H6" s="284">
+      <c r="H6" s="282">
         <v>3</v>
       </c>
-      <c r="I6" s="272">
+      <c r="I6" s="270">
         <f t="shared" si="0"/>
         <v>21.966600281147866</v>
       </c>
@@ -15505,15 +15501,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="348" t="str">
+      <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="348"/>
-      <c r="H7" s="284">
+      <c r="F7" s="346"/>
+      <c r="H7" s="282">
         <v>4</v>
       </c>
-      <c r="I7" s="272" t="str">
+      <c r="I7" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15530,12 +15526,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
-      <c r="H8" s="284">
+      <c r="E8" s="346"/>
+      <c r="F8" s="346"/>
+      <c r="H8" s="282">
         <v>5</v>
       </c>
-      <c r="I8" s="272" t="str">
+      <c r="I8" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15544,7 +15540,7 @@
       <c r="B9" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="208">
+      <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
         <v>1013790.4756970603</v>
       </c>
@@ -15552,37 +15548,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
-      <c r="H9" s="284">
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="H9" s="282">
         <v>6</v>
       </c>
-      <c r="I9" s="272" t="str">
+      <c r="I9" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="348"/>
-      <c r="F10" s="348"/>
-      <c r="H10" s="284">
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
+      <c r="H10" s="282">
         <v>7</v>
       </c>
-      <c r="I10" s="272" t="str">
+      <c r="I10" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="348"/>
-      <c r="F11" s="348"/>
-      <c r="H11" s="284">
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
+      <c r="H11" s="282">
         <v>8</v>
       </c>
-      <c r="I11" s="272" t="str">
+      <c r="I11" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15591,17 +15587,17 @@
       <c r="B12" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="163">
+      <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.20035451325595277</v>
       </c>
-      <c r="D12" s="163"/>
-      <c r="E12" s="348"/>
-      <c r="F12" s="348"/>
-      <c r="H12" s="284">
+      <c r="D12" s="162"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
+      <c r="H12" s="282">
         <v>9</v>
       </c>
-      <c r="I12" s="272" t="str">
+      <c r="I12" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15610,16 +15606,16 @@
       <c r="B13" s="152" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="163">
+      <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="348"/>
-      <c r="F13" s="348"/>
-      <c r="H13" s="284">
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
+      <c r="H13" s="282">
         <v>10</v>
       </c>
-      <c r="I13" s="272" t="str">
+      <c r="I13" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15628,12 +15624,12 @@
       <c r="B14" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="163">
+      <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0882669786354038E-2</v>
       </c>
-      <c r="E14" s="348"/>
-      <c r="F14" s="348"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15648,7 +15644,7 @@
       <c r="B17" s="112" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="164" t="s">
+      <c r="E17" s="163" t="s">
         <v>366</v>
       </c>
     </row>
@@ -15659,27 +15655,27 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="348" t="s">
+      <c r="E18" s="346" t="s">
         <v>367</v>
       </c>
-      <c r="F18" s="349"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="349"/>
-      <c r="F19" s="349"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="163" t="s">
         <v>331</v>
       </c>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="165">
+      <c r="C21" s="164">
         <f>Market_Price</f>
         <v>14.96</v>
       </c>
@@ -15687,14 +15683,14 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="349"/>
-      <c r="F21" s="349"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="C22" s="165">
+      <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
         <v>20.178263834303323</v>
       </c>
@@ -15702,104 +15698,104 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="349"/>
-      <c r="F22" s="349"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B24" s="164" t="s">
+      <c r="B24" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="164"/>
+      <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="171">
+      <c r="C25" s="170">
         <f>C18</f>
         <v>5</v>
       </c>
-      <c r="D25" s="168"/>
-      <c r="E25" s="347"/>
-      <c r="F25" s="347"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="169">
+      <c r="C26" s="168">
         <v>0.02</v>
       </c>
-      <c r="D26" s="169"/>
-      <c r="E26" s="347"/>
-      <c r="F26" s="347"/>
+      <c r="D26" s="168"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="165">
+      <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
         <v>20.874690131176312</v>
       </c>
-      <c r="D27" s="165" t="str">
+      <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="347"/>
-      <c r="F27" s="347"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C28" s="170">
+      <c r="C28" s="169">
         <v>0.6</v>
       </c>
-      <c r="D28" s="170"/>
-      <c r="E28" s="347"/>
-      <c r="F28" s="347"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="163" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="164" t="s">
+      <c r="E30" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="164"/>
+      <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="171">
+      <c r="C31" s="170">
         <f>C18</f>
         <v>5</v>
       </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="347"/>
-      <c r="F31" s="347"/>
+      <c r="D31" s="167"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="169">
+      <c r="C32" s="168">
         <v>-0.05</v>
       </c>
-      <c r="D32" s="169"/>
-      <c r="E32" s="347"/>
-      <c r="F32" s="347"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="345"/>
+      <c r="F32" s="345"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="165">
+      <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
         <v>18.5226941356174</v>
       </c>
@@ -15807,57 +15803,57 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="347"/>
-      <c r="F33" s="347"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C34" s="170">
+      <c r="C34" s="169">
         <v>0.2</v>
       </c>
-      <c r="D34" s="170"/>
-      <c r="E34" s="347"/>
-      <c r="F34" s="347"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B36" s="164" t="s">
+      <c r="B36" s="163" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="164" t="s">
+      <c r="E36" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F36" s="164"/>
+      <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="171">
+      <c r="C37" s="170">
         <f>C18</f>
         <v>5</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="347"/>
-      <c r="F37" s="347"/>
+      <c r="D37" s="167"/>
+      <c r="E37" s="345"/>
+      <c r="F37" s="345"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="169">
+      <c r="C38" s="168">
         <v>0.05</v>
       </c>
-      <c r="D38" s="169"/>
-      <c r="E38" s="347"/>
-      <c r="F38" s="347"/>
+      <c r="D38" s="168"/>
+      <c r="E38" s="345"/>
+      <c r="F38" s="345"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="165">
+      <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
         <v>21.958722625911768</v>
       </c>
@@ -15865,26 +15861,26 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="347"/>
-      <c r="F39" s="347"/>
+      <c r="E39" s="345"/>
+      <c r="F39" s="345"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="172">
+      <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
-      <c r="D40" s="170"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="D40" s="169"/>
+      <c r="E40" s="345"/>
+      <c r="F40" s="345"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="159">
+      <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
         <v>20.62109743101162</v>
       </c>
@@ -15918,47 +15914,47 @@
       <c r="F46" s="103"/>
     </row>
     <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B47" s="164"/>
-      <c r="E47" s="164"/>
-      <c r="F47" s="164"/>
+      <c r="B47" s="163"/>
+      <c r="E47" s="163"/>
+      <c r="F47" s="163"/>
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B48" s="164" t="s">
+      <c r="B48" s="163" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="164" t="s">
+      <c r="E48" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="164"/>
+      <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="171">
+      <c r="C49" s="170">
         <f>C46</f>
         <v>10</v>
       </c>
-      <c r="D49" s="168"/>
-      <c r="E49" s="347"/>
-      <c r="F49" s="347"/>
+      <c r="D49" s="167"/>
+      <c r="E49" s="345"/>
+      <c r="F49" s="345"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="169">
+      <c r="C50" s="168">
         <v>-0.08</v>
       </c>
-      <c r="D50" s="169"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="D50" s="168"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="165">
+      <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
         <v>15.722879464715176</v>
       </c>
@@ -15966,57 +15962,57 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="347"/>
-      <c r="F51" s="347"/>
+      <c r="E51" s="345"/>
+      <c r="F51" s="345"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="170">
+      <c r="C52" s="169">
         <v>0.02</v>
       </c>
-      <c r="D52" s="170"/>
-      <c r="E52" s="347"/>
-      <c r="F52" s="347"/>
+      <c r="D52" s="169"/>
+      <c r="E52" s="345"/>
+      <c r="F52" s="345"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="164" t="s">
+      <c r="B54" s="163" t="s">
         <v>349</v>
       </c>
-      <c r="E54" s="164" t="s">
+      <c r="E54" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F54" s="164"/>
+      <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="171">
+      <c r="C55" s="170">
         <f>C46</f>
         <v>10</v>
       </c>
-      <c r="D55" s="168"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="D55" s="167"/>
+      <c r="E55" s="345"/>
+      <c r="F55" s="345"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C56" s="169">
+      <c r="C56" s="168">
         <v>0.06</v>
       </c>
-      <c r="D56" s="169"/>
-      <c r="E56" s="347"/>
-      <c r="F56" s="347"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="345"/>
+      <c r="F56" s="345"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="165">
+      <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
         <v>24.794457904120378</v>
       </c>
@@ -16024,25 +16020,25 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="347"/>
-      <c r="F57" s="347"/>
+      <c r="E57" s="345"/>
+      <c r="F57" s="345"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C58" s="170">
+      <c r="C58" s="169">
         <v>0.02</v>
       </c>
-      <c r="D58" s="170"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="D58" s="169"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="159">
+      <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
         <v>20.606600281147866</v>
       </c>
@@ -16053,7 +16049,7 @@
       <c r="E60" s="103" t="s">
         <v>324</v>
       </c>
-      <c r="F60" s="321">
+      <c r="F60" s="319">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
@@ -16071,7 +16067,7 @@
       <c r="B63" s="112" t="s">
         <v>332</v>
       </c>
-      <c r="E63" s="290" t="s">
+      <c r="E63" s="288" t="s">
         <v>342</v>
       </c>
     </row>
@@ -16079,11 +16075,11 @@
       <c r="B64" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C64" s="171">
+      <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="289" t="s">
+      <c r="E64" s="287" t="s">
         <v>343</v>
       </c>
     </row>
@@ -16095,7 +16091,7 @@
         <v>6.4006284479398504E-3</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="289" t="s">
+      <c r="E65" s="287" t="s">
         <v>344</v>
       </c>
     </row>
@@ -16103,15 +16099,15 @@
       <c r="B66" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="165">
+      <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
         <v>20.609976602556209</v>
       </c>
-      <c r="D66" s="165" t="str">
+      <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="289" t="s">
+      <c r="E66" s="287" t="s">
         <v>345</v>
       </c>
     </row>
@@ -16119,7 +16115,7 @@
       <c r="B68" s="112" t="s">
         <v>319</v>
       </c>
-      <c r="E68" s="290" t="s">
+      <c r="E68" s="288" t="s">
         <v>346</v>
       </c>
     </row>
@@ -16127,7 +16123,7 @@
       <c r="B69" s="103" t="s">
         <v>333</v>
       </c>
-      <c r="C69" s="281" t="str">
+      <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -16137,11 +16133,11 @@
       <c r="B70" s="103" t="s">
         <v>321</v>
       </c>
-      <c r="C70" s="281" t="str">
+      <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="289" t="s">
+      <c r="E70" s="287" t="s">
         <v>322</v>
       </c>
     </row>
@@ -16149,24 +16145,24 @@
       <c r="B71" s="103" t="s">
         <v>320</v>
       </c>
-      <c r="C71" s="281" t="str">
+      <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="289"/>
+      <c r="E71" s="287"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
         <v>311</v>
       </c>
-      <c r="C72" s="280" t="str">
+      <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
         <v>387</v>
       </c>
-      <c r="F72" s="339">
+      <c r="F72" s="337">
         <f>BS!D89/C60</f>
         <v>-6.8238022613097041E-2</v>
       </c>
@@ -16186,10 +16182,10 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B76" s="283" t="s">
+      <c r="B76" s="281" t="s">
         <v>325</v>
       </c>
-      <c r="C76" s="282">
+      <c r="C76" s="280">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -16199,7 +16195,7 @@
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="C77" s="178">
+      <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
         <v>1.36</v>
       </c>
@@ -16217,7 +16213,7 @@
       <c r="B80" s="152" t="s">
         <v>327</v>
       </c>
-      <c r="C80" s="172">
+      <c r="C80" s="171">
         <f>Thesis!C121</f>
         <v>0.2</v>
       </c>
@@ -16259,9 +16255,9 @@
       <c r="E83" s="150" t="s">
         <v>131</v>
       </c>
-      <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.28227215957658158</v>
+      <c r="F83" s="337">
+        <f>(1-C83/C60)</f>
+        <v>0.28227215957658158</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16276,7 +16272,7 @@
       <c r="B86" s="152" t="s">
         <v>328</v>
       </c>
-      <c r="C86" s="274">
+      <c r="C86" s="272">
         <f>Market_Price</f>
         <v>14.96</v>
       </c>
@@ -16289,7 +16285,7 @@
       <c r="B87" s="103" t="s">
         <v>326</v>
       </c>
-      <c r="C87" s="273">
+      <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.1950811274187132</v>
       </c>
@@ -16298,42 +16294,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="330" t="s">
+      <c r="E89" s="328" t="s">
         <v>361</v>
       </c>
-      <c r="F89" s="327"/>
+      <c r="F89" s="325"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="326"/>
+      <c r="H89" s="324"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="323" t="s">
+      <c r="E90" s="321" t="s">
         <v>362</v>
       </c>
-      <c r="F90" s="328" t="s">
+      <c r="F90" s="326" t="s">
         <v>363</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="326"/>
+      <c r="H90" s="324"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="324" t="s">
+      <c r="E91" s="322" t="s">
         <v>362</v>
       </c>
-      <c r="F91" s="328" t="s">
+      <c r="F91" s="326" t="s">
         <v>364</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="326"/>
+      <c r="H91" s="324"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="325" t="s">
+      <c r="E92" s="323" t="s">
         <v>362</v>
       </c>
-      <c r="F92" s="329" t="s">
+      <c r="F92" s="327" t="s">
         <v>365</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="326"/>
+      <c r="H92" s="324"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87898A2C-E248-4137-9D38-84757BAB4D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F083966D-F194-45B4-9DDF-9ACEEBDC5E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3373,20 +3373,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3800,13 +3800,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="338" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C20" s="258">
         <f>C127</f>
-        <v>14.789930718256866</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>338</v>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1950811274187132</v>
+        <v>0.19343775079136272</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3908,22 +3908,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="338" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
+      <c r="B26" s="342" t="s">
         <v>378</v>
       </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3935,13 +3935,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3961,13 +3961,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="340" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3996,13 +3996,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4018,13 +4018,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="C40" s="330">
         <f>Normalized_FCF!C48</f>
-        <v>12782.030934854472</v>
+        <v>13746.938888322537</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>-46813.969065145531</v>
+        <v>-45849.061111677467</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4088,13 +4088,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="340" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-337930.15856568678</v>
+        <v>-338171.38555405382</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4110,13 +4110,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
+      <c r="B50" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4132,22 +4132,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="338" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>1290469.0309348544</v>
+        <v>1291433.9388883226</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>1013790.4756970603</v>
+        <v>1014514.1566621615</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>0.11542469246132268</v>
+        <v>0.11550708685625866</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4208,22 +4208,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="340" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="342" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4275,22 +4275,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
+      <c r="B72" s="338" t="s">
         <v>383</v>
       </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="338" t="s">
         <v>384</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>21.584417490267342</v>
+        <v>21.599825242120371</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4327,13 +4327,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="338" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4346,13 +4346,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
+      <c r="B84" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
-        <v>1116785.5502773244</v>
+        <v>1050246.6606106577</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.9021812606956703</v>
+        <v>1.7888479273623368</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4456,13 +4456,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4488,13 +4488,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
+      <c r="B103" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>24.79 HKD</v>
+        <v>24.7 HKD</v>
       </c>
       <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>21.96 HKD</v>
+        <v>21.86 HKD</v>
       </c>
       <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>20.87 HKD</v>
+        <v>20.78 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>18.52 HKD</v>
+        <v>18.42 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>15.72 HKD</v>
+        <v>15.62 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>20.606600281147866</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="D112" s="242" t="str">
         <f>Market_currency</f>
@@ -4656,13 +4656,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="339" t="s">
         <v>275</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>11.925115903442052</v>
+        <v>11.868622952542175</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>14.789930718256866</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4744,11 +4744,17 @@
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>0.28227215957658158</v>
+        <v>0.28161042453275964</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4764,12 +4770,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>1116785.5502773244</v>
+        <v>1050246.6606106577</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>231</v>
@@ -8160,12 +8160,12 @@
         <v>352</v>
       </c>
       <c r="C73" s="191">
-        <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
-        <v>-1120765.75</v>
+        <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
+        <v>-1187304.6396666665</v>
       </c>
       <c r="D73" s="191">
-        <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
-        <v>-881433.44972267561</v>
+        <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
+        <v>-947972.33938934223</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8174,11 +8174,11 @@
       </c>
       <c r="C74" s="296">
         <f>-$C$66/C73</f>
-        <v>1.7829051253573729</v>
+        <v>1.6829876118070222</v>
       </c>
       <c r="D74" s="296">
         <f>-$C$66/D73</f>
-        <v>2.2670106298197523</v>
+        <v>2.1078874530107048</v>
       </c>
       <c r="F74" s="289" t="s">
         <v>354</v>
@@ -8191,7 +8191,7 @@
       <c r="C75" s="300"/>
       <c r="D75" s="299">
         <f>MAX(-D73*D76,G5)</f>
-        <v>881433.44972267561</v>
+        <v>947972.33938934223</v>
       </c>
       <c r="F75" s="289" t="s">
         <v>357</v>
@@ -8323,11 +8323,11 @@
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>1116785.5502773244</v>
+        <v>1050246.6606106577</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>1.9021812606956703</v>
+        <v>1.7888479273623368</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8357,11 +8357,11 @@
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>-825563.84972267563</v>
+        <v>-892102.73938934237</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>-1.40615365596402</v>
+        <v>-1.5194869892973535</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8941,28 +8941,28 @@
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>-46813.969065145531</v>
+        <v>-45849.061111677467</v>
       </c>
       <c r="E12" s="309"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>-46813.969065145531</v>
+        <v>-45849.061111677467</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-6151.2467226747285</v>
+        <v>-5048.2141120307824</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
-        <v>15431.271041651278</v>
+        <v>18339.747429397234</v>
       </c>
       <c r="J12" s="197">
         <f t="shared" si="6"/>
-        <v>-883.53783318135538</v>
+        <v>1227.5583615236937</v>
       </c>
       <c r="K12" s="197">
         <f t="shared" si="6"/>
-        <v>-43026.571729677475</v>
+        <v>-41513.127740129785</v>
       </c>
       <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
@@ -8996,28 +8996,28 @@
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>1351720.6342627471</v>
+        <v>1352685.5422162153</v>
       </c>
       <c r="E13" s="309"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>1617635.0309348544</v>
+        <v>1618599.9388883226</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>1622101.7532773253</v>
+        <v>1623204.7858879692</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
-        <v>1414336.2710416513</v>
+        <v>1417244.7474293972</v>
       </c>
       <c r="J13" s="187">
         <f t="shared" si="7"/>
-        <v>1318902.4621668186</v>
+        <v>1321013.5583615238</v>
       </c>
       <c r="K13" s="187">
         <f t="shared" si="7"/>
-        <v>1161741.4282703225</v>
+        <v>1163254.8722598702</v>
       </c>
       <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-337930.15856568678</v>
+        <v>-338171.38555405382</v>
       </c>
       <c r="E14" s="309"/>
       <c r="G14" s="197">
@@ -9163,30 +9163,30 @@
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>1013790.4756970603</v>
+        <v>1014514.1566621615</v>
       </c>
       <c r="D16" s="62"/>
       <c r="E16" s="317"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>1290469.0309348544</v>
+        <v>1291433.9388883226</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1341437.7532773253</v>
+        <v>1342540.7858879692</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
-        <v>1123040.2710416513</v>
+        <v>1125948.7474293972</v>
       </c>
       <c r="J16" s="187">
         <f t="shared" si="8"/>
-        <v>1080800.4621668186</v>
+        <v>1082911.5583615238</v>
       </c>
       <c r="K16" s="187">
         <f t="shared" si="8"/>
-        <v>936995.4282703225</v>
+        <v>938508.87225987017</v>
       </c>
       <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
@@ -9271,30 +9271,30 @@
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>1013790.4756970603</v>
+        <v>1014514.1566621615</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="306"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>1290469.0309348544</v>
+        <v>1291433.9388883226</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1341437.7532773253</v>
+        <v>1342540.7858879692</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
-        <v>1123040.2710416513</v>
+        <v>1125948.7474293972</v>
       </c>
       <c r="J19" s="189">
         <f t="shared" si="9"/>
-        <v>1080800.4621668186</v>
+        <v>1082911.5583615238</v>
       </c>
       <c r="K19" s="189">
         <f t="shared" si="9"/>
-        <v>936995.4282703225</v>
+        <v>938508.87225987017</v>
       </c>
       <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
@@ -10132,23 +10132,23 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.17872083028130542</v>
+        <v>0.17862667618650072</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20672662114033497</v>
+        <v>0.20655880189873316</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.20311442616937492</v>
+        <v>0.20270334015995536</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.25220409972307367</v>
+        <v>0.25163712246423864</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19230527083175997</v>
+        <v>0.1920550735076488</v>
       </c>
       <c r="L43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -10270,28 +10270,28 @@
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>12782.030934854472</v>
+        <v>13746.938888322537</v>
       </c>
       <c r="E48" s="309"/>
       <c r="G48" s="336">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>12782.030934854472</v>
+        <v>13746.938888322537</v>
       </c>
       <c r="H48" s="336">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>14611.753277325271</v>
+        <v>15714.785887969218</v>
       </c>
       <c r="I48" s="336">
         <f t="shared" si="19"/>
-        <v>38528.271041651278</v>
+        <v>41436.747429397234</v>
       </c>
       <c r="J48" s="336">
         <f t="shared" si="19"/>
-        <v>27965.462166818645</v>
+        <v>30076.558361523694</v>
       </c>
       <c r="K48" s="336">
         <f t="shared" si="19"/>
-        <v>20048.428270322525</v>
+        <v>21561.872259870215</v>
       </c>
       <c r="L48" s="336" t="str">
         <f t="shared" si="19"/>
@@ -10382,28 +10382,28 @@
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>-46813.969065145531</v>
+        <v>-45849.061111677467</v>
       </c>
       <c r="E50" s="309"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-46813.969065145531</v>
+        <v>-45849.061111677467</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-6151.2467226747285</v>
+        <v>-5048.2141120307824</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
-        <v>15431.271041651278</v>
+        <v>18339.747429397234</v>
       </c>
       <c r="J50" s="187">
         <f t="shared" si="20"/>
-        <v>-883.53783318135538</v>
+        <v>1227.5583615236937</v>
       </c>
       <c r="K50" s="187">
         <f t="shared" si="20"/>
-        <v>-43026.571729677475</v>
+        <v>-41513.127740129785</v>
       </c>
       <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
@@ -11469,30 +11469,30 @@
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>3.9090682247124959E-3</v>
+        <v>3.8284963121830232E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="306"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>3.0545533823681365E-3</v>
+        <v>2.9915943359168883E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>5.1355208188341142E-4</v>
+        <v>4.2146266991211292E-4</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>1.3146643406480138E-3</v>
+        <v>1.5624514595616603E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>9.970707948422618E-5</v>
+        <v>1.3852973186587503E-4</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>3.8301093844335509E-3</v>
+        <v>3.6953866818301515E-3</v>
       </c>
       <c r="L80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -11526,30 +11526,30 @@
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.11287161258921766</v>
+        <v>0.11295218450174714</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="306"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.10554867817986593</v>
+        <v>0.10561163722631718</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>0.13542518614179022</v>
+        <v>0.13551727555376153</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
-        <v>0.12049412237040026</v>
+        <v>0.1207419094893139</v>
       </c>
       <c r="J81" s="66">
         <f t="shared" si="32"/>
-        <v>0.14883789656601612</v>
+        <v>0.14907613337736625</v>
       </c>
       <c r="K81" s="66">
         <f t="shared" si="32"/>
-        <v>0.10341508904448225</v>
+        <v>0.10354981174708565</v>
       </c>
       <c r="L81" s="66" t="str">
         <f t="shared" si="32"/>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>2.8217903147304414E-2</v>
+        <v>2.8238046125436785E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="306"/>
@@ -11698,30 +11698,30 @@
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>8.465370944191325E-2</v>
+        <v>8.4714138376310352E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="306"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.4201502713816878E-2</v>
+        <v>8.4264461760268139E-2</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>0.11199325632203302</v>
+        <v>0.11208534573400432</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
-        <v>9.5677212425668692E-2</v>
+        <v>9.5924999544582334E-2</v>
       </c>
       <c r="J84" s="66">
         <f t="shared" si="35"/>
-        <v>0.12196813032876182</v>
+        <v>0.12220636714011193</v>
       </c>
       <c r="K84" s="66">
         <f t="shared" si="35"/>
-        <v>8.3408806203217292E-2</v>
+        <v>8.3543528905820688E-2</v>
       </c>
       <c r="L84" s="66" t="str">
         <f t="shared" si="35"/>
@@ -11805,30 +11805,30 @@
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>8.465370944191325E-2</v>
+        <v>8.4714138376310352E-2</v>
       </c>
       <c r="D87" s="77"/>
       <c r="E87" s="306"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.4201502713816878E-2</v>
+        <v>8.4264461760268139E-2</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>0.11199325632203302</v>
+        <v>0.11208534573400432</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
-        <v>9.5677212425668692E-2</v>
+        <v>9.5924999544582334E-2</v>
       </c>
       <c r="J87" s="66">
         <f t="shared" si="36"/>
-        <v>0.12196813032876182</v>
+        <v>0.12220636714011193</v>
       </c>
       <c r="K87" s="66">
         <f t="shared" si="36"/>
-        <v>8.3408806203217292E-2</v>
+        <v>8.3543528905820688E-2</v>
       </c>
       <c r="L87" s="66" t="str">
         <f t="shared" si="36"/>
@@ -11985,28 +11985,28 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.7876052252818726</v>
+        <v>0.7870434047239161</v>
       </c>
       <c r="E92" s="309"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.61874144738023407</v>
+        <v>0.61827914843815168</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>0.48143764660132177</v>
+        <v>0.48104209703606843</v>
       </c>
       <c r="I92" s="174">
         <f t="shared" si="38"/>
-        <v>0.57506275745658275</v>
+        <v>0.57357729334877761</v>
       </c>
       <c r="J92" s="174">
         <f t="shared" si="38"/>
-        <v>0.54321576512185232</v>
+        <v>0.54215678599673545</v>
       </c>
       <c r="K92" s="174">
         <f t="shared" si="38"/>
-        <v>0.62658560787622086</v>
+        <v>0.62557517286574116</v>
       </c>
       <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
@@ -12177,26 +12177,26 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>-0.16438466748487235</v>
+        <v>-0.16428667163718114</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="306"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-2.7536634699063534E-3</v>
+        <v>-2.8368860415400876E-3</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.14689963517845439</v>
+        <v>0.14532425597776455</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>7.2358503841174926E-2</v>
+        <v>7.2846480990876872E-2</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.13528056250045917</v>
+        <v>0.13561833254579359</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12781,28 +12781,28 @@
       </c>
       <c r="C113" s="23">
         <f>C81</f>
-        <v>0.11287161258921766</v>
+        <v>0.11295218450174714</v>
       </c>
       <c r="E113" s="309"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>0.10554867817986593</v>
+        <v>0.10561163722631718</v>
       </c>
       <c r="H113" s="23">
         <f t="shared" si="45"/>
-        <v>0.13542518614179022</v>
+        <v>0.13551727555376153</v>
       </c>
       <c r="I113" s="23">
         <f t="shared" si="45"/>
-        <v>0.12049412237040026</v>
+        <v>0.1207419094893139</v>
       </c>
       <c r="J113" s="23">
         <f t="shared" si="45"/>
-        <v>0.14883789656601612</v>
+        <v>0.14907613337736625</v>
       </c>
       <c r="K113" s="23">
         <f t="shared" si="45"/>
-        <v>0.10341508904448225</v>
+        <v>0.10354981174708565</v>
       </c>
       <c r="L113" s="23" t="str">
         <f t="shared" si="45"/>
@@ -13067,30 +13067,30 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.7267533992213873</v>
+        <v>1.7279860193696295</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="306"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>2.198010179790399</v>
+        <v>2.1996536733213881</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>2.2848233987628088</v>
+        <v>2.2867021551286859</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>1.9128347049722658</v>
+        <v>1.9177886097578105</v>
       </c>
       <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>1.8408891350487284</v>
+        <v>1.8444848904022044</v>
       </c>
       <c r="K120" s="181">
         <f t="shared" si="49"/>
-        <v>1.5959511157452972</v>
+        <v>1.5985289112722136</v>
       </c>
       <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
@@ -13124,30 +13124,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11542469246132268</v>
+        <v>0.11550708685625866</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="306"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.14692581415711223</v>
+        <v>0.14703567335036016</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.15272883681569577</v>
+        <v>0.15285442213427045</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12786328241793221</v>
+        <v>0.12819442578594989</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.12305408656742836</v>
+        <v>0.12329444454560189</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>0.10668122431452522</v>
+        <v>0.1068535368497469</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>1013790.4756970603</v>
+        <v>1014514.1566621615</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>12672380.946213255</v>
+        <v>12681426.958277019</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>1116785.5502773244</v>
+        <v>1050246.6606106577</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14016,7 +14016,7 @@
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>11846817.096490579</v>
+        <v>11789324.218887676</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14097,7 +14097,7 @@
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>20.609976602556209</v>
+        <v>20.512359193543752</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>1020279.3718560574</v>
+        <v>1021007.684834131</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14144,7 +14144,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>944703.12208894198</v>
+        <v>945377.48595752858</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>1026809.8010284055</v>
+        <v>1027542.7756672456</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14166,7 +14166,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>880323.9034880019</v>
+        <v>880952.31110017619</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>1033382.0290514914</v>
+        <v>1034119.6951886564</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>820331.97195191542</v>
+        <v>820917.55511470581</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>1039996.3234642282</v>
+        <v>1040738.7111282558</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>764428.34454476426</v>
+        <v>764974.02164017234</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>1046652.9535179462</v>
+        <v>1047400.0929295756</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>712334.41329006397</v>
+        <v>712842.90381946054</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14242,7 +14242,7 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>1053352.1901873536</v>
+        <v>1054104.1117607555</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>663790.5566668656</v>
+        <v>664264.39480422158</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>1060094.3061815663</v>
+        <v>1060851.0405255819</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>618554.84572901973</v>
+        <v>618996.39295051782</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>1066879.5759552112</v>
+        <v>1067641.1538745963</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>576401.83839926287</v>
+        <v>576813.29525223037</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>1073708.2757195961</v>
+        <v>1074474.7282162774</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>537121.45592922776</v>
+        <v>537504.87299904798</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>1080580.6834539555</v>
+        <v>1081352.041728291</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>500517.93592596968</v>
+        <v>500875.22405562212</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>12753492.148200717</v>
+        <v>12762596.060426638</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14804,7 +14804,7 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>5907334.5133857224</v>
+        <v>5911551.3862448642</v>
       </c>
       <c r="H51" s="124"/>
     </row>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>12925842.901399756</v>
+        <v>12935069.843938548</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14836,7 +14836,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>12925842.901399756</v>
+        <v>12935069.843938548</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -14866,19 +14866,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>11149148.446464211</v>
+        <v>11157107.119090568</v>
       </c>
       <c r="C56" s="127">
-        <v>11700382.979892615</v>
+        <v>11708735.144023098</v>
       </c>
       <c r="D56" s="127">
-        <v>13081258.292053817</v>
+        <v>13090596.175820205</v>
       </c>
       <c r="E56" s="127">
-        <v>13717702.279368088</v>
+        <v>13727494.48028384</v>
       </c>
       <c r="F56" s="127">
-        <v>13936287.458769159</v>
+        <v>13946235.693833362</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14887,19 +14887,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>10056589.808060752</v>
+        <v>10063768.572107553</v>
       </c>
       <c r="C57" s="127">
-        <v>10930146.519100875</v>
+        <v>10937948.860088741</v>
       </c>
       <c r="D57" s="127">
-        <v>13490512.149317097</v>
+        <v>13500142.173553824</v>
       </c>
       <c r="E57" s="127">
-        <v>14874481.968772687</v>
+        <v>14885099.921618555</v>
       </c>
       <c r="F57" s="127">
-        <v>15382584.721726298</v>
+        <v>15393565.377023447</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14908,19 +14908,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>8978458.4789169263</v>
+        <v>8984867.6331286728</v>
       </c>
       <c r="C58" s="127">
-        <v>10121591.313329941</v>
+        <v>10128816.477844289</v>
       </c>
       <c r="D58" s="127">
-        <v>13997077.273141662</v>
+        <v>14007068.902213397</v>
       </c>
       <c r="E58" s="127">
-        <v>16423179.778424198</v>
+        <v>16434903.248783203</v>
       </c>
       <c r="F58" s="127">
-        <v>17372022.406725001</v>
+        <v>17384423.195884526</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14929,19 +14929,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>8094632.8086438356</v>
+        <v>8100411.0555533562</v>
       </c>
       <c r="C59" s="127">
-        <v>9421559.6952345669</v>
+        <v>9428285.1514076646</v>
       </c>
       <c r="D59" s="127">
-        <v>14513185.897714347</v>
+        <v>14523545.944123272</v>
       </c>
       <c r="E59" s="127">
-        <v>18138572.828151789</v>
+        <v>18151520.809223328</v>
       </c>
       <c r="F59" s="127">
-        <v>19641430.04819227</v>
+        <v>19655450.824076422</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14950,19 +14950,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>7425801.6126279347</v>
+        <v>7431102.4232061561</v>
       </c>
       <c r="C60" s="127">
-        <v>8866272.1817560568</v>
+        <v>8872601.2532586548</v>
       </c>
       <c r="D60" s="127">
-        <v>14993195.557439478</v>
+        <v>15003898.252415478</v>
       </c>
       <c r="E60" s="127">
-        <v>19880521.577756252</v>
+        <v>19894713.025976568</v>
       </c>
       <c r="F60" s="127">
-        <v>22019700.25534239</v>
+        <v>22035418.728058424</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14971,19 +14971,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>6940411.8512575254</v>
+        <v>6945366.1727540484</v>
       </c>
       <c r="C61" s="127">
-        <v>8446824.5769606195</v>
+        <v>8452854.2313205972</v>
       </c>
       <c r="D61" s="127">
-        <v>15416630.850586919</v>
+        <v>15427635.809264299</v>
       </c>
       <c r="E61" s="127">
-        <v>21565065.947546452</v>
+        <v>21580459.885555841</v>
       </c>
       <c r="F61" s="127">
-        <v>24397668.230901666</v>
+        <v>24415084.184705544</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -15033,23 +15033,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -15060,23 +15060,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.583795884762118</v>
+        <v>17.484018276541907</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>18.5226941356174</v>
+        <v>18.42358674753498</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>20.874690131176312</v>
+        <v>20.777261684426229</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>21.958722625911768</v>
+        <v>21.862068001465992</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>22.331031017634125</v>
+        <v>22.234642160625206</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15087,23 +15087,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>15.722879464715176</v>
+        <v>15.621773465843134</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>17.210777661000783</v>
+        <v>17.110733778639474</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>21.571757726616021</v>
+        <v>21.474826872378696</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>23.929024486812793</v>
+        <v>23.833776336373653</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>24.794457904120378</v>
+        <v>24.69982753191616</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15114,23 +15114,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>13.886536569378608</v>
+        <v>13.784119721341368</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>15.833594225672956</v>
+        <v>15.732567259073345</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>22.434572154705453</v>
+        <v>22.338257209172138</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>26.566866596489081</v>
+        <v>26.473501434862197</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>28.182996628306579</v>
+        <v>28.090785119795594</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15141,23 +15141,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>12.381147618655005</v>
+        <v>12.277656168562579</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>14.641255172302484</v>
+        <v>14.539377070189611</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>23.313641689498226</v>
+        <v>23.217954256162525</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>29.488634802667203</v>
+        <v>29.397355306753241</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>32.048398260165648</v>
+        <v>31.958946017647488</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15168,23 +15168,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>11.241951138798873</v>
+        <v>11.13764648831865</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>13.69545362412269</v>
+        <v>13.592900374044243</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>24.131225136432434</v>
+        <v>24.036121324261181</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>32.4556343915919</v>
+        <v>32.366472849217097</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>36.09922164321209</v>
+        <v>36.012661027559218</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15194,23 +15194,23 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>10.415203955346277</v>
+        <v>10.310309142289114</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>12.981023379670265</v>
+        <v>12.877960142980976</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>24.852447469173242</v>
+        <v>24.757858492055515</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>35.324859134184244</v>
+        <v>35.237745750063638</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>40.149530245897736</v>
+        <v>40.06586088964098</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>24.794457904120378</v>
+        <v>24.69982753191616</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>21.958722625911768</v>
+        <v>21.862068001465992</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>20.874690131176312</v>
+        <v>20.777261684426229</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>18.5226941356174</v>
+        <v>18.42358674753498</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>15.722879464715176</v>
+        <v>15.621773465843134</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>21.966600281147866</v>
+        <v>21.868980461992876</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>1290469.0309348544</v>
+        <v>1291433.9388883226</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>1013790.4756970603</v>
+        <v>1014514.1566621615</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>6.0882669786354038E-2</v>
+        <v>6.0457013634429568E-2</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>20.178263834303323</v>
+        <v>20.080338252823015</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15739,7 +15739,7 @@
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>20.874690131176312</v>
+        <v>20.777261684426229</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>18.5226941356174</v>
+        <v>18.42358674753498</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>21.958722625911768</v>
+        <v>21.862068001465992</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>20.62109743101162</v>
+        <v>20.523487960455931</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>15.722879464715176</v>
+        <v>15.621773465843134</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16014,7 +16014,7 @@
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>24.794457904120378</v>
+        <v>24.69982753191616</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>20.606600281147866</v>
+        <v>20.508980461992877</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>20.609976602556209</v>
+        <v>20.512359193543752</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="F72" s="337">
         <f>BS!D89/C60</f>
-        <v>-6.8238022613097041E-2</v>
+        <v>-7.4088860346483723E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>11.925115903442052</v>
+        <v>11.868622952542175</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>14.789930718256866</v>
+        <v>14.733437767356989</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16257,7 +16257,7 @@
       </c>
       <c r="F83" s="337">
         <f>(1-C83/C60)</f>
-        <v>0.28227215957658158</v>
+        <v>0.28161042453275964</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1950811274187132</v>
+        <v>0.19343775079136272</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F083966D-F194-45B4-9DDF-9ACEEBDC5E4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF768450-9FFD-4D77-9EA2-1637D5616604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,12 +43,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Reporting Currency:</t>
   </si>
   <si>
     <t>Exchange Rate:</t>
@@ -1566,10 +1563,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Categorize the investment</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1599,10 +1592,6 @@
   </si>
   <si>
     <t>Total Non-FCF Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type of Investment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1662,10 +1651,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Investment Type:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Valuation Overview</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1718,18 +1703,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Status in Portfolio:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Snowball Scenario</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Held</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>C0003</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1751,10 +1728,6 @@
   </si>
   <si>
     <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1x for stable businesses, 2x for for volatile ones</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1994,6 +1967,34 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Reporting Currency:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type of Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variable + Fixed Costs &amp; Dividends</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selected:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>六福珠宝</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2003,6 +2004,10 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3271,9 +3276,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3336,9 +3338,6 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3373,20 +3372,26 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3692,22 +3697,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="290" t="s">
-        <v>348</v>
-      </c>
-      <c r="F1" s="291" t="s">
-        <v>350</v>
+      <c r="E1" s="337" t="s">
+        <v>387</v>
+      </c>
+      <c r="F1" s="290" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3731,7 +3736,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>388</v>
@@ -3742,13 +3747,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="50">
         <v>14.96</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3764,7 +3769,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3774,7 +3779,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3800,24 +3805,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>286</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="339" t="s">
+        <v>285</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>334</v>
+        <v>382</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3827,17 +3832,17 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>381</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="50">
         <v>1</v>
@@ -3850,16 +3855,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3876,15 +3881,15 @@
         <v>14.733437767356989</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E20" s="320">
+        <v>334</v>
+      </c>
+      <c r="E20" s="336">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -3899,7 +3904,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3908,26 +3913,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="339" t="s">
+        <v>235</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>378</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3935,17 +3940,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="B29" s="338" t="s">
+        <v>237</v>
+      </c>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3961,17 +3966,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
-        <v>240</v>
-      </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="B32" s="338" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3984,7 +3989,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -3996,17 +4001,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
-        <v>243</v>
-      </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="B36" s="338" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4018,19 +4023,19 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
-        <v>247</v>
-      </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="B39" s="338" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>379</v>
-      </c>
-      <c r="C40" s="330">
+        <v>372</v>
+      </c>
+      <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
         <v>13746.938888322537</v>
       </c>
@@ -4038,14 +4043,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="329"/>
-      <c r="F40" s="329"/>
+      <c r="E40" s="327"/>
+      <c r="F40" s="327"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>380</v>
-      </c>
-      <c r="C41" s="330">
+        <v>373</v>
+      </c>
+      <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
         <v>-59596</v>
       </c>
@@ -4053,12 +4058,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="329"/>
-      <c r="F41" s="329"/>
+      <c r="E41" s="327"/>
+      <c r="F41" s="327"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
@@ -4071,12 +4076,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4088,17 +4093,17 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
-        <v>248</v>
-      </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="B47" s="338" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
@@ -4110,17 +4115,17 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>377</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="338" t="s">
+        <v>370</v>
+      </c>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4132,26 +4137,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>382</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>268</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="339" t="s">
+        <v>267</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4164,7 +4169,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
@@ -4177,7 +4182,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4186,7 +4191,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4195,7 +4200,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4208,63 +4213,63 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="B63" s="338" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
-        <v>259</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="B64" s="340" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="C67" s="318">
+        <v>306</v>
+      </c>
+      <c r="C67" s="317">
         <v>0.08</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D68" s="293" t="s">
-        <v>356</v>
+      <c r="D68" s="292" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="293" t="s">
-        <v>356</v>
+      <c r="D69" s="292" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4275,26 +4280,26 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="338" t="s">
-        <v>383</v>
-      </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+      <c r="B72" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>384</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="B73" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="269">
         <v>0</v>
@@ -4302,7 +4307,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4315,7 +4320,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A78" s="253" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4327,36 +4332,36 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
-        <v>261</v>
-      </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+      <c r="B80" s="339" t="s">
+        <v>260</v>
+      </c>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
-        <v>385</v>
-      </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
+      <c r="B84" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
@@ -4369,7 +4374,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
@@ -4382,12 +4387,12 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C89" s="191">
         <f>BS!C66</f>
@@ -4400,7 +4405,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
@@ -4413,7 +4418,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4426,12 +4431,12 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
@@ -4444,7 +4449,7 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
@@ -4456,17 +4461,17 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
-        <v>267</v>
-      </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
+      <c r="B97" s="339" t="s">
+        <v>266</v>
+      </c>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
@@ -4479,7 +4484,7 @@
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A101" s="253" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B101" s="36"/>
       <c r="C101" s="36"/>
@@ -4488,29 +4493,29 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
-        <v>368</v>
-      </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="B103" s="338" t="s">
+        <v>361</v>
+      </c>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C105" s="266" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D105" s="266" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E105" s="266" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F105" s="266" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4625,7 +4630,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B112" s="241" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
@@ -4638,7 +4643,7 @@
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="343" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C114" s="343"/>
       <c r="D114" s="343"/>
@@ -4647,7 +4652,7 @@
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="253" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -4656,22 +4661,22 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
-        <v>275</v>
-      </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+      <c r="B118" s="341" t="s">
+        <v>274</v>
+      </c>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C120" s="257">
         <f>E20</f>
@@ -4680,7 +4685,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C121" s="256">
         <f>C19</f>
@@ -4689,7 +4694,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="242" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C122" s="243">
         <f>Scenarios!C77</f>
@@ -4702,7 +4707,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B124" s="240" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -4727,7 +4732,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B127" s="82" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
@@ -4740,7 +4745,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B128" s="244" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
@@ -4749,12 +4754,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4770,6 +4769,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4777,7 +4782,7 @@
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
-      <formula1>"Not Held, Held"</formula1>
+      <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
@@ -4853,7 +4858,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4869,7 +4874,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="109">
         <v>1000</v>
@@ -4877,7 +4882,7 @@
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="193">
         <v>15325962</v>
@@ -4903,7 +4908,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="193">
         <v>11151623</v>
@@ -4929,7 +4934,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="193">
         <v>2297566</v>
@@ -4955,7 +4960,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="194">
         <v>2043459</v>
@@ -4981,7 +4986,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4997,7 +5002,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9" s="193">
         <v>639</v>
@@ -5017,7 +5022,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5033,7 +5038,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5049,7 +5054,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="193">
         <v>59596</v>
@@ -5075,7 +5080,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="193">
         <v>28977</v>
@@ -5101,7 +5106,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="193">
         <v>327166</v>
@@ -5127,7 +5132,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="195">
         <v>1767305</v>
@@ -5153,7 +5158,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="193">
         <v>-9467</v>
@@ -5179,13 +5184,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="184">
         <v>463424</v>
@@ -5209,7 +5214,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="184">
         <v>676387</v>
@@ -5233,7 +5238,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="184">
         <v>626583</v>
@@ -5286,13 +5291,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="186"/>
       <c r="D25" s="184">
@@ -5314,7 +5319,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="186"/>
       <c r="D26" s="184">
@@ -5336,7 +5341,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="185">
         <v>3990166</v>
@@ -5360,7 +5365,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="185">
         <v>12863898</v>
@@ -5384,7 +5389,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="184"/>
       <c r="D29" s="184"/>
@@ -5400,13 +5405,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="184">
         <v>1095356</v>
@@ -5430,7 +5435,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5446,12 +5451,12 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -5500,7 +5505,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5549,7 +5554,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5598,7 +5603,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5647,7 +5652,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5696,7 +5701,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5745,7 +5750,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5794,7 +5799,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5843,7 +5848,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5892,7 +5897,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5941,7 +5946,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5990,7 +5995,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6039,7 +6044,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6088,12 +6093,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6142,7 +6147,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6191,12 +6196,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6245,7 +6250,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6294,7 +6299,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
@@ -6343,7 +6348,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6392,13 +6397,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6447,7 +6452,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6496,7 +6501,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6545,7 +6550,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6594,7 +6599,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6849,7 +6854,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6865,13 +6870,13 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C74" s="9"/>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B75" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" s="78">
         <f>IF(C$4="","",C78+C79)</f>
@@ -6920,7 +6925,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6954,7 +6959,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6988,7 +6993,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -7037,7 +7042,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -7129,7 +7134,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7145,7 +7150,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7156,177 +7161,177 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="210" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="209" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="210" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>190</v>
-      </c>
       <c r="G3" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H3" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="19">
         <v>265773</v>
       </c>
-      <c r="D4" s="301">
+      <c r="D4" s="300">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="19">
         <v>1998219</v>
       </c>
-      <c r="H4" s="301">
+      <c r="H4" s="300">
         <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="301">
+      <c r="D5" s="300">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="301">
+      <c r="H5" s="300">
         <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="19">
         <v>9672256</v>
       </c>
-      <c r="D6" s="301">
+      <c r="D6" s="300">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="301">
+      <c r="H6" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="301">
+      <c r="D7" s="300">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="301">
+      <c r="H7" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="301">
+      <c r="D8" s="300">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="301">
+      <c r="H8" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="19">
         <v>366595</v>
       </c>
-      <c r="D9" s="301">
+      <c r="D9" s="300">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="301">
+      <c r="H9" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="19">
         <v>29465</v>
       </c>
-      <c r="D10" s="301">
+      <c r="D10" s="300">
         <v>0.9</v>
       </c>
-      <c r="H10" s="302"/>
+      <c r="H10" s="301"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="301">
+      <c r="D11" s="300">
         <v>0.05</v>
       </c>
-      <c r="H11" s="302"/>
+      <c r="H11" s="301"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7337,7 +7342,7 @@
         <v>5058769.8</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7355,191 +7360,191 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" s="19">
         <v>103050</v>
       </c>
-      <c r="D15" s="301">
+      <c r="D15" s="300">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="301">
+      <c r="H15" s="300">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="301">
+      <c r="D16" s="300">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="301">
+      <c r="H16" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="301">
+      <c r="D17" s="300">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="301">
+      <c r="H17" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="301">
+      <c r="D18" s="300">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="301">
+      <c r="H18" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="19">
         <v>2522337</v>
       </c>
-      <c r="D19" s="301">
+      <c r="D19" s="300">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="301">
+      <c r="H19" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="301">
+      <c r="D20" s="300">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="301">
+      <c r="H20" s="300">
         <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="19">
         <v>538321</v>
       </c>
-      <c r="D21" s="301">
+      <c r="D21" s="300">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="19">
         <v>925726</v>
       </c>
-      <c r="H21" s="301">
+      <c r="H21" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="19">
         <v>154648</v>
       </c>
-      <c r="D22" s="301">
+      <c r="D22" s="300">
         <v>0.9</v>
       </c>
-      <c r="H22" s="302"/>
+      <c r="H22" s="301"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="19">
         <v>277674</v>
       </c>
-      <c r="D23" s="301">
-        <v>0</v>
-      </c>
-      <c r="H23" s="302"/>
+      <c r="D23" s="300">
+        <v>0</v>
+      </c>
+      <c r="H23" s="301"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7550,7 +7555,7 @@
         <v>459552.95</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7563,30 +7568,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H26" s="213" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="19">
         <v>1427805</v>
       </c>
       <c r="F27" s="214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7599,13 +7604,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19">
         <v>287697</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G28" s="184">
         <v>-26962</v>
@@ -7614,13 +7619,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7633,13 +7638,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
@@ -7649,14 +7654,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1715502</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7666,14 +7671,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>1801307</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7686,7 +7691,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="86">
         <v>3516809</v>
@@ -7699,24 +7704,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="225" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
@@ -7729,13 +7734,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7745,13 +7750,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="19">
         <v>0</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7761,13 +7766,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C38" s="19">
         <v>319420</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7777,13 +7782,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7796,14 +7801,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>319420</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -7816,14 +7821,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>153937</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -7836,13 +7841,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="86">
         <v>473357</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -7855,7 +7860,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7866,21 +7871,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" s="267" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="209" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="267" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="209" t="s">
-        <v>288</v>
-      </c>
-      <c r="F45" s="294" t="s">
-        <v>63</v>
+      <c r="F45" s="293" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -7912,20 +7917,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7939,7 +7944,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -7953,19 +7958,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7979,7 +7984,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7996,19 +8001,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -8019,7 +8024,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -8033,19 +8038,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8056,12 +8061,12 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8072,21 +8077,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>312</v>
-      </c>
-      <c r="F65" s="294" t="s">
-        <v>63</v>
+        <v>310</v>
+      </c>
+      <c r="F65" s="293" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8097,12 +8102,12 @@
         <v>1050246.6606106577</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8112,7 +8117,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8122,7 +8127,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8132,7 +8137,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8144,20 +8149,20 @@
       <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="292" t="s">
-        <v>353</v>
+      <c r="B72" s="291" t="s">
+        <v>347</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8167,47 +8172,50 @@
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-947972.33938934223</v>
       </c>
+      <c r="F73" s="1" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="295" t="s">
-        <v>358</v>
-      </c>
-      <c r="C74" s="296">
+      <c r="B74" s="294" t="s">
+        <v>351</v>
+      </c>
+      <c r="C74" s="295">
         <f>-$C$66/C73</f>
         <v>1.6829876118070222</v>
       </c>
-      <c r="D74" s="296">
+      <c r="D74" s="295">
         <f>-$C$66/D73</f>
         <v>2.1078874530107048</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>355</v>
-      </c>
-      <c r="C75" s="300"/>
-      <c r="D75" s="299">
+        <v>349</v>
+      </c>
+      <c r="C75" s="299"/>
+      <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
         <v>947972.33938934223</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="297" t="s">
-        <v>359</v>
-      </c>
-      <c r="C76" s="298"/>
-      <c r="D76" s="335">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;12,IF(D74&gt;24,12,6),2))</f>
+      <c r="B76" s="296" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" s="297"/>
+      <c r="D76" s="333">
+        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8215,19 +8223,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8241,7 +8249,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8255,7 +8263,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8269,7 +8277,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8283,7 +8291,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8294,15 +8302,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8319,7 +8327,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8336,7 +8344,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8353,7 +8361,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -8401,7 +8409,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8454,12 +8462,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8477,28 +8485,28 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="309"/>
+      <c r="E3" s="308"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="196">
         <f>AVERAGE(G4:J4)</f>
         <v>11975736</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="307"/>
+      <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
@@ -8548,13 +8556,13 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
         <v>-10274842.146672107</v>
       </c>
-      <c r="E5" s="309"/>
+      <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-13195082</v>
@@ -8603,13 +8611,13 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
         <v>1700893.8533278927</v>
       </c>
-      <c r="E6" s="309"/>
+      <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>2130880</v>
@@ -8658,13 +8666,13 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
         <v>-302359.25</v>
       </c>
-      <c r="E7" s="309"/>
+      <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-254107</v>
@@ -8713,14 +8721,14 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
         <v>1398534.6033278927</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="315"/>
+      <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8770,13 +8778,13 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>463424</v>
       </c>
-      <c r="E9" s="309"/>
+      <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>463424</v>
@@ -8825,13 +8833,13 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-463424.00000000006</v>
       </c>
-      <c r="E10" s="309"/>
+      <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-676387</v>
@@ -8880,14 +8888,14 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="172"/>
-      <c r="E11" s="308"/>
+      <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
@@ -8937,13 +8945,13 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
         <v>-45849.061111677467</v>
       </c>
-      <c r="E12" s="309"/>
+      <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
         <v>-45849.061111677467</v>
@@ -8992,13 +9000,13 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
         <v>1352685.5422162153</v>
       </c>
-      <c r="E13" s="309"/>
+      <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>1618599.9388883226</v>
@@ -9047,13 +9055,13 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-338171.38555405382</v>
       </c>
-      <c r="E14" s="309"/>
+      <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-327166</v>
@@ -9102,14 +9110,14 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="316"/>
+      <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
@@ -9159,14 +9167,14 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
         <v>1014514.1566621615</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="317"/>
+      <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -9216,15 +9224,15 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="308" t="s">
-        <v>370</v>
+      <c r="E17" s="307" t="s">
+        <v>363</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9242,14 +9250,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="308" t="s">
-        <v>371</v>
+      <c r="E18" s="307" t="s">
+        <v>364</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9267,14 +9275,14 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
         <v>1014514.1566621615</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="306"/>
+      <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
@@ -9343,12 +9351,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9366,11 +9374,11 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="306"/>
+      <c r="E22" s="305"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9387,14 +9395,14 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-8638608.2360938303</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="308"/>
+      <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
@@ -9444,14 +9452,14 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>-1636233.9105782772</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="306"/>
+      <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
@@ -9501,14 +9509,14 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-10274842.146672107</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="314"/>
+      <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9557,27 +9565,27 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="309"/>
+      <c r="E26" s="308"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="309"/>
+        <v>210</v>
+      </c>
+      <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
         <v>0.72134257435984139</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="307" t="s">
-        <v>372</v>
+      <c r="E28" s="306" t="s">
+        <v>365</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9636,8 +9644,8 @@
         <v>0.13662908990130354</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="307" t="s">
-        <v>372</v>
+      <c r="E29" s="306" t="s">
+        <v>365</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9688,13 +9696,13 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
         <v>0.85797166426114502</v>
       </c>
-      <c r="E30" s="309"/>
+      <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.86096272455849754</v>
@@ -9742,26 +9750,26 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="309"/>
+      <c r="E31" s="308"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="309"/>
+        <v>47</v>
+      </c>
+      <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
         <v>-302359.25</v>
       </c>
-      <c r="E33" s="307" t="s">
-        <v>372</v>
+      <c r="E33" s="306" t="s">
+        <v>365</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9811,15 +9819,15 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="307" t="s">
-        <v>372</v>
+      <c r="E34" s="306" t="s">
+        <v>365</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9870,14 +9878,14 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-302359.25</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="308"/>
+      <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9926,14 +9934,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="309"/>
+      <c r="E36" s="308"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>212</v>
-      </c>
-      <c r="E37" s="309"/>
+        <v>211</v>
+      </c>
+      <c r="E37" s="308"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9946,7 +9954,7 @@
         <v>2.5247654924924864E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="306"/>
+      <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -10004,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="306"/>
+      <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -10054,13 +10062,13 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
         <v>2.5247654924924864E-2</v>
       </c>
-      <c r="E40" s="309"/>
+      <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>1.6580166386945237E-2</v>
@@ -10108,26 +10116,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="309"/>
+      <c r="E41" s="308"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>213</v>
-      </c>
-      <c r="E42" s="309"/>
+        <v>212</v>
+      </c>
+      <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C43" s="303">
+        <v>175</v>
+      </c>
+      <c r="C43" s="302">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="306" t="s">
-        <v>373</v>
+      <c r="E43" s="305" t="s">
+        <v>366</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10181,12 +10189,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10204,20 +10212,20 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="309"/>
+        <v>63</v>
+      </c>
+      <c r="E46" s="308"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-59596</v>
       </c>
-      <c r="E47" s="309"/>
+      <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-59596</v>
@@ -10266,111 +10274,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
         <v>13746.938888322537</v>
       </c>
-      <c r="E48" s="309"/>
-      <c r="G48" s="336">
+      <c r="E48" s="308"/>
+      <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>13746.938888322537</v>
       </c>
-      <c r="H48" s="336">
+      <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>15714.785887969218</v>
       </c>
-      <c r="I48" s="336">
+      <c r="I48" s="334">
         <f t="shared" si="19"/>
         <v>41436.747429397234</v>
       </c>
-      <c r="J48" s="336">
+      <c r="J48" s="334">
         <f t="shared" si="19"/>
         <v>30076.558361523694</v>
       </c>
-      <c r="K48" s="336">
+      <c r="K48" s="334">
         <f t="shared" si="19"/>
         <v>21561.872259870215</v>
       </c>
-      <c r="L48" s="336" t="str">
+      <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="336" t="str">
+      <c r="M48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="336" t="str">
+      <c r="N48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="336" t="str">
+      <c r="O48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="336" t="str">
+      <c r="P48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="336" t="str">
+      <c r="Q48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="331" t="s">
-        <v>381</v>
-      </c>
-      <c r="C49" s="332">
+      <c r="B49" s="329" t="s">
+        <v>374</v>
+      </c>
+      <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
         <v>28977</v>
       </c>
-      <c r="D49" s="333"/>
-      <c r="E49" s="334"/>
-      <c r="F49" s="333"/>
-      <c r="G49" s="332">
+      <c r="D49" s="331"/>
+      <c r="E49" s="332"/>
+      <c r="F49" s="331"/>
+      <c r="G49" s="330">
         <f>Data!C52</f>
         <v>28977</v>
       </c>
-      <c r="H49" s="332">
+      <c r="H49" s="330">
         <f>Data!D52</f>
         <v>33125</v>
       </c>
-      <c r="I49" s="332">
+      <c r="I49" s="330">
         <f>Data!E52</f>
         <v>87344</v>
       </c>
-      <c r="J49" s="332">
+      <c r="J49" s="330">
         <f>Data!F52</f>
         <v>63398</v>
       </c>
-      <c r="K49" s="332">
+      <c r="K49" s="330">
         <f>Data!G52</f>
         <v>45450</v>
       </c>
-      <c r="L49" s="332" t="str">
+      <c r="L49" s="330" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="332" t="str">
+      <c r="M49" s="330" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="332" t="str">
+      <c r="N49" s="330" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="332" t="str">
+      <c r="O49" s="330" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="332" t="str">
+      <c r="P49" s="330" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="332" t="str">
+      <c r="Q49" s="330" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10378,13 +10386,13 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
         <v>-45849.061111677467</v>
       </c>
-      <c r="E50" s="309"/>
+      <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-45849.061111677467</v>
@@ -10432,29 +10440,29 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="309"/>
+      <c r="E51" s="308"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" s="309"/>
+        <v>159</v>
+      </c>
+      <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="89">
         <f>G53</f>
         <v>1.4501413508729523E-2</v>
       </c>
-      <c r="E53" s="306" t="s">
-        <v>374</v>
+      <c r="E53" s="305" t="s">
+        <v>367</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10474,14 +10482,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>2.9286626219579916E-2</v>
       </c>
-      <c r="E54" s="306" t="s">
-        <v>375</v>
+      <c r="E54" s="305" t="s">
+        <v>368</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10501,13 +10509,13 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
         <v>23.466920654538772</v>
       </c>
-      <c r="E55" s="309"/>
+      <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>31.4915933955299</v>
@@ -10555,28 +10563,28 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="309"/>
+      <c r="E56" s="308"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="E57" s="309"/>
+        <v>172</v>
+      </c>
+      <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="309"/>
+      <c r="E58" s="308"/>
       <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
@@ -10625,13 +10633,13 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="309"/>
+      <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
@@ -10680,13 +10688,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="309"/>
+      <c r="E60" s="308"/>
       <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
@@ -10735,13 +10743,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="309"/>
+      <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
@@ -10790,13 +10798,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="304">
-        <v>0</v>
-      </c>
-      <c r="E62" s="307" t="s">
-        <v>376</v>
+        <v>164</v>
+      </c>
+      <c r="C62" s="303">
+        <v>0</v>
+      </c>
+      <c r="E62" s="306" t="s">
+        <v>369</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10846,13 +10854,13 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="309"/>
+      <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>248317</v>
@@ -10900,28 +10908,28 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="309"/>
+      <c r="E64" s="308"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>174</v>
-      </c>
-      <c r="E65" s="309"/>
+        <v>173</v>
+      </c>
+      <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="309"/>
+      <c r="E66" s="308"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -10940,13 +10948,13 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="309"/>
+      <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -10965,13 +10973,13 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="309"/>
+      <c r="E68" s="308"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
@@ -10990,14 +10998,14 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="314"/>
+      <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
@@ -11020,12 +11028,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11043,11 +11051,11 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="306"/>
+      <c r="E72" s="305"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -11064,14 +11072,14 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
         <v>0.85797166426114502</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="306"/>
+      <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11121,14 +11129,14 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
         <v>0.14202833573885504</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="306"/>
+      <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11178,14 +11186,14 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
         <v>2.5247654924924864E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="306"/>
+      <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11235,14 +11243,14 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
         <v>0.11678068081393016</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="306"/>
+      <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11292,14 +11300,14 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
         <v>3.8696911822371505E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="306"/>
+      <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11349,14 +11357,14 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
         <v>3.8696911822371505E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="307" t="s">
+      <c r="E78" s="306" t="s">
         <v>390</v>
       </c>
       <c r="F78" s="27"/>
@@ -11408,14 +11416,14 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="306"/>
+      <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11465,14 +11473,14 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
         <v>3.8284963121830232E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="306"/>
+      <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11522,14 +11530,14 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
         <v>0.11295218450174714</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="306"/>
+      <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -11579,14 +11587,14 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
         <v>2.8238046125436785E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="306"/>
+      <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11639,12 +11647,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="305">
+      <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="306"/>
+      <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11694,14 +11702,14 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
         <v>8.4714138376310352E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="306"/>
+      <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11751,13 +11759,13 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C85" s="305">
+        <v>54</v>
+      </c>
+      <c r="C85" s="304">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="308" t="str">
+      <c r="E85" s="307" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11777,12 +11785,12 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="308" t="str">
+      <c r="E86" s="307" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11801,14 +11809,14 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
         <v>8.4714138376310352E-2</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="306"/>
+      <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11857,14 +11865,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="309"/>
+      <c r="E88" s="308"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>219</v>
-      </c>
-      <c r="E89" s="309"/>
+        <v>218</v>
+      </c>
+      <c r="E89" s="308"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11876,7 +11884,7 @@
         <f>G90</f>
         <v>1.36</v>
       </c>
-      <c r="E90" s="309"/>
+      <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>1.36</v>
@@ -11932,7 +11940,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>798466.67599999998</v>
       </c>
-      <c r="E91" s="309"/>
+      <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>798466.67599999998</v>
@@ -11981,13 +11989,13 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
         <v>0.7870434047239161</v>
       </c>
-      <c r="E92" s="309"/>
+      <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
         <v>0.61827914843815168</v>
@@ -12036,13 +12044,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>9.0909090909090912E-2</v>
       </c>
-      <c r="E93" s="309"/>
+      <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>9.0909090909090912E-2</v>
@@ -12090,16 +12098,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="309"/>
+      <c r="E94" s="308"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="306"/>
+      <c r="E95" s="305"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12116,14 +12124,14 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
         <v>-0.2185980886550547</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="306"/>
+      <c r="E96" s="305"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12173,14 +12181,14 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
         <v>-0.16428667163718114</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="306"/>
+      <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -12233,12 +12241,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12256,24 +12264,24 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10"/>
       <c r="B100" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E100" s="309"/>
+        <v>28</v>
+      </c>
+      <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
         <v>16854064</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="310"/>
+      <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -12323,14 +12331,14 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
         <v>265773</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="311"/>
+      <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12380,14 +12388,14 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>9672256</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="311"/>
+      <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12437,14 +12445,14 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
         <v>3990166</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="310"/>
+      <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C78</f>
@@ -12494,14 +12502,14 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
         <v>12863898</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="310"/>
+      <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C79</f>
@@ -12550,19 +12558,19 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="309"/>
+      <c r="E106" s="308"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="310"/>
+      <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12578,14 +12586,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
         <v>2.2192623484686036E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="310"/>
+      <c r="E108" s="309"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12635,14 +12643,14 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
         <v>0.80765441055146836</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="310"/>
+      <c r="E109" s="309"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12692,14 +12700,14 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="310"/>
+      <c r="E110" s="309"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12718,16 +12726,16 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="309"/>
+      <c r="E111" s="308"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="312"/>
+      <c r="E112" s="311"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12777,13 +12785,13 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
         <v>0.11295218450174714</v>
       </c>
-      <c r="E113" s="309"/>
+      <c r="E113" s="308"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
         <v>0.10561163722631718</v>
@@ -12831,13 +12839,13 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
         <v>0.71055479556740742</v>
       </c>
-      <c r="E114" s="309"/>
+      <c r="E114" s="308"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>0.90933332162498015</v>
@@ -12885,14 +12893,14 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
         <v>1.3101832741522048</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="313"/>
+      <c r="E115" s="312"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12942,14 +12950,14 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
         <v>0.10871779326358874</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="312"/>
+      <c r="E116" s="311"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -13018,12 +13026,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -13041,11 +13049,11 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="305"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -13070,7 +13078,7 @@
         <v>1.7279860193696295</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="306"/>
+      <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -13120,14 +13128,14 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
         <v>0.11550708685625866</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="306"/>
+      <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
@@ -13889,32 +13897,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13925,7 +13933,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C75</f>
@@ -13935,7 +13943,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -13946,7 +13954,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13957,14 +13965,14 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="344" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -13980,7 +13988,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
@@ -13996,7 +14004,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -14012,7 +14020,7 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
@@ -14026,7 +14034,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -14040,7 +14048,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -14057,7 +14065,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14067,13 +14075,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -14083,7 +14091,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -14093,7 +14101,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -14110,19 +14118,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>114</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>115</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14788,7 +14796,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14811,7 +14819,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14825,7 +14833,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14996,7 +15004,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15215,19 +15223,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C73" s="175" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="175" t="s">
+        <v>116</v>
+      </c>
+      <c r="E73" s="176" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="176" t="s">
-        <v>118</v>
-      </c>
       <c r="F73" s="176" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15352,20 +15360,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15417,20 +15425,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15442,14 +15450,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15471,14 +15479,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15491,7 +15499,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15516,7 +15524,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15538,7 +15546,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
@@ -15571,7 +15579,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="346"/>
       <c r="F11" s="346"/>
@@ -15585,7 +15593,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15604,7 +15612,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15622,7 +15630,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15633,7 +15641,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15642,21 +15650,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="154">
         <v>5</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15666,14 +15674,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E20" s="347"/>
       <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15688,7 +15696,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15703,16 +15711,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
@@ -15724,7 +15732,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="168">
         <v>0.02</v>
@@ -15735,7 +15743,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
@@ -15750,7 +15758,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="169">
         <v>0.6</v>
@@ -15761,16 +15769,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
@@ -15782,7 +15790,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C32" s="168">
         <v>-0.05</v>
@@ -15793,7 +15801,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
@@ -15808,7 +15816,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="169">
         <v>0.2</v>
@@ -15819,16 +15827,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
@@ -15840,7 +15848,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C38" s="168">
         <v>0.05</v>
@@ -15851,7 +15859,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
@@ -15866,7 +15874,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
@@ -15878,7 +15886,7 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15891,7 +15899,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15900,12 +15908,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" s="154">
         <v>10</v>
@@ -15920,16 +15928,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
@@ -15941,7 +15949,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" s="168">
         <v>-0.08</v>
@@ -15952,7 +15960,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
@@ -15967,7 +15975,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C52" s="169">
         <v>0.02</v>
@@ -15978,16 +15986,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
@@ -15999,7 +16007,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C56" s="168">
         <v>0.06</v>
@@ -16010,7 +16018,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
@@ -16025,7 +16033,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C58" s="169">
         <v>0.02</v>
@@ -16036,7 +16044,7 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -16047,16 +16055,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>324</v>
-      </c>
-      <c r="F60" s="319">
+        <v>321</v>
+      </c>
+      <c r="F60" s="318">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>310</v>
+        <v>383</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16065,39 +16073,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C65" s="155">
         <v>6.4006284479398504E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
@@ -16108,20 +16116,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>319</v>
+        <v>384</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16131,19 +16139,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16153,23 +16161,23 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>387</v>
-      </c>
-      <c r="F72" s="337">
+        <v>380</v>
+      </c>
+      <c r="F72" s="335">
         <f>BS!D89/C60</f>
         <v>-7.4088860346483723E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16178,12 +16186,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16193,7 +16201,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16206,12 +16214,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C121</f>
@@ -16220,7 +16228,7 @@
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16232,7 +16240,7 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16242,7 +16250,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16253,9 +16261,9 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>131</v>
-      </c>
-      <c r="F83" s="337">
+        <v>130</v>
+      </c>
+      <c r="F83" s="335">
         <f>(1-C83/C60)</f>
         <v>0.28161042453275964</v>
       </c>
@@ -16265,12 +16273,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16283,7 +16291,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16294,42 +16302,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="328" t="s">
-        <v>361</v>
-      </c>
-      <c r="F89" s="325"/>
+      <c r="E89" s="326" t="s">
+        <v>354</v>
+      </c>
+      <c r="F89" s="323"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="324"/>
+      <c r="H89" s="322"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="321" t="s">
-        <v>362</v>
-      </c>
-      <c r="F90" s="326" t="s">
-        <v>363</v>
+      <c r="E90" s="319" t="s">
+        <v>355</v>
+      </c>
+      <c r="F90" s="324" t="s">
+        <v>356</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="324"/>
+      <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="322" t="s">
-        <v>362</v>
-      </c>
-      <c r="F91" s="326" t="s">
-        <v>364</v>
+      <c r="E91" s="320" t="s">
+        <v>355</v>
+      </c>
+      <c r="F91" s="324" t="s">
+        <v>357</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="324"/>
+      <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="323" t="s">
-        <v>362</v>
-      </c>
-      <c r="F92" s="327" t="s">
-        <v>365</v>
+      <c r="E92" s="321" t="s">
+        <v>355</v>
+      </c>
+      <c r="F92" s="325" t="s">
+        <v>358</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="324"/>
+      <c r="H92" s="322"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF768450-9FFD-4D77-9EA2-1637D5616604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EB9936-E9C1-40EE-A2AF-5E4319478F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1551,6 +1551,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1704,10 +1708,6 @@
   </si>
   <si>
     <t>Snowball Scenario</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C0003</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2003,11 +2003,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>CNS_05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3690,7 +3690,7 @@
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -3707,7 +3707,7 @@
         <v>387</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>391</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3736,7 +3736,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
         <v>388</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3805,17 +3805,17 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="338" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
@@ -3858,7 +3858,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3881,7 +3881,7 @@
         <v>14.733437767356989</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
+      <c r="B26" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="340" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
+      <c r="B50" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4191,7 +4191,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="340" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="342" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4237,7 +4237,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4245,7 +4245,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
+      <c r="B72" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="338" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
+      <c r="B84" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="338" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
+      <c r="B103" s="340" t="s">
         <v>361</v>
       </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="339" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,6 +4754,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4769,12 +4775,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8083,7 +8083,7 @@
         <v>140</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>62</v>
@@ -8291,7 +8291,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8302,15 +8302,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8327,7 +8327,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8361,7 +8361,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12044,7 +12044,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -15360,7 +15360,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>109</v>
@@ -15432,7 +15432,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -15674,7 +15674,7 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E20" s="347"/>
       <c r="F20" s="347"/>
@@ -15986,7 +15986,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>153</v>
@@ -16055,7 +16055,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16073,10 +16073,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16116,7 +16116,7 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
@@ -16124,12 +16124,12 @@
         <v>384</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16139,19 +16139,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16161,7 +16161,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
@@ -16191,7 +16191,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16214,12 +16214,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C121</f>
@@ -16273,12 +16273,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16291,7 +16291,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8EB9936-E9C1-40EE-A2AF-5E4319478F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E4D40E-7143-47D3-8313-44EB183A6378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E4D40E-7143-47D3-8313-44EB183A6378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0889004A-0BB5-4CCB-8816-4F198193409F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3750,7 +3750,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="50">
-        <v>14.96</v>
+        <v>14.94</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>42</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8783.1334360000001</v>
+        <v>8771.3912789999995</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="339" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19343775079136272</v>
+        <v>0.19401142226230528</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="338" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="338" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="338" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="338" t="s">
         <v>370</v>
       </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="339" t="s">
         <v>375</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>0.11550708685625866</v>
+        <v>0.11566171481724427</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>9.0909090909090912E-2</v>
+        <v>9.1030789825970557E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="340" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="338" t="s">
+      <c r="B72" s="339" t="s">
         <v>376</v>
       </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="339" t="s">
         <v>377</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
+      <c r="B80" s="339" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
+      <c r="B84" s="339" t="s">
         <v>378</v>
       </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
+      <c r="B97" s="339" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
+      <c r="B103" s="338" t="s">
         <v>361</v>
       </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
+      <c r="B118" s="341" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,12 +4754,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4775,6 +4769,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12048,28 +12048,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.0909090909090912E-2</v>
+        <v>9.1030789825970557E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.0909090909090912E-2</v>
+        <v>9.1030789825970557E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3529411764705885E-2</v>
+        <v>7.3627844712182075E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3529411764705885E-2</v>
+        <v>7.3627844712182075E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6844919786096246E-2</v>
+        <v>6.6934404283801874E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6844919786096246E-2</v>
+        <v>6.6934404283801874E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13132,30 +13132,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11550708685625866</v>
+        <v>0.11566171481724427</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.14703567335036016</v>
+        <v>0.14723250825444364</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.15285442213427045</v>
+        <v>0.15305904652802449</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12819442578594989</v>
+        <v>0.12836603813639963</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.12329444454560189</v>
+        <v>0.12345949734954514</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>0.1068535368497469</v>
+        <v>0.10699658040644</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-14.96</v>
+        <v>-14.94</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>14.96</v>
+        <v>14.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>14.96</v>
+        <v>14.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19343775079136272</v>
+        <v>0.19401142226230528</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0889004A-0BB5-4CCB-8816-4F198193409F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9A68F0-2330-4DAB-8475-0E387C845EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3750,7 +3750,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="50">
-        <v>14.94</v>
+        <v>15.4</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>42</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8771.3912789999995</v>
+        <v>9041.4608900000003</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="338" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19401142226230528</v>
+        <v>0.18108249888642258</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
+      <c r="B26" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="340" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
+      <c r="B50" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>0.11566171481724427</v>
+        <v>0.11220688437465126</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>9.1030789825970557E-2</v>
+        <v>8.8311688311688313E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="340" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="342" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
+      <c r="B72" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="338" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
+      <c r="B84" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="338" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
+      <c r="B103" s="340" t="s">
         <v>361</v>
       </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="339" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,6 +4754,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4769,12 +4775,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12048,28 +12048,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.1030789825970557E-2</v>
+        <v>8.8311688311688313E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.1030789825970557E-2</v>
+        <v>8.8311688311688313E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3627844712182075E-2</v>
+        <v>7.1428571428571438E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3627844712182075E-2</v>
+        <v>7.1428571428571438E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6934404283801874E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6934404283801874E-2</v>
+        <v>6.4935064935064929E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13132,30 +13132,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11566171481724427</v>
+        <v>0.11220688437465126</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.14723250825444364</v>
+        <v>0.14283465411177845</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.15305904652802449</v>
+        <v>0.14848715293043416</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12836603813639963</v>
+        <v>0.12453172790635134</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.12345949734954514</v>
+        <v>0.11977174613001328</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>0.10699658040644</v>
+        <v>0.10380057865403984</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-14.94</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>14.94</v>
+        <v>15.4</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16282,7 +16282,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>14.94</v>
+        <v>15.4</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19401142226230528</v>
+        <v>0.18108249888642258</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9A68F0-2330-4DAB-8475-0E387C845EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB31924-6C51-402F-8EDA-E097C3C11A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="339" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="338" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="338" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="338" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="338" t="s">
         <v>370</v>
       </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="339" t="s">
         <v>375</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="340" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="338" t="s">
+      <c r="B72" s="339" t="s">
         <v>376</v>
       </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="339" t="s">
         <v>377</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
+      <c r="B80" s="339" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
+      <c r="B84" s="339" t="s">
         <v>378</v>
       </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
+      <c r="B97" s="339" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
+      <c r="B103" s="338" t="s">
         <v>361</v>
       </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
+      <c r="B118" s="341" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,12 +4754,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4775,6 +4769,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB31924-6C51-402F-8EDA-E097C3C11A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3B3171-CB88-466E-9938-8E4ED2BE43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="394">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -952,14 +952,6 @@
   </si>
   <si>
     <t>Implied Growth Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 1: Calculate FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE represents the cash available to equity holders after accounting for operating expenses, reinvestments, taxes, and interest obligations.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1254,14 +1246,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 3: Calculate Equity Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Equity Value adjusts the stable income value for debt and incorporates non-operating resources available to equity holders. The formula is:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1325,58 +1309,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Purpose:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> This step ensures the equity value reflects all resources available to shareholders by deducting debt and adding excess cash and non-operating assets, avoiding double-counting of income-generating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Expected Equity Value =</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1401,18 +1333,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assume the Equity Value will be realized over the holding period.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Step 4: Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Cash =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1445,32 +1369,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This valuation method estimates the equity value of a company through a five-step process. Each step is designed to systematically derive cash flows available to equity holders, discount them appropriately, and adjust for debt and non-operating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Value Stress Test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1519,23 +1417,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Calculate Target Buy Price</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>No Growth SIV Per Share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 2: Calculate Stable Income Value (SIV) Using FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Stable Income Value (SIV) represents the present value of FCFE, assuming it grows at a constant rate indefinitely. This is calculated using the Gordon Growth Model:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1663,10 +1549,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1768,14 +1650,6 @@
   </si>
   <si>
     <t>Fundamental analysis and market signal analysis should be combined, with fundamental analysis given priority and market signal analysis serving as a supplement. Market signal analysis predicts a company's future trend, while fundamental analysis interprets the trend and identifies relevant fundamental factors and possibilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Based on fundamental research, the following scenarios have been developed, considering driving factors of high growth periods (HGP) and high growth rates (HGR), along with their associated probabilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1891,58 +1765,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Note on Cost of Equity:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile, while target annual return is the investor’s hurdle rate.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Note on Terminal Growth Rate:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Setting g=0 can be a conservative assumption to avoid overestimating the stock’s value, especially if future growth is uncertain or unreliable.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t xml:space="preserve">Note on debt: </t>
     </r>
     <r>
@@ -2008,6 +1830,344 @@
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Implied Market Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Insight: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile and represents the minimum return the investor requires for taking on the general risk of owning this type of business, while the target annual return serves as the investor’s hurdle rate.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Setting g=0% is a conservative assumption, valuing the company based only on its current demonstrated earning power without relying on potentially optimistic future growth projections.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To refine the Stable Income Value (SIV) by incorporating the company’s balance sheet structure. </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The No Growth Equity Value per share represents an estimate of the company’s intrinsic worth based on its current sustainable operations and net financial position, before factoring in any future growth potential. It serves as a fundamentally anchored valuation baseline.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To translate our estimate of the company’s intrinsic value (from Step 4) into a concrete buy price that meets the specific investment requirements.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2675,7 +2835,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3378,22 +3538,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3408,6 +3568,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3684,7 +3845,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3704,15 +3865,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3736,13 +3897,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3769,7 +3930,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3779,7 +3940,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3805,24 +3966,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="338" t="s">
+        <v>382</v>
+      </c>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3832,7 +3993,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>42</v>
@@ -3858,13 +4019,13 @@
         <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3877,11 +4038,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="258">
-        <f>C127</f>
+        <f>C129</f>
         <v>14.733437767356989</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -3889,7 +4050,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -3904,7 +4065,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>234</v>
+        <v>375</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3912,27 +4073,27 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="338" t="s">
+        <v>383</v>
+      </c>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
-        <v>371</v>
-      </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="B26" s="342" t="s">
+        <v>356</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3940,17 +4101,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
-        <v>237</v>
-      </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="B29" s="340" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3966,17 +4127,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
-        <v>239</v>
-      </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="B32" s="340" t="s">
+        <v>237</v>
+      </c>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3989,7 +4150,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -4001,17 +4162,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="B36" s="340" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4023,17 +4184,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
-        <v>246</v>
-      </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="B39" s="340" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4048,7 +4209,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4063,7 +4224,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
@@ -4076,12 +4237,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4093,17 +4254,17 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="B47" s="340" t="s">
+        <v>245</v>
+      </c>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
@@ -4115,17 +4276,17 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>370</v>
-      </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="B50" s="340" t="s">
+        <v>355</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4137,26 +4298,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>375</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="338" t="s">
+        <v>360</v>
+      </c>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="338" t="s">
+        <v>384</v>
+      </c>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4169,7 +4330,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
@@ -4182,7 +4343,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4191,7 +4352,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4200,7 +4361,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>301</v>
+        <v>376</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4214,7 +4375,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>302</v>
+        <v>385</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4222,22 +4383,22 @@
       <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
-        <v>258</v>
-      </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="B64" s="342" t="s">
+        <v>256</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4245,31 +4406,31 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4280,136 +4441,129 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
-        <v>376</v>
-      </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="B72" s="348" t="s">
+        <v>377</v>
+      </c>
+      <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B75" s="47" t="s">
-        <v>257</v>
-      </c>
-      <c r="C75" s="269">
-        <v>0</v>
-      </c>
+      <c r="B73" s="338" t="s">
+        <v>386</v>
+      </c>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="338" t="s">
+        <v>387</v>
+      </c>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="254">
+        <v>255</v>
+      </c>
+      <c r="C76" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B77" s="47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
         <v>21.599825242120371</v>
       </c>
-      <c r="D76" s="1" t="str">
+      <c r="D77" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="253" t="s">
+    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A79" s="253" t="s">
+        <v>378</v>
+      </c>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="239"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B81" s="338" t="s">
+        <v>388</v>
+      </c>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B84" s="240" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="338" t="s">
+        <v>361</v>
+      </c>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B86" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="239"/>
-    </row>
-    <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
-        <v>260</v>
-      </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B85" s="47" t="s">
-        <v>263</v>
-      </c>
-      <c r="C85" s="191">
+      <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
         <v>2034922</v>
       </c>
-      <c r="D85" s="1" t="str">
+      <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B86" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="254">
-        <f>C85*C28*Exchange_Rate/Common_Shares</f>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B87" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C87" s="254">
+        <f>C86*C28*Exchange_Rate/Common_Shares</f>
         <v>3.4660105464438944</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B88" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C89" s="191">
+      <c r="B89" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="C90" s="191">
         <f>BS!C66</f>
         <v>1998219</v>
-      </c>
-      <c r="D89" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="C90" s="191">
-        <f>Valuation_Model!C8</f>
-        <v>1050246.6606106577</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,363 +4572,386 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>304</v>
-      </c>
-      <c r="C91" s="254">
-        <f>C90*C28*Exchange_Rate/Common_Shares</f>
+        <v>271</v>
+      </c>
+      <c r="C91" s="191">
+        <f>Valuation_Model!C8</f>
+        <v>1050246.6606106577</v>
+      </c>
+      <c r="D91" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="47" t="s">
+        <v>292</v>
+      </c>
+      <c r="C92" s="254">
+        <f>C91*C28*Exchange_Rate/Common_Shares</f>
         <v>1.7888479273623368</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B93" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="C94" s="191">
+      <c r="B94" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
         <v>92572.6</v>
       </c>
-      <c r="D94" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="C95" s="254">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B96" s="47" t="s">
+        <v>293</v>
+      </c>
+      <c r="C96" s="254">
+        <f>C95*C28*Exchange_Rate/Common_Shares</f>
         <v>0.15767562978420405</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
-        <v>266</v>
-      </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B99" s="47" t="s">
-        <v>299</v>
-      </c>
-      <c r="C99" s="254">
+    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="338" t="s">
+        <v>389</v>
+      </c>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B100" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
         <v>20.080338252823015</v>
       </c>
-      <c r="D99" s="1" t="str">
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="253" t="s">
-        <v>276</v>
-      </c>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-    </row>
-    <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
-        <v>361</v>
-      </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
-    </row>
-    <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="266" t="s">
+    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A102" s="253" t="s">
+        <v>379</v>
+      </c>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+    </row>
+    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="340" t="s">
+        <v>390</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
+    </row>
+    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B106" s="266" t="s">
         <v>121</v>
       </c>
-      <c r="C105" s="266" t="s">
+      <c r="C106" s="266" t="s">
         <v>136</v>
       </c>
-      <c r="D105" s="266" t="s">
+      <c r="D106" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="E105" s="266" t="s">
-        <v>269</v>
-      </c>
-      <c r="F105" s="266" t="s">
+      <c r="E106" s="266" t="s">
+        <v>263</v>
+      </c>
+      <c r="F106" s="266" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="261" t="str">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B107" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="262">
+      <c r="C107" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D106" s="263">
+      <c r="D107" s="263">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E106" s="264" t="str">
+      <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>24.7 HKD</v>
       </c>
-      <c r="F106" s="265">
+      <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="248" t="str">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="249">
+      <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.05</v>
       </c>
-      <c r="D107" s="250">
+      <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
         <v>5</v>
       </c>
-      <c r="E107" s="251" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.86 HKD</v>
       </c>
-      <c r="F107" s="252">
+      <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.192</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="248" t="str">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="249">
+      <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D108" s="250">
+      <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
         <v>5</v>
       </c>
-      <c r="E108" s="251" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>20.78 HKD</v>
       </c>
-      <c r="F108" s="252">
+      <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.57599999999999996</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="248" t="str">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="249">
+      <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D109" s="250">
+      <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
         <v>5</v>
       </c>
-      <c r="E109" s="251" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>18.42 HKD</v>
       </c>
-      <c r="F109" s="252">
+      <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.192</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="248" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="249">
+      <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.08</v>
       </c>
-      <c r="D110" s="250">
+      <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
         <v>10</v>
       </c>
-      <c r="E110" s="251" t="str">
+      <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.62 HKD</v>
       </c>
-      <c r="F110" s="252">
+      <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="241" t="s">
-        <v>268</v>
-      </c>
-      <c r="C112" s="247">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="241" t="s">
+        <v>262</v>
+      </c>
+      <c r="C113" s="247">
         <f>Scenarios!C60</f>
         <v>20.508980461992877</v>
       </c>
-      <c r="D112" s="242" t="str">
+      <c r="D113" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="343" t="s">
-        <v>362</v>
-      </c>
-      <c r="C114" s="343"/>
-      <c r="D114" s="343"/>
-      <c r="E114" s="343"/>
-      <c r="F114" s="343"/>
-    </row>
-    <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="253" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
-        <v>274</v>
-      </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="343" t="s">
+        <v>393</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
+    </row>
+    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A117" s="253" t="s">
+        <v>380</v>
+      </c>
+      <c r="B117" s="36"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B120" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C120" s="257">
+      <c r="B119" s="339" t="s">
+        <v>391</v>
+      </c>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="338" t="s">
+        <v>392</v>
+      </c>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B121" s="240" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B122" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C122" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C121" s="256">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C123" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="242" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="243">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B124" s="242" t="s">
+        <v>265</v>
+      </c>
+      <c r="C124" s="243">
         <f>Scenarios!C77</f>
         <v>1.36</v>
       </c>
-      <c r="D122" s="242" t="str">
+      <c r="D124" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="240" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="242" t="str">
-        <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="240" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="242" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="246">
+      <c r="C127" s="246">
         <f>Scenarios!C81</f>
         <v>2.8648148148148147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="242" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="242" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="246">
+      <c r="C128" s="246">
         <f>Scenarios!C82</f>
         <v>11.868622952542175</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="82" t="s">
-        <v>270</v>
-      </c>
-      <c r="C127" s="245">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B129" s="82" t="s">
+        <v>264</v>
+      </c>
+      <c r="C129" s="245">
         <f>Scenarios!C83</f>
         <v>14.733437767356989</v>
       </c>
-      <c r="D127" s="47" t="str">
+      <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="244" t="s">
-        <v>272</v>
-      </c>
-      <c r="C128" s="94">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B130" s="244" t="s">
+        <v>266</v>
+      </c>
+      <c r="C130" s="94">
         <f>Scenarios!F83</f>
         <v>0.28161042453275964</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B118:F118"/>
+  <mergeCells count="22">
+    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -7610,7 +7787,7 @@
         <v>287697</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G28" s="184">
         <v>-26962</v>
@@ -7871,13 +8048,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C45" s="267" t="s">
         <v>140</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F45" s="293" t="s">
         <v>62</v>
@@ -7885,7 +8062,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -8038,7 +8215,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C61" s="268" t="s">
         <v>141</v>
@@ -8050,7 +8227,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8061,7 +8238,7 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8083,7 +8260,7 @@
         <v>140</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>62</v>
@@ -8150,7 +8327,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>99</v>
@@ -8162,7 +8339,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8173,12 +8350,12 @@
         <v>-947972.33938934223</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8189,12 +8366,12 @@
         <v>2.1078874530107048</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8202,12 +8379,12 @@
         <v>947972.33938934223</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8215,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8291,7 +8468,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8302,15 +8479,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8327,7 +8504,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8361,7 +8538,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -9110,7 +9287,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
@@ -9232,7 +9409,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9257,7 +9434,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9585,7 +9762,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9645,7 +9822,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9769,7 +9946,7 @@
         <v>-302359.25</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9827,7 +10004,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10135,7 +10312,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10274,7 +10451,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10329,7 +10506,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10462,7 +10639,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10489,7 +10666,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10804,7 +10981,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11365,7 +11542,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12044,7 +12221,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13128,7 +13305,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13933,10 +14110,10 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F4" s="138">
-        <f>Thesis!C75</f>
+        <f>Thesis!C76</f>
         <v>0</v>
       </c>
       <c r="H4" s="124"/>
@@ -13965,7 +14142,7 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="344" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F6" s="344"/>
       <c r="H6" s="124"/>
@@ -15360,7 +15537,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>109</v>
@@ -15432,7 +15609,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -15486,7 +15663,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15499,7 +15676,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15579,7 +15756,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E11" s="346"/>
       <c r="F11" s="346"/>
@@ -15653,7 +15830,7 @@
         <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15664,7 +15841,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15674,14 +15851,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E20" s="347"/>
       <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15696,7 +15873,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15986,7 +16163,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>153</v>
@@ -16055,7 +16232,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16064,7 +16241,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16073,10 +16250,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16088,7 +16265,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16100,7 +16277,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16116,20 +16293,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16139,19 +16316,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16161,14 +16338,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16191,7 +16368,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16214,15 +16391,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C80" s="171">
-        <f>Thesis!C121</f>
+        <f>Thesis!C123</f>
         <v>0.2</v>
       </c>
     </row>
@@ -16273,12 +16450,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16291,7 +16468,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16303,7 +16480,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16311,30 +16488,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F90" s="324" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C3B3171-CB88-466E-9938-8E4ED2BE43AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E83DB6-62B3-4D8A-AAC6-9175F8D95587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -183,10 +183,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Contingent Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -240,10 +236,6 @@
   </si>
   <si>
     <t>CAPX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Data</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1361,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FCFE/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Latest FCFE =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2168,6 +2156,161 @@
       </rPr>
       <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 6:  Risk Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Risk Factors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sustainable Revenue &amp; Margins</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Capital Expenditures</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Working Capital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Accuracy of Normalized FCFE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, which is affacted by uncertainties include:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The extreme scenarios (“Snowball”, “Devil’s Advocate”) have low probabilities; if market conditions shift drastically, these might become more relevant than anticipated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Appropriateness of Cost of Equity</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Reliability of Growth Scenarios</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Macroeconomic Sensitivity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Input Cost Volatility</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Intense Competition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>External &amp; Company-Specific Risks</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized FCFE/Market Cap =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2835,7 +2978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="351">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3538,20 +3681,21 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3568,7 +3712,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3845,7 +3994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3858,22 +4007,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3897,24 +4046,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="50">
         <v>15.4</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3930,7 +4079,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3940,7 +4089,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3966,24 +4115,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>382</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3993,10 +4142,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4016,16 +4165,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -4042,7 +4191,7 @@
         <v>14.733437767356989</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -4050,7 +4199,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -4065,7 +4214,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4074,26 +4223,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>383</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="339" t="s">
+        <v>380</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>356</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="341" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -4102,7 +4251,7 @@
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="340" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C29" s="340"/>
       <c r="D29" s="340"/>
@@ -4111,7 +4260,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -4128,7 +4277,7 @@
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="340" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C32" s="340"/>
       <c r="D32" s="340"/>
@@ -4137,7 +4286,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -4150,7 +4299,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -4163,7 +4312,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="340" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C36" s="340"/>
       <c r="D36" s="340"/>
@@ -4172,7 +4321,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4185,7 +4334,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="340" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C39" s="340"/>
       <c r="D39" s="340"/>
@@ -4194,7 +4343,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4209,7 +4358,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4224,7 +4373,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
@@ -4237,12 +4386,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4255,7 +4404,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B47" s="340" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C47" s="340"/>
       <c r="D47" s="340"/>
@@ -4264,7 +4413,7 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
@@ -4277,16 +4426,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>355</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+        <v>352</v>
+      </c>
+      <c r="C50" s="343"/>
+      <c r="D50" s="343"/>
+      <c r="E50" s="343"/>
+      <c r="F50" s="343"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4298,26 +4447,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>360</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="339" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>384</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="339" t="s">
+        <v>381</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4330,7 +4479,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
@@ -4343,7 +4492,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>275</v>
+        <v>410</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4352,7 +4501,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4361,7 +4510,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4374,31 +4523,31 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>385</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
-        <v>256</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="B64" s="341" t="s">
+        <v>254</v>
+      </c>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4406,31 +4555,31 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4441,32 +4590,32 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="348" t="s">
-        <v>377</v>
+      <c r="B72" s="338" t="s">
+        <v>374</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>386</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="B73" s="339" t="s">
+        <v>383</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
-        <v>387</v>
-      </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="B74" s="339" t="s">
+        <v>384</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C76" s="269">
         <v>0</v>
@@ -4474,7 +4623,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4487,7 +4636,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4499,36 +4648,36 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
-        <v>388</v>
-      </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="B81" s="339" t="s">
+        <v>385</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="240" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
-        <v>361</v>
-      </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="B85" s="339" t="s">
+        <v>358</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
@@ -4541,7 +4690,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4554,12 +4703,12 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C90" s="191">
         <f>BS!C66</f>
@@ -4572,7 +4721,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C91" s="191">
         <f>Valuation_Model!C8</f>
@@ -4585,7 +4734,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4598,12 +4747,12 @@
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
@@ -4616,7 +4765,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4628,17 +4777,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
-        <v>389</v>
-      </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="B98" s="339" t="s">
+        <v>386</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
@@ -4651,7 +4800,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4661,7 +4810,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="340" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C104" s="340"/>
       <c r="D104" s="340"/>
@@ -4670,19 +4819,19 @@
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C106" s="266" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D106" s="266" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E106" s="266" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F106" s="266" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
@@ -4797,7 +4946,7 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B113" s="241" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C113" s="247">
         <f>Scenarios!C60</f>
@@ -4809,17 +4958,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>393</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
+      <c r="B115" s="344" t="s">
+        <v>390</v>
+      </c>
+      <c r="C115" s="344"/>
+      <c r="D115" s="344"/>
+      <c r="E115" s="344"/>
+      <c r="F115" s="344"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4828,31 +4977,31 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>391</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="342" t="s">
+        <v>388</v>
+      </c>
+      <c r="C119" s="342"/>
+      <c r="D119" s="342"/>
+      <c r="E119" s="342"/>
+      <c r="F119" s="342"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
-        <v>392</v>
-      </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="B120" s="339" t="s">
+        <v>389</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C122" s="257">
         <f>E20</f>
@@ -4861,7 +5010,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C123" s="256">
         <f>C19</f>
@@ -4870,7 +5019,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B124" s="242" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C124" s="243">
         <f>Scenarios!C77</f>
@@ -4883,7 +5032,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="240" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -4906,9 +5055,9 @@
         <v>11.868622952542175</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B129" s="82" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
@@ -4919,17 +5068,133 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B130" s="244" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
         <v>0.28161042453275964</v>
       </c>
     </row>
+    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A132" s="253" t="s">
+        <v>394</v>
+      </c>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="349" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" s="339"/>
+      <c r="D134" s="339"/>
+      <c r="E134" s="339"/>
+      <c r="F134" s="339"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="240" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="343" t="s">
+        <v>400</v>
+      </c>
+      <c r="C137" s="343"/>
+      <c r="D137" s="343"/>
+      <c r="E137" s="343"/>
+      <c r="F137" s="343"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="244" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="244" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="244" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="340" t="s">
+        <v>401</v>
+      </c>
+      <c r="C143" s="340"/>
+      <c r="D143" s="340"/>
+      <c r="E143" s="340"/>
+      <c r="F143" s="340"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="350" t="s">
+        <v>402</v>
+      </c>
+      <c r="C146" s="350"/>
+      <c r="D146" s="350"/>
+      <c r="E146" s="350"/>
+      <c r="F146" s="350"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="350" t="s">
+        <v>403</v>
+      </c>
+      <c r="C147" s="350"/>
+      <c r="D147" s="350"/>
+      <c r="E147" s="350"/>
+      <c r="F147" s="350"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="244" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="244" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="244" t="s">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -4946,15 +5211,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5035,7 +5294,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -5085,7 +5344,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="193">
         <v>11151623</v>
@@ -5111,7 +5370,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" s="193">
         <v>2297566</v>
@@ -5137,7 +5396,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="194">
         <v>2043459</v>
@@ -5163,7 +5422,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -5179,7 +5438,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C9" s="193">
         <v>639</v>
@@ -5199,7 +5458,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5215,7 +5474,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5257,7 +5516,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="193">
         <v>28977</v>
@@ -5283,7 +5542,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="193">
         <v>327166</v>
@@ -5309,7 +5568,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="195">
         <v>1767305</v>
@@ -5335,7 +5594,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="193">
         <v>-9467</v>
@@ -5361,13 +5620,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="184">
         <v>463424</v>
@@ -5391,7 +5650,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="184">
         <v>676387</v>
@@ -5415,7 +5674,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="184">
         <v>626583</v>
@@ -5438,181 +5697,199 @@
       <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="str">
+      <c r="B22" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="C22" s="184"/>
+      <c r="D22" s="184"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="184"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="184"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C23" s="184"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="184"/>
+      <c r="M23" s="184"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="C24" s="184"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="184"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="184"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="184"/>
+      <c r="M24" s="184"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C25" s="39">
         <v>1.36</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D25" s="39">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E25" s="39">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F25" s="39">
         <v>1</v>
       </c>
-      <c r="G22" s="39">
+      <c r="G25" s="39">
         <v>1</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H25" s="39">
         <v>1.1499999999999999</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="16" t="s">
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="26" t="s">
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="186"/>
-      <c r="D25" s="184">
+      <c r="C28" s="186"/>
+      <c r="D28" s="184">
         <v>213823</v>
       </c>
-      <c r="E25" s="184">
+      <c r="E28" s="184">
         <v>187711</v>
       </c>
-      <c r="F25" s="184">
+      <c r="F28" s="184">
         <v>277338</v>
       </c>
-      <c r="G25" s="184"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="184"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="184"/>
-      <c r="M25" s="184"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B26" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="186"/>
-      <c r="D26" s="184">
-        <v>8852611</v>
-      </c>
-      <c r="E26" s="184">
-        <v>8769304</v>
-      </c>
-      <c r="F26" s="184">
-        <v>7321614</v>
-      </c>
-      <c r="G26" s="184"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="184"/>
-      <c r="M26" s="184"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="185">
-        <v>3990166</v>
-      </c>
-      <c r="D27" s="185">
-        <v>2466431</v>
-      </c>
-      <c r="E27" s="185">
-        <v>3908586</v>
-      </c>
-      <c r="F27" s="185">
-        <v>2946772</v>
-      </c>
-      <c r="G27" s="185"/>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="185"/>
-      <c r="M27" s="185"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="185">
-        <v>12863898</v>
-      </c>
-      <c r="D28" s="185">
-        <v>12220942</v>
-      </c>
-      <c r="E28" s="185">
-        <v>12078528</v>
-      </c>
-      <c r="F28" s="185">
-        <v>11324224</v>
-      </c>
-      <c r="G28" s="185"/>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="185"/>
-      <c r="M28" s="185"/>
+      <c r="G28" s="184"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="184"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="184"/>
+      <c r="M28" s="184"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="184"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
-      <c r="F29" s="184"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
+        <v>32</v>
+      </c>
+      <c r="C29" s="186"/>
+      <c r="D29" s="184">
+        <v>8852611</v>
+      </c>
+      <c r="E29" s="184">
+        <v>8769304</v>
+      </c>
+      <c r="F29" s="184">
+        <v>7321614</v>
+      </c>
+      <c r="G29" s="184"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="184"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="184"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="185">
+        <v>3990166</v>
+      </c>
+      <c r="D30" s="185">
+        <v>2466431</v>
+      </c>
+      <c r="E30" s="185">
+        <v>3908586</v>
+      </c>
+      <c r="F30" s="185">
+        <v>2946772</v>
+      </c>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B31" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="9"/>
+      <c r="B31" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="185">
+        <v>12863898</v>
+      </c>
+      <c r="D31" s="185">
+        <v>12220942</v>
+      </c>
+      <c r="E31" s="185">
+        <v>12078528</v>
+      </c>
+      <c r="F31" s="185">
+        <v>11324224</v>
+      </c>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="185"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="184">
-        <v>1095356</v>
-      </c>
-      <c r="D32" s="184">
-        <v>1099308</v>
-      </c>
-      <c r="E32" s="184">
-        <v>1107736</v>
-      </c>
-      <c r="F32" s="184">
-        <v>1122325</v>
-      </c>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="184"/>
-      <c r="M32" s="184"/>
+        <v>174</v>
+      </c>
+      <c r="C32" s="184"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="185"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5682,7 +5959,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5731,7 +6008,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5780,7 +6057,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5829,7 +6106,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5878,7 +6155,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5927,7 +6204,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5976,7 +6253,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6025,7 +6302,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6074,7 +6351,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -6123,7 +6400,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -6172,7 +6449,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6221,7 +6498,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6270,7 +6547,7 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
@@ -6324,7 +6601,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6373,12 +6650,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6427,7 +6704,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6476,14 +6753,14 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C57" s="191">
-        <f>IF(C$4="","",C11)</f>
+        <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
       <c r="D57" s="191">
-        <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="E57" s="191">
@@ -6525,7 +6802,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6574,13 +6851,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6629,7 +6906,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6678,7 +6955,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6730,7 +7007,7 @@
         <v>36</v>
       </c>
       <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
+        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
         <v>1.36</v>
       </c>
       <c r="D64" s="75">
@@ -6776,7 +7053,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -7031,7 +7308,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -7102,10 +7379,10 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
+        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D76" s="74">
@@ -7136,7 +7413,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -7173,7 +7450,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
+        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
         <v>3990166</v>
       </c>
       <c r="D78" s="58">
@@ -7222,7 +7499,7 @@
         <v>30</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
         <v>12863898</v>
       </c>
       <c r="D79" s="58">
@@ -7268,14 +7545,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M22 C32:M32 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:M29">
+  <conditionalFormatting sqref="C28:M32">
     <cfRule type="expression" dxfId="4" priority="1">
-      <formula>ISBLANK(C25)</formula>
+      <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M64">
@@ -7327,7 +7604,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7338,19 +7615,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H3" s="210" t="s">
         <v>35</v>
@@ -7368,7 +7645,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G4" s="19">
         <v>1998219</v>
@@ -7410,7 +7687,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -7421,7 +7698,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -7431,7 +7708,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7442,7 +7719,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7452,7 +7729,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7473,7 +7750,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7508,7 +7785,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7519,7 +7796,7 @@
         <v>5058769.8</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7537,19 +7814,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D14" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H14" s="210" t="s">
         <v>35</v>
@@ -7557,7 +7834,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="19">
         <v>103050</v>
@@ -7566,7 +7843,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7586,7 +7863,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -7597,7 +7874,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -7606,7 +7883,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -7617,7 +7894,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7626,7 +7903,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -7646,7 +7923,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7666,7 +7943,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7686,7 +7963,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G21" s="19">
         <v>925726</v>
@@ -7721,7 +7998,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7732,7 +8009,7 @@
         <v>459552.95</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7745,16 +8022,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H26" s="213" t="s">
         <v>35</v>
@@ -7787,7 +8064,7 @@
         <v>287697</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G28" s="184">
         <v>-26962</v>
@@ -7802,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7831,14 +8108,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1715502</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7855,7 +8132,7 @@
         <v>1801307</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7881,10 +8158,10 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H34" s="225" t="s">
         <v>35</v>
@@ -7892,10 +8169,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F35" s="226" t="s">
         <v>31</v>
@@ -7917,7 +8194,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7933,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7949,7 +8226,7 @@
         <v>319420</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7965,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7978,14 +8255,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>319420</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -8005,7 +8282,7 @@
         <v>153937</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -8024,7 +8301,7 @@
         <v>473357</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -8037,7 +8314,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8048,21 +8325,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C45" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F45" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -8094,20 +8371,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -8121,7 +8398,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -8135,19 +8412,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -8161,7 +8438,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -8178,19 +8455,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -8201,7 +8478,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -8215,19 +8492,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8238,12 +8515,12 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8254,21 +8531,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F65" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8279,12 +8556,12 @@
         <v>1050246.6606106577</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8294,7 +8571,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8304,7 +8581,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8314,7 +8591,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8327,19 +8604,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8350,12 +8627,12 @@
         <v>-947972.33938934223</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8366,12 +8643,12 @@
         <v>2.1078874530107048</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8379,12 +8656,12 @@
         <v>947972.33938934223</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8392,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8400,10 +8677,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" s="210" t="s">
         <v>35</v>
@@ -8412,7 +8689,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8426,7 +8703,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8440,7 +8717,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8454,7 +8731,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8468,7 +8745,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8479,15 +8756,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8504,7 +8781,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8521,7 +8798,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8538,7 +8815,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -8586,7 +8863,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8639,12 +8916,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8662,7 +8939,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8733,7 +9010,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
@@ -8788,7 +9065,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
@@ -8843,7 +9120,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
@@ -8898,7 +9175,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
@@ -8955,7 +9232,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
@@ -9010,7 +9287,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
@@ -9065,7 +9342,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
@@ -9122,7 +9399,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
@@ -9177,7 +9454,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
@@ -9232,7 +9509,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9287,7 +9564,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
@@ -9344,7 +9621,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
@@ -9401,7 +9678,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
@@ -9409,7 +9686,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9427,14 +9704,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9452,7 +9729,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
@@ -9528,12 +9805,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9551,7 +9828,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9572,7 +9849,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
@@ -9629,7 +9906,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
@@ -9686,7 +9963,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
@@ -9747,14 +10024,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:J28)</f>
@@ -9762,7 +10039,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9822,7 +10099,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9873,7 +10150,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9932,21 +10209,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:J33)</f>
         <v>-302359.25</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9996,7 +10273,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
@@ -10004,7 +10281,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10055,7 +10332,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
@@ -10116,7 +10393,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E37" s="308"/>
     </row>
@@ -10239,7 +10516,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -10298,21 +10575,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="302">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10366,12 +10643,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10389,7 +10666,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46" s="308"/>
     </row>
@@ -10451,7 +10728,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10506,7 +10783,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10563,7 +10840,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
@@ -10622,24 +10899,24 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C53" s="89">
         <f>G53</f>
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10659,14 +10936,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10686,7 +10963,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -10745,17 +11022,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
@@ -10810,7 +11087,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
@@ -10865,7 +11142,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
@@ -10920,7 +11197,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
@@ -10975,13 +11252,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C62" s="303">
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11031,7 +11308,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
@@ -11090,17 +11367,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
@@ -11125,7 +11402,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
@@ -11150,7 +11427,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
@@ -11175,7 +11452,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
@@ -11205,12 +11482,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11228,7 +11505,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
@@ -11249,7 +11526,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
@@ -11306,7 +11583,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
@@ -11363,7 +11640,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11420,7 +11697,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11477,7 +11754,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11534,7 +11811,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -11542,7 +11819,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11593,7 +11870,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11650,7 +11927,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11707,7 +11984,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
@@ -11764,7 +12041,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11879,7 +12156,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11936,7 +12213,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C85" s="304">
         <v>0</v>
@@ -11962,7 +12239,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
@@ -11986,7 +12263,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
@@ -12047,7 +12324,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E89" s="308"/>
     </row>
@@ -12166,7 +12443,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
@@ -12221,7 +12498,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12280,7 +12557,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
@@ -12301,7 +12578,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
@@ -12358,7 +12635,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
@@ -12418,12 +12695,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12445,7 +12722,7 @@
       </c>
       <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12508,7 +12785,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
@@ -12565,7 +12842,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
@@ -12740,14 +13017,14 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12763,7 +13040,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12820,7 +13097,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
@@ -12877,7 +13154,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12962,7 +13239,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
@@ -13016,7 +13293,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
@@ -13070,7 +13347,7 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
@@ -13127,7 +13404,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
@@ -13203,12 +13480,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -13226,7 +13503,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
@@ -13305,7 +13582,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14074,32 +14351,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -14110,7 +14387,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C76</f>
@@ -14120,7 +14397,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -14131,7 +14408,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -14141,15 +14418,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="344" t="s">
-        <v>253</v>
-      </c>
-      <c r="F6" s="344"/>
+      <c r="E6" s="345" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" s="345"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -14159,13 +14436,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
@@ -14175,13 +14452,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -14191,13 +14468,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
@@ -14211,7 +14488,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -14225,7 +14502,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -14242,7 +14519,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14252,13 +14529,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -14268,7 +14545,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -14278,7 +14555,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -14295,19 +14572,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>112</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="132" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>114</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14973,7 +15250,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14996,7 +15273,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -15010,7 +15287,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -15181,7 +15458,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15400,19 +15677,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="175" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" s="175" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="176" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="176" t="s">
         <v>121</v>
-      </c>
-      <c r="C73" s="175" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="175" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="176" t="s">
-        <v>117</v>
-      </c>
-      <c r="F73" s="176" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15537,20 +15814,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15602,20 +15879,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15627,14 +15904,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15656,14 +15933,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15676,7 +15953,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15686,11 +15963,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15701,7 +15978,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15711,8 +15988,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15723,7 +16000,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
@@ -15733,8 +16010,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15744,8 +16021,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15756,10 +16033,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>285</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>282</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15770,15 +16047,15 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.20035451325595277</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15789,14 +16066,14 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15807,18 +16084,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0457013634429568E-2</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15827,38 +16104,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>347</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>344</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>317</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>314</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15868,12 +16145,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15883,44 +16160,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C26" s="168">
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
@@ -15930,55 +16207,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C28" s="169">
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="168">
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
@@ -15988,55 +16265,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" s="169">
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="168">
         <v>0.05</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
@@ -16046,24 +16323,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -16076,7 +16353,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -16085,12 +16362,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C46" s="154">
         <v>10</v>
@@ -16105,39 +16382,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C50" s="168">
         <v>-0.08</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
@@ -16147,55 +16424,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C52" s="169">
         <v>0.02</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C56" s="168">
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
@@ -16205,23 +16482,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C58" s="169">
         <v>0.02</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -16232,7 +16509,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16241,7 +16518,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16250,39 +16527,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C65" s="155">
         <v>6.4006284479398504E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
@@ -16293,20 +16570,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16316,19 +16593,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16338,14 +16615,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16354,7 +16631,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16363,12 +16640,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16378,7 +16655,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16391,12 +16668,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
@@ -16405,7 +16682,7 @@
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16417,7 +16694,7 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16427,7 +16704,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16438,7 +16715,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
@@ -16450,12 +16727,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16468,7 +16745,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16480,7 +16757,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16488,30 +16765,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F90" s="324" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
+        <v>339</v>
+      </c>
+      <c r="F92" s="325" t="s">
         <v>342</v>
-      </c>
-      <c r="F92" s="325" t="s">
-        <v>345</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E83DB6-62B3-4D8A-AAC6-9175F8D95587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13647EF-E154-4C16-A443-E96DE44A9C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3700,6 +3700,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3711,12 +3717,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4060,7 +4060,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>15.4</v>
+        <v>14.92</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>9041.4608900000003</v>
+        <v>8759.6491220000007</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18108249888642258</v>
+        <v>0.19458617050699911</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>0.11220688437465126</v>
+        <v>0.11581675733040411</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.1152815013404831E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5088,7 +5088,7 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="346" t="s">
         <v>396</v>
       </c>
       <c r="C134" s="339"/>
@@ -5145,22 +5145,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="350" t="s">
+      <c r="B146" s="345" t="s">
         <v>402</v>
       </c>
-      <c r="C146" s="350"/>
-      <c r="D146" s="350"/>
-      <c r="E146" s="350"/>
-      <c r="F146" s="350"/>
+      <c r="C146" s="345"/>
+      <c r="D146" s="345"/>
+      <c r="E146" s="345"/>
+      <c r="F146" s="345"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="350" t="s">
+      <c r="B147" s="345" t="s">
         <v>403</v>
       </c>
-      <c r="C147" s="350"/>
-      <c r="D147" s="350"/>
-      <c r="E147" s="350"/>
-      <c r="F147" s="350"/>
+      <c r="C147" s="345"/>
+      <c r="D147" s="345"/>
+      <c r="E147" s="345"/>
+      <c r="F147" s="345"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -12502,28 +12502,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.1152815013404831E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.8311688311688313E-2</v>
+        <v>9.1152815013404831E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1428571428571438E-2</v>
+        <v>7.3726541554959793E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1428571428571438E-2</v>
+        <v>7.3726541554959793E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4935064935064929E-2</v>
+        <v>6.7024128686327081E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.4935064935064929E-2</v>
+        <v>6.7024128686327081E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13586,30 +13586,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11220688437465126</v>
+        <v>0.11581675733040411</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.14283465411177845</v>
+        <v>0.14742987086604478</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.14848715293043416</v>
+        <v>0.15326421951264652</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12453172790635134</v>
+        <v>0.12853811057357981</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.11977174613001328</v>
+        <v>0.12362499265430324</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>0.10380057865403984</v>
+        <v>0.10714000745792317</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -14418,10 +14418,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="347" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="347"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14436,8 +14436,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="347"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14452,8 +14452,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14468,8 +14468,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-15.4</v>
+        <v>-14.92</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15963,11 +15963,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="349" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15988,8 +15988,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -16010,8 +16010,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -16021,8 +16021,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -16035,8 +16035,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+      <c r="E11" s="349"/>
+      <c r="F11" s="349"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -16054,8 +16054,8 @@
         <v>0.20035451325595277</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="349"/>
+      <c r="F12" s="349"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -16072,8 +16072,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="349"/>
+      <c r="F13" s="349"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -16090,8 +16090,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0457013634429568E-2</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="349"/>
+      <c r="F14" s="349"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16117,21 +16117,21 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="347" t="s">
+      <c r="E18" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="348"/>
+      <c r="F18" s="350"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="350"/>
+      <c r="F19" s="350"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+      <c r="E20" s="350"/>
+      <c r="F20" s="350"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16139,14 +16139,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>14.92</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="350"/>
+      <c r="F21" s="350"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16160,8 +16160,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="350"/>
+      <c r="F22" s="350"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16181,8 +16181,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -16192,8 +16192,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16207,8 +16207,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="348"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16218,8 +16218,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16239,8 +16239,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -16250,8 +16250,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16265,8 +16265,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="348"/>
+      <c r="F33" s="348"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16276,8 +16276,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16297,8 +16297,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -16308,8 +16308,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="348"/>
+      <c r="F38" s="348"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16323,8 +16323,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="348"/>
+      <c r="F39" s="348"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16335,8 +16335,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16398,8 +16398,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="348"/>
+      <c r="F49" s="348"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16409,8 +16409,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16424,8 +16424,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="348"/>
+      <c r="F51" s="348"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16435,8 +16435,8 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="348"/>
+      <c r="F52" s="348"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16456,8 +16456,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="348"/>
+      <c r="F55" s="348"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16467,8 +16467,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="348"/>
+      <c r="F56" s="348"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16482,8 +16482,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="348"/>
+      <c r="F57" s="348"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16493,8 +16493,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>14.92</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18108249888642258</v>
+        <v>0.19458617050699911</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13647EF-E154-4C16-A443-E96DE44A9C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5049DDF6-00B3-4E8A-A3BA-0FACC872942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="414">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1805,14 +1805,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>六福珠宝</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0590.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNS_05</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2311,6 +2303,26 @@
   </si>
   <si>
     <t>Normalized FCFE/Market Cap =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>六福珠宝</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0590.HK</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2338,7 +2350,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2771,6 +2783,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2978,7 +2997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="351">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3682,6 +3701,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4044,15 +4067,15 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>368</v>
+      <c r="C5" s="339" t="s">
+        <v>412</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>369</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4060,7 +4083,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>14.92</v>
+        <v>14.44</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4105,7 +4128,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8759.6491220000007</v>
+        <v>8477.8373539999993</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4115,13 +4138,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4168,7 +4191,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4199,11 +4222,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19458617050699911</v>
+        <v>0.20871253483792285</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4214,7 +4237,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4223,22 +4246,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>380</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="343" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4250,13 +4273,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4276,13 +4299,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4311,13 +4334,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4333,13 +4356,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4403,13 +4426,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4425,13 +4448,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="345"/>
+      <c r="D50" s="345"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4447,22 +4470,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4492,11 +4515,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C58" s="94">
-        <f>Normalized_FCF!C121</f>
-        <v>0.11581675733040411</v>
+        <f>Normalized_FCF!C125</f>
+        <v>0.11966662184000204</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4505,12 +4528,12 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>9.1152815013404831E-2</v>
+        <v>9.418282548476456E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4523,22 +4546,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4591,27 +4614,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="B73" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="B74" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4636,7 +4659,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4648,13 +4671,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>385</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4667,13 +4690,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
+      <c r="B85" s="341" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4777,13 +4800,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>386</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
+      <c r="B98" s="341" t="s">
+        <v>384</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4800,7 +4823,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4809,13 +4832,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>387</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
+      <c r="B104" s="342" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4958,17 +4981,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="344" t="s">
-        <v>390</v>
-      </c>
-      <c r="C115" s="344"/>
-      <c r="D115" s="344"/>
-      <c r="E115" s="344"/>
-      <c r="F115" s="344"/>
+      <c r="B115" s="346" t="s">
+        <v>388</v>
+      </c>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4977,22 +5000,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
-        <v>388</v>
-      </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
+      <c r="B119" s="344" t="s">
+        <v>386</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>389</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
+      <c r="B120" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5079,7 +5102,7 @@
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="253" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5088,98 +5111,98 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="346" t="s">
-        <v>396</v>
-      </c>
-      <c r="C134" s="339"/>
-      <c r="D134" s="339"/>
-      <c r="E134" s="339"/>
-      <c r="F134" s="339"/>
+      <c r="B134" s="348" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="343" t="s">
-        <v>400</v>
-      </c>
-      <c r="C137" s="343"/>
-      <c r="D137" s="343"/>
-      <c r="E137" s="343"/>
-      <c r="F137" s="343"/>
+      <c r="B137" s="345" t="s">
+        <v>398</v>
+      </c>
+      <c r="C137" s="345"/>
+      <c r="D137" s="345"/>
+      <c r="E137" s="345"/>
+      <c r="F137" s="345"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="244" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="244" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="340" t="s">
-        <v>401</v>
-      </c>
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
+      <c r="B143" s="342" t="s">
+        <v>399</v>
+      </c>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="345" t="s">
-        <v>402</v>
-      </c>
-      <c r="C146" s="345"/>
-      <c r="D146" s="345"/>
-      <c r="E146" s="345"/>
-      <c r="F146" s="345"/>
+      <c r="B146" s="347" t="s">
+        <v>400</v>
+      </c>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="345" t="s">
-        <v>403</v>
-      </c>
-      <c r="C147" s="345"/>
-      <c r="D147" s="345"/>
-      <c r="E147" s="345"/>
-      <c r="F147" s="345"/>
+      <c r="B147" s="347" t="s">
+        <v>401</v>
+      </c>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="244" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="244" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="244" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -5213,7 +5236,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5225,7 +5248,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5234,7 +5257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M79"/>
+  <dimension ref="B1:M80"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -5460,7 +5483,7 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="184"/>
       <c r="D10" s="184"/>
       <c r="E10" s="184"/>
       <c r="F10" s="184"/>
@@ -5698,7 +5721,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C22" s="184"/>
       <c r="D22" s="184"/>
@@ -5714,7 +5737,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C23" s="184"/>
       <c r="D23" s="184"/>
@@ -5730,7 +5753,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C24" s="184"/>
       <c r="D24" s="184"/>
@@ -5783,7 +5806,7 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="184"/>
       <c r="D28" s="184">
         <v>213823</v>
       </c>
@@ -5805,7 +5828,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="184"/>
       <c r="D29" s="184">
         <v>8852611</v>
       </c>
@@ -7003,440 +7026,455 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
+        <v>411</v>
+      </c>
+      <c r="C64" s="186">
+        <f>IF(C$4="","",C22+C23+C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="186">
+        <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="I64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="L64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="M64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
+      <c r="C65" s="75">
+        <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
         <v>1.36</v>
       </c>
-      <c r="D64" s="75">
-        <f t="shared" si="32"/>
+      <c r="D65" s="75">
+        <f t="shared" si="33"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="E64" s="75">
-        <f t="shared" si="32"/>
+      <c r="E65" s="75">
+        <f t="shared" si="33"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="F64" s="75">
-        <f t="shared" si="32"/>
+      <c r="F65" s="75">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
-      <c r="G64" s="75">
-        <f t="shared" si="32"/>
+      <c r="G65" s="75">
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
-      <c r="H64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="93" t="s">
+      <c r="H65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="I65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="L65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="M65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="str">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94">
-        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
+      <c r="C68" s="94">
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
         <v>0.27952593137796744</v>
       </c>
-      <c r="D67" s="94">
-        <f t="shared" si="33"/>
+      <c r="D68" s="94">
+        <f t="shared" si="34"/>
         <v>2.0450249505806095E-2</v>
       </c>
-      <c r="E67" s="94">
-        <f t="shared" si="33"/>
+      <c r="E68" s="94">
+        <f t="shared" si="34"/>
         <v>0.32460887665346139</v>
       </c>
-      <c r="F67" s="94">
-        <f t="shared" si="33"/>
+      <c r="F68" s="94">
+        <f t="shared" si="34"/>
         <v>-0.21118785490642455</v>
       </c>
-      <c r="G67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="82" t="str">
+      <c r="G68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="L68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="M68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="82" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104">
-        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
+      <c r="C69" s="104">
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
         <v>0.27484316281081789</v>
       </c>
-      <c r="D68" s="104">
-        <f t="shared" si="34"/>
+      <c r="D69" s="104">
+        <f t="shared" si="35"/>
         <v>2.8630254836090829E-2</v>
       </c>
-      <c r="E68" s="104">
-        <f t="shared" si="34"/>
+      <c r="E69" s="104">
+        <f t="shared" si="35"/>
         <v>0.36521892689379709</v>
       </c>
-      <c r="F68" s="104">
-        <f t="shared" si="34"/>
+      <c r="F69" s="104">
+        <f t="shared" si="35"/>
         <v>-0.21258803367720713</v>
       </c>
-      <c r="G68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="str">
+      <c r="G69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="H69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="L69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="M69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="str">
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94">
-        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
+      <c r="C70" s="94">
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
         <v>0.29220619013700166</v>
       </c>
-      <c r="D69" s="94">
-        <f t="shared" si="35"/>
+      <c r="D70" s="94">
+        <f t="shared" si="36"/>
         <v>-1.0606627998344109E-3</v>
       </c>
-      <c r="E69" s="94">
-        <f t="shared" si="35"/>
+      <c r="E70" s="94">
+        <f t="shared" si="36"/>
         <v>0.22851064557243328</v>
       </c>
-      <c r="F69" s="94">
-        <f t="shared" si="35"/>
+      <c r="F70" s="94">
+        <f t="shared" si="36"/>
         <v>-0.20785460213901807</v>
       </c>
-      <c r="G69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="I69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="82" t="str">
+      <c r="G70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="H70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="I70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="L70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="M70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B71" s="82" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104">
-        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
+      <c r="C71" s="104">
+        <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
         <v>0.23027981033619538</v>
       </c>
-      <c r="D70" s="104">
-        <f t="shared" si="36"/>
+      <c r="D71" s="104">
+        <f t="shared" si="37"/>
         <v>2.88709616106122E-2</v>
       </c>
-      <c r="E70" s="104">
-        <f t="shared" si="36"/>
+      <c r="E71" s="104">
+        <f t="shared" si="37"/>
         <v>7.1190571738822594E-2</v>
       </c>
-      <c r="F70" s="104">
-        <f t="shared" si="36"/>
+      <c r="F71" s="104">
+        <f t="shared" si="37"/>
         <v>-0.20005740582329201</v>
       </c>
-      <c r="G70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="str">
+      <c r="G71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="str">
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94">
-        <f>IF(D$36="","",C64/D64-1)</f>
+      <c r="C72" s="94">
+        <f>IF(D$36="","",C65/D65-1)</f>
         <v>0.23636363636363633</v>
       </c>
-      <c r="D71" s="94">
-        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="94">
-        <f t="shared" si="37"/>
+      <c r="D72" s="94">
+        <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="94">
+        <f t="shared" si="38"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="F71" s="94">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="36" t="s">
+      <c r="F72" s="94">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="G72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="H72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="I72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="L72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="M72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-      <c r="M73" s="37"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="9"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="78">
-        <f>IF(C$4="","",C78+C79)</f>
+      <c r="C76" s="78">
+        <f>IF(C$4="","",C79+C80)</f>
         <v>16854064</v>
       </c>
-      <c r="D75" s="78">
-        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
+      <c r="D76" s="78">
+        <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
         <v>14687373</v>
       </c>
-      <c r="E75" s="78">
-        <f t="shared" si="38"/>
+      <c r="E76" s="78">
+        <f t="shared" si="39"/>
         <v>15987114</v>
       </c>
-      <c r="F75" s="78">
-        <f t="shared" si="38"/>
+      <c r="F76" s="78">
+        <f t="shared" si="39"/>
         <v>14270996</v>
       </c>
-      <c r="G75" s="78">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="74">
+      <c r="G76" s="78">
         <f t="shared" si="39"/>
-        <v>213823</v>
-      </c>
-      <c r="E76" s="74">
+        <v>0</v>
+      </c>
+      <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>187711</v>
-      </c>
-      <c r="F76" s="74">
+        <v/>
+      </c>
+      <c r="I76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>277338</v>
-      </c>
-      <c r="G76" s="74">
+        <v/>
+      </c>
+      <c r="J76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="74" t="str">
+        <v/>
+      </c>
+      <c r="K76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="96"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
-      <c r="L76" s="96"/>
-      <c r="M76" s="96"/>
+      <c r="L76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="M76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D77" s="74">
-        <f t="shared" si="39"/>
-        <v>8852611</v>
+        <f t="shared" si="40"/>
+        <v>213823</v>
       </c>
       <c r="E77" s="74">
-        <f t="shared" si="39"/>
-        <v>8769304</v>
+        <f t="shared" si="40"/>
+        <v>187711</v>
       </c>
       <c r="F77" s="74">
-        <f t="shared" si="39"/>
-        <v>7321614</v>
+        <f t="shared" si="40"/>
+        <v>277338</v>
       </c>
       <c r="G77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7446,73 +7484,58 @@
       <c r="M77" s="96"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
-        <v>3990166</v>
-      </c>
-      <c r="D78" s="58">
+      <c r="B78" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>2466431</v>
-      </c>
-      <c r="E78" s="58">
+        <v>0</v>
+      </c>
+      <c r="D78" s="74">
         <f t="shared" si="40"/>
-        <v>3908586</v>
-      </c>
-      <c r="F78" s="58">
+        <v>8852611</v>
+      </c>
+      <c r="E78" s="74">
         <f t="shared" si="40"/>
-        <v>2946772</v>
-      </c>
-      <c r="G78" s="58">
+        <v>8769304</v>
+      </c>
+      <c r="F78" s="74">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="58" t="str">
+        <v>7321614</v>
+      </c>
+      <c r="G78" s="74">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="I78" s="58" t="str">
+        <v>0</v>
+      </c>
+      <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="J78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="I78" s="96"/>
+      <c r="J78" s="96"/>
+      <c r="K78" s="96"/>
+      <c r="L78" s="96"/>
+      <c r="M78" s="96"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
-        <v>12863898</v>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <v>3990166</v>
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
-        <v>12220942</v>
+        <v>2466431</v>
       </c>
       <c r="E79" s="58">
         <f t="shared" si="41"/>
-        <v>12078528</v>
+        <v>3908586</v>
       </c>
       <c r="F79" s="58">
         <f t="shared" si="41"/>
-        <v>11324224</v>
+        <v>2946772</v>
       </c>
       <c r="G79" s="58">
         <f t="shared" si="41"/>
@@ -7543,9 +7566,58 @@
         <v/>
       </c>
     </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B80" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="58">
+        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <v>12863898</v>
+      </c>
+      <c r="D80" s="58">
+        <f t="shared" si="42"/>
+        <v>12220942</v>
+      </c>
+      <c r="E80" s="58">
+        <f t="shared" si="42"/>
+        <v>12078528</v>
+      </c>
+      <c r="F80" s="58">
+        <f t="shared" si="42"/>
+        <v>11324224</v>
+      </c>
+      <c r="G80" s="58">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="I80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -7555,7 +7627,7 @@
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:M37 C61:M64">
+  <conditionalFormatting sqref="C36:M37 C61:M65">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
@@ -8843,7 +8915,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q808"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -11819,7 +11891,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12340,47 +12412,47 @@
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
-        <f>Data!C64</f>
+        <f>Data!C65</f>
         <v>1.36</v>
       </c>
       <c r="H90" s="116">
-        <f>Data!D64</f>
+        <f>Data!D65</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="I90" s="116">
-        <f>Data!E64</f>
+        <f>Data!E65</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="J90" s="116">
-        <f>Data!F64</f>
+        <f>Data!F65</f>
         <v>1</v>
       </c>
       <c r="K90" s="116">
-        <f>Data!G64</f>
+        <f>Data!G65</f>
         <v>1</v>
       </c>
       <c r="L90" s="116" t="str">
-        <f>Data!H64</f>
+        <f>Data!H65</f>
         <v/>
       </c>
       <c r="M90" s="116" t="str">
-        <f>Data!I64</f>
+        <f>Data!I65</f>
         <v/>
       </c>
       <c r="N90" s="116" t="str">
-        <f>Data!J64</f>
+        <f>Data!J65</f>
         <v/>
       </c>
       <c r="O90" s="116" t="str">
-        <f>Data!K64</f>
+        <f>Data!K65</f>
         <v/>
       </c>
       <c r="P90" s="116" t="str">
-        <f>Data!L64</f>
+        <f>Data!L65</f>
         <v/>
       </c>
       <c r="Q90" s="116" t="str">
-        <f>Data!M64</f>
+        <f>Data!M65</f>
         <v/>
       </c>
     </row>
@@ -12502,28 +12574,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.1152815013404831E-2</v>
+        <v>9.418282548476456E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.1152815013404831E-2</v>
+        <v>9.418282548476456E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3726541554959793E-2</v>
+        <v>7.6177285318559565E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3726541554959793E-2</v>
+        <v>7.6177285318559565E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.7024128686327081E-2</v>
+        <v>6.9252077562326875E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.7024128686327081E-2</v>
+        <v>6.9252077562326875E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -12795,47 +12867,47 @@
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
-        <f>IF(G$4="","",Data!D76)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v>213823</v>
       </c>
       <c r="H102" s="188">
-        <f>IF(H$4="","",Data!E76)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v>187711</v>
       </c>
       <c r="I102" s="188">
-        <f>IF(I$4="","",Data!F76)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v>277338</v>
       </c>
       <c r="J102" s="188">
-        <f>IF(J$4="","",Data!G76)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
       <c r="K102" s="188" t="str">
-        <f>IF(K$4="","",Data!H76)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L102" s="188" t="str">
-        <f>IF(L$4="","",Data!I76)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M102" s="188" t="str">
-        <f>IF(M$4="","",Data!J76)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N102" s="188" t="str">
-        <f>IF(N$4="","",Data!K76)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O102" s="188" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P102" s="188" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q102" s="188" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
@@ -12852,47 +12924,47 @@
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
-        <f>IF(G$4="","",Data!D77)</f>
+        <f>IF(G$4="","",Data!D78)</f>
         <v>8852611</v>
       </c>
       <c r="H103" s="188">
-        <f>IF(H$4="","",Data!E77)</f>
+        <f>IF(H$4="","",Data!E78)</f>
         <v>8769304</v>
       </c>
       <c r="I103" s="188">
-        <f>IF(I$4="","",Data!F77)</f>
+        <f>IF(I$4="","",Data!F78)</f>
         <v>7321614</v>
       </c>
       <c r="J103" s="188">
-        <f>IF(J$4="","",Data!G77)</f>
+        <f>IF(J$4="","",Data!G78)</f>
         <v>0</v>
       </c>
       <c r="K103" s="188" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
+        <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
       <c r="L103" s="188" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
+        <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
       <c r="M103" s="188" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
+        <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
       <c r="N103" s="188" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
+        <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
       <c r="O103" s="188" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
+        <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
       <c r="P103" s="188" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
+        <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
       <c r="Q103" s="188" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
@@ -12909,47 +12981,47 @@
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
-        <f>Data!C78</f>
+        <f>Data!C79</f>
         <v>3990166</v>
       </c>
       <c r="H104" s="186">
-        <f>Data!D78</f>
+        <f>Data!D79</f>
         <v>2466431</v>
       </c>
       <c r="I104" s="186">
-        <f>Data!E78</f>
+        <f>Data!E79</f>
         <v>3908586</v>
       </c>
       <c r="J104" s="186">
-        <f>Data!F78</f>
+        <f>Data!F79</f>
         <v>2946772</v>
       </c>
       <c r="K104" s="186">
-        <f>Data!G78</f>
+        <f>Data!G79</f>
         <v>0</v>
       </c>
       <c r="L104" s="186" t="str">
-        <f>Data!H78</f>
+        <f>Data!H79</f>
         <v/>
       </c>
       <c r="M104" s="186" t="str">
-        <f>Data!I78</f>
+        <f>Data!I79</f>
         <v/>
       </c>
       <c r="N104" s="186" t="str">
-        <f>Data!J78</f>
+        <f>Data!J79</f>
         <v/>
       </c>
       <c r="O104" s="186" t="str">
-        <f>Data!K78</f>
+        <f>Data!K79</f>
         <v/>
       </c>
       <c r="P104" s="186" t="str">
-        <f>Data!L78</f>
+        <f>Data!L79</f>
         <v/>
       </c>
       <c r="Q104" s="186" t="str">
-        <f>Data!M78</f>
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
@@ -12966,47 +13038,47 @@
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
-        <f>Data!C79</f>
+        <f>Data!C80</f>
         <v>12863898</v>
       </c>
       <c r="H105" s="186">
-        <f>Data!D79</f>
+        <f>Data!D80</f>
         <v>12220942</v>
       </c>
       <c r="I105" s="186">
-        <f>Data!E79</f>
+        <f>Data!E80</f>
         <v>12078528</v>
       </c>
       <c r="J105" s="186">
-        <f>Data!F79</f>
+        <f>Data!F80</f>
         <v>11324224</v>
       </c>
       <c r="K105" s="186">
-        <f>Data!G79</f>
+        <f>Data!G80</f>
         <v>0</v>
       </c>
       <c r="L105" s="186" t="str">
-        <f>Data!H79</f>
+        <f>Data!H80</f>
         <v/>
       </c>
       <c r="M105" s="186" t="str">
-        <f>Data!I79</f>
+        <f>Data!I80</f>
         <v/>
       </c>
       <c r="N105" s="186" t="str">
-        <f>Data!J79</f>
+        <f>Data!J80</f>
         <v/>
       </c>
       <c r="O105" s="186" t="str">
-        <f>Data!K79</f>
+        <f>Data!K80</f>
         <v/>
       </c>
       <c r="P105" s="186" t="str">
-        <f>Data!L79</f>
+        <f>Data!L80</f>
         <v/>
       </c>
       <c r="Q105" s="186" t="str">
-        <f>Data!M79</f>
+        <f>Data!M80</f>
         <v/>
       </c>
     </row>
@@ -13184,462 +13256,573 @@
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
-      <c r="B112" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H114*(1/#REF!)=H116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I114*(1/#REF!)=I116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J114*(1/#REF!)=J116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K114*(1/#REF!)=K116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L114*(1/#REF!)=L116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M114*(1/#REF!)=M116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N114*(1/#REF!)=N116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O114*(1/#REF!)=O116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P114*(1/#REF!)=P116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q114*(1/#REF!)=Q116,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B112" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="308"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C113" s="173"/>
+      <c r="E113" s="308"/>
+      <c r="G113" s="340">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="340">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="340">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="340">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0</v>
+      </c>
+      <c r="K113" s="340">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>0</v>
+      </c>
+      <c r="L113" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M113" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N113" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O113" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P113" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="10"/>
+      <c r="B114" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C114" s="173"/>
+      <c r="E114" s="308"/>
+      <c r="G114" s="340">
+        <f>IF(G$4="","",Data!C$22/G19)</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="340">
+        <f>IF(H$4="","",Data!D$22/H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I114" s="340">
+        <f>IF(I$4="","",Data!E$22/I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="340">
+        <f>IF(J$4="","",Data!F$22/J19)</f>
+        <v>0</v>
+      </c>
+      <c r="K114" s="340">
+        <f>IF(K$4="","",Data!G$22/K19)</f>
+        <v>0</v>
+      </c>
+      <c r="L114" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/L19)</f>
+        <v/>
+      </c>
+      <c r="M114" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/M19)</f>
+        <v/>
+      </c>
+      <c r="N114" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/N19)</f>
+        <v/>
+      </c>
+      <c r="O114" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/O19)</f>
+        <v/>
+      </c>
+      <c r="P114" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/P19)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Q19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="10"/>
+      <c r="E115" s="308"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10"/>
+      <c r="B116" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
+      <c r="E116" s="311"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10"/>
+      <c r="B117" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C113" s="23">
+      <c r="C117" s="23">
         <f>C81</f>
         <v>0.11295218450174714</v>
       </c>
-      <c r="E113" s="308"/>
-      <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="45">G81</f>
+      <c r="E117" s="308"/>
+      <c r="G117" s="23">
+        <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.10561163722631718</v>
       </c>
-      <c r="H113" s="23">
+      <c r="H117" s="23">
         <f t="shared" si="45"/>
         <v>0.13551727555376153</v>
       </c>
-      <c r="I113" s="23">
+      <c r="I117" s="23">
         <f t="shared" si="45"/>
         <v>0.1207419094893139</v>
       </c>
-      <c r="J113" s="23">
+      <c r="J117" s="23">
         <f t="shared" si="45"/>
         <v>0.14907613337736625</v>
       </c>
-      <c r="K113" s="23">
+      <c r="K117" s="23">
         <f t="shared" si="45"/>
         <v>0.10354981174708565</v>
       </c>
-      <c r="L113" s="23" t="str">
+      <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="M113" s="23" t="str">
+      <c r="M117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="N113" s="23" t="str">
+      <c r="N117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="O113" s="23" t="str">
+      <c r="O117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="P113" s="23" t="str">
+      <c r="P117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="Q113" s="23" t="str">
+      <c r="Q117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C114" s="42">
+      <c r="C118" s="42">
         <f>C4/C101</f>
         <v>0.71055479556740742</v>
       </c>
-      <c r="E114" s="308"/>
-      <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
+      <c r="E118" s="308"/>
+      <c r="G118" s="42">
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.90933332162498015</v>
       </c>
-      <c r="H114" s="42">
+      <c r="H118" s="42">
         <f t="shared" si="46"/>
         <v>0.81551983462257005</v>
       </c>
-      <c r="I114" s="42">
+      <c r="I118" s="42">
         <f t="shared" si="46"/>
         <v>0.73420399704411943</v>
       </c>
-      <c r="J114" s="42">
+      <c r="J118" s="42">
         <f t="shared" si="46"/>
         <v>0.62093318504188499</v>
       </c>
-      <c r="K114" s="42" t="e">
+      <c r="K118" s="42" t="e">
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L114" s="42" t="str">
+      <c r="L118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="M114" s="42" t="str">
+      <c r="M118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="N114" s="42" t="str">
+      <c r="N118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="O114" s="42" t="str">
+      <c r="O118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="P114" s="42" t="str">
+      <c r="P118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="Q114" s="42" t="str">
+      <c r="Q118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C119" s="15">
         <f>C101/C105</f>
         <v>1.3101832741522048</v>
       </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="312"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D119" s="11"/>
+      <c r="E119" s="312"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="15">
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.3101832741522048</v>
       </c>
-      <c r="H115" s="15">
+      <c r="H119" s="15">
         <f t="shared" si="47"/>
         <v>1.2018200397317982</v>
       </c>
-      <c r="I115" s="15">
+      <c r="I119" s="15">
         <f t="shared" si="47"/>
         <v>1.3235978755027102</v>
       </c>
-      <c r="J115" s="15">
+      <c r="J119" s="15">
         <f t="shared" si="47"/>
         <v>1.2602184485223888</v>
       </c>
-      <c r="K115" s="15" t="e">
+      <c r="K119" s="15" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L115" s="15" t="str">
+      <c r="L119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="M115" s="15" t="str">
+      <c r="M119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="N115" s="15" t="str">
+      <c r="N119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O115" s="15" t="str">
+      <c r="O119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P115" s="15" t="str">
+      <c r="P119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q115" s="15" t="str">
+      <c r="Q119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="10"/>
-      <c r="B116" s="71" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="10"/>
+      <c r="B120" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="C116" s="105">
+      <c r="C120" s="105">
         <f>C8/C105</f>
         <v>0.10871779326358874</v>
       </c>
-      <c r="D116" s="106"/>
-      <c r="E116" s="311"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
+      <c r="D120" s="106"/>
+      <c r="E120" s="311"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="105">
+        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
         <v>0.14589458032083277</v>
       </c>
-      <c r="H116" s="105">
+      <c r="H120" s="105">
         <f t="shared" si="48"/>
         <v>0.11152020850765841</v>
       </c>
-      <c r="I116" s="105">
+      <c r="I120" s="105">
         <f t="shared" si="48"/>
         <v>0.1174576902086082</v>
       </c>
-      <c r="J116" s="105">
+      <c r="J120" s="105">
         <f t="shared" si="48"/>
         <v>8.2816712209154458E-2</v>
       </c>
-      <c r="K116" s="105" t="e">
+      <c r="K120" s="105" t="e">
         <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L116" s="105" t="str">
+      <c r="L120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="M116" s="105" t="str">
+      <c r="M120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="N116" s="105" t="str">
+      <c r="N120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="O116" s="105" t="str">
+      <c r="O120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="P116" s="105" t="str">
+      <c r="P120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="Q116" s="105" t="str">
+      <c r="Q120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="10"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="54" t="s">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="10"/>
+      <c r="B122" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="C118" s="54"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="67" t="s">
+      <c r="C122" s="54"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="F118" s="56"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
-      <c r="K118" s="37"/>
-      <c r="L118" s="37"/>
-      <c r="M118" s="37"/>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
-    </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="10"/>
-      <c r="B119" s="182" t="s">
+      <c r="F122" s="56"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="C119" s="183"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="305"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
-    </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="10"/>
-      <c r="B120" s="27" t="str">
+      <c r="C123" s="183"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="305"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10"/>
+      <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="181">
+      <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
         <v>1.7279860193696295</v>
       </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="305"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="181">
-        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="D124" s="27"/>
+      <c r="E124" s="305"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="181">
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>2.1996536733213881</v>
       </c>
-      <c r="H120" s="181">
+      <c r="H124" s="181">
         <f t="shared" si="49"/>
         <v>2.2867021551286859</v>
       </c>
-      <c r="I120" s="181">
+      <c r="I124" s="181">
         <f t="shared" si="49"/>
         <v>1.9177886097578105</v>
       </c>
-      <c r="J120" s="181">
+      <c r="J124" s="181">
         <f t="shared" si="49"/>
         <v>1.8444848904022044</v>
       </c>
-      <c r="K120" s="181">
+      <c r="K124" s="181">
         <f t="shared" si="49"/>
         <v>1.5985289112722136</v>
       </c>
-      <c r="L120" s="181" t="str">
+      <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="181" t="str">
+      <c r="M124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="181" t="str">
+      <c r="N124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="181" t="str">
+      <c r="O124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="181" t="str">
+      <c r="P124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="181" t="str">
+      <c r="Q124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27" t="s">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10"/>
+      <c r="B125" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="79">
+      <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11581675733040411</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="305"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="79">
-        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>0.14742987086604478</v>
-      </c>
-      <c r="H121" s="79">
-        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>0.15326421951264652</v>
-      </c>
-      <c r="I121" s="79">
-        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>0.12853811057357981</v>
-      </c>
-      <c r="J121" s="79">
-        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.12362499265430324</v>
-      </c>
-      <c r="K121" s="79">
-        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>0.10714000745792317</v>
-      </c>
-      <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>0.11966662184000204</v>
+      </c>
+      <c r="D125" s="27"/>
+      <c r="E125" s="305"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="79">
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <v>0.15233058679510997</v>
+      </c>
+      <c r="H125" s="79">
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <v>0.15835887500891177</v>
+      </c>
+      <c r="I125" s="79">
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <v>0.1328108455510949</v>
+      </c>
+      <c r="J125" s="79">
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <v>0.12773441069267344</v>
+      </c>
+      <c r="K125" s="79">
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <v>0.11070144814904527</v>
+      </c>
+      <c r="L125" s="79" t="str">
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M125" s="79" t="str">
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N125" s="79" t="str">
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O125" s="79" t="str">
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P125" s="79" t="str">
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="79" t="str">
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14319,6 +14502,10 @@
     <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14418,10 +14605,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="347" t="s">
+      <c r="E6" s="349" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="347"/>
+      <c r="F6" s="349"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14436,8 +14623,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14452,8 +14639,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14468,8 +14655,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15899,7 +16086,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-14.92</v>
+        <v>-14.44</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15963,11 +16150,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="349" t="str">
+      <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="349"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15988,8 +16175,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -16010,8 +16197,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -16021,8 +16208,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -16035,8 +16222,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="349"/>
-      <c r="F11" s="349"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -16054,8 +16241,8 @@
         <v>0.20035451325595277</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -16072,8 +16259,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="349"/>
-      <c r="F13" s="349"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -16090,8 +16277,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0457013634429568E-2</v>
       </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16117,21 +16304,21 @@
       <c r="C18" s="154">
         <v>5</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="351" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="350"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="350"/>
-      <c r="F19" s="350"/>
+      <c r="E19" s="352"/>
+      <c r="F19" s="352"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="350"/>
-      <c r="F20" s="350"/>
+      <c r="E20" s="352"/>
+      <c r="F20" s="352"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16139,14 +16326,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>14.92</v>
+        <v>14.44</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="350"/>
-      <c r="F21" s="350"/>
+      <c r="E21" s="352"/>
+      <c r="F21" s="352"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16160,8 +16347,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16181,8 +16368,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
+      <c r="E25" s="350"/>
+      <c r="F25" s="350"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -16192,8 +16379,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
+      <c r="E26" s="350"/>
+      <c r="F26" s="350"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16207,8 +16394,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="348"/>
-      <c r="F27" s="348"/>
+      <c r="E27" s="350"/>
+      <c r="F27" s="350"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16218,8 +16405,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="348"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16239,8 +16426,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -16250,8 +16437,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16265,8 +16452,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="348"/>
-      <c r="F33" s="348"/>
+      <c r="E33" s="350"/>
+      <c r="F33" s="350"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16276,8 +16463,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="350"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16297,8 +16484,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -16308,8 +16495,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="348"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16323,8 +16510,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="348"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16335,8 +16522,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16398,8 +16585,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="348"/>
-      <c r="F49" s="348"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16409,8 +16596,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16424,8 +16611,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16435,8 +16622,8 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16456,8 +16643,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="348"/>
-      <c r="F55" s="348"/>
+      <c r="E55" s="350"/>
+      <c r="F55" s="350"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16467,8 +16654,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
+      <c r="E56" s="350"/>
+      <c r="F56" s="350"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16482,8 +16669,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="348"/>
-      <c r="F57" s="348"/>
+      <c r="E57" s="350"/>
+      <c r="F57" s="350"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16493,8 +16680,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16736,7 +16923,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>14.92</v>
+        <v>14.44</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16749,7 +16936,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19458617050699911</v>
+        <v>0.20871253483792285</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5049DDF6-00B3-4E8A-A3BA-0FACC872942B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586920ED-204C-4009-9E11-1594CA078AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="415">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2315,6 +2315,10 @@
   </si>
   <si>
     <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Income/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -4072,10 +4076,10 @@
         <v>328</v>
       </c>
       <c r="C5" s="339" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -5800,13 +5804,13 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="100"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="184"/>
+      <c r="C28" s="186"/>
       <c r="D28" s="184">
         <v>213823</v>
       </c>
@@ -5828,7 +5832,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="184"/>
+      <c r="C29" s="186"/>
       <c r="D29" s="184">
         <v>8852611</v>
       </c>
@@ -5850,7 +5854,7 @@
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="185">
+      <c r="C30" s="189">
         <v>3990166</v>
       </c>
       <c r="D30" s="185">
@@ -5874,7 +5878,7 @@
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="185">
+      <c r="C31" s="189">
         <v>12863898</v>
       </c>
       <c r="D31" s="185">
@@ -5898,7 +5902,7 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184"/>
+      <c r="C32" s="186"/>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -7632,7 +7636,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13823,7 +13827,56 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C126" s="173"/>
+      <c r="G126" s="23">
+        <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.20846177228985796</v>
+      </c>
+      <c r="H126" s="23">
+        <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.15154301107154738</v>
+      </c>
+      <c r="I126" s="23">
+        <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.16423575280588001</v>
+      </c>
+      <c r="J126" s="23">
+        <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.11999935331620895</v>
+      </c>
+      <c r="K126" s="23">
+        <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.102185848091466</v>
+      </c>
+      <c r="L126" s="23" t="str">
+        <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="M126" s="23" t="str">
+        <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="N126" s="23" t="str">
+        <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="O126" s="23" t="str">
+        <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="P126" s="23" t="str">
+        <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="23" t="str">
+        <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+    </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{586920ED-204C-4009-9E11-1594CA078AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14CE718-A305-4EFE-9D08-98A51B582F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="416">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2328,6 +2328,9 @@
   <si>
     <t>0590.HK</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -4109,7 +4112,7 @@
         <v>318</v>
       </c>
       <c r="C8" s="285">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
@@ -4120,7 +4123,7 @@
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45716</v>
+        <v>45808</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -4204,7 +4207,7 @@
         <v>280</v>
       </c>
       <c r="C19" s="255">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -4215,7 +4218,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>14.733437767356989</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -5041,7 +5044,7 @@
       </c>
       <c r="C123" s="256">
         <f>C19</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5069,7 +5072,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>2.8648148148148147</v>
+        <v>2.6547200000000002</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5079,7 +5082,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>11.868622952542175</v>
+        <v>10.500597996540353</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5088,7 +5091,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>14.733437767356989</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5101,7 +5104,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.28161042453275964</v>
+        <v>0.35855816816834396</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5804,13 +5807,18 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="100"/>
+      <c r="C27" s="100" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="186">
+        <f>BS!C4</f>
+        <v>265773</v>
+      </c>
       <c r="D28" s="184">
         <v>213823</v>
       </c>
@@ -5832,7 +5840,10 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="186">
+        <f>BS!C6</f>
+        <v>9672256</v>
+      </c>
       <c r="D29" s="184">
         <v>8852611</v>
       </c>
@@ -5855,6 +5866,7 @@
         <v>40</v>
       </c>
       <c r="C30" s="189">
+        <f>BS!C33+BS!C42</f>
         <v>3990166</v>
       </c>
       <c r="D30" s="185">
@@ -5879,6 +5891,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="189">
+        <f>BS!G27</f>
         <v>12863898</v>
       </c>
       <c r="D31" s="185">
@@ -5902,7 +5915,10 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="186"/>
+      <c r="C32" s="186">
+        <f>BS!G28</f>
+        <v>-26962</v>
+      </c>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -7459,7 +7475,7 @@
       </c>
       <c r="C77" s="74">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>0</v>
+        <v>265773</v>
       </c>
       <c r="D77" s="74">
         <f t="shared" si="40"/>
@@ -7493,7 +7509,7 @@
       </c>
       <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>9672256</v>
       </c>
       <c r="D78" s="74">
         <f t="shared" si="40"/>
@@ -7667,11 +7683,11 @@
         <v>37</v>
       </c>
       <c r="C1" s="102">
-        <v>45473</v>
+        <v>45381</v>
       </c>
       <c r="F1" s="88" t="str">
         <f>IF(MONTH(C1)=MONTH(Normalized_FCF!G1),"FY","Quarter")&amp;" Report"</f>
-        <v>Quarter Report</v>
+        <v>FY Report</v>
       </c>
       <c r="H1" s="110">
         <f>Data!C3</f>
@@ -16917,7 +16933,7 @@
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
@@ -16926,7 +16942,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.8648148148148147</v>
+        <v>2.6547200000000002</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16938,7 +16954,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>11.868622952542175</v>
+        <v>10.500597996540353</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16948,7 +16964,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>14.733437767356989</v>
+        <v>13.155317996540354</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16959,7 +16975,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.28161042453275964</v>
+        <v>0.35855816816834396</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE05C35-2376-446C-A2FF-7632CEC556C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841766C2-017E-4CB8-9BA4-917F9F8ADF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1557,10 +1557,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,6 +2327,10 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="284" t="s">
         <v>291</v>
@@ -4061,13 +4061,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>413</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>14.44</v>
+        <v>15.32</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8477.8373539999993</v>
+        <v>8994.4922619999998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="338" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C12" s="338"/>
       <c r="D12" s="338"/>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4214,11 +4214,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20871253483792285</v>
+        <v>0.18329188684945863</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C25" s="338"/>
       <c r="D25" s="338"/>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="341" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C26" s="341"/>
       <c r="D26" s="341"/>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="339" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C50" s="340"/>
       <c r="D50" s="340"/>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="338" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C53" s="338"/>
       <c r="D53" s="338"/>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="338" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C54" s="338"/>
       <c r="D54" s="338"/>
@@ -4507,11 +4507,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11966662184000204</v>
+        <v>0.11279282110767816</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.418282548476456E-2</v>
+        <v>8.877284595300261E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,7 +4539,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,13 +4606,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="338" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C73" s="338"/>
       <c r="D73" s="338"/>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C74" s="338"/>
       <c r="D74" s="338"/>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="338" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C81" s="338"/>
       <c r="D81" s="338"/>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="338" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C85" s="338"/>
       <c r="D85" s="338"/>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="338" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C98" s="338"/>
       <c r="D98" s="338"/>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="339" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C104" s="339"/>
       <c r="D104" s="339"/>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="342" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C115" s="342"/>
       <c r="D115" s="342"/>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="343" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C119" s="343"/>
       <c r="D119" s="343"/>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="338" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C120" s="338"/>
       <c r="D120" s="338"/>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B134" s="337" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C134" s="338"/>
       <c r="D134" s="338"/>
@@ -5113,12 +5113,12 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="340" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C137" s="340"/>
       <c r="D137" s="340"/>
@@ -5127,27 +5127,27 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="339" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C143" s="339"/>
       <c r="D143" s="339"/>
@@ -5156,12 +5156,12 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="336" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C146" s="336"/>
       <c r="D146" s="336"/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="336" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C147" s="336"/>
       <c r="D147" s="336"/>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5729,7 +5729,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5745,7 +5745,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5793,7 +5793,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7032,7 +7032,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8679,7 +8679,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8691,7 +8691,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8702,12 +8702,12 @@
         <v>-947972.33938934223</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8718,12 +8718,12 @@
         <v>2.1078874530107048</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8731,12 +8731,12 @@
         <v>947972.33938934223</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8744,7 +8744,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10298,7 +10298,7 @@
         <v>-302359.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10803,7 +10803,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10858,7 +10858,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10991,7 +10991,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11018,7 +11018,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11333,7 +11333,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12577,28 +12577,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.418282548476456E-2</v>
+        <v>8.877284595300261E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.418282548476456E-2</v>
+        <v>8.877284595300261E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6177285318559565E-2</v>
+        <v>7.1801566579634463E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6177285318559565E-2</v>
+        <v>7.1801566579634463E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9252077562326875E-2</v>
+        <v>6.5274151436031325E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9252077562326875E-2</v>
+        <v>6.5274151436031325E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13267,7 +13267,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13319,7 +13319,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13776,30 +13776,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11966662184000204</v>
+        <v>0.11279282110767816</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.15233058679510997</v>
+        <v>0.14358052697920287</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.15835887500891177</v>
+        <v>0.14926254276296905</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1328108455510949</v>
+        <v>0.12518202413562732</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12773441069267344</v>
+        <v>0.12039718605758515</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.11070144814904527</v>
+        <v>0.10434261822925676</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13828,28 +13828,28 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20846177228985796</v>
+        <v>0.19648746683195489</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15154301107154738</v>
+        <v>0.14283819059224179</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16423575280588001</v>
+        <v>0.15480184533400179</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11999935331620895</v>
+        <v>0.11310644007089146</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.102185848091466</v>
+        <v>9.6316164911277341E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>20.512359193543752</v>
+        <v>20.510149835892964</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14833,11 +14833,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>1021007.684834131</v>
+        <v>1027097.8781909549</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>945377.48595752858</v>
+        <v>951016.55388051365</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14855,11 +14855,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>1027542.7756672456</v>
+        <v>1039837.6843307657</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>880952.31110017619</v>
+        <v>891493.21358947677</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14877,11 +14877,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>1034119.6951886564</v>
+        <v>1052735.5111070964</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>820917.55511470581</v>
+        <v>835695.38998365996</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14899,11 +14899,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>1040738.7111282558</v>
+        <v>1065793.3185593141</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>764974.02164017234</v>
+        <v>783389.90605209605</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14921,11 +14921,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>1047400.0929295756</v>
+        <v>1079013.0910385123</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -14933,7 +14933,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>712842.90381946054</v>
+        <v>734358.17914026265</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14943,19 +14943,19 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>1054104.1117607555</v>
+        <v>0</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>0</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>664264.39480422158</v>
+        <v>0</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14965,19 +14965,19 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>1060851.0405255819</v>
+        <v>0</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>0</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>618996.39295051782</v>
+        <v>0</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -14987,19 +14987,19 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>1067641.1538745963</v>
+        <v>0</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>0</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>576813.29525223037</v>
+        <v>0</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15009,19 +15009,19 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>1074474.7282162774</v>
+        <v>0</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>537504.87299904798</v>
+        <v>0</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15031,19 +15031,19 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>1081352.041728291</v>
+        <v>0</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>6.4006284479398504E-3</v>
+        <v>0</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>500875.22405562212</v>
+        <v>0</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>12762596.060426638</v>
+        <v>12838723.477386937</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15501,11 +15501,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.68058319703375303</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>5911551.3862448642</v>
+        <v>8737819.4700723048</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>12935069.843938548</v>
+        <v>12933772.712718314</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15537,7 +15537,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>12935069.843938548</v>
+        <v>12933772.712718314</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.44</v>
+        <v>-15.32</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16346,7 +16346,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16357,7 +16357,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -16378,7 +16378,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.44</v>
+        <v>15.32</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16679,7 +16679,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16757,7 +16757,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16777,11 +16777,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
-        <v>10</v>
+        <f>C18</f>
+        <v>5</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16789,11 +16790,11 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>6.4006284479398504E-3</v>
+        <v>1.2403692394194735E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16802,22 +16803,22 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>20.512359193543752</v>
+        <v>20.510149835892964</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16861,7 +16862,7 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16975,7 +16976,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.44</v>
+        <v>15.32</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16988,7 +16989,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20871253483792285</v>
+        <v>0.18329188684945863</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16996,7 +16997,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -17004,30 +17005,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841766C2-017E-4CB8-9BA4-917F9F8ADF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE779868-9529-4901-A5E7-489397719D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2318,6 +2318,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>六福珠宝</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2327,10 +2331,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,10 +4064,10 @@
         <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>15.32</v>
+        <v>15.3</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8994.4922619999998</v>
+        <v>8982.7501049999992</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18329188684945863</v>
+        <v>0.18384675850766619</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11279282110767816</v>
+        <v>0.11294026270389734</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>8.877284595300261E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>384</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>387</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>386</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>400</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5793,7 +5793,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -10811,11 +10811,11 @@
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>13746.938888322537</v>
       </c>
       <c r="H48" s="328">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>15714.785887969218</v>
       </c>
       <c r="I48" s="328">
@@ -11110,7 +11110,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11220,7 +11220,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -12577,28 +12577,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.877284595300261E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.877284595300261E-2</v>
+        <v>8.8888888888888892E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1801566579634463E-2</v>
+        <v>7.1895424836601315E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1801566579634463E-2</v>
+        <v>7.1895424836601315E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5274151436031325E-2</v>
+        <v>6.535947712418301E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.5274151436031325E-2</v>
+        <v>6.535947712418301E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13776,30 +13776,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11279282110767816</v>
+        <v>0.11294026270389734</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14358052697920287</v>
+        <v>0.14376821394257439</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14926254276296905</v>
+        <v>0.14945765719795331</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.12518202413562732</v>
+        <v>0.12534566076848433</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12039718605758515</v>
+        <v>0.12055456800014408</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10434261822925676</v>
+        <v>0.10447901380864141</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13833,23 +13833,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19648746683195489</v>
+        <v>0.19674431319382674</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14283819059224179</v>
+        <v>0.14302490718125127</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15480184533400179</v>
+        <v>0.15500420068737958</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11310644007089146</v>
+        <v>0.11325429162653969</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6316164911277341E-2</v>
+        <v>9.6442068394821501E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14859,7 +14859,7 @@
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14881,7 +14881,7 @@
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.32</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.32</v>
+        <v>15.3</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16782,7 +16782,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16790,7 +16790,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>1.2403692394194735E-2</v>
+        <v>1.24036923941947E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.32</v>
+        <v>15.3</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16989,7 +16989,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18329188684945863</v>
+        <v>0.18384675850766619</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE779868-9529-4901-A5E7-489397719D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C131A-7408-439C-9A85-361A3B4AEEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>15.3</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>8982.7501049999992</v>
+        <v>9640.3108970000012</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18384675850766619</v>
+        <v>0.15425024630514339</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.11294026270389734</v>
+        <v>0.1052366637862137</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>8.8888888888888892E-2</v>
+        <v>8.282582216808769E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>387</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>386</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>400</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,17 +5199,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,6 +5215,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12577,28 +12577,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.8888888888888892E-2</v>
+        <v>8.282582216808769E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.8888888888888892E-2</v>
+        <v>8.282582216808769E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1895424836601315E-2</v>
+        <v>6.6991473812423874E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1895424836601315E-2</v>
+        <v>6.6991473812423874E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.535947712418301E-2</v>
+        <v>6.0901339829476243E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.535947712418301E-2</v>
+        <v>6.0901339829476243E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13776,30 +13776,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.11294026270389734</v>
+        <v>0.1052366637862137</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.14376821394257439</v>
+        <v>0.13396185586610157</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14945765719795331</v>
+        <v>0.13926322503828781</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.12534566076848433</v>
+        <v>0.11679589584395922</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.12055456800014408</v>
+        <v>0.1123316011207189</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.10447901380864141</v>
+        <v>9.735255245263176E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13833,23 +13833,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.19674431319382674</v>
+        <v>0.18332448184321246</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14302490718125127</v>
+        <v>0.1332692496877676</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15500420068737958</v>
+        <v>0.14443144156619411</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.11325429162653969</v>
+        <v>0.10552927295286582</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6442068394821501E-2</v>
+        <v>8.9863803071910386E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.3</v>
+        <v>-16.420000000000002</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.3</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.3</v>
+        <v>16.420000000000002</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16989,7 +16989,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18384675850766619</v>
+        <v>0.15425024630514339</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87C131A-7408-439C-9A85-361A3B4AEEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53469FB-2410-40AF-B1EF-0C9CC64640B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>16.420000000000002</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>9640.3108970000012</v>
+        <v>9652.053054</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15425024630514339</v>
+        <v>0.15374754303551685</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1052366637862137</v>
+        <v>0.10510863864778767</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>8.282582216808769E-2</v>
+        <v>8.2725060827250604E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>384</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>387</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>386</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>400</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12577,28 +12577,28 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>8.282582216808769E-2</v>
+        <v>8.2725060827250604E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>8.282582216808769E-2</v>
+        <v>8.2725060827250604E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6991473812423874E-2</v>
+        <v>6.6909975669099758E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.6991473812423874E-2</v>
+        <v>6.6909975669099758E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0901339829476243E-2</v>
+        <v>6.0827250608272501E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>6.0901339829476243E-2</v>
+        <v>6.0827250608272501E-2</v>
       </c>
       <c r="L93" s="23" t="str">
         <f t="shared" si="39"/>
@@ -13776,30 +13776,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1052366637862137</v>
+        <v>0.10510863864778767</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.13396185586610157</v>
+        <v>0.13379888523852723</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.13926322503828781</v>
+        <v>0.13909380505648941</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11679589584395922</v>
+        <v>0.11665380837942886</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1123316011207189</v>
+        <v>0.11219494467166692</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>9.735255245263176E-2</v>
+        <v>9.7234118690523938E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13833,23 +13833,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.18332448184321246</v>
+        <v>0.18310145935921832</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1332692496877676</v>
+        <v>0.13310712164678493</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14443144156619411</v>
+        <v>0.1442557342163569</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10552927295286582</v>
+        <v>0.1054008918422176</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9863803071910386E-2</v>
+        <v>8.9754479710509052E-2</v>
       </c>
       <c r="L126" s="23" t="str">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-16.420000000000002</v>
+        <v>-16.440000000000001</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>16.420000000000002</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>16.420000000000002</v>
+        <v>16.440000000000001</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16989,7 +16989,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15425024630514339</v>
+        <v>0.15374754303551685</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53469FB-2410-40AF-B1EF-0C9CC64640B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7ACB445-C7E4-4F4E-B538-C36DAFA5E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1829,14 +1825,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2319,6 +2307,45 @@
   </si>
   <si>
     <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3004,7 +3031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3697,6 +3724,9 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4009,7 +4039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4029,15 +4059,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4061,13 +4091,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4094,7 +4124,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>12</v>
@@ -4104,7 +4134,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4130,24 +4160,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="337" t="s">
+        <v>373</v>
+      </c>
+      <c r="C12" s="337"/>
+      <c r="D12" s="337"/>
+      <c r="E12" s="337"/>
+      <c r="F12" s="337"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,7 +4187,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4183,18 +4213,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4206,7 +4241,7 @@
         <v>13.155317996540354</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4214,7 +4249,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4229,7 +4264,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4238,22 +4273,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="337" t="s">
+        <v>374</v>
+      </c>
+      <c r="C25" s="337"/>
+      <c r="D25" s="337"/>
+      <c r="E25" s="337"/>
+      <c r="F25" s="337"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="339" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="339"/>
+      <c r="D26" s="339"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4300,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="338" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4326,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4361,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="338" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,17 +4383,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4373,7 +4408,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4406,7 +4441,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4418,13 +4453,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="338" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,13 +4475,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="338" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4462,26 +4497,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="337" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="337"/>
+      <c r="D53" s="337"/>
+      <c r="E53" s="337"/>
+      <c r="F53" s="337"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="337" t="s">
+        <v>375</v>
+      </c>
+      <c r="C54" s="337"/>
+      <c r="D54" s="337"/>
+      <c r="E54" s="337"/>
+      <c r="F54" s="337"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4507,7 +4542,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4516,7 +4551,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4525,7 +4560,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4538,22 +4573,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="337" t="s">
+        <v>376</v>
+      </c>
+      <c r="C63" s="337"/>
+      <c r="D63" s="337"/>
+      <c r="E63" s="337"/>
+      <c r="F63" s="337"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="339" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="339"/>
+      <c r="D64" s="339"/>
+      <c r="E64" s="339"/>
+      <c r="F64" s="339"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4562,7 +4597,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4570,26 +4605,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,27 +4641,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="337" t="s">
+        <v>377</v>
+      </c>
+      <c r="C73" s="337"/>
+      <c r="D73" s="337"/>
+      <c r="E73" s="337"/>
+      <c r="F73" s="337"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="337" t="s">
+        <v>378</v>
+      </c>
+      <c r="C74" s="337"/>
+      <c r="D74" s="337"/>
+      <c r="E74" s="337"/>
+      <c r="F74" s="337"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4638,7 +4673,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4651,7 +4686,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4663,13 +4698,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>382</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="337" t="s">
+        <v>379</v>
+      </c>
+      <c r="C81" s="337"/>
+      <c r="D81" s="337"/>
+      <c r="E81" s="337"/>
+      <c r="F81" s="337"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4717,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="337" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="337"/>
+      <c r="D85" s="337"/>
+      <c r="E85" s="337"/>
+      <c r="F85" s="337"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4705,7 +4740,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4723,7 +4758,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4736,7 +4771,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4749,7 +4784,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4780,7 +4815,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4792,17 +4827,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>383</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="337" t="s">
+        <v>380</v>
+      </c>
+      <c r="C98" s="337"/>
+      <c r="D98" s="337"/>
+      <c r="E98" s="337"/>
+      <c r="F98" s="337"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4815,7 +4850,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4824,13 +4859,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>384</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="338" t="s">
+        <v>381</v>
+      </c>
+      <c r="C104" s="338"/>
+      <c r="D104" s="338"/>
+      <c r="E104" s="338"/>
+      <c r="F104" s="338"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,17 +5008,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="342" t="s">
+        <v>384</v>
+      </c>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>374</v>
+        <v>419</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4992,22 +5027,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>385</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="340" t="s">
+        <v>382</v>
+      </c>
+      <c r="C119" s="340"/>
+      <c r="D119" s="340"/>
+      <c r="E119" s="340"/>
+      <c r="F119" s="340"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>386</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="337" t="s">
+        <v>383</v>
+      </c>
+      <c r="C120" s="337"/>
+      <c r="D120" s="337"/>
+      <c r="E120" s="337"/>
+      <c r="F120" s="337"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5016,7 +5051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5025,7 +5060,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5047,7 +5082,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>416</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5092,118 +5127,165 @@
         <v>0.35855816816834396</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>3.8138683808049407</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>18.52475983870195</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>22.338628219506891</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-8.9212028891670458E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>388</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="344" t="s">
+        <v>390</v>
+      </c>
+      <c r="C140" s="337"/>
+      <c r="D140" s="337"/>
+      <c r="E140" s="337"/>
+      <c r="F140" s="337"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>394</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>391</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="338" t="s">
+        <v>395</v>
+      </c>
+      <c r="C149" s="338"/>
+      <c r="D149" s="338"/>
+      <c r="E149" s="338"/>
+      <c r="F149" s="338"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="343" t="s">
+        <v>396</v>
+      </c>
+      <c r="C152" s="343"/>
+      <c r="D152" s="343"/>
+      <c r="E152" s="343"/>
+      <c r="F152" s="343"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>397</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>398</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>402</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>399</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>400</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>405</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B104:F104"/>
     <mergeCell ref="B73:F73"/>
@@ -5228,7 +5310,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5713,7 +5795,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5729,7 +5811,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5745,7 +5827,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5793,7 +5875,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7032,7 +7114,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8400,13 +8482,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8414,7 +8496,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8567,7 +8649,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8590,7 +8672,7 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8612,7 +8694,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8679,7 +8761,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8691,7 +8773,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8702,12 +8784,12 @@
         <v>-947972.33938934223</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8718,12 +8800,12 @@
         <v>2.1078874530107048</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8731,12 +8813,12 @@
         <v>947972.33938934223</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8744,7 +8826,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8820,7 +8902,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8831,15 +8913,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8856,7 +8938,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8890,7 +8972,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9761,7 +9843,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9786,7 +9868,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10114,7 +10196,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10174,7 +10256,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10298,7 +10380,7 @@
         <v>-302359.25</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10356,7 +10438,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10664,7 +10746,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10803,7 +10885,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10858,7 +10940,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10991,7 +11073,7 @@
         <v>1.4501413508729523E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11018,7 +11100,7 @@
         <v>2.9286626219579916E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11333,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11894,7 +11976,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12573,7 +12655,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13267,7 +13349,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13319,7 +13401,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13772,7 +13854,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13828,7 +13910,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14657,10 +14739,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14675,8 +14757,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14691,8 +14773,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14707,8 +14789,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16053,7 +16135,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16105,7 +16187,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16125,7 +16207,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16179,7 +16261,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16192,7 +16274,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16202,11 +16284,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 六福珠宝(0590.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16227,8 +16309,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16249,8 +16331,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16260,8 +16342,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16272,10 +16354,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16293,8 +16375,8 @@
         <v>0.20035451325595277</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16311,8 +16393,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.26016796976901468</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16329,8 +16411,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>6.0457013634429568E-2</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16346,7 +16428,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16356,25 +16438,25 @@
       <c r="C18" s="151">
         <v>5</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16384,12 +16466,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16399,8 +16481,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16420,8 +16502,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16431,8 +16513,8 @@
         <v>0.02</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16446,8 +16528,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16457,8 +16539,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16478,8 +16560,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16489,8 +16571,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16504,8 +16586,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16515,8 +16597,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16536,8 +16618,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16547,8 +16629,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16562,8 +16644,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16574,8 +16656,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16637,8 +16719,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16648,8 +16730,8 @@
         <v>-0.08</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16663,8 +16745,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16674,12 +16756,12 @@
         <v>0.02</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16695,8 +16777,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16706,8 +16788,8 @@
         <v>0.06</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16721,8 +16803,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16732,8 +16814,8 @@
         <v>0.02</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16748,7 +16830,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16757,7 +16839,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16766,10 +16848,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16782,7 +16864,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16794,7 +16876,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16810,20 +16892,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16833,19 +16915,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16855,14 +16937,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16885,7 +16967,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16908,12 +16990,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -16967,12 +17049,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -16985,7 +17067,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16995,43 +17077,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>413</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>3.8138683808049407</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>18.52475983870195</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>414</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>22.338628219506891</v>
+      </c>
+      <c r="D93" t="s">
+        <v>411</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-8.9212028891670458E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0590.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0590.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7ACB445-C7E4-4F4E-B538-C36DAFA5E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002C7C4B-F7A3-48A4-B33E-D51C177AB35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2321,31 +2317,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3031,7 +3043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3727,29 +3739,34 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4039,7 +4056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4059,10 +4076,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4091,13 +4108,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4124,7 +4141,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>12</v>
@@ -4160,24 +4177,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="337" t="s">
-        <v>373</v>
-      </c>
-      <c r="C12" s="337"/>
-      <c r="D12" s="337"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="B12" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4187,7 +4204,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4213,19 +4230,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4237,11 +4254,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>13.155317996540354</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4249,7 +4266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4264,7 +4281,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4273,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="337" t="s">
-        <v>374</v>
-      </c>
-      <c r="C25" s="337"/>
-      <c r="D25" s="337"/>
-      <c r="E25" s="337"/>
-      <c r="F25" s="337"/>
+      <c r="B25" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="339" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="339"/>
-      <c r="D26" s="339"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="339"/>
+      <c r="B26" s="345" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4300,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4326,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4361,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4383,17 +4400,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4408,7 +4425,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4453,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4475,13 +4492,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4497,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="337" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="337"/>
-      <c r="D53" s="337"/>
-      <c r="E53" s="337"/>
-      <c r="F53" s="337"/>
+      <c r="B53" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="337" t="s">
-        <v>375</v>
-      </c>
-      <c r="C54" s="337"/>
-      <c r="D54" s="337"/>
-      <c r="E54" s="337"/>
-      <c r="F54" s="337"/>
+      <c r="B54" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4559,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4551,7 +4568,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4560,7 +4577,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4573,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="337" t="s">
-        <v>376</v>
-      </c>
-      <c r="C63" s="337"/>
-      <c r="D63" s="337"/>
-      <c r="E63" s="337"/>
-      <c r="F63" s="337"/>
+      <c r="B63" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="339" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="339"/>
-      <c r="D64" s="339"/>
-      <c r="E64" s="339"/>
-      <c r="F64" s="339"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4597,7 +4614,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4605,26 +4622,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4641,27 +4658,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="337" t="s">
+      <c r="B73" s="342" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C73" s="337"/>
-      <c r="D73" s="337"/>
-      <c r="E73" s="337"/>
-      <c r="F73" s="337"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="337" t="s">
-        <v>378</v>
-      </c>
-      <c r="C74" s="337"/>
-      <c r="D74" s="337"/>
-      <c r="E74" s="337"/>
-      <c r="F74" s="337"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4673,7 +4690,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4686,7 +4703,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4698,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="337" t="s">
-        <v>379</v>
-      </c>
-      <c r="C81" s="337"/>
-      <c r="D81" s="337"/>
-      <c r="E81" s="337"/>
-      <c r="F81" s="337"/>
+      <c r="B81" s="342" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4717,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="337" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="337"/>
-      <c r="D85" s="337"/>
-      <c r="E85" s="337"/>
-      <c r="F85" s="337"/>
+      <c r="B85" s="342" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4740,7 +4757,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4751,508 +4768,525 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>0.31018327415220487</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>0.15818859882129041</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>422</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>1.4550387206421544</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>1998219</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>1050246.6606106577</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>1.7888479273623368</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>92572.6</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>0.15767562978420405</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="337" t="s">
-        <v>380</v>
-      </c>
-      <c r="C98" s="337"/>
-      <c r="D98" s="337"/>
-      <c r="E98" s="337"/>
-      <c r="F98" s="337"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>379</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>20.080338252823015</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>372</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="338" t="s">
-        <v>381</v>
-      </c>
-      <c r="C104" s="338"/>
-      <c r="D104" s="338"/>
-      <c r="E104" s="338"/>
-      <c r="F104" s="338"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>421</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>5.8696003638854428</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>371</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>380</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.06</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>10</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>24.7 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.05</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>5</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>21.86 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.192</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.02</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>5</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>20.78 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.57599999999999996</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>5</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>18.42 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.192</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.08</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>10</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>15.62 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>20.508980461992877</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>384</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>419</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="340" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>383</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>417</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>381</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>382</v>
       </c>
-      <c r="C119" s="340"/>
-      <c r="D119" s="340"/>
-      <c r="E119" s="340"/>
-      <c r="F119" s="340"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="337" t="s">
-        <v>383</v>
-      </c>
-      <c r="C120" s="337"/>
-      <c r="D120" s="337"/>
-      <c r="E120" s="337"/>
-      <c r="F120" s="337"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>1.36</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>2.6547200000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>10.500597996540353</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>13.155317996540354</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.35855816816834396</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>3.8138683808049407</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>3.6538719773739974</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>18.52475983870195</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="239">
+        <v>17.354455410566345</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>22.338628219506891</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>21.008327387940341</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-8.9212028891670458E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>-2.4347720593563826E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>389</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>388</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="344" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>393</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C140" s="337"/>
-      <c r="D140" s="337"/>
-      <c r="E140" s="337"/>
-      <c r="F140" s="337"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>394</v>
-      </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="338" t="s">
-        <v>395</v>
-      </c>
-      <c r="C149" s="338"/>
-      <c r="D149" s="338"/>
-      <c r="E149" s="338"/>
-      <c r="F149" s="338"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="343" t="s">
-        <v>396</v>
-      </c>
-      <c r="C152" s="343"/>
-      <c r="D152" s="343"/>
-      <c r="E152" s="343"/>
-      <c r="F152" s="343"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>397</v>
       </c>
       <c r="C153" s="343"/>
       <c r="D153" s="343"/>
@@ -5261,38 +5295,50 @@
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>395</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>396</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5301,13 +5347,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5795,7 +5852,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5811,7 +5868,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5827,7 +5884,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5875,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7114,7 +7171,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8488,7 +8545,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>421</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8496,7 +8553,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8649,7 +8706,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8672,7 +8729,7 @@
         <v>-2.0915594459950692E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8694,7 +8751,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8761,7 +8818,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-       